--- a/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
@@ -5564,16 +5564,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5589,7 +5581,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -5597,30 +5589,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5920,52 +5894,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6043,7 +6017,7 @@
       <c r="C4">
         <v>2026</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>45972</v>
       </c>
       <c r="F4" t="s">
@@ -6180,7 +6154,7 @@
       <c r="C8">
         <v>2026</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>46014</v>
       </c>
       <c r="F8" t="s">
@@ -6317,7 +6291,7 @@
       <c r="C12">
         <v>2026</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>45916</v>
       </c>
       <c r="F12" t="s">
@@ -6358,7 +6332,7 @@
       <c r="C13">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>45897</v>
       </c>
       <c r="H13" t="s">
@@ -6393,7 +6367,7 @@
       <c r="C14">
         <v>2026</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>45916</v>
       </c>
       <c r="F14" t="s">
@@ -6434,7 +6408,7 @@
       <c r="C15">
         <v>2026</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>46086</v>
       </c>
       <c r="G15" t="s">
@@ -6472,7 +6446,7 @@
       <c r="C16">
         <v>2026</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>45869</v>
       </c>
       <c r="F16" t="s">
@@ -6513,7 +6487,7 @@
       <c r="C17">
         <v>2026</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>45877</v>
       </c>
       <c r="F17" t="s">
@@ -6554,7 +6528,7 @@
       <c r="C18">
         <v>2026</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>46086</v>
       </c>
       <c r="G18" t="s">
@@ -6592,7 +6566,7 @@
       <c r="C19">
         <v>2026</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>45863</v>
       </c>
       <c r="F19" t="s">
@@ -6633,7 +6607,7 @@
       <c r="C20">
         <v>2026</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>45863</v>
       </c>
       <c r="F20" t="s">
@@ -6674,7 +6648,7 @@
       <c r="C21">
         <v>2026</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>45873</v>
       </c>
       <c r="F21" t="s">
@@ -6715,7 +6689,7 @@
       <c r="C22">
         <v>2026</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
@@ -6756,7 +6730,7 @@
       <c r="C23">
         <v>2026</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>46086</v>
       </c>
       <c r="G23" t="s">
@@ -6858,7 +6832,7 @@
       <c r="C26">
         <v>2026</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>45838</v>
       </c>
       <c r="F26" t="s">
@@ -6899,7 +6873,7 @@
       <c r="C27">
         <v>2026</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>45800</v>
       </c>
       <c r="F27" t="s">
@@ -6940,7 +6914,7 @@
       <c r="C28">
         <v>2026</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>45849</v>
       </c>
       <c r="F28" t="s">
@@ -6981,7 +6955,7 @@
       <c r="C29">
         <v>2026</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>45838</v>
       </c>
       <c r="F29" t="s">
@@ -7022,7 +6996,7 @@
       <c r="C30">
         <v>2026</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>45915</v>
       </c>
       <c r="F30" t="s">
@@ -7063,7 +7037,7 @@
       <c r="C31">
         <v>2026</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>45849</v>
       </c>
       <c r="F31" t="s">
@@ -7136,7 +7110,7 @@
       <c r="C33">
         <v>2026</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>45800</v>
       </c>
       <c r="F33" t="s">
@@ -7209,7 +7183,7 @@
       <c r="C35">
         <v>2026</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>46119</v>
       </c>
       <c r="F35" t="s">
@@ -7250,7 +7224,7 @@
       <c r="C36">
         <v>2026</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>45854</v>
       </c>
       <c r="F36" t="s">
@@ -7291,7 +7265,7 @@
       <c r="C37">
         <v>2026</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>45849</v>
       </c>
       <c r="F37" t="s">
@@ -7332,7 +7306,7 @@
       <c r="C38">
         <v>2026</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>46119</v>
       </c>
       <c r="F38" t="s">
@@ -7405,7 +7379,7 @@
       <c r="C40">
         <v>2026</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>46092</v>
       </c>
       <c r="F40" t="s">
@@ -7510,7 +7484,7 @@
       <c r="C43">
         <v>2026</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>46122</v>
       </c>
       <c r="F43" t="s">
@@ -7551,7 +7525,7 @@
       <c r="C44">
         <v>2026</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>46122</v>
       </c>
       <c r="F44" t="s">
@@ -7592,7 +7566,7 @@
       <c r="C45">
         <v>2026</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>46135</v>
       </c>
       <c r="F45" t="s">
@@ -7633,7 +7607,7 @@
       <c r="C46">
         <v>2026</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>46086</v>
       </c>
       <c r="F46" t="s">
@@ -7674,7 +7648,7 @@
       <c r="C47">
         <v>2026</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>46104</v>
       </c>
       <c r="F47" t="s">
@@ -7715,7 +7689,7 @@
       <c r="C48">
         <v>2026</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>45972</v>
       </c>
       <c r="G48" t="s">
@@ -7753,7 +7727,7 @@
       <c r="C49">
         <v>2026</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>45810</v>
       </c>
       <c r="F49" t="s">
@@ -7794,7 +7768,7 @@
       <c r="C50">
         <v>2026</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>45937</v>
       </c>
       <c r="F50" t="s">
@@ -7835,7 +7809,7 @@
       <c r="C51">
         <v>2026</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>45937</v>
       </c>
       <c r="F51" t="s">
@@ -7908,7 +7882,7 @@
       <c r="C53">
         <v>2026</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="1">
         <v>45845</v>
       </c>
       <c r="F53" t="s">
@@ -7949,7 +7923,7 @@
       <c r="C54">
         <v>2026</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="1">
         <v>46077</v>
       </c>
       <c r="F54" t="s">
@@ -8022,7 +7996,7 @@
       <c r="C56">
         <v>2026</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>45971</v>
       </c>
       <c r="F56" t="s">
@@ -8095,7 +8069,7 @@
       <c r="C58">
         <v>2026</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>45817</v>
       </c>
       <c r="F58" t="s">
@@ -8168,7 +8142,7 @@
       <c r="C60">
         <v>2026</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>45965</v>
       </c>
       <c r="G60" t="s">
@@ -8238,7 +8212,7 @@
       <c r="C62">
         <v>2026</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>46072</v>
       </c>
       <c r="F62" t="s">
@@ -8311,7 +8285,7 @@
       <c r="C64">
         <v>2026</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>46072</v>
       </c>
       <c r="H64" t="s">
@@ -8346,7 +8320,7 @@
       <c r="C65">
         <v>2026</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>45804</v>
       </c>
       <c r="F65" t="s">
@@ -8387,7 +8361,7 @@
       <c r="C66">
         <v>2026</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>45804</v>
       </c>
       <c r="F66" t="s">
@@ -8428,7 +8402,7 @@
       <c r="C67">
         <v>2026</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>45804</v>
       </c>
       <c r="F67" t="s">
@@ -8469,7 +8443,7 @@
       <c r="C68">
         <v>2026</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="1">
         <v>45804</v>
       </c>
       <c r="F68" t="s">
@@ -8510,7 +8484,7 @@
       <c r="C69">
         <v>2026</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="1">
         <v>45804</v>
       </c>
       <c r="F69" t="s">
@@ -8551,7 +8525,7 @@
       <c r="C70">
         <v>2026</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>45804</v>
       </c>
       <c r="F70" t="s">
@@ -8592,7 +8566,7 @@
       <c r="C71">
         <v>2026</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="1">
         <v>45821</v>
       </c>
       <c r="F71" t="s">
@@ -8633,7 +8607,7 @@
       <c r="C72">
         <v>2026</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="1">
         <v>45821</v>
       </c>
       <c r="H72" t="s">
@@ -8668,7 +8642,7 @@
       <c r="C73">
         <v>2026</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="1">
         <v>45891</v>
       </c>
       <c r="F73" t="s">
@@ -8709,7 +8683,7 @@
       <c r="C74">
         <v>2026</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="1">
         <v>45817</v>
       </c>
       <c r="G74" t="s">
@@ -8747,7 +8721,7 @@
       <c r="C75">
         <v>2026</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="1">
         <v>45883</v>
       </c>
       <c r="G75" t="s">
@@ -8785,7 +8759,7 @@
       <c r="C76">
         <v>2026</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="1">
         <v>45817</v>
       </c>
       <c r="G76" t="s">
@@ -8823,7 +8797,7 @@
       <c r="C77">
         <v>2026</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="1">
         <v>45883</v>
       </c>
       <c r="G77" t="s">
@@ -8861,7 +8835,7 @@
       <c r="C78">
         <v>2026</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>45971</v>
       </c>
       <c r="F78" t="s">
@@ -8902,7 +8876,7 @@
       <c r="C79">
         <v>2026</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>45849</v>
       </c>
       <c r="F79" t="s">
@@ -8943,7 +8917,7 @@
       <c r="C80">
         <v>2026</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="1">
         <v>45849</v>
       </c>
       <c r="F80" t="s">
@@ -8984,7 +8958,7 @@
       <c r="C81">
         <v>2026</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="1">
         <v>45863</v>
       </c>
       <c r="F81" t="s">
@@ -9025,7 +8999,7 @@
       <c r="C82">
         <v>2026</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>45810</v>
       </c>
       <c r="F82" t="s">
@@ -9066,7 +9040,7 @@
       <c r="C83">
         <v>2026</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="1">
         <v>45926</v>
       </c>
       <c r="F83" t="s">
@@ -9107,7 +9081,7 @@
       <c r="C84">
         <v>2026</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="1">
         <v>45971</v>
       </c>
       <c r="F84" t="s">
@@ -9148,7 +9122,7 @@
       <c r="C85">
         <v>2026</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="1">
         <v>46164</v>
       </c>
       <c r="F85" t="s">
@@ -9189,7 +9163,7 @@
       <c r="C86">
         <v>2026</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>45986</v>
       </c>
       <c r="G86" t="s">
@@ -9268,7 +9242,7 @@
       <c r="C88">
         <v>2026</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="1">
         <v>45786</v>
       </c>
       <c r="F88" t="s">
@@ -9309,7 +9283,7 @@
       <c r="C89">
         <v>2026</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="1">
         <v>45777</v>
       </c>
       <c r="F89" t="s">
@@ -9350,7 +9324,7 @@
       <c r="C90">
         <v>2026</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="1">
         <v>45869</v>
       </c>
       <c r="F90" t="s">
@@ -9391,7 +9365,7 @@
       <c r="C91">
         <v>2026</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="1">
         <v>45891</v>
       </c>
       <c r="F91" t="s">
@@ -9432,7 +9406,7 @@
       <c r="C92">
         <v>2026</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="1">
         <v>45863</v>
       </c>
       <c r="F92" t="s">
@@ -9473,7 +9447,7 @@
       <c r="C93">
         <v>2026</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="1">
         <v>45769</v>
       </c>
       <c r="F93" t="s">
@@ -9514,7 +9488,7 @@
       <c r="C94">
         <v>2026</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="1">
         <v>45769</v>
       </c>
       <c r="F94" t="s">
@@ -9555,7 +9529,7 @@
       <c r="C95">
         <v>2026</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="1">
         <v>45894</v>
       </c>
       <c r="F95" t="s">
@@ -9628,7 +9602,7 @@
       <c r="C97">
         <v>2026</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="1">
         <v>45894</v>
       </c>
       <c r="F97" t="s">
@@ -9669,7 +9643,7 @@
       <c r="C98">
         <v>2026</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="1">
         <v>45971</v>
       </c>
       <c r="F98" t="s">
@@ -9710,7 +9684,7 @@
       <c r="C99">
         <v>2026</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>45971</v>
       </c>
       <c r="F99" t="s">
@@ -9751,7 +9725,7 @@
       <c r="C100">
         <v>2026</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="1">
         <v>45971</v>
       </c>
       <c r="F100" t="s">
@@ -9792,7 +9766,7 @@
       <c r="C101">
         <v>2026</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="1">
         <v>45996</v>
       </c>
       <c r="G101" t="s">
@@ -9830,7 +9804,7 @@
       <c r="C102">
         <v>2026</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="1">
         <v>45986</v>
       </c>
       <c r="G102" t="s">
@@ -9900,7 +9874,7 @@
       <c r="C104">
         <v>2026</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="1">
         <v>45769</v>
       </c>
       <c r="F104" t="s">
@@ -9941,7 +9915,7 @@
       <c r="C105">
         <v>2026</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="1">
         <v>45769</v>
       </c>
       <c r="F105" t="s">
@@ -9982,7 +9956,7 @@
       <c r="C106">
         <v>2026</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="1">
         <v>45849</v>
       </c>
       <c r="F106" t="s">
@@ -10023,7 +9997,7 @@
       <c r="C107">
         <v>2026</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="1">
         <v>45849</v>
       </c>
       <c r="G107" t="s">
@@ -10125,7 +10099,7 @@
       <c r="C110">
         <v>2026</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="1">
         <v>45891</v>
       </c>
       <c r="F110" t="s">
@@ -10166,7 +10140,7 @@
       <c r="C111">
         <v>2026</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="1">
         <v>45769</v>
       </c>
       <c r="F111" t="s">
@@ -10207,7 +10181,7 @@
       <c r="C112">
         <v>2026</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="1">
         <v>45889</v>
       </c>
       <c r="F112" t="s">
@@ -10248,7 +10222,7 @@
       <c r="C113">
         <v>2026</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="1">
         <v>45945</v>
       </c>
       <c r="G113" t="s">
@@ -10286,7 +10260,7 @@
       <c r="C114">
         <v>2026</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="1">
         <v>45945</v>
       </c>
       <c r="G114" t="s">
@@ -10324,7 +10298,7 @@
       <c r="C115">
         <v>2026</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="1">
         <v>46119</v>
       </c>
       <c r="F115" t="s">
@@ -10365,7 +10339,7 @@
       <c r="C116">
         <v>2026</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="1">
         <v>46029</v>
       </c>
       <c r="F116" t="s">
@@ -10406,7 +10380,7 @@
       <c r="C117">
         <v>2026</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="1">
         <v>46029</v>
       </c>
       <c r="F117" t="s">
@@ -10447,7 +10421,7 @@
       <c r="C118">
         <v>2026</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="1">
         <v>46119</v>
       </c>
       <c r="F118" t="s">
@@ -10488,7 +10462,7 @@
       <c r="C119">
         <v>2026</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="1">
         <v>46230</v>
       </c>
       <c r="F119" t="s">
@@ -10529,7 +10503,7 @@
       <c r="C120">
         <v>2026</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="1">
         <v>46119</v>
       </c>
       <c r="F120" t="s">
@@ -10570,7 +10544,7 @@
       <c r="C121">
         <v>2026</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="1">
         <v>46119</v>
       </c>
       <c r="F121" t="s">
@@ -10611,7 +10585,7 @@
       <c r="C122">
         <v>2026</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="1">
         <v>45931</v>
       </c>
       <c r="F122" t="s">
@@ -10652,7 +10626,7 @@
       <c r="C123">
         <v>2026</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="1">
         <v>45894</v>
       </c>
       <c r="G123" t="s">
@@ -10690,7 +10664,7 @@
       <c r="C124">
         <v>2026</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="1">
         <v>46119</v>
       </c>
       <c r="F124" t="s">
@@ -10731,7 +10705,7 @@
       <c r="C125">
         <v>2026</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="1">
         <v>45889</v>
       </c>
       <c r="F125" t="s">
@@ -10772,7 +10746,7 @@
       <c r="C126">
         <v>2026</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="1">
         <v>45876</v>
       </c>
       <c r="G126" t="s">
@@ -10842,7 +10816,7 @@
       <c r="C128">
         <v>2026</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="1">
         <v>45876</v>
       </c>
       <c r="F128" t="s">
@@ -10915,7 +10889,7 @@
       <c r="C130">
         <v>2026</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="1">
         <v>46230</v>
       </c>
       <c r="F130" t="s">
@@ -10956,7 +10930,7 @@
       <c r="C131">
         <v>2026</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="1">
         <v>45889</v>
       </c>
       <c r="F131" t="s">
@@ -10997,7 +10971,7 @@
       <c r="C132">
         <v>2026</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="1">
         <v>46230</v>
       </c>
       <c r="F132" t="s">
@@ -11070,7 +11044,7 @@
       <c r="C134">
         <v>2026</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="1">
         <v>46140</v>
       </c>
       <c r="F134" t="s">
@@ -11111,7 +11085,7 @@
       <c r="C135">
         <v>2026</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="1">
         <v>45889</v>
       </c>
       <c r="F135" t="s">
@@ -11152,7 +11126,7 @@
       <c r="C136">
         <v>2026</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="1">
         <v>45952</v>
       </c>
       <c r="F136" t="s">
@@ -11190,7 +11164,7 @@
       <c r="C137">
         <v>2026</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="1">
         <v>46230</v>
       </c>
       <c r="F137" t="s">
@@ -11263,7 +11237,7 @@
       <c r="C139">
         <v>2026</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="1">
         <v>46029</v>
       </c>
       <c r="G139" t="s">
@@ -11301,7 +11275,7 @@
       <c r="C140">
         <v>2026</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="1">
         <v>46029</v>
       </c>
       <c r="G140" t="s">
@@ -11371,7 +11345,7 @@
       <c r="C142">
         <v>2026</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="1">
         <v>46119</v>
       </c>
       <c r="F142" t="s">
@@ -11476,7 +11450,7 @@
       <c r="C145">
         <v>2026</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="1">
         <v>46140</v>
       </c>
       <c r="F145" t="s">
@@ -11517,7 +11491,7 @@
       <c r="C146">
         <v>2026</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="1">
         <v>46230</v>
       </c>
       <c r="F146" t="s">
@@ -11558,7 +11532,7 @@
       <c r="C147">
         <v>2026</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="1">
         <v>46230</v>
       </c>
       <c r="F147" t="s">
@@ -11599,7 +11573,7 @@
       <c r="C148">
         <v>2026</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="1">
         <v>46119</v>
       </c>
       <c r="F148" t="s">
@@ -11640,7 +11614,7 @@
       <c r="C149">
         <v>2026</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="1">
         <v>46230</v>
       </c>
       <c r="F149" t="s">
@@ -11681,7 +11655,7 @@
       <c r="C150">
         <v>2026</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="1">
         <v>46140</v>
       </c>
       <c r="F150" t="s">
@@ -11722,7 +11696,7 @@
       <c r="C151">
         <v>2026</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="1">
         <v>45876</v>
       </c>
       <c r="F151" t="s">
@@ -11795,7 +11769,7 @@
       <c r="C153">
         <v>2026</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="1">
         <v>45863</v>
       </c>
       <c r="F153" t="s">
@@ -11836,7 +11810,7 @@
       <c r="C154">
         <v>2026</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="1">
         <v>45863</v>
       </c>
       <c r="F154" t="s">
@@ -11877,7 +11851,7 @@
       <c r="C155">
         <v>2026</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="1">
         <v>45863</v>
       </c>
       <c r="F155" t="s">
@@ -11918,7 +11892,7 @@
       <c r="C156">
         <v>2026</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="1">
         <v>45860</v>
       </c>
       <c r="F156" t="s">
@@ -11988,7 +11962,7 @@
       <c r="C158">
         <v>2026</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="1">
         <v>46119</v>
       </c>
       <c r="F158" t="s">
@@ -12029,7 +12003,7 @@
       <c r="C159">
         <v>2026</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="1">
         <v>45814</v>
       </c>
       <c r="F159" t="s">
@@ -12070,7 +12044,7 @@
       <c r="C160">
         <v>2026</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="1">
         <v>45817</v>
       </c>
       <c r="F160" t="s">
@@ -12111,7 +12085,7 @@
       <c r="C161">
         <v>2026</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="1">
         <v>45971</v>
       </c>
       <c r="F161" t="s">
@@ -12152,7 +12126,7 @@
       <c r="C162">
         <v>2026</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="1">
         <v>45971</v>
       </c>
       <c r="F162" t="s">
@@ -12193,7 +12167,7 @@
       <c r="C163">
         <v>2026</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="1">
         <v>45860</v>
       </c>
       <c r="G163" t="s">
@@ -12231,7 +12205,7 @@
       <c r="C164">
         <v>2026</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="1">
         <v>45856</v>
       </c>
       <c r="F164" t="s">
@@ -12304,7 +12278,7 @@
       <c r="C166">
         <v>2026</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="1">
         <v>46064</v>
       </c>
       <c r="F166" t="s">
@@ -12345,7 +12319,7 @@
       <c r="C167">
         <v>2026</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="1">
         <v>45982</v>
       </c>
       <c r="G167" t="s">
@@ -12383,7 +12357,7 @@
       <c r="C168">
         <v>2026</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="1">
         <v>46157</v>
       </c>
       <c r="H168" t="s">
@@ -12418,7 +12392,7 @@
       <c r="C169">
         <v>2026</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="1">
         <v>45762</v>
       </c>
       <c r="F169" t="s">
@@ -12459,7 +12433,7 @@
       <c r="C170">
         <v>2026</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="1">
         <v>45816</v>
       </c>
       <c r="F170" t="s">
@@ -12500,7 +12474,7 @@
       <c r="C171">
         <v>2026</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="1">
         <v>45816</v>
       </c>
       <c r="F171" t="s">
@@ -12579,7 +12553,7 @@
       <c r="C173">
         <v>2026</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="1">
         <v>46101</v>
       </c>
       <c r="F173" t="s">
@@ -12620,7 +12594,7 @@
       <c r="C174">
         <v>2026</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="1">
         <v>46101</v>
       </c>
       <c r="F174" t="s">
@@ -12661,7 +12635,7 @@
       <c r="C175">
         <v>2026</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="1">
         <v>46105</v>
       </c>
       <c r="F175" t="s">
@@ -12702,7 +12676,7 @@
       <c r="C176">
         <v>2026</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="1">
         <v>45889</v>
       </c>
       <c r="F176" t="s">
@@ -12743,7 +12717,7 @@
       <c r="C177">
         <v>2026</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="1">
         <v>45814</v>
       </c>
       <c r="F177" t="s">
@@ -12784,7 +12758,7 @@
       <c r="C178">
         <v>2026</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="1">
         <v>45889</v>
       </c>
       <c r="F178" t="s">
@@ -12825,7 +12799,7 @@
       <c r="C179">
         <v>2026</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="1">
         <v>45814</v>
       </c>
       <c r="F179" t="s">
@@ -12866,7 +12840,7 @@
       <c r="C180">
         <v>2026</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="1">
         <v>45889</v>
       </c>
       <c r="F180" t="s">
@@ -12939,7 +12913,7 @@
       <c r="C182">
         <v>2026</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="1">
         <v>46139</v>
       </c>
       <c r="H182" t="s">
@@ -13006,7 +12980,7 @@
       <c r="C184">
         <v>2026</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="1">
         <v>45889</v>
       </c>
       <c r="F184" t="s">
@@ -13079,7 +13053,7 @@
       <c r="C186">
         <v>2026</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="1">
         <v>45814</v>
       </c>
       <c r="F186" t="s">
@@ -13120,7 +13094,7 @@
       <c r="C187">
         <v>2026</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="1">
         <v>45889</v>
       </c>
       <c r="F187" t="s">
@@ -13161,7 +13135,7 @@
       <c r="C188">
         <v>2026</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="1">
         <v>45931</v>
       </c>
       <c r="F188" t="s">
@@ -13202,7 +13176,7 @@
       <c r="C189">
         <v>2026</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="1">
         <v>45889</v>
       </c>
       <c r="F189" t="s">
@@ -13243,7 +13217,7 @@
       <c r="C190">
         <v>2026</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="1">
         <v>45876</v>
       </c>
       <c r="F190" t="s">
@@ -13284,7 +13258,7 @@
       <c r="C191">
         <v>2026</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="1">
         <v>45876</v>
       </c>
       <c r="F191" t="s">
@@ -13357,7 +13331,7 @@
       <c r="C193">
         <v>2026</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="1">
         <v>45876</v>
       </c>
       <c r="F193" t="s">
@@ -13398,7 +13372,7 @@
       <c r="C194">
         <v>2026</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194" s="1">
         <v>46119</v>
       </c>
       <c r="F194" t="s">
@@ -13439,7 +13413,7 @@
       <c r="C195">
         <v>2026</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="1">
         <v>46119</v>
       </c>
       <c r="F195" t="s">
@@ -13480,7 +13454,7 @@
       <c r="C196">
         <v>2026</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196" s="1">
         <v>45961</v>
       </c>
       <c r="F196" t="s">
@@ -13521,7 +13495,7 @@
       <c r="C197">
         <v>2026</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="1">
         <v>45860</v>
       </c>
       <c r="F197" t="s">
@@ -13562,7 +13536,7 @@
       <c r="C198">
         <v>2026</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="1">
         <v>45993</v>
       </c>
       <c r="G198" t="s">
@@ -13600,7 +13574,7 @@
       <c r="C199">
         <v>2026</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="1">
         <v>45853</v>
       </c>
       <c r="F199" t="s">
@@ -13641,7 +13615,7 @@
       <c r="C200">
         <v>2026</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200" s="1">
         <v>46119</v>
       </c>
       <c r="F200" t="s">
@@ -13720,7 +13694,7 @@
       <c r="C202">
         <v>2026</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202" s="1">
         <v>46191</v>
       </c>
       <c r="F202" t="s">
@@ -13761,7 +13735,7 @@
       <c r="C203">
         <v>2026</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203" s="1">
         <v>46191</v>
       </c>
       <c r="F203" t="s">
@@ -13802,7 +13776,7 @@
       <c r="C204">
         <v>2026</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="1">
         <v>46191</v>
       </c>
       <c r="F204" t="s">
@@ -13843,7 +13817,7 @@
       <c r="C205">
         <v>2026</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="1">
         <v>45932</v>
       </c>
       <c r="G205" t="s">
@@ -13881,7 +13855,7 @@
       <c r="C206">
         <v>2026</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206" s="1">
         <v>46191</v>
       </c>
       <c r="F206" t="s">
@@ -13922,7 +13896,7 @@
       <c r="C207">
         <v>2026</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207" s="1">
         <v>46119</v>
       </c>
       <c r="F207" t="s">
@@ -13963,7 +13937,7 @@
       <c r="C208">
         <v>2026</v>
       </c>
-      <c r="D208" s="2">
+      <c r="D208" s="1">
         <v>45946</v>
       </c>
       <c r="G208" t="s">
@@ -14001,7 +13975,7 @@
       <c r="C209">
         <v>2026</v>
       </c>
-      <c r="D209" s="2">
+      <c r="D209" s="1">
         <v>45937</v>
       </c>
       <c r="F209" t="s">
@@ -14042,7 +14016,7 @@
       <c r="C210">
         <v>2026</v>
       </c>
-      <c r="D210" s="2">
+      <c r="D210" s="1">
         <v>45849</v>
       </c>
       <c r="F210" t="s">
@@ -14083,7 +14057,7 @@
       <c r="C211">
         <v>2026</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211" s="1">
         <v>45876</v>
       </c>
       <c r="F211" t="s">
@@ -14124,7 +14098,7 @@
       <c r="C212">
         <v>2026</v>
       </c>
-      <c r="D212" s="2">
+      <c r="D212" s="1">
         <v>46008</v>
       </c>
       <c r="F212" t="s">
@@ -14238,7 +14212,7 @@
       <c r="C215">
         <v>2026</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215" s="1">
         <v>45973</v>
       </c>
       <c r="F215" t="s">
@@ -14279,7 +14253,7 @@
       <c r="C216">
         <v>2026</v>
       </c>
-      <c r="D216" s="2">
+      <c r="D216" s="1">
         <v>46014</v>
       </c>
       <c r="F216" t="s">
@@ -14320,7 +14294,7 @@
       <c r="C217">
         <v>2026</v>
       </c>
-      <c r="D217" s="2">
+      <c r="D217" s="1">
         <v>45876</v>
       </c>
       <c r="F217" t="s">
@@ -14361,7 +14335,7 @@
       <c r="C218">
         <v>2026</v>
       </c>
-      <c r="D218" s="2">
+      <c r="D218" s="1">
         <v>45937</v>
       </c>
       <c r="F218" t="s">
@@ -14402,7 +14376,7 @@
       <c r="C219">
         <v>2026</v>
       </c>
-      <c r="D219" s="2">
+      <c r="D219" s="1">
         <v>45980</v>
       </c>
       <c r="F219" t="s">
@@ -14763,7 +14737,7 @@
       <c r="C230">
         <v>2026</v>
       </c>
-      <c r="D230" s="2">
+      <c r="D230" s="1">
         <v>45979</v>
       </c>
       <c r="F230" t="s">
@@ -14804,7 +14778,7 @@
       <c r="C231">
         <v>2026</v>
       </c>
-      <c r="D231" s="2">
+      <c r="D231" s="1">
         <v>45979</v>
       </c>
       <c r="F231" t="s">
@@ -14845,7 +14819,7 @@
       <c r="C232">
         <v>2026</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232" s="1">
         <v>45979</v>
       </c>
       <c r="F232" t="s">
@@ -14886,7 +14860,7 @@
       <c r="C233">
         <v>2026</v>
       </c>
-      <c r="D233" s="2">
+      <c r="D233" s="1">
         <v>45971</v>
       </c>
       <c r="F233" t="s">
@@ -14927,7 +14901,7 @@
       <c r="C234">
         <v>2026</v>
       </c>
-      <c r="D234" s="2">
+      <c r="D234" s="1">
         <v>45971</v>
       </c>
       <c r="F234" t="s">
@@ -14968,7 +14942,7 @@
       <c r="C235">
         <v>2026</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235" s="1">
         <v>45971</v>
       </c>
       <c r="F235" t="s">
@@ -15009,7 +14983,7 @@
       <c r="C236">
         <v>2026</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236" s="1">
         <v>45889</v>
       </c>
       <c r="F236" t="s">
@@ -15146,7 +15120,7 @@
       <c r="C240">
         <v>2026</v>
       </c>
-      <c r="D240" s="2">
+      <c r="D240" s="1">
         <v>45859</v>
       </c>
       <c r="F240" t="s">
@@ -15187,7 +15161,7 @@
       <c r="C241">
         <v>2026</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241" s="1">
         <v>45918</v>
       </c>
       <c r="F241" t="s">
@@ -15260,7 +15234,7 @@
       <c r="C243">
         <v>2026</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="1">
         <v>45874</v>
       </c>
       <c r="F243" t="s">
@@ -15301,7 +15275,7 @@
       <c r="C244">
         <v>2026</v>
       </c>
-      <c r="D244" s="2">
+      <c r="D244" s="1">
         <v>45975</v>
       </c>
       <c r="F244" t="s">
@@ -15339,7 +15313,7 @@
       <c r="C245">
         <v>2026</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245" s="1">
         <v>45975</v>
       </c>
       <c r="F245" t="s">
@@ -15377,7 +15351,7 @@
       <c r="C246">
         <v>2026</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="1">
         <v>45975</v>
       </c>
       <c r="F246" t="s">
@@ -15639,7 +15613,7 @@
       <c r="C254">
         <v>2026</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254" s="1">
         <v>46119</v>
       </c>
       <c r="F254" t="s">
@@ -15744,7 +15718,7 @@
       <c r="C257">
         <v>2026</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257" s="1">
         <v>45802</v>
       </c>
       <c r="F257" t="s">
@@ -15785,7 +15759,7 @@
       <c r="C258">
         <v>2026</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="1">
         <v>45804</v>
       </c>
       <c r="F258" t="s">
@@ -15826,7 +15800,7 @@
       <c r="C259">
         <v>2026</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="1">
         <v>46097</v>
       </c>
       <c r="F259" t="s">
@@ -15867,7 +15841,7 @@
       <c r="C260">
         <v>2026</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="1">
         <v>45860</v>
       </c>
       <c r="G260" t="s">
@@ -15905,7 +15879,7 @@
       <c r="C261">
         <v>2026</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="1">
         <v>45889</v>
       </c>
       <c r="F261" t="s">
@@ -15946,7 +15920,7 @@
       <c r="C262">
         <v>2026</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="1">
         <v>45744</v>
       </c>
       <c r="F262" t="s">
@@ -15987,7 +15961,7 @@
       <c r="C263">
         <v>2026</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="1">
         <v>45744</v>
       </c>
       <c r="F263" t="s">
@@ -16028,7 +16002,7 @@
       <c r="C264">
         <v>2026</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="1">
         <v>46408</v>
       </c>
       <c r="F264" t="s">
@@ -16072,7 +16046,7 @@
       <c r="C265">
         <v>2026</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="1">
         <v>45898</v>
       </c>
       <c r="F265" t="s">
@@ -16113,7 +16087,7 @@
       <c r="C266">
         <v>2026</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="1">
         <v>45971</v>
       </c>
       <c r="F266" t="s">
@@ -16154,7 +16128,7 @@
       <c r="C267">
         <v>2026</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="1">
         <v>45744</v>
       </c>
       <c r="F267" t="s">
@@ -16195,7 +16169,7 @@
       <c r="C268">
         <v>2026</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="1">
         <v>46092</v>
       </c>
       <c r="F268" t="s">
@@ -16236,7 +16210,7 @@
       <c r="C269">
         <v>2026</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="1">
         <v>46204</v>
       </c>
       <c r="F269" t="s">
@@ -16280,7 +16254,7 @@
       <c r="C270">
         <v>2026</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="1">
         <v>46185</v>
       </c>
       <c r="H270" t="s">
@@ -16315,7 +16289,7 @@
       <c r="C271">
         <v>2026</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="1">
         <v>45890</v>
       </c>
       <c r="G271" t="s">
@@ -16353,7 +16327,7 @@
       <c r="C272">
         <v>2026</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="1">
         <v>46185</v>
       </c>
       <c r="H272" t="s">
@@ -16388,7 +16362,7 @@
       <c r="C273">
         <v>2026</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="1">
         <v>46175</v>
       </c>
       <c r="F273" t="s">
@@ -16429,7 +16403,7 @@
       <c r="C274">
         <v>2026</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="1">
         <v>45890</v>
       </c>
       <c r="G274" t="s">
@@ -16467,7 +16441,7 @@
       <c r="C275">
         <v>2026</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="1">
         <v>46175</v>
       </c>
       <c r="F275" t="s">
@@ -16508,7 +16482,7 @@
       <c r="C276">
         <v>2026</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="1">
         <v>46185</v>
       </c>
       <c r="G276" t="s">
@@ -16546,7 +16520,7 @@
       <c r="C277">
         <v>2026</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="1">
         <v>45890</v>
       </c>
       <c r="G277" t="s">
@@ -16584,7 +16558,7 @@
       <c r="C278">
         <v>2026</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="1">
         <v>45890</v>
       </c>
       <c r="G278" t="s">
@@ -16622,7 +16596,7 @@
       <c r="C279">
         <v>2026</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="1">
         <v>45890</v>
       </c>
       <c r="G279" t="s">
@@ -16660,7 +16634,7 @@
       <c r="C280">
         <v>2026</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="1">
         <v>46175</v>
       </c>
       <c r="F280" t="s">
@@ -16701,7 +16675,7 @@
       <c r="C281">
         <v>2026</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="1">
         <v>45890</v>
       </c>
       <c r="G281" t="s">
@@ -16739,7 +16713,7 @@
       <c r="C282">
         <v>2026</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="1">
         <v>46119</v>
       </c>
       <c r="F282" t="s">
@@ -16780,7 +16754,7 @@
       <c r="C283">
         <v>2026</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="1">
         <v>46119</v>
       </c>
       <c r="F283" t="s">
@@ -16821,7 +16795,7 @@
       <c r="C284">
         <v>2026</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="1">
         <v>46119</v>
       </c>
       <c r="F284" t="s">
@@ -16926,7 +16900,7 @@
       <c r="C287">
         <v>2026</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="1">
         <v>45856</v>
       </c>
       <c r="F287" t="s">
@@ -16967,7 +16941,7 @@
       <c r="C288">
         <v>2026</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="1">
         <v>45769</v>
       </c>
       <c r="F288" t="s">
@@ -17008,7 +16982,7 @@
       <c r="C289">
         <v>2026</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="1">
         <v>45769</v>
       </c>
       <c r="F289" t="s">
@@ -17049,7 +17023,7 @@
       <c r="C290">
         <v>2026</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="1">
         <v>45769</v>
       </c>
       <c r="F290" t="s">
@@ -17090,7 +17064,7 @@
       <c r="C291">
         <v>2026</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="1">
         <v>45769</v>
       </c>
       <c r="F291" t="s">
@@ -17131,7 +17105,7 @@
       <c r="C292">
         <v>2026</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292" s="1">
         <v>45769</v>
       </c>
       <c r="F292" t="s">
@@ -17172,7 +17146,7 @@
       <c r="C293">
         <v>2026</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293" s="1">
         <v>45769</v>
       </c>
       <c r="F293" t="s">
@@ -17213,7 +17187,7 @@
       <c r="C294">
         <v>2026</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294" s="1">
         <v>45769</v>
       </c>
       <c r="F294" t="s">
@@ -17254,7 +17228,7 @@
       <c r="C295">
         <v>2026</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295" s="1">
         <v>46147</v>
       </c>
       <c r="H295" t="s">
@@ -17289,7 +17263,7 @@
       <c r="C296">
         <v>2026</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296" s="1">
         <v>46147</v>
       </c>
       <c r="H296" t="s">
@@ -17324,7 +17298,7 @@
       <c r="C297">
         <v>2026</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="1">
         <v>46147</v>
       </c>
       <c r="H297" t="s">
@@ -17359,7 +17333,7 @@
       <c r="C298">
         <v>2026</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298" s="1">
         <v>45814</v>
       </c>
       <c r="F298" t="s">
@@ -17432,7 +17406,7 @@
       <c r="C300">
         <v>2026</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="1">
         <v>45860</v>
       </c>
       <c r="F300" t="s">
@@ -17473,7 +17447,7 @@
       <c r="C301">
         <v>2026</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="1">
         <v>45971</v>
       </c>
       <c r="F301" t="s">
@@ -17514,7 +17488,7 @@
       <c r="C302">
         <v>2026</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302" s="1">
         <v>45863</v>
       </c>
       <c r="F302" t="s">
@@ -17555,7 +17529,7 @@
       <c r="C303">
         <v>2026</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303" s="1">
         <v>45905</v>
       </c>
       <c r="G303" t="s">
@@ -17593,7 +17567,7 @@
       <c r="C304">
         <v>2026</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304" s="1">
         <v>45971</v>
       </c>
       <c r="F304" t="s">
@@ -17634,7 +17608,7 @@
       <c r="C305">
         <v>2026</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305" s="1">
         <v>45971</v>
       </c>
       <c r="F305" t="s">
@@ -17675,7 +17649,7 @@
       <c r="C306">
         <v>2026</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306" s="1">
         <v>45744</v>
       </c>
       <c r="F306" t="s">
@@ -17716,7 +17690,7 @@
       <c r="C307">
         <v>2026</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="1">
         <v>45814</v>
       </c>
       <c r="F307" t="s">
@@ -17757,7 +17731,7 @@
       <c r="C308">
         <v>2026</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="1">
         <v>45807</v>
       </c>
       <c r="F308" t="s">
@@ -17798,7 +17772,7 @@
       <c r="C309">
         <v>2026</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309" s="1">
         <v>45802</v>
       </c>
       <c r="F309" t="s">
@@ -17839,7 +17813,7 @@
       <c r="C310">
         <v>2026</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310" s="1">
         <v>45802</v>
       </c>
       <c r="F310" t="s">
@@ -17880,7 +17854,7 @@
       <c r="C311">
         <v>2026</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311" s="1">
         <v>45802</v>
       </c>
       <c r="F311" t="s">
@@ -17921,7 +17895,7 @@
       <c r="C312">
         <v>2026</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312" s="1">
         <v>45897</v>
       </c>
       <c r="H312" t="s">
@@ -17956,7 +17930,7 @@
       <c r="C313">
         <v>2026</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313" s="1">
         <v>45802</v>
       </c>
       <c r="F313" t="s">
@@ -17997,7 +17971,7 @@
       <c r="C314">
         <v>2026</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314" s="1">
         <v>45802</v>
       </c>
       <c r="F314" t="s">
@@ -18038,7 +18012,7 @@
       <c r="C315">
         <v>2026</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="1">
         <v>45876</v>
       </c>
       <c r="F315" t="s">
@@ -18079,7 +18053,7 @@
       <c r="C316">
         <v>2026</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316" s="1">
         <v>45889</v>
       </c>
       <c r="F316" t="s">
@@ -18120,7 +18094,7 @@
       <c r="C317">
         <v>2026</v>
       </c>
-      <c r="D317" s="2">
+      <c r="D317" s="1">
         <v>45876</v>
       </c>
       <c r="F317" t="s">
@@ -18161,7 +18135,7 @@
       <c r="C318">
         <v>2026</v>
       </c>
-      <c r="D318" s="2">
+      <c r="D318" s="1">
         <v>45926</v>
       </c>
       <c r="F318" t="s">
@@ -18202,7 +18176,7 @@
       <c r="C319">
         <v>2026</v>
       </c>
-      <c r="D319" s="2">
+      <c r="D319" s="1">
         <v>45909</v>
       </c>
       <c r="F319" t="s">
@@ -18243,7 +18217,7 @@
       <c r="C320">
         <v>2026</v>
       </c>
-      <c r="D320" s="2">
+      <c r="D320" s="1">
         <v>46119</v>
       </c>
       <c r="F320" t="s">
@@ -18348,7 +18322,7 @@
       <c r="C323">
         <v>2026</v>
       </c>
-      <c r="D323" s="2">
+      <c r="D323" s="1">
         <v>46119</v>
       </c>
       <c r="F323" t="s">
@@ -18389,7 +18363,7 @@
       <c r="C324">
         <v>2026</v>
       </c>
-      <c r="D324" s="2">
+      <c r="D324" s="1">
         <v>46119</v>
       </c>
       <c r="F324" t="s">
@@ -18526,7 +18500,7 @@
       <c r="C328">
         <v>2026</v>
       </c>
-      <c r="D328" s="2">
+      <c r="D328" s="1">
         <v>46086</v>
       </c>
       <c r="G328" t="s">
@@ -18596,7 +18570,7 @@
       <c r="C330">
         <v>2026</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330" s="1">
         <v>45965</v>
       </c>
       <c r="F330" t="s">
@@ -18637,7 +18611,7 @@
       <c r="C331">
         <v>2026</v>
       </c>
-      <c r="D331" s="2">
+      <c r="D331" s="1">
         <v>46064</v>
       </c>
       <c r="H331" t="s">
@@ -18669,7 +18643,7 @@
       <c r="C332">
         <v>2026</v>
       </c>
-      <c r="D332" s="2">
+      <c r="D332" s="1">
         <v>46049</v>
       </c>
       <c r="F332" t="s">
@@ -18710,7 +18684,7 @@
       <c r="C333">
         <v>2026</v>
       </c>
-      <c r="D333" s="2">
+      <c r="D333" s="1">
         <v>45996</v>
       </c>
       <c r="G333" t="s">
@@ -18748,7 +18722,7 @@
       <c r="C334">
         <v>2026</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334" s="1">
         <v>45996</v>
       </c>
       <c r="G334" t="s">
@@ -18786,7 +18760,7 @@
       <c r="C335">
         <v>2026</v>
       </c>
-      <c r="D335" s="2">
+      <c r="D335" s="1">
         <v>45989</v>
       </c>
       <c r="G335" t="s">
@@ -18824,7 +18798,7 @@
       <c r="C336">
         <v>2026</v>
       </c>
-      <c r="D336" s="2">
+      <c r="D336" s="1">
         <v>46156</v>
       </c>
       <c r="H336" t="s">
@@ -18859,7 +18833,7 @@
       <c r="C337">
         <v>2026</v>
       </c>
-      <c r="D337" s="2">
+      <c r="D337" s="1">
         <v>45996</v>
       </c>
       <c r="G337" t="s">
@@ -18897,7 +18871,7 @@
       <c r="C338">
         <v>2026</v>
       </c>
-      <c r="D338" s="2">
+      <c r="D338" s="1">
         <v>45989</v>
       </c>
       <c r="G338" t="s">
@@ -18935,7 +18909,7 @@
       <c r="C339">
         <v>2026</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339" s="1">
         <v>46002</v>
       </c>
       <c r="G339" t="s">
@@ -18973,7 +18947,7 @@
       <c r="C340">
         <v>2026</v>
       </c>
-      <c r="D340" s="2">
+      <c r="D340" s="1">
         <v>46002</v>
       </c>
       <c r="G340" t="s">
@@ -19011,7 +18985,7 @@
       <c r="C341">
         <v>2026</v>
       </c>
-      <c r="D341" s="2">
+      <c r="D341" s="1">
         <v>45996</v>
       </c>
       <c r="G341" t="s">
@@ -19049,7 +19023,7 @@
       <c r="C342">
         <v>2026</v>
       </c>
-      <c r="D342" s="2">
+      <c r="D342" s="1">
         <v>46002</v>
       </c>
       <c r="G342" t="s">
@@ -19087,7 +19061,7 @@
       <c r="C343">
         <v>2026</v>
       </c>
-      <c r="D343" s="2">
+      <c r="D343" s="1">
         <v>46031</v>
       </c>
       <c r="G343" t="s">
@@ -19125,7 +19099,7 @@
       <c r="C344">
         <v>2026</v>
       </c>
-      <c r="D344" s="2">
+      <c r="D344" s="1">
         <v>46153</v>
       </c>
       <c r="F344" t="s">
@@ -19166,7 +19140,7 @@
       <c r="C345">
         <v>2026</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345" s="1">
         <v>46135</v>
       </c>
       <c r="F345" t="s">
@@ -19271,7 +19245,7 @@
       <c r="C348">
         <v>2026</v>
       </c>
-      <c r="D348" s="2">
+      <c r="D348" s="1">
         <v>46230</v>
       </c>
       <c r="F348" t="s">
@@ -19376,7 +19350,7 @@
       <c r="C351">
         <v>2026</v>
       </c>
-      <c r="D351" s="2">
+      <c r="D351" s="1">
         <v>45996</v>
       </c>
       <c r="G351" t="s">
@@ -19414,7 +19388,7 @@
       <c r="C352">
         <v>2026</v>
       </c>
-      <c r="D352" s="2">
+      <c r="D352" s="1">
         <v>45996</v>
       </c>
       <c r="G352" t="s">
@@ -19484,7 +19458,7 @@
       <c r="C354">
         <v>2026</v>
       </c>
-      <c r="D354" s="2">
+      <c r="D354" s="1">
         <v>46164</v>
       </c>
       <c r="H354" t="s">
@@ -19519,7 +19493,7 @@
       <c r="C355">
         <v>2026</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355" s="1">
         <v>46020</v>
       </c>
       <c r="G355" t="s">
@@ -19557,7 +19531,7 @@
       <c r="C356">
         <v>2026</v>
       </c>
-      <c r="D356" s="2">
+      <c r="D356" s="1">
         <v>46225</v>
       </c>
       <c r="F356" t="s">
@@ -19601,7 +19575,7 @@
       <c r="C357">
         <v>2026</v>
       </c>
-      <c r="D357" s="2">
+      <c r="D357" s="1">
         <v>46176</v>
       </c>
       <c r="H357" t="s">
@@ -19636,7 +19610,7 @@
       <c r="C358">
         <v>2026</v>
       </c>
-      <c r="D358" s="2">
+      <c r="D358" s="1">
         <v>46086</v>
       </c>
       <c r="G358" t="s">
@@ -19674,7 +19648,7 @@
       <c r="C359">
         <v>2026</v>
       </c>
-      <c r="D359" s="2">
+      <c r="D359" s="1">
         <v>46052</v>
       </c>
       <c r="G359" t="s">
@@ -19750,7 +19724,7 @@
       <c r="C361">
         <v>2026</v>
       </c>
-      <c r="D361" s="2">
+      <c r="D361" s="1">
         <v>46010</v>
       </c>
       <c r="G361" t="s">
@@ -19788,7 +19762,7 @@
       <c r="C362">
         <v>2026</v>
       </c>
-      <c r="D362" s="2">
+      <c r="D362" s="1">
         <v>46010</v>
       </c>
       <c r="G362" t="s">
@@ -19858,7 +19832,7 @@
       <c r="C364">
         <v>2026</v>
       </c>
-      <c r="D364" s="2">
+      <c r="D364" s="1">
         <v>46079</v>
       </c>
       <c r="F364" t="s">
@@ -19899,7 +19873,7 @@
       <c r="C365">
         <v>2026</v>
       </c>
-      <c r="D365" s="2">
+      <c r="D365" s="1">
         <v>46010</v>
       </c>
       <c r="G365" t="s">
@@ -19937,7 +19911,7 @@
       <c r="C366">
         <v>2026</v>
       </c>
-      <c r="D366" s="2">
+      <c r="D366" s="1">
         <v>46010</v>
       </c>
       <c r="G366" t="s">
@@ -19975,7 +19949,7 @@
       <c r="C367">
         <v>2026</v>
       </c>
-      <c r="D367" s="2">
+      <c r="D367" s="1">
         <v>46230</v>
       </c>
       <c r="F367" t="s">
@@ -20019,7 +19993,7 @@
       <c r="C368">
         <v>2026</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368" s="1">
         <v>46063</v>
       </c>
       <c r="G368" t="s">
@@ -20057,7 +20031,7 @@
       <c r="C369">
         <v>2026</v>
       </c>
-      <c r="D369" s="2">
+      <c r="D369" s="1">
         <v>46063</v>
       </c>
       <c r="F369" t="s">
@@ -20098,7 +20072,7 @@
       <c r="C370">
         <v>2026</v>
       </c>
-      <c r="D370" s="2">
+      <c r="D370" s="1">
         <v>46063</v>
       </c>
       <c r="F370" t="s">
@@ -20139,7 +20113,7 @@
       <c r="C371">
         <v>2026</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371" s="1">
         <v>46063</v>
       </c>
       <c r="F371" t="s">
@@ -20180,7 +20154,7 @@
       <c r="C372">
         <v>2026</v>
       </c>
-      <c r="D372" s="2">
+      <c r="D372" s="1">
         <v>46063</v>
       </c>
       <c r="G372" t="s">
@@ -20346,7 +20320,7 @@
       <c r="C377">
         <v>2026</v>
       </c>
-      <c r="D377" s="2">
+      <c r="D377" s="1">
         <v>46114</v>
       </c>
       <c r="F377" t="s">
@@ -20387,7 +20361,7 @@
       <c r="C378">
         <v>2026</v>
       </c>
-      <c r="D378" s="2">
+      <c r="D378" s="1">
         <v>46191</v>
       </c>
       <c r="F378" t="s">
@@ -20428,7 +20402,7 @@
       <c r="C379">
         <v>2026</v>
       </c>
-      <c r="D379" s="2">
+      <c r="D379" s="1">
         <v>46230</v>
       </c>
       <c r="F379" t="s">
@@ -20469,7 +20443,7 @@
       <c r="C380">
         <v>2026</v>
       </c>
-      <c r="D380" s="2">
+      <c r="D380" s="1">
         <v>46230</v>
       </c>
       <c r="F380" t="s">
@@ -20510,7 +20484,7 @@
       <c r="C381">
         <v>2026</v>
       </c>
-      <c r="D381" s="2">
+      <c r="D381" s="1">
         <v>46230</v>
       </c>
       <c r="F381" t="s">
@@ -20551,7 +20525,7 @@
       <c r="C382">
         <v>2026</v>
       </c>
-      <c r="D382" s="2">
+      <c r="D382" s="1">
         <v>46230</v>
       </c>
       <c r="F382" t="s">
@@ -20592,7 +20566,7 @@
       <c r="C383">
         <v>2026</v>
       </c>
-      <c r="D383" s="2">
+      <c r="D383" s="1">
         <v>46230</v>
       </c>
       <c r="F383" t="s">
@@ -20633,7 +20607,7 @@
       <c r="C384">
         <v>2026</v>
       </c>
-      <c r="D384" s="2">
+      <c r="D384" s="1">
         <v>46230</v>
       </c>
       <c r="F384" t="s">
@@ -20674,7 +20648,7 @@
       <c r="C385">
         <v>2026</v>
       </c>
-      <c r="D385" s="2">
+      <c r="D385" s="1">
         <v>46230</v>
       </c>
       <c r="F385" t="s">
@@ -20747,7 +20721,7 @@
       <c r="C387">
         <v>2026</v>
       </c>
-      <c r="D387" s="2">
+      <c r="D387" s="1">
         <v>45996</v>
       </c>
       <c r="G387" t="s">
@@ -20977,7 +20951,7 @@
       <c r="C394">
         <v>2026</v>
       </c>
-      <c r="D394" s="2">
+      <c r="D394" s="1">
         <v>46052</v>
       </c>
       <c r="F394" t="s">
@@ -21018,7 +20992,7 @@
       <c r="C395">
         <v>2026</v>
       </c>
-      <c r="D395" s="2">
+      <c r="D395" s="1">
         <v>46057</v>
       </c>
       <c r="F395" t="s">
@@ -21059,7 +21033,7 @@
       <c r="C396">
         <v>2026</v>
       </c>
-      <c r="D396" s="2">
+      <c r="D396" s="1">
         <v>46112</v>
       </c>
       <c r="F396" t="s">
@@ -21132,7 +21106,7 @@
       <c r="C398">
         <v>2026</v>
       </c>
-      <c r="D398" s="2">
+      <c r="D398" s="1">
         <v>46063</v>
       </c>
       <c r="G398" t="s">
@@ -21170,7 +21144,7 @@
       <c r="C399">
         <v>2026</v>
       </c>
-      <c r="D399" s="2">
+      <c r="D399" s="1">
         <v>46048</v>
       </c>
       <c r="G399" t="s">
@@ -21208,7 +21182,7 @@
       <c r="C400">
         <v>2026</v>
       </c>
-      <c r="D400" s="2">
+      <c r="D400" s="1">
         <v>46063</v>
       </c>
       <c r="H400" t="s">
@@ -21275,7 +21249,7 @@
       <c r="C402">
         <v>2026</v>
       </c>
-      <c r="D402" s="2">
+      <c r="D402" s="1">
         <v>46119</v>
       </c>
       <c r="F402" t="s">
@@ -21348,7 +21322,7 @@
       <c r="C404">
         <v>2026</v>
       </c>
-      <c r="D404" s="2">
+      <c r="D404" s="1">
         <v>46119</v>
       </c>
       <c r="F404" t="s">
@@ -21389,7 +21363,7 @@
       <c r="C405">
         <v>2026</v>
       </c>
-      <c r="D405" s="2">
+      <c r="D405" s="1">
         <v>46113</v>
       </c>
       <c r="F405" t="s">
@@ -21430,7 +21404,7 @@
       <c r="C406">
         <v>2026</v>
       </c>
-      <c r="D406" s="2">
+      <c r="D406" s="1">
         <v>46104</v>
       </c>
       <c r="F406" t="s">
@@ -21471,7 +21445,7 @@
       <c r="C407">
         <v>2026</v>
       </c>
-      <c r="D407" s="2">
+      <c r="D407" s="1">
         <v>46135</v>
       </c>
       <c r="H407" t="s">
@@ -21538,7 +21512,7 @@
       <c r="C409">
         <v>2026</v>
       </c>
-      <c r="D409" s="2">
+      <c r="D409" s="1">
         <v>46230</v>
       </c>
       <c r="F409" t="s">
@@ -21579,7 +21553,7 @@
       <c r="C410">
         <v>2026</v>
       </c>
-      <c r="D410" s="2">
+      <c r="D410" s="1">
         <v>46086</v>
       </c>
       <c r="G410" t="s">
@@ -21617,7 +21591,7 @@
       <c r="C411">
         <v>2026</v>
       </c>
-      <c r="D411" s="2">
+      <c r="D411" s="1">
         <v>46086</v>
       </c>
       <c r="G411" t="s">
@@ -21655,7 +21629,7 @@
       <c r="C412">
         <v>2026</v>
       </c>
-      <c r="D412" s="2">
+      <c r="D412" s="1">
         <v>46086</v>
       </c>
       <c r="H412" t="s">
@@ -21690,7 +21664,7 @@
       <c r="C413">
         <v>2026</v>
       </c>
-      <c r="D413" s="2">
+      <c r="D413" s="1">
         <v>46230</v>
       </c>
       <c r="F413" t="s">
@@ -21827,7 +21801,7 @@
       <c r="C417">
         <v>2026</v>
       </c>
-      <c r="D417" s="2">
+      <c r="D417" s="1">
         <v>46176</v>
       </c>
       <c r="H417" t="s">
@@ -21862,7 +21836,7 @@
       <c r="C418">
         <v>2026</v>
       </c>
-      <c r="D418" s="2">
+      <c r="D418" s="1">
         <v>46147</v>
       </c>
       <c r="H418" t="s">
@@ -21897,7 +21871,7 @@
       <c r="C419">
         <v>2026</v>
       </c>
-      <c r="D419" s="2">
+      <c r="D419" s="1">
         <v>46135</v>
       </c>
       <c r="H419" t="s">
@@ -21964,7 +21938,7 @@
       <c r="C421">
         <v>2026</v>
       </c>
-      <c r="D421" s="2">
+      <c r="D421" s="1">
         <v>46227</v>
       </c>
       <c r="G421" t="s">
@@ -22005,7 +21979,7 @@
       <c r="C422">
         <v>2026</v>
       </c>
-      <c r="D422" s="2">
+      <c r="D422" s="1">
         <v>46230</v>
       </c>
       <c r="F422" t="s">
@@ -22046,7 +22020,7 @@
       <c r="C423">
         <v>2026</v>
       </c>
-      <c r="D423" s="2">
+      <c r="D423" s="1">
         <v>46083</v>
       </c>
       <c r="F423" t="s">
@@ -22087,7 +22061,7 @@
       <c r="C424">
         <v>2026</v>
       </c>
-      <c r="D424" s="2">
+      <c r="D424" s="1">
         <v>46083</v>
       </c>
       <c r="G424" t="s">
@@ -22125,7 +22099,7 @@
       <c r="C425">
         <v>2026</v>
       </c>
-      <c r="D425" s="2">
+      <c r="D425" s="1">
         <v>46083</v>
       </c>
       <c r="F425" t="s">
@@ -22166,7 +22140,7 @@
       <c r="C426">
         <v>2026</v>
       </c>
-      <c r="D426" s="2">
+      <c r="D426" s="1">
         <v>46127</v>
       </c>
       <c r="F426" t="s">
@@ -22207,7 +22181,7 @@
       <c r="C427">
         <v>2026</v>
       </c>
-      <c r="D427" s="2">
+      <c r="D427" s="1">
         <v>46100</v>
       </c>
       <c r="F427" t="s">
@@ -22405,7 +22379,7 @@
       <c r="C433">
         <v>2026</v>
       </c>
-      <c r="D433" s="2">
+      <c r="D433" s="1">
         <v>46230</v>
       </c>
       <c r="F433" t="s">
@@ -22446,7 +22420,7 @@
       <c r="C434">
         <v>2026</v>
       </c>
-      <c r="D434" s="2">
+      <c r="D434" s="1">
         <v>46079</v>
       </c>
       <c r="H434" t="s">
@@ -22577,7 +22551,7 @@
       <c r="C438">
         <v>2026</v>
       </c>
-      <c r="D438" s="2">
+      <c r="D438" s="1">
         <v>46176</v>
       </c>
       <c r="F438" t="s">
@@ -22618,7 +22592,7 @@
       <c r="C439">
         <v>2026</v>
       </c>
-      <c r="D439" s="2">
+      <c r="D439" s="1">
         <v>46176</v>
       </c>
       <c r="F439" t="s">
@@ -22659,7 +22633,7 @@
       <c r="C440">
         <v>2026</v>
       </c>
-      <c r="D440" s="2">
+      <c r="D440" s="1">
         <v>46155</v>
       </c>
       <c r="F440" t="s">
@@ -22700,7 +22674,7 @@
       <c r="C441">
         <v>2026</v>
       </c>
-      <c r="D441" s="2">
+      <c r="D441" s="1">
         <v>46155</v>
       </c>
       <c r="G441" t="s">
@@ -22738,7 +22712,7 @@
       <c r="C442">
         <v>2026</v>
       </c>
-      <c r="D442" s="2">
+      <c r="D442" s="1">
         <v>46129</v>
       </c>
       <c r="F442" t="s">
@@ -22779,7 +22753,7 @@
       <c r="C443">
         <v>2026</v>
       </c>
-      <c r="D443" s="2">
+      <c r="D443" s="1">
         <v>46119</v>
       </c>
       <c r="F443" t="s">
@@ -22820,7 +22794,7 @@
       <c r="C444">
         <v>2026</v>
       </c>
-      <c r="D444" s="2">
+      <c r="D444" s="1">
         <v>46135</v>
       </c>
       <c r="H444" t="s">
@@ -22855,7 +22829,7 @@
       <c r="C445">
         <v>2026</v>
       </c>
-      <c r="D445" s="2">
+      <c r="D445" s="1">
         <v>46127</v>
       </c>
       <c r="H445" t="s">
@@ -22890,7 +22864,7 @@
       <c r="C446">
         <v>2026</v>
       </c>
-      <c r="D446" s="2">
+      <c r="D446" s="1">
         <v>46127</v>
       </c>
       <c r="H446" t="s">
@@ -22957,7 +22931,7 @@
       <c r="C448">
         <v>2026</v>
       </c>
-      <c r="D448" s="2">
+      <c r="D448" s="1">
         <v>46175</v>
       </c>
       <c r="F448" t="s">
@@ -22998,7 +22972,7 @@
       <c r="C449">
         <v>2026</v>
       </c>
-      <c r="D449" s="2">
+      <c r="D449" s="1">
         <v>46139</v>
       </c>
       <c r="H449" t="s">
@@ -23033,7 +23007,7 @@
       <c r="C450">
         <v>2026</v>
       </c>
-      <c r="D450" s="2">
+      <c r="D450" s="1">
         <v>46155</v>
       </c>
       <c r="H450" t="s">
@@ -23068,7 +23042,7 @@
       <c r="C451">
         <v>2026</v>
       </c>
-      <c r="D451" s="2">
+      <c r="D451" s="1">
         <v>46175</v>
       </c>
       <c r="F451" t="s">
@@ -23141,7 +23115,7 @@
       <c r="C453">
         <v>2026</v>
       </c>
-      <c r="D453" s="2">
+      <c r="D453" s="1">
         <v>46156</v>
       </c>
       <c r="F453" t="s">
@@ -23182,7 +23156,7 @@
       <c r="C454">
         <v>2026</v>
       </c>
-      <c r="D454" s="2">
+      <c r="D454" s="1">
         <v>46157</v>
       </c>
       <c r="G454" t="s">
@@ -23220,7 +23194,7 @@
       <c r="C455">
         <v>2026</v>
       </c>
-      <c r="D455" s="2">
+      <c r="D455" s="1">
         <v>46183</v>
       </c>
       <c r="H455" t="s">
@@ -23255,7 +23229,7 @@
       <c r="C456">
         <v>2026</v>
       </c>
-      <c r="D456" s="2">
+      <c r="D456" s="1">
         <v>46183</v>
       </c>
       <c r="H456" t="s">
@@ -23354,7 +23328,7 @@
       <c r="C459">
         <v>2026</v>
       </c>
-      <c r="D459" s="2">
+      <c r="D459" s="1">
         <v>46230</v>
       </c>
       <c r="F459" t="s">
@@ -23398,7 +23372,7 @@
       <c r="C460">
         <v>2026</v>
       </c>
-      <c r="D460" s="2">
+      <c r="D460" s="1">
         <v>46185</v>
       </c>
       <c r="H460" t="s">
@@ -23465,7 +23439,7 @@
       <c r="C462">
         <v>2026</v>
       </c>
-      <c r="D462" s="2">
+      <c r="D462" s="1">
         <v>46185</v>
       </c>
       <c r="H462" t="s">
@@ -23564,7 +23538,7 @@
       <c r="C465">
         <v>2026</v>
       </c>
-      <c r="D465" s="2">
+      <c r="D465" s="1">
         <v>46175</v>
       </c>
       <c r="F465" t="s">
@@ -23605,7 +23579,7 @@
       <c r="C466">
         <v>2026</v>
       </c>
-      <c r="D466" s="2">
+      <c r="D466" s="1">
         <v>46175</v>
       </c>
       <c r="F466" t="s">
@@ -23646,7 +23620,7 @@
       <c r="C467">
         <v>2026</v>
       </c>
-      <c r="D467" s="2">
+      <c r="D467" s="1">
         <v>46230</v>
       </c>
       <c r="F467" t="s">
@@ -23687,7 +23661,7 @@
       <c r="C468">
         <v>2026</v>
       </c>
-      <c r="D468" s="2">
+      <c r="D468" s="1">
         <v>46175</v>
       </c>
       <c r="G468" t="s">
@@ -23725,7 +23699,7 @@
       <c r="C469">
         <v>2026</v>
       </c>
-      <c r="D469" s="2">
+      <c r="D469" s="1">
         <v>46175</v>
       </c>
       <c r="G469" t="s">
@@ -23763,7 +23737,7 @@
       <c r="C470">
         <v>2026</v>
       </c>
-      <c r="D470" s="2">
+      <c r="D470" s="1">
         <v>46175</v>
       </c>
       <c r="G470" t="s">
@@ -23801,7 +23775,7 @@
       <c r="C471">
         <v>2026</v>
       </c>
-      <c r="D471" s="2">
+      <c r="D471" s="1">
         <v>46230</v>
       </c>
       <c r="F471" t="s">
@@ -23842,7 +23816,7 @@
       <c r="C472">
         <v>2026</v>
       </c>
-      <c r="D472" s="2">
+      <c r="D472" s="1">
         <v>46175</v>
       </c>
       <c r="G472" t="s">
@@ -23880,7 +23854,7 @@
       <c r="C473">
         <v>2026</v>
       </c>
-      <c r="D473" s="2">
+      <c r="D473" s="1">
         <v>46175</v>
       </c>
       <c r="G473" t="s">
@@ -23918,7 +23892,7 @@
       <c r="C474">
         <v>2026</v>
       </c>
-      <c r="D474" s="2">
+      <c r="D474" s="1">
         <v>46175</v>
       </c>
       <c r="G474" t="s">
@@ -23956,7 +23930,7 @@
       <c r="C475">
         <v>2026</v>
       </c>
-      <c r="D475" s="2">
+      <c r="D475" s="1">
         <v>46230</v>
       </c>
       <c r="F475" t="s">
@@ -24029,7 +24003,7 @@
       <c r="C477">
         <v>2026</v>
       </c>
-      <c r="D477" s="2">
+      <c r="D477" s="1">
         <v>46209</v>
       </c>
       <c r="F477" t="s">
@@ -24201,7 +24175,7 @@
       <c r="C482">
         <v>2026</v>
       </c>
-      <c r="D482" s="2">
+      <c r="D482" s="1">
         <v>46230</v>
       </c>
       <c r="F482" t="s">
@@ -24242,7 +24216,7 @@
       <c r="C483">
         <v>2026</v>
       </c>
-      <c r="D483" s="2">
+      <c r="D483" s="1">
         <v>46230</v>
       </c>
       <c r="F483" t="s">
@@ -24283,7 +24257,7 @@
       <c r="C484">
         <v>2026</v>
       </c>
-      <c r="D484" s="2">
+      <c r="D484" s="1">
         <v>46230</v>
       </c>
       <c r="F484" t="s">
@@ -24548,7 +24522,7 @@
       <c r="C492">
         <v>2026</v>
       </c>
-      <c r="D492" s="2">
+      <c r="D492" s="1">
         <v>46230</v>
       </c>
       <c r="F492" t="s">
@@ -24589,7 +24563,7 @@
       <c r="C493">
         <v>2026</v>
       </c>
-      <c r="D493" s="2">
+      <c r="D493" s="1">
         <v>46230</v>
       </c>
       <c r="F493" t="s">
@@ -24694,7 +24668,7 @@
       <c r="C496">
         <v>2026</v>
       </c>
-      <c r="D496" s="2">
+      <c r="D496" s="1">
         <v>46230</v>
       </c>
       <c r="F496" t="s">
@@ -24738,7 +24712,7 @@
       <c r="C497">
         <v>2026</v>
       </c>
-      <c r="D497" s="2">
+      <c r="D497" s="1">
         <v>46230</v>
       </c>
       <c r="F497" t="s">
@@ -24779,7 +24753,7 @@
       <c r="C498">
         <v>2026</v>
       </c>
-      <c r="D498" s="2">
+      <c r="D498" s="1">
         <v>46157</v>
       </c>
       <c r="G498" t="s">
@@ -24817,7 +24791,7 @@
       <c r="C499">
         <v>2026</v>
       </c>
-      <c r="D499" s="2">
+      <c r="D499" s="1">
         <v>46213</v>
       </c>
       <c r="F499" t="s">
@@ -24893,7 +24867,7 @@
       <c r="C501">
         <v>2026</v>
       </c>
-      <c r="D501" s="2">
+      <c r="D501" s="1">
         <v>46205</v>
       </c>
       <c r="F501" t="s">
@@ -24937,7 +24911,7 @@
       <c r="C502">
         <v>2026</v>
       </c>
-      <c r="D502" s="2">
+      <c r="D502" s="1">
         <v>46176</v>
       </c>
       <c r="F502" t="s">
@@ -24978,7 +24952,7 @@
       <c r="C503">
         <v>2026</v>
       </c>
-      <c r="D503" s="2">
+      <c r="D503" s="1">
         <v>46150</v>
       </c>
       <c r="F503" t="s">
@@ -25083,7 +25057,7 @@
       <c r="C506">
         <v>2026</v>
       </c>
-      <c r="D506" s="2">
+      <c r="D506" s="1">
         <v>46220</v>
       </c>
       <c r="F506" t="s">
@@ -25127,7 +25101,7 @@
       <c r="C507">
         <v>2026</v>
       </c>
-      <c r="D507" s="2">
+      <c r="D507" s="1">
         <v>46224</v>
       </c>
       <c r="F507" t="s">
@@ -25203,7 +25177,7 @@
       <c r="C509">
         <v>2026</v>
       </c>
-      <c r="D509" s="2">
+      <c r="D509" s="1">
         <v>46155</v>
       </c>
       <c r="H509" t="s">
@@ -25238,7 +25212,7 @@
       <c r="C510">
         <v>2026</v>
       </c>
-      <c r="D510" s="2">
+      <c r="D510" s="1">
         <v>46156</v>
       </c>
       <c r="F510" t="s">
@@ -25279,7 +25253,7 @@
       <c r="C511">
         <v>2026</v>
       </c>
-      <c r="D511" s="2">
+      <c r="D511" s="1">
         <v>46185</v>
       </c>
       <c r="H511" t="s">
@@ -25314,7 +25288,7 @@
       <c r="C512">
         <v>2026</v>
       </c>
-      <c r="D512" s="2">
+      <c r="D512" s="1">
         <v>46230</v>
       </c>
       <c r="F512" t="s">
@@ -25355,7 +25329,7 @@
       <c r="C513">
         <v>2026</v>
       </c>
-      <c r="D513" s="2">
+      <c r="D513" s="1">
         <v>46230</v>
       </c>
       <c r="F513" t="s">
@@ -25396,7 +25370,7 @@
       <c r="C514">
         <v>2026</v>
       </c>
-      <c r="D514" s="2">
+      <c r="D514" s="1">
         <v>46230</v>
       </c>
       <c r="F514" t="s">
@@ -25437,7 +25411,7 @@
       <c r="C515">
         <v>2026</v>
       </c>
-      <c r="D515" s="2">
+      <c r="D515" s="1">
         <v>46230</v>
       </c>
       <c r="F515" t="s">
@@ -25478,7 +25452,7 @@
       <c r="C516">
         <v>2026</v>
       </c>
-      <c r="D516" s="2">
+      <c r="D516" s="1">
         <v>46230</v>
       </c>
       <c r="F516" t="s">
@@ -25583,7 +25557,7 @@
       <c r="C519">
         <v>2026</v>
       </c>
-      <c r="D519" s="2">
+      <c r="D519" s="1">
         <v>46147</v>
       </c>
       <c r="G519" t="s">
@@ -25717,7 +25691,7 @@
       <c r="C523">
         <v>2026</v>
       </c>
-      <c r="D523" s="2">
+      <c r="D523" s="1">
         <v>46164</v>
       </c>
       <c r="F523" t="s">
@@ -25854,7 +25828,7 @@
       <c r="C527">
         <v>2026</v>
       </c>
-      <c r="D527" s="2">
+      <c r="D527" s="1">
         <v>46230</v>
       </c>
       <c r="F527" t="s">
@@ -25991,7 +25965,7 @@
       <c r="C531">
         <v>2026</v>
       </c>
-      <c r="D531" s="2">
+      <c r="D531" s="1">
         <v>46171</v>
       </c>
       <c r="F531" t="s">
@@ -26096,7 +26070,7 @@
       <c r="C534">
         <v>2026</v>
       </c>
-      <c r="D534" s="2">
+      <c r="D534" s="1">
         <v>46176</v>
       </c>
       <c r="G534" t="s">
@@ -26134,7 +26108,7 @@
       <c r="C535">
         <v>2026</v>
       </c>
-      <c r="D535" s="2">
+      <c r="D535" s="1">
         <v>46230</v>
       </c>
       <c r="F535" t="s">
@@ -26335,7 +26309,7 @@
       <c r="C541">
         <v>2026</v>
       </c>
-      <c r="D541" s="2">
+      <c r="D541" s="1">
         <v>46211</v>
       </c>
       <c r="F541" t="s">
@@ -26379,7 +26353,7 @@
       <c r="C542">
         <v>2026</v>
       </c>
-      <c r="D542" s="2">
+      <c r="D542" s="1">
         <v>46183</v>
       </c>
       <c r="H542" t="s">
@@ -26414,7 +26388,7 @@
       <c r="C543">
         <v>2026</v>
       </c>
-      <c r="D543" s="2">
+      <c r="D543" s="1">
         <v>46191</v>
       </c>
       <c r="H543" t="s">
@@ -26449,7 +26423,7 @@
       <c r="C544">
         <v>2026</v>
       </c>
-      <c r="D544" s="2">
+      <c r="D544" s="1">
         <v>46191</v>
       </c>
       <c r="G544" t="s">
@@ -26647,7 +26621,7 @@
       <c r="C550">
         <v>2026</v>
       </c>
-      <c r="D550" s="2">
+      <c r="D550" s="1">
         <v>46230</v>
       </c>
       <c r="F550" t="s">
@@ -26752,7 +26726,7 @@
       <c r="C553">
         <v>2026</v>
       </c>
-      <c r="D553" s="2">
+      <c r="D553" s="1">
         <v>46230</v>
       </c>
       <c r="F553" t="s">
@@ -26793,7 +26767,7 @@
       <c r="C554">
         <v>2026</v>
       </c>
-      <c r="D554" s="2">
+      <c r="D554" s="1">
         <v>46191</v>
       </c>
       <c r="G554" t="s">
@@ -26959,7 +26933,7 @@
       <c r="C559">
         <v>2026</v>
       </c>
-      <c r="D559" s="2">
+      <c r="D559" s="1">
         <v>46191</v>
       </c>
       <c r="G559" t="s">
@@ -27157,7 +27131,7 @@
       <c r="C565">
         <v>2026</v>
       </c>
-      <c r="D565" s="2">
+      <c r="D565" s="1">
         <v>46230</v>
       </c>
       <c r="F565" t="s">
@@ -27777,7 +27751,7 @@
       <c r="C584">
         <v>2026</v>
       </c>
-      <c r="D584" s="2">
+      <c r="D584" s="1">
         <v>46226</v>
       </c>
       <c r="F584" t="s">
@@ -28301,7 +28275,7 @@
       <c r="C600">
         <v>2026</v>
       </c>
-      <c r="D600" s="2">
+      <c r="D600" s="1">
         <v>45802</v>
       </c>
       <c r="F600" t="s">
@@ -28345,7 +28319,7 @@
       <c r="C601">
         <v>2026</v>
       </c>
-      <c r="D601" s="2">
+      <c r="D601" s="1">
         <v>45860</v>
       </c>
       <c r="F601" t="s">
@@ -28386,7 +28360,7 @@
       <c r="C602">
         <v>2026</v>
       </c>
-      <c r="D602" s="2">
+      <c r="D602" s="1">
         <v>45860</v>
       </c>
       <c r="H602" t="s">
@@ -28421,7 +28395,7 @@
       <c r="C603">
         <v>2026</v>
       </c>
-      <c r="D603" s="2">
+      <c r="D603" s="1">
         <v>45856</v>
       </c>
       <c r="F603" t="s">
@@ -28462,7 +28436,7 @@
       <c r="C604">
         <v>2026</v>
       </c>
-      <c r="D604" s="2">
+      <c r="D604" s="1">
         <v>46101</v>
       </c>
       <c r="F604" t="s">
@@ -28503,7 +28477,7 @@
       <c r="C605">
         <v>2026</v>
       </c>
-      <c r="D605" s="2">
+      <c r="D605" s="1">
         <v>46101</v>
       </c>
       <c r="F605" t="s">
@@ -28544,7 +28518,7 @@
       <c r="C606">
         <v>2026</v>
       </c>
-      <c r="D606" s="2">
+      <c r="D606" s="1">
         <v>45863</v>
       </c>
       <c r="F606" t="s">
@@ -28585,7 +28559,7 @@
       <c r="C607">
         <v>2026</v>
       </c>
-      <c r="D607" s="2">
+      <c r="D607" s="1">
         <v>45863</v>
       </c>
       <c r="F607" t="s">
@@ -28626,7 +28600,7 @@
       <c r="C608">
         <v>2026</v>
       </c>
-      <c r="D608" s="2">
+      <c r="D608" s="1">
         <v>46086</v>
       </c>
       <c r="F608" t="s">
@@ -28667,7 +28641,7 @@
       <c r="C609">
         <v>2026</v>
       </c>
-      <c r="D609" s="2">
+      <c r="D609" s="1">
         <v>45874</v>
       </c>
       <c r="F609" t="s">
@@ -28708,7 +28682,7 @@
       <c r="C610">
         <v>2026</v>
       </c>
-      <c r="D610" s="2">
+      <c r="D610" s="1">
         <v>45894</v>
       </c>
       <c r="F610" t="s">
@@ -28749,7 +28723,7 @@
       <c r="C611">
         <v>2026</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="1">
         <v>45894</v>
       </c>
       <c r="F611" t="s">
@@ -28790,7 +28764,7 @@
       <c r="C612">
         <v>2026</v>
       </c>
-      <c r="D612" s="2">
+      <c r="D612" s="1">
         <v>46119</v>
       </c>
       <c r="F612" t="s">
@@ -28831,7 +28805,7 @@
       <c r="C613">
         <v>2026</v>
       </c>
-      <c r="D613" s="2">
+      <c r="D613" s="1">
         <v>45898</v>
       </c>
       <c r="F613" t="s">
@@ -28872,7 +28846,7 @@
       <c r="C614">
         <v>2026</v>
       </c>
-      <c r="D614" s="2">
+      <c r="D614" s="1">
         <v>45971</v>
       </c>
       <c r="F614" t="s">
@@ -28913,7 +28887,7 @@
       <c r="C615">
         <v>2026</v>
       </c>
-      <c r="D615" s="2">
+      <c r="D615" s="1">
         <v>46119</v>
       </c>
       <c r="F615" t="s">
@@ -28954,7 +28928,7 @@
       <c r="C616">
         <v>2026</v>
       </c>
-      <c r="D616" s="2">
+      <c r="D616" s="1">
         <v>46092</v>
       </c>
       <c r="F616" t="s">
@@ -28995,7 +28969,7 @@
       <c r="C617">
         <v>2026</v>
       </c>
-      <c r="D617" s="2">
+      <c r="D617" s="1">
         <v>46119</v>
       </c>
       <c r="F617" t="s">
@@ -29036,7 +29010,7 @@
       <c r="C618">
         <v>2026</v>
       </c>
-      <c r="D618" s="2">
+      <c r="D618" s="1">
         <v>46029</v>
       </c>
       <c r="F618" t="s">
@@ -29077,7 +29051,7 @@
       <c r="C619">
         <v>2026</v>
       </c>
-      <c r="D619" s="2">
+      <c r="D619" s="1">
         <v>46029</v>
       </c>
       <c r="F619" t="s">
@@ -29118,7 +29092,7 @@
       <c r="C620">
         <v>2026</v>
       </c>
-      <c r="D620" s="2">
+      <c r="D620" s="1">
         <v>46063</v>
       </c>
       <c r="H620" t="s">
@@ -29153,7 +29127,7 @@
       <c r="C621">
         <v>2026</v>
       </c>
-      <c r="D621" s="2">
+      <c r="D621" s="1">
         <v>46232</v>
       </c>
       <c r="G621" t="s">
@@ -29191,7 +29165,7 @@
       <c r="C622">
         <v>2026</v>
       </c>
-      <c r="D622" s="2">
+      <c r="D622" s="1">
         <v>46232</v>
       </c>
       <c r="G622" t="s">
@@ -29229,7 +29203,7 @@
       <c r="C623">
         <v>2026</v>
       </c>
-      <c r="D623" s="2">
+      <c r="D623" s="1">
         <v>46232</v>
       </c>
       <c r="G623" t="s">
@@ -29267,7 +29241,7 @@
       <c r="C624">
         <v>2026</v>
       </c>
-      <c r="D624" s="2">
+      <c r="D624" s="1">
         <v>46232</v>
       </c>
       <c r="G624" t="s">
@@ -29305,7 +29279,7 @@
       <c r="C625">
         <v>2026</v>
       </c>
-      <c r="D625" s="2">
+      <c r="D625" s="1">
         <v>46155</v>
       </c>
       <c r="H625" t="s">
@@ -29340,7 +29314,7 @@
       <c r="C626">
         <v>2026</v>
       </c>
-      <c r="D626" s="2">
+      <c r="D626" s="1">
         <v>46139</v>
       </c>
       <c r="F626" t="s">
@@ -29381,7 +29355,7 @@
       <c r="C627">
         <v>2026</v>
       </c>
-      <c r="D627" s="2">
+      <c r="D627" s="1">
         <v>46155</v>
       </c>
       <c r="F627" t="s">
@@ -29422,7 +29396,7 @@
       <c r="C628">
         <v>2026</v>
       </c>
-      <c r="D628" s="2">
+      <c r="D628" s="1">
         <v>46155</v>
       </c>
       <c r="H628" t="s">
@@ -29457,7 +29431,7 @@
       <c r="C629">
         <v>2026</v>
       </c>
-      <c r="D629" s="2">
+      <c r="D629" s="1">
         <v>46147</v>
       </c>
       <c r="H629" t="s">
@@ -29492,7 +29466,7 @@
       <c r="C630">
         <v>2026</v>
       </c>
-      <c r="D630" s="2">
+      <c r="D630" s="1">
         <v>46164</v>
       </c>
       <c r="F630" t="s">
@@ -29533,7 +29507,7 @@
       <c r="C631">
         <v>2026</v>
       </c>
-      <c r="D631" s="2">
+      <c r="D631" s="1">
         <v>46225</v>
       </c>
       <c r="F631" t="s">
@@ -29574,7 +29548,7 @@
       <c r="C632">
         <v>2026</v>
       </c>
-      <c r="D632" s="2">
+      <c r="D632" s="1">
         <v>46225</v>
       </c>
       <c r="F632" t="s">
@@ -29615,7 +29589,7 @@
       <c r="C633">
         <v>2026</v>
       </c>
-      <c r="D633" s="2">
+      <c r="D633" s="1">
         <v>46225</v>
       </c>
       <c r="F633" t="s">
@@ -29656,7 +29630,7 @@
       <c r="C634">
         <v>2026</v>
       </c>
-      <c r="D634" s="2">
+      <c r="D634" s="1">
         <v>46248</v>
       </c>
       <c r="H634" t="s">
@@ -29691,7 +29665,7 @@
       <c r="C635">
         <v>2026</v>
       </c>
-      <c r="D635" s="2">
+      <c r="D635" s="1">
         <v>46248</v>
       </c>
       <c r="F635" t="s">
@@ -29732,7 +29706,7 @@
       <c r="C636">
         <v>2026</v>
       </c>
-      <c r="D636" s="2">
+      <c r="D636" s="1">
         <v>46171</v>
       </c>
       <c r="H636" t="s">
@@ -29767,7 +29741,7 @@
       <c r="C637">
         <v>2026</v>
       </c>
-      <c r="D637" s="2">
+      <c r="D637" s="1">
         <v>46176</v>
       </c>
       <c r="H637" t="s">
@@ -29802,7 +29776,7 @@
       <c r="C638">
         <v>2026</v>
       </c>
-      <c r="D638" s="2">
+      <c r="D638" s="1">
         <v>46225</v>
       </c>
       <c r="F638" t="s">
@@ -29843,7 +29817,7 @@
       <c r="C639">
         <v>2026</v>
       </c>
-      <c r="D639" s="2">
+      <c r="D639" s="1">
         <v>46211</v>
       </c>
       <c r="H639" t="s">
@@ -29878,7 +29852,7 @@
       <c r="C640">
         <v>2026</v>
       </c>
-      <c r="D640" s="2">
+      <c r="D640" s="1">
         <v>46183</v>
       </c>
       <c r="H640" t="s">
@@ -29913,7 +29887,7 @@
       <c r="C641">
         <v>2026</v>
       </c>
-      <c r="D641" s="2">
+      <c r="D641" s="1">
         <v>46191</v>
       </c>
       <c r="F641" t="s">
@@ -29954,7 +29928,7 @@
       <c r="C642">
         <v>2026</v>
       </c>
-      <c r="D642" s="2">
+      <c r="D642" s="1">
         <v>46176</v>
       </c>
       <c r="H642" t="s">
@@ -29989,7 +29963,7 @@
       <c r="C643">
         <v>2026</v>
       </c>
-      <c r="D643" s="2">
+      <c r="D643" s="1">
         <v>46191</v>
       </c>
       <c r="H643" t="s">
@@ -30024,7 +29998,7 @@
       <c r="C644">
         <v>2026</v>
       </c>
-      <c r="D644" s="2">
+      <c r="D644" s="1">
         <v>46241</v>
       </c>
       <c r="F644" t="s">
@@ -30068,7 +30042,7 @@
       <c r="C645">
         <v>2026</v>
       </c>
-      <c r="D645" s="2">
+      <c r="D645" s="1">
         <v>46191</v>
       </c>
       <c r="F645" t="s">
@@ -30109,7 +30083,7 @@
       <c r="C646">
         <v>2026</v>
       </c>
-      <c r="D646" s="2">
+      <c r="D646" s="1">
         <v>46191</v>
       </c>
       <c r="F646" t="s">
@@ -30150,7 +30124,7 @@
       <c r="C647">
         <v>2026</v>
       </c>
-      <c r="D647" s="2">
+      <c r="D647" s="1">
         <v>46191</v>
       </c>
       <c r="H647" t="s">
@@ -30185,7 +30159,7 @@
       <c r="C648">
         <v>2026</v>
       </c>
-      <c r="D648" s="2">
+      <c r="D648" s="1">
         <v>46241</v>
       </c>
       <c r="F648" t="s">
@@ -30226,7 +30200,7 @@
       <c r="C649">
         <v>2026</v>
       </c>
-      <c r="D649" s="2">
+      <c r="D649" s="1">
         <v>46191</v>
       </c>
       <c r="H649" t="s">
@@ -30261,7 +30235,7 @@
       <c r="C650">
         <v>2026</v>
       </c>
-      <c r="D650" s="2">
+      <c r="D650" s="1">
         <v>46248</v>
       </c>
       <c r="H650" t="s">
@@ -30296,7 +30270,7 @@
       <c r="C651">
         <v>2026</v>
       </c>
-      <c r="D651" s="2">
+      <c r="D651" s="1">
         <v>46241</v>
       </c>
       <c r="F651" t="s">
@@ -30337,7 +30311,7 @@
       <c r="C652">
         <v>2026</v>
       </c>
-      <c r="D652" s="2">
+      <c r="D652" s="1">
         <v>46241</v>
       </c>
       <c r="F652" t="s">
@@ -30378,7 +30352,7 @@
       <c r="C653">
         <v>2026</v>
       </c>
-      <c r="D653" s="2">
+      <c r="D653" s="1">
         <v>46225</v>
       </c>
       <c r="F653" t="s">
@@ -30419,7 +30393,7 @@
       <c r="C654">
         <v>2026</v>
       </c>
-      <c r="D654" s="2">
+      <c r="D654" s="1">
         <v>46241</v>
       </c>
       <c r="F654" t="s">
@@ -30460,7 +30434,7 @@
       <c r="C655">
         <v>2026</v>
       </c>
-      <c r="D655" s="2">
+      <c r="D655" s="1">
         <v>46241</v>
       </c>
       <c r="F655" t="s">
@@ -30501,7 +30475,7 @@
       <c r="C656">
         <v>2026</v>
       </c>
-      <c r="D656" s="2">
+      <c r="D656" s="1">
         <v>46241</v>
       </c>
       <c r="F656" t="s">
@@ -30542,7 +30516,7 @@
       <c r="C657">
         <v>2026</v>
       </c>
-      <c r="D657" s="2">
+      <c r="D657" s="1">
         <v>46248</v>
       </c>
       <c r="H657" t="s">
@@ -30577,7 +30551,7 @@
       <c r="C658">
         <v>2026</v>
       </c>
-      <c r="D658" s="2">
+      <c r="D658" s="1">
         <v>46248</v>
       </c>
       <c r="H658" t="s">
@@ -30612,7 +30586,7 @@
       <c r="C659">
         <v>2026</v>
       </c>
-      <c r="D659" s="2">
+      <c r="D659" s="1">
         <v>46248</v>
       </c>
       <c r="F659" t="s">
@@ -30653,7 +30627,7 @@
       <c r="C660">
         <v>2026</v>
       </c>
-      <c r="D660" s="2">
+      <c r="D660" s="1">
         <v>46248</v>
       </c>
       <c r="F660" t="s">
@@ -30694,7 +30668,7 @@
       <c r="C661">
         <v>2026</v>
       </c>
-      <c r="D661" s="2">
+      <c r="D661" s="1">
         <v>46248</v>
       </c>
       <c r="F661" t="s">
@@ -30735,7 +30709,7 @@
       <c r="C662">
         <v>2026</v>
       </c>
-      <c r="D662" s="2">
+      <c r="D662" s="1">
         <v>45989</v>
       </c>
       <c r="G662" t="s">
@@ -30773,7 +30747,7 @@
       <c r="C663">
         <v>2026</v>
       </c>
-      <c r="D663" s="2">
+      <c r="D663" s="1">
         <v>46002</v>
       </c>
       <c r="G663" t="s">
@@ -30811,7 +30785,7 @@
       <c r="C664">
         <v>2026</v>
       </c>
-      <c r="D664" s="2">
+      <c r="D664" s="1">
         <v>46002</v>
       </c>
       <c r="G664" t="s">
@@ -30849,7 +30823,7 @@
       <c r="C665">
         <v>2026</v>
       </c>
-      <c r="D665" s="2">
+      <c r="D665" s="1">
         <v>46225</v>
       </c>
       <c r="F665" t="s">
@@ -30890,7 +30864,7 @@
       <c r="C666">
         <v>2026</v>
       </c>
-      <c r="D666" s="2">
+      <c r="D666" s="1">
         <v>46211</v>
       </c>
       <c r="F666" t="s">
@@ -30931,7 +30905,7 @@
       <c r="C667">
         <v>2026</v>
       </c>
-      <c r="D667" s="2">
+      <c r="D667" s="1">
         <v>46248</v>
       </c>
       <c r="F667" t="s">
@@ -30972,7 +30946,7 @@
       <c r="C668">
         <v>2026</v>
       </c>
-      <c r="D668" s="2">
+      <c r="D668" s="1">
         <v>46248</v>
       </c>
       <c r="F668" t="s">
@@ -31045,7 +31019,7 @@
       <c r="C670">
         <v>2026</v>
       </c>
-      <c r="D670" s="2">
+      <c r="D670" s="1">
         <v>46255</v>
       </c>
       <c r="F670" t="s">
@@ -31246,7 +31220,7 @@
       <c r="C676">
         <v>2026</v>
       </c>
-      <c r="D676" s="2">
+      <c r="D676" s="1">
         <v>46265</v>
       </c>
       <c r="H676" t="s">
@@ -31281,7 +31255,7 @@
       <c r="C677">
         <v>2026</v>
       </c>
-      <c r="D677" s="2">
+      <c r="D677" s="1">
         <v>46265</v>
       </c>
       <c r="H677" t="s">
@@ -31316,7 +31290,7 @@
       <c r="C678">
         <v>2026</v>
       </c>
-      <c r="D678" s="2">
+      <c r="D678" s="1">
         <v>46265</v>
       </c>
       <c r="H678" t="s">
@@ -31671,7 +31645,7 @@
       <c r="C689">
         <v>2026</v>
       </c>
-      <c r="D689" s="2">
+      <c r="D689" s="1">
         <v>46265</v>
       </c>
       <c r="H689" t="s">
@@ -31706,7 +31680,7 @@
       <c r="C690">
         <v>2026</v>
       </c>
-      <c r="D690" s="2">
+      <c r="D690" s="1">
         <v>46265</v>
       </c>
       <c r="H690" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
@@ -5570,16 +5570,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5595,7 +5587,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -5603,30 +5595,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5926,52 +5900,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6049,7 +6023,7 @@
       <c r="C4">
         <v>2026</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>45972</v>
       </c>
       <c r="F4" t="s">
@@ -6186,7 +6160,7 @@
       <c r="C8">
         <v>2026</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>46014</v>
       </c>
       <c r="F8" t="s">
@@ -6323,7 +6297,7 @@
       <c r="C12">
         <v>2026</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>45916</v>
       </c>
       <c r="F12" t="s">
@@ -6364,7 +6338,7 @@
       <c r="C13">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>45897</v>
       </c>
       <c r="H13" t="s">
@@ -6399,7 +6373,7 @@
       <c r="C14">
         <v>2026</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>45916</v>
       </c>
       <c r="F14" t="s">
@@ -6440,7 +6414,7 @@
       <c r="C15">
         <v>2026</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>46086</v>
       </c>
       <c r="G15" t="s">
@@ -6478,7 +6452,7 @@
       <c r="C16">
         <v>2026</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>45869</v>
       </c>
       <c r="F16" t="s">
@@ -6519,7 +6493,7 @@
       <c r="C17">
         <v>2026</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>45877</v>
       </c>
       <c r="F17" t="s">
@@ -6560,7 +6534,7 @@
       <c r="C18">
         <v>2026</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>46086</v>
       </c>
       <c r="G18" t="s">
@@ -6598,7 +6572,7 @@
       <c r="C19">
         <v>2026</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>45863</v>
       </c>
       <c r="F19" t="s">
@@ -6639,7 +6613,7 @@
       <c r="C20">
         <v>2026</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>45863</v>
       </c>
       <c r="F20" t="s">
@@ -6680,7 +6654,7 @@
       <c r="C21">
         <v>2026</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>45873</v>
       </c>
       <c r="F21" t="s">
@@ -6721,7 +6695,7 @@
       <c r="C22">
         <v>2026</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
@@ -6762,7 +6736,7 @@
       <c r="C23">
         <v>2026</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>46086</v>
       </c>
       <c r="G23" t="s">
@@ -6864,7 +6838,7 @@
       <c r="C26">
         <v>2026</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>45838</v>
       </c>
       <c r="F26" t="s">
@@ -6905,7 +6879,7 @@
       <c r="C27">
         <v>2026</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>45800</v>
       </c>
       <c r="F27" t="s">
@@ -6946,7 +6920,7 @@
       <c r="C28">
         <v>2026</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>45849</v>
       </c>
       <c r="F28" t="s">
@@ -6987,7 +6961,7 @@
       <c r="C29">
         <v>2026</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>45838</v>
       </c>
       <c r="F29" t="s">
@@ -7028,7 +7002,7 @@
       <c r="C30">
         <v>2026</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>45915</v>
       </c>
       <c r="F30" t="s">
@@ -7069,7 +7043,7 @@
       <c r="C31">
         <v>2026</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>45849</v>
       </c>
       <c r="F31" t="s">
@@ -7142,7 +7116,7 @@
       <c r="C33">
         <v>2026</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>45800</v>
       </c>
       <c r="F33" t="s">
@@ -7215,7 +7189,7 @@
       <c r="C35">
         <v>2026</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>46119</v>
       </c>
       <c r="F35" t="s">
@@ -7256,7 +7230,7 @@
       <c r="C36">
         <v>2026</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>45854</v>
       </c>
       <c r="F36" t="s">
@@ -7297,7 +7271,7 @@
       <c r="C37">
         <v>2026</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>45849</v>
       </c>
       <c r="F37" t="s">
@@ -7338,7 +7312,7 @@
       <c r="C38">
         <v>2026</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>46119</v>
       </c>
       <c r="F38" t="s">
@@ -7411,7 +7385,7 @@
       <c r="C40">
         <v>2026</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>46092</v>
       </c>
       <c r="F40" t="s">
@@ -7516,7 +7490,7 @@
       <c r="C43">
         <v>2026</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>46122</v>
       </c>
       <c r="F43" t="s">
@@ -7557,7 +7531,7 @@
       <c r="C44">
         <v>2026</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>46122</v>
       </c>
       <c r="F44" t="s">
@@ -7598,7 +7572,7 @@
       <c r="C45">
         <v>2026</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>46135</v>
       </c>
       <c r="F45" t="s">
@@ -7639,7 +7613,7 @@
       <c r="C46">
         <v>2026</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>46086</v>
       </c>
       <c r="F46" t="s">
@@ -7680,7 +7654,7 @@
       <c r="C47">
         <v>2026</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>46104</v>
       </c>
       <c r="F47" t="s">
@@ -7721,7 +7695,7 @@
       <c r="C48">
         <v>2026</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>45972</v>
       </c>
       <c r="G48" t="s">
@@ -7759,7 +7733,7 @@
       <c r="C49">
         <v>2026</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>45810</v>
       </c>
       <c r="F49" t="s">
@@ -7800,7 +7774,7 @@
       <c r="C50">
         <v>2026</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>45937</v>
       </c>
       <c r="F50" t="s">
@@ -7841,7 +7815,7 @@
       <c r="C51">
         <v>2026</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>45937</v>
       </c>
       <c r="F51" t="s">
@@ -7914,7 +7888,7 @@
       <c r="C53">
         <v>2026</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="1">
         <v>45845</v>
       </c>
       <c r="F53" t="s">
@@ -7955,7 +7929,7 @@
       <c r="C54">
         <v>2026</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="1">
         <v>46077</v>
       </c>
       <c r="F54" t="s">
@@ -8028,7 +8002,7 @@
       <c r="C56">
         <v>2026</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>45971</v>
       </c>
       <c r="F56" t="s">
@@ -8101,7 +8075,7 @@
       <c r="C58">
         <v>2026</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>45817</v>
       </c>
       <c r="F58" t="s">
@@ -8174,7 +8148,7 @@
       <c r="C60">
         <v>2026</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>45965</v>
       </c>
       <c r="G60" t="s">
@@ -8244,7 +8218,7 @@
       <c r="C62">
         <v>2026</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>46072</v>
       </c>
       <c r="F62" t="s">
@@ -8317,7 +8291,7 @@
       <c r="C64">
         <v>2026</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>46072</v>
       </c>
       <c r="H64" t="s">
@@ -8352,7 +8326,7 @@
       <c r="C65">
         <v>2026</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>45804</v>
       </c>
       <c r="F65" t="s">
@@ -8393,7 +8367,7 @@
       <c r="C66">
         <v>2026</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>45804</v>
       </c>
       <c r="F66" t="s">
@@ -8434,7 +8408,7 @@
       <c r="C67">
         <v>2026</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>45804</v>
       </c>
       <c r="F67" t="s">
@@ -8475,7 +8449,7 @@
       <c r="C68">
         <v>2026</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="1">
         <v>45804</v>
       </c>
       <c r="F68" t="s">
@@ -8516,7 +8490,7 @@
       <c r="C69">
         <v>2026</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="1">
         <v>45804</v>
       </c>
       <c r="F69" t="s">
@@ -8557,7 +8531,7 @@
       <c r="C70">
         <v>2026</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>45804</v>
       </c>
       <c r="F70" t="s">
@@ -8598,7 +8572,7 @@
       <c r="C71">
         <v>2026</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="1">
         <v>45821</v>
       </c>
       <c r="F71" t="s">
@@ -8639,7 +8613,7 @@
       <c r="C72">
         <v>2026</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="1">
         <v>45821</v>
       </c>
       <c r="H72" t="s">
@@ -8674,7 +8648,7 @@
       <c r="C73">
         <v>2026</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="1">
         <v>45891</v>
       </c>
       <c r="F73" t="s">
@@ -8715,7 +8689,7 @@
       <c r="C74">
         <v>2026</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="1">
         <v>45817</v>
       </c>
       <c r="G74" t="s">
@@ -8753,7 +8727,7 @@
       <c r="C75">
         <v>2026</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="1">
         <v>45883</v>
       </c>
       <c r="G75" t="s">
@@ -8791,7 +8765,7 @@
       <c r="C76">
         <v>2026</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="1">
         <v>45817</v>
       </c>
       <c r="G76" t="s">
@@ -8829,7 +8803,7 @@
       <c r="C77">
         <v>2026</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="1">
         <v>45883</v>
       </c>
       <c r="G77" t="s">
@@ -8867,7 +8841,7 @@
       <c r="C78">
         <v>2026</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>45971</v>
       </c>
       <c r="F78" t="s">
@@ -8908,7 +8882,7 @@
       <c r="C79">
         <v>2026</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>45849</v>
       </c>
       <c r="F79" t="s">
@@ -8949,7 +8923,7 @@
       <c r="C80">
         <v>2026</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="1">
         <v>45849</v>
       </c>
       <c r="F80" t="s">
@@ -8990,7 +8964,7 @@
       <c r="C81">
         <v>2026</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="1">
         <v>45863</v>
       </c>
       <c r="F81" t="s">
@@ -9031,7 +9005,7 @@
       <c r="C82">
         <v>2026</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>45810</v>
       </c>
       <c r="F82" t="s">
@@ -9072,7 +9046,7 @@
       <c r="C83">
         <v>2026</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="1">
         <v>45926</v>
       </c>
       <c r="F83" t="s">
@@ -9113,7 +9087,7 @@
       <c r="C84">
         <v>2026</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="1">
         <v>45971</v>
       </c>
       <c r="F84" t="s">
@@ -9154,7 +9128,7 @@
       <c r="C85">
         <v>2026</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="1">
         <v>46164</v>
       </c>
       <c r="F85" t="s">
@@ -9195,7 +9169,7 @@
       <c r="C86">
         <v>2026</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>45986</v>
       </c>
       <c r="G86" t="s">
@@ -9274,7 +9248,7 @@
       <c r="C88">
         <v>2026</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="1">
         <v>45786</v>
       </c>
       <c r="F88" t="s">
@@ -9315,7 +9289,7 @@
       <c r="C89">
         <v>2026</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="1">
         <v>45777</v>
       </c>
       <c r="F89" t="s">
@@ -9356,7 +9330,7 @@
       <c r="C90">
         <v>2026</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="1">
         <v>45869</v>
       </c>
       <c r="F90" t="s">
@@ -9397,7 +9371,7 @@
       <c r="C91">
         <v>2026</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="1">
         <v>45891</v>
       </c>
       <c r="F91" t="s">
@@ -9438,7 +9412,7 @@
       <c r="C92">
         <v>2026</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="1">
         <v>45863</v>
       </c>
       <c r="F92" t="s">
@@ -9479,7 +9453,7 @@
       <c r="C93">
         <v>2026</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="1">
         <v>45769</v>
       </c>
       <c r="F93" t="s">
@@ -9520,7 +9494,7 @@
       <c r="C94">
         <v>2026</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="1">
         <v>45769</v>
       </c>
       <c r="F94" t="s">
@@ -9561,7 +9535,7 @@
       <c r="C95">
         <v>2026</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="1">
         <v>45894</v>
       </c>
       <c r="F95" t="s">
@@ -9634,7 +9608,7 @@
       <c r="C97">
         <v>2026</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="1">
         <v>45894</v>
       </c>
       <c r="F97" t="s">
@@ -9675,7 +9649,7 @@
       <c r="C98">
         <v>2026</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="1">
         <v>45971</v>
       </c>
       <c r="F98" t="s">
@@ -9716,7 +9690,7 @@
       <c r="C99">
         <v>2026</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>45971</v>
       </c>
       <c r="F99" t="s">
@@ -9757,7 +9731,7 @@
       <c r="C100">
         <v>2026</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="1">
         <v>45971</v>
       </c>
       <c r="F100" t="s">
@@ -9798,7 +9772,7 @@
       <c r="C101">
         <v>2026</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="1">
         <v>45996</v>
       </c>
       <c r="G101" t="s">
@@ -9836,7 +9810,7 @@
       <c r="C102">
         <v>2026</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="1">
         <v>45986</v>
       </c>
       <c r="G102" t="s">
@@ -9906,7 +9880,7 @@
       <c r="C104">
         <v>2026</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="1">
         <v>45769</v>
       </c>
       <c r="F104" t="s">
@@ -9947,7 +9921,7 @@
       <c r="C105">
         <v>2026</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="1">
         <v>45769</v>
       </c>
       <c r="F105" t="s">
@@ -9988,7 +9962,7 @@
       <c r="C106">
         <v>2026</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="1">
         <v>45849</v>
       </c>
       <c r="F106" t="s">
@@ -10029,7 +10003,7 @@
       <c r="C107">
         <v>2026</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="1">
         <v>45849</v>
       </c>
       <c r="G107" t="s">
@@ -10131,7 +10105,7 @@
       <c r="C110">
         <v>2026</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="1">
         <v>45891</v>
       </c>
       <c r="F110" t="s">
@@ -10172,7 +10146,7 @@
       <c r="C111">
         <v>2026</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="1">
         <v>45769</v>
       </c>
       <c r="F111" t="s">
@@ -10213,7 +10187,7 @@
       <c r="C112">
         <v>2026</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="1">
         <v>45889</v>
       </c>
       <c r="F112" t="s">
@@ -10254,7 +10228,7 @@
       <c r="C113">
         <v>2026</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="1">
         <v>45945</v>
       </c>
       <c r="G113" t="s">
@@ -10292,7 +10266,7 @@
       <c r="C114">
         <v>2026</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="1">
         <v>45945</v>
       </c>
       <c r="G114" t="s">
@@ -10330,7 +10304,7 @@
       <c r="C115">
         <v>2026</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="1">
         <v>46119</v>
       </c>
       <c r="F115" t="s">
@@ -10371,7 +10345,7 @@
       <c r="C116">
         <v>2026</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="1">
         <v>46029</v>
       </c>
       <c r="F116" t="s">
@@ -10412,7 +10386,7 @@
       <c r="C117">
         <v>2026</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="1">
         <v>46029</v>
       </c>
       <c r="F117" t="s">
@@ -10453,7 +10427,7 @@
       <c r="C118">
         <v>2026</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="1">
         <v>46119</v>
       </c>
       <c r="F118" t="s">
@@ -10494,7 +10468,7 @@
       <c r="C119">
         <v>2026</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="1">
         <v>46230</v>
       </c>
       <c r="F119" t="s">
@@ -10535,7 +10509,7 @@
       <c r="C120">
         <v>2026</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="1">
         <v>46119</v>
       </c>
       <c r="F120" t="s">
@@ -10576,7 +10550,7 @@
       <c r="C121">
         <v>2026</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="1">
         <v>46119</v>
       </c>
       <c r="F121" t="s">
@@ -10617,7 +10591,7 @@
       <c r="C122">
         <v>2026</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="1">
         <v>45931</v>
       </c>
       <c r="F122" t="s">
@@ -10658,7 +10632,7 @@
       <c r="C123">
         <v>2026</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="1">
         <v>45894</v>
       </c>
       <c r="G123" t="s">
@@ -10696,7 +10670,7 @@
       <c r="C124">
         <v>2026</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="1">
         <v>46119</v>
       </c>
       <c r="F124" t="s">
@@ -10737,7 +10711,7 @@
       <c r="C125">
         <v>2026</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="1">
         <v>45889</v>
       </c>
       <c r="F125" t="s">
@@ -10778,7 +10752,7 @@
       <c r="C126">
         <v>2026</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="1">
         <v>45876</v>
       </c>
       <c r="G126" t="s">
@@ -10848,7 +10822,7 @@
       <c r="C128">
         <v>2026</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="1">
         <v>45876</v>
       </c>
       <c r="F128" t="s">
@@ -10921,7 +10895,7 @@
       <c r="C130">
         <v>2026</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="1">
         <v>46230</v>
       </c>
       <c r="F130" t="s">
@@ -10962,7 +10936,7 @@
       <c r="C131">
         <v>2026</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="1">
         <v>45889</v>
       </c>
       <c r="F131" t="s">
@@ -11003,7 +10977,7 @@
       <c r="C132">
         <v>2026</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="1">
         <v>46230</v>
       </c>
       <c r="F132" t="s">
@@ -11076,7 +11050,7 @@
       <c r="C134">
         <v>2026</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="1">
         <v>46140</v>
       </c>
       <c r="F134" t="s">
@@ -11117,7 +11091,7 @@
       <c r="C135">
         <v>2026</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="1">
         <v>45889</v>
       </c>
       <c r="F135" t="s">
@@ -11158,7 +11132,7 @@
       <c r="C136">
         <v>2026</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="1">
         <v>45952</v>
       </c>
       <c r="F136" t="s">
@@ -11196,7 +11170,7 @@
       <c r="C137">
         <v>2026</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="1">
         <v>46230</v>
       </c>
       <c r="F137" t="s">
@@ -11269,7 +11243,7 @@
       <c r="C139">
         <v>2026</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="1">
         <v>46029</v>
       </c>
       <c r="G139" t="s">
@@ -11307,7 +11281,7 @@
       <c r="C140">
         <v>2026</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="1">
         <v>46029</v>
       </c>
       <c r="G140" t="s">
@@ -11377,7 +11351,7 @@
       <c r="C142">
         <v>2026</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="1">
         <v>46119</v>
       </c>
       <c r="F142" t="s">
@@ -11482,7 +11456,7 @@
       <c r="C145">
         <v>2026</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="1">
         <v>46140</v>
       </c>
       <c r="F145" t="s">
@@ -11523,7 +11497,7 @@
       <c r="C146">
         <v>2026</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="1">
         <v>46230</v>
       </c>
       <c r="F146" t="s">
@@ -11564,7 +11538,7 @@
       <c r="C147">
         <v>2026</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="1">
         <v>46230</v>
       </c>
       <c r="F147" t="s">
@@ -11605,7 +11579,7 @@
       <c r="C148">
         <v>2026</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="1">
         <v>46119</v>
       </c>
       <c r="F148" t="s">
@@ -11646,7 +11620,7 @@
       <c r="C149">
         <v>2026</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="1">
         <v>46230</v>
       </c>
       <c r="F149" t="s">
@@ -11687,7 +11661,7 @@
       <c r="C150">
         <v>2026</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="1">
         <v>46140</v>
       </c>
       <c r="F150" t="s">
@@ -11728,7 +11702,7 @@
       <c r="C151">
         <v>2026</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="1">
         <v>45876</v>
       </c>
       <c r="F151" t="s">
@@ -11801,7 +11775,7 @@
       <c r="C153">
         <v>2026</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="1">
         <v>45863</v>
       </c>
       <c r="F153" t="s">
@@ -11842,7 +11816,7 @@
       <c r="C154">
         <v>2026</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="1">
         <v>45863</v>
       </c>
       <c r="F154" t="s">
@@ -11883,7 +11857,7 @@
       <c r="C155">
         <v>2026</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="1">
         <v>45863</v>
       </c>
       <c r="F155" t="s">
@@ -11924,7 +11898,7 @@
       <c r="C156">
         <v>2026</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="1">
         <v>45860</v>
       </c>
       <c r="F156" t="s">
@@ -11994,7 +11968,7 @@
       <c r="C158">
         <v>2026</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="1">
         <v>46119</v>
       </c>
       <c r="F158" t="s">
@@ -12035,7 +12009,7 @@
       <c r="C159">
         <v>2026</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="1">
         <v>45814</v>
       </c>
       <c r="F159" t="s">
@@ -12076,7 +12050,7 @@
       <c r="C160">
         <v>2026</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="1">
         <v>45817</v>
       </c>
       <c r="F160" t="s">
@@ -12117,7 +12091,7 @@
       <c r="C161">
         <v>2026</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="1">
         <v>45971</v>
       </c>
       <c r="F161" t="s">
@@ -12158,7 +12132,7 @@
       <c r="C162">
         <v>2026</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="1">
         <v>45971</v>
       </c>
       <c r="F162" t="s">
@@ -12199,7 +12173,7 @@
       <c r="C163">
         <v>2026</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="1">
         <v>45860</v>
       </c>
       <c r="G163" t="s">
@@ -12237,7 +12211,7 @@
       <c r="C164">
         <v>2026</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="1">
         <v>45856</v>
       </c>
       <c r="F164" t="s">
@@ -12310,7 +12284,7 @@
       <c r="C166">
         <v>2026</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="1">
         <v>46064</v>
       </c>
       <c r="F166" t="s">
@@ -12351,7 +12325,7 @@
       <c r="C167">
         <v>2026</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="1">
         <v>45982</v>
       </c>
       <c r="G167" t="s">
@@ -12389,7 +12363,7 @@
       <c r="C168">
         <v>2026</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="1">
         <v>46157</v>
       </c>
       <c r="H168" t="s">
@@ -12424,7 +12398,7 @@
       <c r="C169">
         <v>2026</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="1">
         <v>45762</v>
       </c>
       <c r="F169" t="s">
@@ -12465,7 +12439,7 @@
       <c r="C170">
         <v>2026</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="1">
         <v>45816</v>
       </c>
       <c r="F170" t="s">
@@ -12506,7 +12480,7 @@
       <c r="C171">
         <v>2026</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="1">
         <v>45816</v>
       </c>
       <c r="F171" t="s">
@@ -12585,7 +12559,7 @@
       <c r="C173">
         <v>2026</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="1">
         <v>46101</v>
       </c>
       <c r="F173" t="s">
@@ -12626,7 +12600,7 @@
       <c r="C174">
         <v>2026</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="1">
         <v>46101</v>
       </c>
       <c r="F174" t="s">
@@ -12667,7 +12641,7 @@
       <c r="C175">
         <v>2026</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="1">
         <v>46105</v>
       </c>
       <c r="F175" t="s">
@@ -12708,7 +12682,7 @@
       <c r="C176">
         <v>2026</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="1">
         <v>45889</v>
       </c>
       <c r="F176" t="s">
@@ -12749,7 +12723,7 @@
       <c r="C177">
         <v>2026</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="1">
         <v>45814</v>
       </c>
       <c r="F177" t="s">
@@ -12790,7 +12764,7 @@
       <c r="C178">
         <v>2026</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="1">
         <v>45889</v>
       </c>
       <c r="F178" t="s">
@@ -12831,7 +12805,7 @@
       <c r="C179">
         <v>2026</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="1">
         <v>45814</v>
       </c>
       <c r="F179" t="s">
@@ -12872,7 +12846,7 @@
       <c r="C180">
         <v>2026</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="1">
         <v>45889</v>
       </c>
       <c r="F180" t="s">
@@ -12945,7 +12919,7 @@
       <c r="C182">
         <v>2026</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="1">
         <v>46139</v>
       </c>
       <c r="H182" t="s">
@@ -13012,7 +12986,7 @@
       <c r="C184">
         <v>2026</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="1">
         <v>45889</v>
       </c>
       <c r="F184" t="s">
@@ -13085,7 +13059,7 @@
       <c r="C186">
         <v>2026</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="1">
         <v>45814</v>
       </c>
       <c r="F186" t="s">
@@ -13126,7 +13100,7 @@
       <c r="C187">
         <v>2026</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="1">
         <v>45889</v>
       </c>
       <c r="F187" t="s">
@@ -13167,7 +13141,7 @@
       <c r="C188">
         <v>2026</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="1">
         <v>45931</v>
       </c>
       <c r="F188" t="s">
@@ -13208,7 +13182,7 @@
       <c r="C189">
         <v>2026</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="1">
         <v>45889</v>
       </c>
       <c r="F189" t="s">
@@ -13249,7 +13223,7 @@
       <c r="C190">
         <v>2026</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="1">
         <v>45876</v>
       </c>
       <c r="F190" t="s">
@@ -13290,7 +13264,7 @@
       <c r="C191">
         <v>2026</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="1">
         <v>45876</v>
       </c>
       <c r="F191" t="s">
@@ -13363,7 +13337,7 @@
       <c r="C193">
         <v>2026</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="1">
         <v>45876</v>
       </c>
       <c r="F193" t="s">
@@ -13404,7 +13378,7 @@
       <c r="C194">
         <v>2026</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194" s="1">
         <v>46119</v>
       </c>
       <c r="F194" t="s">
@@ -13445,7 +13419,7 @@
       <c r="C195">
         <v>2026</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="1">
         <v>46119</v>
       </c>
       <c r="F195" t="s">
@@ -13486,7 +13460,7 @@
       <c r="C196">
         <v>2026</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196" s="1">
         <v>45961</v>
       </c>
       <c r="F196" t="s">
@@ -13527,7 +13501,7 @@
       <c r="C197">
         <v>2026</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="1">
         <v>45860</v>
       </c>
       <c r="F197" t="s">
@@ -13568,7 +13542,7 @@
       <c r="C198">
         <v>2026</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="1">
         <v>45993</v>
       </c>
       <c r="G198" t="s">
@@ -13606,7 +13580,7 @@
       <c r="C199">
         <v>2026</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="1">
         <v>45853</v>
       </c>
       <c r="F199" t="s">
@@ -13647,7 +13621,7 @@
       <c r="C200">
         <v>2026</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200" s="1">
         <v>46119</v>
       </c>
       <c r="F200" t="s">
@@ -13726,7 +13700,7 @@
       <c r="C202">
         <v>2026</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202" s="1">
         <v>46191</v>
       </c>
       <c r="F202" t="s">
@@ -13767,7 +13741,7 @@
       <c r="C203">
         <v>2026</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203" s="1">
         <v>46191</v>
       </c>
       <c r="F203" t="s">
@@ -13808,7 +13782,7 @@
       <c r="C204">
         <v>2026</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="1">
         <v>46191</v>
       </c>
       <c r="F204" t="s">
@@ -13849,7 +13823,7 @@
       <c r="C205">
         <v>2026</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="1">
         <v>45932</v>
       </c>
       <c r="G205" t="s">
@@ -13887,7 +13861,7 @@
       <c r="C206">
         <v>2026</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206" s="1">
         <v>46191</v>
       </c>
       <c r="F206" t="s">
@@ -13928,7 +13902,7 @@
       <c r="C207">
         <v>2026</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207" s="1">
         <v>46119</v>
       </c>
       <c r="F207" t="s">
@@ -13969,7 +13943,7 @@
       <c r="C208">
         <v>2026</v>
       </c>
-      <c r="D208" s="2">
+      <c r="D208" s="1">
         <v>45946</v>
       </c>
       <c r="G208" t="s">
@@ -14007,7 +13981,7 @@
       <c r="C209">
         <v>2026</v>
       </c>
-      <c r="D209" s="2">
+      <c r="D209" s="1">
         <v>45937</v>
       </c>
       <c r="F209" t="s">
@@ -14048,7 +14022,7 @@
       <c r="C210">
         <v>2026</v>
       </c>
-      <c r="D210" s="2">
+      <c r="D210" s="1">
         <v>45849</v>
       </c>
       <c r="F210" t="s">
@@ -14089,7 +14063,7 @@
       <c r="C211">
         <v>2026</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211" s="1">
         <v>45876</v>
       </c>
       <c r="F211" t="s">
@@ -14130,7 +14104,7 @@
       <c r="C212">
         <v>2026</v>
       </c>
-      <c r="D212" s="2">
+      <c r="D212" s="1">
         <v>46008</v>
       </c>
       <c r="F212" t="s">
@@ -14244,7 +14218,7 @@
       <c r="C215">
         <v>2026</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215" s="1">
         <v>45973</v>
       </c>
       <c r="F215" t="s">
@@ -14285,7 +14259,7 @@
       <c r="C216">
         <v>2026</v>
       </c>
-      <c r="D216" s="2">
+      <c r="D216" s="1">
         <v>46014</v>
       </c>
       <c r="F216" t="s">
@@ -14326,7 +14300,7 @@
       <c r="C217">
         <v>2026</v>
       </c>
-      <c r="D217" s="2">
+      <c r="D217" s="1">
         <v>45876</v>
       </c>
       <c r="F217" t="s">
@@ -14367,7 +14341,7 @@
       <c r="C218">
         <v>2026</v>
       </c>
-      <c r="D218" s="2">
+      <c r="D218" s="1">
         <v>45937</v>
       </c>
       <c r="F218" t="s">
@@ -14408,7 +14382,7 @@
       <c r="C219">
         <v>2026</v>
       </c>
-      <c r="D219" s="2">
+      <c r="D219" s="1">
         <v>45980</v>
       </c>
       <c r="F219" t="s">
@@ -14769,7 +14743,7 @@
       <c r="C230">
         <v>2026</v>
       </c>
-      <c r="D230" s="2">
+      <c r="D230" s="1">
         <v>45979</v>
       </c>
       <c r="F230" t="s">
@@ -14810,7 +14784,7 @@
       <c r="C231">
         <v>2026</v>
       </c>
-      <c r="D231" s="2">
+      <c r="D231" s="1">
         <v>45979</v>
       </c>
       <c r="F231" t="s">
@@ -14851,7 +14825,7 @@
       <c r="C232">
         <v>2026</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232" s="1">
         <v>45979</v>
       </c>
       <c r="F232" t="s">
@@ -14892,7 +14866,7 @@
       <c r="C233">
         <v>2026</v>
       </c>
-      <c r="D233" s="2">
+      <c r="D233" s="1">
         <v>45971</v>
       </c>
       <c r="F233" t="s">
@@ -14933,7 +14907,7 @@
       <c r="C234">
         <v>2026</v>
       </c>
-      <c r="D234" s="2">
+      <c r="D234" s="1">
         <v>45971</v>
       </c>
       <c r="F234" t="s">
@@ -14974,7 +14948,7 @@
       <c r="C235">
         <v>2026</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235" s="1">
         <v>45971</v>
       </c>
       <c r="F235" t="s">
@@ -15015,7 +14989,7 @@
       <c r="C236">
         <v>2026</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236" s="1">
         <v>45889</v>
       </c>
       <c r="F236" t="s">
@@ -15152,7 +15126,7 @@
       <c r="C240">
         <v>2026</v>
       </c>
-      <c r="D240" s="2">
+      <c r="D240" s="1">
         <v>45859</v>
       </c>
       <c r="F240" t="s">
@@ -15193,7 +15167,7 @@
       <c r="C241">
         <v>2026</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241" s="1">
         <v>45918</v>
       </c>
       <c r="F241" t="s">
@@ -15266,7 +15240,7 @@
       <c r="C243">
         <v>2026</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="1">
         <v>45874</v>
       </c>
       <c r="F243" t="s">
@@ -15307,7 +15281,7 @@
       <c r="C244">
         <v>2026</v>
       </c>
-      <c r="D244" s="2">
+      <c r="D244" s="1">
         <v>45975</v>
       </c>
       <c r="F244" t="s">
@@ -15345,7 +15319,7 @@
       <c r="C245">
         <v>2026</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245" s="1">
         <v>45975</v>
       </c>
       <c r="F245" t="s">
@@ -15383,7 +15357,7 @@
       <c r="C246">
         <v>2026</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="1">
         <v>45975</v>
       </c>
       <c r="F246" t="s">
@@ -15645,7 +15619,7 @@
       <c r="C254">
         <v>2026</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254" s="1">
         <v>46119</v>
       </c>
       <c r="F254" t="s">
@@ -15750,7 +15724,7 @@
       <c r="C257">
         <v>2026</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257" s="1">
         <v>45802</v>
       </c>
       <c r="F257" t="s">
@@ -15791,7 +15765,7 @@
       <c r="C258">
         <v>2026</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="1">
         <v>45804</v>
       </c>
       <c r="F258" t="s">
@@ -15832,7 +15806,7 @@
       <c r="C259">
         <v>2026</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="1">
         <v>46097</v>
       </c>
       <c r="F259" t="s">
@@ -15873,7 +15847,7 @@
       <c r="C260">
         <v>2026</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="1">
         <v>45860</v>
       </c>
       <c r="G260" t="s">
@@ -15911,7 +15885,7 @@
       <c r="C261">
         <v>2026</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="1">
         <v>45889</v>
       </c>
       <c r="F261" t="s">
@@ -15952,7 +15926,7 @@
       <c r="C262">
         <v>2026</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="1">
         <v>45744</v>
       </c>
       <c r="F262" t="s">
@@ -15993,7 +15967,7 @@
       <c r="C263">
         <v>2026</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="1">
         <v>45744</v>
       </c>
       <c r="F263" t="s">
@@ -16034,7 +16008,7 @@
       <c r="C264">
         <v>2026</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="1">
         <v>46408</v>
       </c>
       <c r="F264" t="s">
@@ -16078,7 +16052,7 @@
       <c r="C265">
         <v>2026</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="1">
         <v>45898</v>
       </c>
       <c r="F265" t="s">
@@ -16119,7 +16093,7 @@
       <c r="C266">
         <v>2026</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="1">
         <v>45971</v>
       </c>
       <c r="F266" t="s">
@@ -16160,7 +16134,7 @@
       <c r="C267">
         <v>2026</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="1">
         <v>45744</v>
       </c>
       <c r="F267" t="s">
@@ -16201,7 +16175,7 @@
       <c r="C268">
         <v>2026</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="1">
         <v>46092</v>
       </c>
       <c r="F268" t="s">
@@ -16242,7 +16216,7 @@
       <c r="C269">
         <v>2026</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="1">
         <v>46204</v>
       </c>
       <c r="F269" t="s">
@@ -16286,7 +16260,7 @@
       <c r="C270">
         <v>2026</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="1">
         <v>46185</v>
       </c>
       <c r="H270" t="s">
@@ -16321,7 +16295,7 @@
       <c r="C271">
         <v>2026</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="1">
         <v>45890</v>
       </c>
       <c r="G271" t="s">
@@ -16359,7 +16333,7 @@
       <c r="C272">
         <v>2026</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="1">
         <v>46185</v>
       </c>
       <c r="H272" t="s">
@@ -16394,7 +16368,7 @@
       <c r="C273">
         <v>2026</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="1">
         <v>46175</v>
       </c>
       <c r="F273" t="s">
@@ -16435,7 +16409,7 @@
       <c r="C274">
         <v>2026</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="1">
         <v>45890</v>
       </c>
       <c r="G274" t="s">
@@ -16473,7 +16447,7 @@
       <c r="C275">
         <v>2026</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="1">
         <v>46175</v>
       </c>
       <c r="F275" t="s">
@@ -16514,7 +16488,7 @@
       <c r="C276">
         <v>2026</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="1">
         <v>46185</v>
       </c>
       <c r="G276" t="s">
@@ -16552,7 +16526,7 @@
       <c r="C277">
         <v>2026</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="1">
         <v>45890</v>
       </c>
       <c r="G277" t="s">
@@ -16590,7 +16564,7 @@
       <c r="C278">
         <v>2026</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="1">
         <v>45890</v>
       </c>
       <c r="G278" t="s">
@@ -16628,7 +16602,7 @@
       <c r="C279">
         <v>2026</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="1">
         <v>45890</v>
       </c>
       <c r="G279" t="s">
@@ -16666,7 +16640,7 @@
       <c r="C280">
         <v>2026</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="1">
         <v>46175</v>
       </c>
       <c r="F280" t="s">
@@ -16707,7 +16681,7 @@
       <c r="C281">
         <v>2026</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="1">
         <v>45890</v>
       </c>
       <c r="G281" t="s">
@@ -16745,7 +16719,7 @@
       <c r="C282">
         <v>2026</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="1">
         <v>46119</v>
       </c>
       <c r="F282" t="s">
@@ -16786,7 +16760,7 @@
       <c r="C283">
         <v>2026</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="1">
         <v>46119</v>
       </c>
       <c r="F283" t="s">
@@ -16827,7 +16801,7 @@
       <c r="C284">
         <v>2026</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="1">
         <v>46119</v>
       </c>
       <c r="F284" t="s">
@@ -16932,7 +16906,7 @@
       <c r="C287">
         <v>2026</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="1">
         <v>45856</v>
       </c>
       <c r="F287" t="s">
@@ -16973,7 +16947,7 @@
       <c r="C288">
         <v>2026</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="1">
         <v>45769</v>
       </c>
       <c r="F288" t="s">
@@ -17014,7 +16988,7 @@
       <c r="C289">
         <v>2026</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="1">
         <v>45769</v>
       </c>
       <c r="F289" t="s">
@@ -17055,7 +17029,7 @@
       <c r="C290">
         <v>2026</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="1">
         <v>45769</v>
       </c>
       <c r="F290" t="s">
@@ -17096,7 +17070,7 @@
       <c r="C291">
         <v>2026</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="1">
         <v>45769</v>
       </c>
       <c r="F291" t="s">
@@ -17137,7 +17111,7 @@
       <c r="C292">
         <v>2026</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292" s="1">
         <v>45769</v>
       </c>
       <c r="F292" t="s">
@@ -17178,7 +17152,7 @@
       <c r="C293">
         <v>2026</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293" s="1">
         <v>45769</v>
       </c>
       <c r="F293" t="s">
@@ -17219,7 +17193,7 @@
       <c r="C294">
         <v>2026</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294" s="1">
         <v>45769</v>
       </c>
       <c r="F294" t="s">
@@ -17260,7 +17234,7 @@
       <c r="C295">
         <v>2026</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295" s="1">
         <v>46147</v>
       </c>
       <c r="H295" t="s">
@@ -17295,7 +17269,7 @@
       <c r="C296">
         <v>2026</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296" s="1">
         <v>46147</v>
       </c>
       <c r="H296" t="s">
@@ -17330,7 +17304,7 @@
       <c r="C297">
         <v>2026</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="1">
         <v>46147</v>
       </c>
       <c r="H297" t="s">
@@ -17365,7 +17339,7 @@
       <c r="C298">
         <v>2026</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298" s="1">
         <v>45814</v>
       </c>
       <c r="F298" t="s">
@@ -17438,7 +17412,7 @@
       <c r="C300">
         <v>2026</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="1">
         <v>45860</v>
       </c>
       <c r="F300" t="s">
@@ -17479,7 +17453,7 @@
       <c r="C301">
         <v>2026</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="1">
         <v>45971</v>
       </c>
       <c r="F301" t="s">
@@ -17520,7 +17494,7 @@
       <c r="C302">
         <v>2026</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302" s="1">
         <v>45863</v>
       </c>
       <c r="F302" t="s">
@@ -17561,7 +17535,7 @@
       <c r="C303">
         <v>2026</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303" s="1">
         <v>45905</v>
       </c>
       <c r="G303" t="s">
@@ -17599,7 +17573,7 @@
       <c r="C304">
         <v>2026</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304" s="1">
         <v>45971</v>
       </c>
       <c r="F304" t="s">
@@ -17640,7 +17614,7 @@
       <c r="C305">
         <v>2026</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305" s="1">
         <v>45971</v>
       </c>
       <c r="F305" t="s">
@@ -17681,7 +17655,7 @@
       <c r="C306">
         <v>2026</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306" s="1">
         <v>45744</v>
       </c>
       <c r="F306" t="s">
@@ -17722,7 +17696,7 @@
       <c r="C307">
         <v>2026</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="1">
         <v>45814</v>
       </c>
       <c r="F307" t="s">
@@ -17763,7 +17737,7 @@
       <c r="C308">
         <v>2026</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="1">
         <v>45807</v>
       </c>
       <c r="F308" t="s">
@@ -17804,7 +17778,7 @@
       <c r="C309">
         <v>2026</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309" s="1">
         <v>45802</v>
       </c>
       <c r="F309" t="s">
@@ -17845,7 +17819,7 @@
       <c r="C310">
         <v>2026</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310" s="1">
         <v>45802</v>
       </c>
       <c r="F310" t="s">
@@ -17886,7 +17860,7 @@
       <c r="C311">
         <v>2026</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311" s="1">
         <v>45802</v>
       </c>
       <c r="F311" t="s">
@@ -17927,7 +17901,7 @@
       <c r="C312">
         <v>2026</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312" s="1">
         <v>45897</v>
       </c>
       <c r="H312" t="s">
@@ -17962,7 +17936,7 @@
       <c r="C313">
         <v>2026</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313" s="1">
         <v>45802</v>
       </c>
       <c r="F313" t="s">
@@ -18003,7 +17977,7 @@
       <c r="C314">
         <v>2026</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314" s="1">
         <v>45802</v>
       </c>
       <c r="F314" t="s">
@@ -18044,7 +18018,7 @@
       <c r="C315">
         <v>2026</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="1">
         <v>45876</v>
       </c>
       <c r="F315" t="s">
@@ -18085,7 +18059,7 @@
       <c r="C316">
         <v>2026</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316" s="1">
         <v>45889</v>
       </c>
       <c r="F316" t="s">
@@ -18126,7 +18100,7 @@
       <c r="C317">
         <v>2026</v>
       </c>
-      <c r="D317" s="2">
+      <c r="D317" s="1">
         <v>45876</v>
       </c>
       <c r="F317" t="s">
@@ -18167,7 +18141,7 @@
       <c r="C318">
         <v>2026</v>
       </c>
-      <c r="D318" s="2">
+      <c r="D318" s="1">
         <v>45926</v>
       </c>
       <c r="F318" t="s">
@@ -18208,7 +18182,7 @@
       <c r="C319">
         <v>2026</v>
       </c>
-      <c r="D319" s="2">
+      <c r="D319" s="1">
         <v>45909</v>
       </c>
       <c r="F319" t="s">
@@ -18249,7 +18223,7 @@
       <c r="C320">
         <v>2026</v>
       </c>
-      <c r="D320" s="2">
+      <c r="D320" s="1">
         <v>46119</v>
       </c>
       <c r="F320" t="s">
@@ -18354,7 +18328,7 @@
       <c r="C323">
         <v>2026</v>
       </c>
-      <c r="D323" s="2">
+      <c r="D323" s="1">
         <v>46119</v>
       </c>
       <c r="F323" t="s">
@@ -18395,7 +18369,7 @@
       <c r="C324">
         <v>2026</v>
       </c>
-      <c r="D324" s="2">
+      <c r="D324" s="1">
         <v>46119</v>
       </c>
       <c r="F324" t="s">
@@ -18532,7 +18506,7 @@
       <c r="C328">
         <v>2026</v>
       </c>
-      <c r="D328" s="2">
+      <c r="D328" s="1">
         <v>46086</v>
       </c>
       <c r="G328" t="s">
@@ -18602,7 +18576,7 @@
       <c r="C330">
         <v>2026</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330" s="1">
         <v>45965</v>
       </c>
       <c r="F330" t="s">
@@ -18643,7 +18617,7 @@
       <c r="C331">
         <v>2026</v>
       </c>
-      <c r="D331" s="2">
+      <c r="D331" s="1">
         <v>46064</v>
       </c>
       <c r="H331" t="s">
@@ -18675,7 +18649,7 @@
       <c r="C332">
         <v>2026</v>
       </c>
-      <c r="D332" s="2">
+      <c r="D332" s="1">
         <v>46049</v>
       </c>
       <c r="F332" t="s">
@@ -18716,7 +18690,7 @@
       <c r="C333">
         <v>2026</v>
       </c>
-      <c r="D333" s="2">
+      <c r="D333" s="1">
         <v>45996</v>
       </c>
       <c r="G333" t="s">
@@ -18754,7 +18728,7 @@
       <c r="C334">
         <v>2026</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334" s="1">
         <v>45996</v>
       </c>
       <c r="G334" t="s">
@@ -18792,7 +18766,7 @@
       <c r="C335">
         <v>2026</v>
       </c>
-      <c r="D335" s="2">
+      <c r="D335" s="1">
         <v>45989</v>
       </c>
       <c r="G335" t="s">
@@ -18830,7 +18804,7 @@
       <c r="C336">
         <v>2026</v>
       </c>
-      <c r="D336" s="2">
+      <c r="D336" s="1">
         <v>46156</v>
       </c>
       <c r="H336" t="s">
@@ -18865,7 +18839,7 @@
       <c r="C337">
         <v>2026</v>
       </c>
-      <c r="D337" s="2">
+      <c r="D337" s="1">
         <v>45996</v>
       </c>
       <c r="G337" t="s">
@@ -18903,7 +18877,7 @@
       <c r="C338">
         <v>2026</v>
       </c>
-      <c r="D338" s="2">
+      <c r="D338" s="1">
         <v>45989</v>
       </c>
       <c r="G338" t="s">
@@ -18941,7 +18915,7 @@
       <c r="C339">
         <v>2026</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339" s="1">
         <v>46002</v>
       </c>
       <c r="G339" t="s">
@@ -18979,7 +18953,7 @@
       <c r="C340">
         <v>2026</v>
       </c>
-      <c r="D340" s="2">
+      <c r="D340" s="1">
         <v>46002</v>
       </c>
       <c r="G340" t="s">
@@ -19017,7 +18991,7 @@
       <c r="C341">
         <v>2026</v>
       </c>
-      <c r="D341" s="2">
+      <c r="D341" s="1">
         <v>45996</v>
       </c>
       <c r="G341" t="s">
@@ -19055,7 +19029,7 @@
       <c r="C342">
         <v>2026</v>
       </c>
-      <c r="D342" s="2">
+      <c r="D342" s="1">
         <v>46002</v>
       </c>
       <c r="G342" t="s">
@@ -19093,7 +19067,7 @@
       <c r="C343">
         <v>2026</v>
       </c>
-      <c r="D343" s="2">
+      <c r="D343" s="1">
         <v>46031</v>
       </c>
       <c r="G343" t="s">
@@ -19131,7 +19105,7 @@
       <c r="C344">
         <v>2026</v>
       </c>
-      <c r="D344" s="2">
+      <c r="D344" s="1">
         <v>46153</v>
       </c>
       <c r="F344" t="s">
@@ -19172,7 +19146,7 @@
       <c r="C345">
         <v>2026</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345" s="1">
         <v>46135</v>
       </c>
       <c r="F345" t="s">
@@ -19277,7 +19251,7 @@
       <c r="C348">
         <v>2026</v>
       </c>
-      <c r="D348" s="2">
+      <c r="D348" s="1">
         <v>46230</v>
       </c>
       <c r="F348" t="s">
@@ -19382,7 +19356,7 @@
       <c r="C351">
         <v>2026</v>
       </c>
-      <c r="D351" s="2">
+      <c r="D351" s="1">
         <v>45996</v>
       </c>
       <c r="G351" t="s">
@@ -19420,7 +19394,7 @@
       <c r="C352">
         <v>2026</v>
       </c>
-      <c r="D352" s="2">
+      <c r="D352" s="1">
         <v>45996</v>
       </c>
       <c r="G352" t="s">
@@ -19490,7 +19464,7 @@
       <c r="C354">
         <v>2026</v>
       </c>
-      <c r="D354" s="2">
+      <c r="D354" s="1">
         <v>46164</v>
       </c>
       <c r="H354" t="s">
@@ -19525,7 +19499,7 @@
       <c r="C355">
         <v>2026</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355" s="1">
         <v>46020</v>
       </c>
       <c r="G355" t="s">
@@ -19563,7 +19537,7 @@
       <c r="C356">
         <v>2026</v>
       </c>
-      <c r="D356" s="2">
+      <c r="D356" s="1">
         <v>46225</v>
       </c>
       <c r="F356" t="s">
@@ -19607,7 +19581,7 @@
       <c r="C357">
         <v>2026</v>
       </c>
-      <c r="D357" s="2">
+      <c r="D357" s="1">
         <v>46176</v>
       </c>
       <c r="H357" t="s">
@@ -19642,7 +19616,7 @@
       <c r="C358">
         <v>2026</v>
       </c>
-      <c r="D358" s="2">
+      <c r="D358" s="1">
         <v>46086</v>
       </c>
       <c r="G358" t="s">
@@ -19680,7 +19654,7 @@
       <c r="C359">
         <v>2026</v>
       </c>
-      <c r="D359" s="2">
+      <c r="D359" s="1">
         <v>46052</v>
       </c>
       <c r="G359" t="s">
@@ -19756,7 +19730,7 @@
       <c r="C361">
         <v>2026</v>
       </c>
-      <c r="D361" s="2">
+      <c r="D361" s="1">
         <v>46010</v>
       </c>
       <c r="G361" t="s">
@@ -19794,7 +19768,7 @@
       <c r="C362">
         <v>2026</v>
       </c>
-      <c r="D362" s="2">
+      <c r="D362" s="1">
         <v>46010</v>
       </c>
       <c r="G362" t="s">
@@ -19864,7 +19838,7 @@
       <c r="C364">
         <v>2026</v>
       </c>
-      <c r="D364" s="2">
+      <c r="D364" s="1">
         <v>46079</v>
       </c>
       <c r="F364" t="s">
@@ -19905,7 +19879,7 @@
       <c r="C365">
         <v>2026</v>
       </c>
-      <c r="D365" s="2">
+      <c r="D365" s="1">
         <v>46010</v>
       </c>
       <c r="G365" t="s">
@@ -19943,7 +19917,7 @@
       <c r="C366">
         <v>2026</v>
       </c>
-      <c r="D366" s="2">
+      <c r="D366" s="1">
         <v>46010</v>
       </c>
       <c r="G366" t="s">
@@ -19981,7 +19955,7 @@
       <c r="C367">
         <v>2026</v>
       </c>
-      <c r="D367" s="2">
+      <c r="D367" s="1">
         <v>46230</v>
       </c>
       <c r="F367" t="s">
@@ -20025,7 +19999,7 @@
       <c r="C368">
         <v>2026</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368" s="1">
         <v>46063</v>
       </c>
       <c r="G368" t="s">
@@ -20063,7 +20037,7 @@
       <c r="C369">
         <v>2026</v>
       </c>
-      <c r="D369" s="2">
+      <c r="D369" s="1">
         <v>46063</v>
       </c>
       <c r="F369" t="s">
@@ -20104,7 +20078,7 @@
       <c r="C370">
         <v>2026</v>
       </c>
-      <c r="D370" s="2">
+      <c r="D370" s="1">
         <v>46063</v>
       </c>
       <c r="F370" t="s">
@@ -20145,7 +20119,7 @@
       <c r="C371">
         <v>2026</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371" s="1">
         <v>46063</v>
       </c>
       <c r="F371" t="s">
@@ -20186,7 +20160,7 @@
       <c r="C372">
         <v>2026</v>
       </c>
-      <c r="D372" s="2">
+      <c r="D372" s="1">
         <v>46063</v>
       </c>
       <c r="G372" t="s">
@@ -20352,7 +20326,7 @@
       <c r="C377">
         <v>2026</v>
       </c>
-      <c r="D377" s="2">
+      <c r="D377" s="1">
         <v>46114</v>
       </c>
       <c r="F377" t="s">
@@ -20393,7 +20367,7 @@
       <c r="C378">
         <v>2026</v>
       </c>
-      <c r="D378" s="2">
+      <c r="D378" s="1">
         <v>46191</v>
       </c>
       <c r="F378" t="s">
@@ -20434,7 +20408,7 @@
       <c r="C379">
         <v>2026</v>
       </c>
-      <c r="D379" s="2">
+      <c r="D379" s="1">
         <v>46230</v>
       </c>
       <c r="F379" t="s">
@@ -20475,7 +20449,7 @@
       <c r="C380">
         <v>2026</v>
       </c>
-      <c r="D380" s="2">
+      <c r="D380" s="1">
         <v>46230</v>
       </c>
       <c r="F380" t="s">
@@ -20516,7 +20490,7 @@
       <c r="C381">
         <v>2026</v>
       </c>
-      <c r="D381" s="2">
+      <c r="D381" s="1">
         <v>46230</v>
       </c>
       <c r="F381" t="s">
@@ -20557,7 +20531,7 @@
       <c r="C382">
         <v>2026</v>
       </c>
-      <c r="D382" s="2">
+      <c r="D382" s="1">
         <v>46230</v>
       </c>
       <c r="F382" t="s">
@@ -20598,7 +20572,7 @@
       <c r="C383">
         <v>2026</v>
       </c>
-      <c r="D383" s="2">
+      <c r="D383" s="1">
         <v>46230</v>
       </c>
       <c r="F383" t="s">
@@ -20639,7 +20613,7 @@
       <c r="C384">
         <v>2026</v>
       </c>
-      <c r="D384" s="2">
+      <c r="D384" s="1">
         <v>46230</v>
       </c>
       <c r="F384" t="s">
@@ -20680,7 +20654,7 @@
       <c r="C385">
         <v>2026</v>
       </c>
-      <c r="D385" s="2">
+      <c r="D385" s="1">
         <v>46230</v>
       </c>
       <c r="F385" t="s">
@@ -20753,7 +20727,7 @@
       <c r="C387">
         <v>2026</v>
       </c>
-      <c r="D387" s="2">
+      <c r="D387" s="1">
         <v>45996</v>
       </c>
       <c r="G387" t="s">
@@ -20983,7 +20957,7 @@
       <c r="C394">
         <v>2026</v>
       </c>
-      <c r="D394" s="2">
+      <c r="D394" s="1">
         <v>46052</v>
       </c>
       <c r="F394" t="s">
@@ -21024,7 +20998,7 @@
       <c r="C395">
         <v>2026</v>
       </c>
-      <c r="D395" s="2">
+      <c r="D395" s="1">
         <v>46057</v>
       </c>
       <c r="F395" t="s">
@@ -21065,7 +21039,7 @@
       <c r="C396">
         <v>2026</v>
       </c>
-      <c r="D396" s="2">
+      <c r="D396" s="1">
         <v>46112</v>
       </c>
       <c r="F396" t="s">
@@ -21138,7 +21112,7 @@
       <c r="C398">
         <v>2026</v>
       </c>
-      <c r="D398" s="2">
+      <c r="D398" s="1">
         <v>46063</v>
       </c>
       <c r="G398" t="s">
@@ -21176,7 +21150,7 @@
       <c r="C399">
         <v>2026</v>
       </c>
-      <c r="D399" s="2">
+      <c r="D399" s="1">
         <v>46048</v>
       </c>
       <c r="G399" t="s">
@@ -21214,7 +21188,7 @@
       <c r="C400">
         <v>2026</v>
       </c>
-      <c r="D400" s="2">
+      <c r="D400" s="1">
         <v>46063</v>
       </c>
       <c r="H400" t="s">
@@ -21281,7 +21255,7 @@
       <c r="C402">
         <v>2026</v>
       </c>
-      <c r="D402" s="2">
+      <c r="D402" s="1">
         <v>46119</v>
       </c>
       <c r="F402" t="s">
@@ -21354,7 +21328,7 @@
       <c r="C404">
         <v>2026</v>
       </c>
-      <c r="D404" s="2">
+      <c r="D404" s="1">
         <v>46119</v>
       </c>
       <c r="F404" t="s">
@@ -21395,7 +21369,7 @@
       <c r="C405">
         <v>2026</v>
       </c>
-      <c r="D405" s="2">
+      <c r="D405" s="1">
         <v>46113</v>
       </c>
       <c r="F405" t="s">
@@ -21436,7 +21410,7 @@
       <c r="C406">
         <v>2026</v>
       </c>
-      <c r="D406" s="2">
+      <c r="D406" s="1">
         <v>46104</v>
       </c>
       <c r="F406" t="s">
@@ -21477,7 +21451,7 @@
       <c r="C407">
         <v>2026</v>
       </c>
-      <c r="D407" s="2">
+      <c r="D407" s="1">
         <v>46135</v>
       </c>
       <c r="H407" t="s">
@@ -21544,7 +21518,7 @@
       <c r="C409">
         <v>2026</v>
       </c>
-      <c r="D409" s="2">
+      <c r="D409" s="1">
         <v>46230</v>
       </c>
       <c r="F409" t="s">
@@ -21585,7 +21559,7 @@
       <c r="C410">
         <v>2026</v>
       </c>
-      <c r="D410" s="2">
+      <c r="D410" s="1">
         <v>46086</v>
       </c>
       <c r="G410" t="s">
@@ -21623,7 +21597,7 @@
       <c r="C411">
         <v>2026</v>
       </c>
-      <c r="D411" s="2">
+      <c r="D411" s="1">
         <v>46086</v>
       </c>
       <c r="G411" t="s">
@@ -21661,7 +21635,7 @@
       <c r="C412">
         <v>2026</v>
       </c>
-      <c r="D412" s="2">
+      <c r="D412" s="1">
         <v>46086</v>
       </c>
       <c r="H412" t="s">
@@ -21696,7 +21670,7 @@
       <c r="C413">
         <v>2026</v>
       </c>
-      <c r="D413" s="2">
+      <c r="D413" s="1">
         <v>46230</v>
       </c>
       <c r="F413" t="s">
@@ -21833,7 +21807,7 @@
       <c r="C417">
         <v>2026</v>
       </c>
-      <c r="D417" s="2">
+      <c r="D417" s="1">
         <v>46176</v>
       </c>
       <c r="H417" t="s">
@@ -21868,7 +21842,7 @@
       <c r="C418">
         <v>2026</v>
       </c>
-      <c r="D418" s="2">
+      <c r="D418" s="1">
         <v>46147</v>
       </c>
       <c r="H418" t="s">
@@ -21903,7 +21877,7 @@
       <c r="C419">
         <v>2026</v>
       </c>
-      <c r="D419" s="2">
+      <c r="D419" s="1">
         <v>46135</v>
       </c>
       <c r="H419" t="s">
@@ -21970,7 +21944,7 @@
       <c r="C421">
         <v>2026</v>
       </c>
-      <c r="D421" s="2">
+      <c r="D421" s="1">
         <v>46227</v>
       </c>
       <c r="G421" t="s">
@@ -22011,7 +21985,7 @@
       <c r="C422">
         <v>2026</v>
       </c>
-      <c r="D422" s="2">
+      <c r="D422" s="1">
         <v>46230</v>
       </c>
       <c r="F422" t="s">
@@ -22052,7 +22026,7 @@
       <c r="C423">
         <v>2026</v>
       </c>
-      <c r="D423" s="2">
+      <c r="D423" s="1">
         <v>46083</v>
       </c>
       <c r="F423" t="s">
@@ -22093,7 +22067,7 @@
       <c r="C424">
         <v>2026</v>
       </c>
-      <c r="D424" s="2">
+      <c r="D424" s="1">
         <v>46083</v>
       </c>
       <c r="G424" t="s">
@@ -22131,7 +22105,7 @@
       <c r="C425">
         <v>2026</v>
       </c>
-      <c r="D425" s="2">
+      <c r="D425" s="1">
         <v>46083</v>
       </c>
       <c r="F425" t="s">
@@ -22172,7 +22146,7 @@
       <c r="C426">
         <v>2026</v>
       </c>
-      <c r="D426" s="2">
+      <c r="D426" s="1">
         <v>46127</v>
       </c>
       <c r="F426" t="s">
@@ -22213,7 +22187,7 @@
       <c r="C427">
         <v>2026</v>
       </c>
-      <c r="D427" s="2">
+      <c r="D427" s="1">
         <v>46100</v>
       </c>
       <c r="F427" t="s">
@@ -22411,7 +22385,7 @@
       <c r="C433">
         <v>2026</v>
       </c>
-      <c r="D433" s="2">
+      <c r="D433" s="1">
         <v>46230</v>
       </c>
       <c r="F433" t="s">
@@ -22452,7 +22426,7 @@
       <c r="C434">
         <v>2026</v>
       </c>
-      <c r="D434" s="2">
+      <c r="D434" s="1">
         <v>46079</v>
       </c>
       <c r="H434" t="s">
@@ -22583,7 +22557,7 @@
       <c r="C438">
         <v>2026</v>
       </c>
-      <c r="D438" s="2">
+      <c r="D438" s="1">
         <v>46176</v>
       </c>
       <c r="F438" t="s">
@@ -22624,7 +22598,7 @@
       <c r="C439">
         <v>2026</v>
       </c>
-      <c r="D439" s="2">
+      <c r="D439" s="1">
         <v>46176</v>
       </c>
       <c r="F439" t="s">
@@ -22665,7 +22639,7 @@
       <c r="C440">
         <v>2026</v>
       </c>
-      <c r="D440" s="2">
+      <c r="D440" s="1">
         <v>46155</v>
       </c>
       <c r="F440" t="s">
@@ -22706,7 +22680,7 @@
       <c r="C441">
         <v>2026</v>
       </c>
-      <c r="D441" s="2">
+      <c r="D441" s="1">
         <v>46155</v>
       </c>
       <c r="G441" t="s">
@@ -22744,7 +22718,7 @@
       <c r="C442">
         <v>2026</v>
       </c>
-      <c r="D442" s="2">
+      <c r="D442" s="1">
         <v>46129</v>
       </c>
       <c r="F442" t="s">
@@ -22785,7 +22759,7 @@
       <c r="C443">
         <v>2026</v>
       </c>
-      <c r="D443" s="2">
+      <c r="D443" s="1">
         <v>46119</v>
       </c>
       <c r="F443" t="s">
@@ -22826,7 +22800,7 @@
       <c r="C444">
         <v>2026</v>
       </c>
-      <c r="D444" s="2">
+      <c r="D444" s="1">
         <v>46135</v>
       </c>
       <c r="H444" t="s">
@@ -22861,7 +22835,7 @@
       <c r="C445">
         <v>2026</v>
       </c>
-      <c r="D445" s="2">
+      <c r="D445" s="1">
         <v>46127</v>
       </c>
       <c r="H445" t="s">
@@ -22896,7 +22870,7 @@
       <c r="C446">
         <v>2026</v>
       </c>
-      <c r="D446" s="2">
+      <c r="D446" s="1">
         <v>46127</v>
       </c>
       <c r="H446" t="s">
@@ -22963,7 +22937,7 @@
       <c r="C448">
         <v>2026</v>
       </c>
-      <c r="D448" s="2">
+      <c r="D448" s="1">
         <v>46175</v>
       </c>
       <c r="F448" t="s">
@@ -23004,7 +22978,7 @@
       <c r="C449">
         <v>2026</v>
       </c>
-      <c r="D449" s="2">
+      <c r="D449" s="1">
         <v>46139</v>
       </c>
       <c r="H449" t="s">
@@ -23039,7 +23013,7 @@
       <c r="C450">
         <v>2026</v>
       </c>
-      <c r="D450" s="2">
+      <c r="D450" s="1">
         <v>46155</v>
       </c>
       <c r="H450" t="s">
@@ -23074,7 +23048,7 @@
       <c r="C451">
         <v>2026</v>
       </c>
-      <c r="D451" s="2">
+      <c r="D451" s="1">
         <v>46175</v>
       </c>
       <c r="F451" t="s">
@@ -23147,7 +23121,7 @@
       <c r="C453">
         <v>2026</v>
       </c>
-      <c r="D453" s="2">
+      <c r="D453" s="1">
         <v>46156</v>
       </c>
       <c r="F453" t="s">
@@ -23188,7 +23162,7 @@
       <c r="C454">
         <v>2026</v>
       </c>
-      <c r="D454" s="2">
+      <c r="D454" s="1">
         <v>46157</v>
       </c>
       <c r="G454" t="s">
@@ -23226,7 +23200,7 @@
       <c r="C455">
         <v>2026</v>
       </c>
-      <c r="D455" s="2">
+      <c r="D455" s="1">
         <v>46183</v>
       </c>
       <c r="H455" t="s">
@@ -23261,7 +23235,7 @@
       <c r="C456">
         <v>2026</v>
       </c>
-      <c r="D456" s="2">
+      <c r="D456" s="1">
         <v>46183</v>
       </c>
       <c r="H456" t="s">
@@ -23360,7 +23334,7 @@
       <c r="C459">
         <v>2026</v>
       </c>
-      <c r="D459" s="2">
+      <c r="D459" s="1">
         <v>46230</v>
       </c>
       <c r="F459" t="s">
@@ -23404,7 +23378,7 @@
       <c r="C460">
         <v>2026</v>
       </c>
-      <c r="D460" s="2">
+      <c r="D460" s="1">
         <v>46185</v>
       </c>
       <c r="H460" t="s">
@@ -23471,7 +23445,7 @@
       <c r="C462">
         <v>2026</v>
       </c>
-      <c r="D462" s="2">
+      <c r="D462" s="1">
         <v>46185</v>
       </c>
       <c r="H462" t="s">
@@ -23570,7 +23544,7 @@
       <c r="C465">
         <v>2026</v>
       </c>
-      <c r="D465" s="2">
+      <c r="D465" s="1">
         <v>46175</v>
       </c>
       <c r="F465" t="s">
@@ -23611,7 +23585,7 @@
       <c r="C466">
         <v>2026</v>
       </c>
-      <c r="D466" s="2">
+      <c r="D466" s="1">
         <v>46175</v>
       </c>
       <c r="F466" t="s">
@@ -23652,7 +23626,7 @@
       <c r="C467">
         <v>2026</v>
       </c>
-      <c r="D467" s="2">
+      <c r="D467" s="1">
         <v>46230</v>
       </c>
       <c r="F467" t="s">
@@ -23693,7 +23667,7 @@
       <c r="C468">
         <v>2026</v>
       </c>
-      <c r="D468" s="2">
+      <c r="D468" s="1">
         <v>46175</v>
       </c>
       <c r="G468" t="s">
@@ -23731,7 +23705,7 @@
       <c r="C469">
         <v>2026</v>
       </c>
-      <c r="D469" s="2">
+      <c r="D469" s="1">
         <v>46175</v>
       </c>
       <c r="G469" t="s">
@@ -23769,7 +23743,7 @@
       <c r="C470">
         <v>2026</v>
       </c>
-      <c r="D470" s="2">
+      <c r="D470" s="1">
         <v>46175</v>
       </c>
       <c r="G470" t="s">
@@ -23807,7 +23781,7 @@
       <c r="C471">
         <v>2026</v>
       </c>
-      <c r="D471" s="2">
+      <c r="D471" s="1">
         <v>46230</v>
       </c>
       <c r="F471" t="s">
@@ -23848,7 +23822,7 @@
       <c r="C472">
         <v>2026</v>
       </c>
-      <c r="D472" s="2">
+      <c r="D472" s="1">
         <v>46175</v>
       </c>
       <c r="G472" t="s">
@@ -23886,7 +23860,7 @@
       <c r="C473">
         <v>2026</v>
       </c>
-      <c r="D473" s="2">
+      <c r="D473" s="1">
         <v>46175</v>
       </c>
       <c r="G473" t="s">
@@ -23924,7 +23898,7 @@
       <c r="C474">
         <v>2026</v>
       </c>
-      <c r="D474" s="2">
+      <c r="D474" s="1">
         <v>46175</v>
       </c>
       <c r="G474" t="s">
@@ -23962,7 +23936,7 @@
       <c r="C475">
         <v>2026</v>
       </c>
-      <c r="D475" s="2">
+      <c r="D475" s="1">
         <v>46230</v>
       </c>
       <c r="F475" t="s">
@@ -24035,7 +24009,7 @@
       <c r="C477">
         <v>2026</v>
       </c>
-      <c r="D477" s="2">
+      <c r="D477" s="1">
         <v>46209</v>
       </c>
       <c r="F477" t="s">
@@ -24207,7 +24181,7 @@
       <c r="C482">
         <v>2026</v>
       </c>
-      <c r="D482" s="2">
+      <c r="D482" s="1">
         <v>46230</v>
       </c>
       <c r="F482" t="s">
@@ -24248,7 +24222,7 @@
       <c r="C483">
         <v>2026</v>
       </c>
-      <c r="D483" s="2">
+      <c r="D483" s="1">
         <v>46230</v>
       </c>
       <c r="F483" t="s">
@@ -24289,7 +24263,7 @@
       <c r="C484">
         <v>2026</v>
       </c>
-      <c r="D484" s="2">
+      <c r="D484" s="1">
         <v>46230</v>
       </c>
       <c r="F484" t="s">
@@ -24554,7 +24528,7 @@
       <c r="C492">
         <v>2026</v>
       </c>
-      <c r="D492" s="2">
+      <c r="D492" s="1">
         <v>46230</v>
       </c>
       <c r="F492" t="s">
@@ -24595,7 +24569,7 @@
       <c r="C493">
         <v>2026</v>
       </c>
-      <c r="D493" s="2">
+      <c r="D493" s="1">
         <v>46230</v>
       </c>
       <c r="F493" t="s">
@@ -24700,7 +24674,7 @@
       <c r="C496">
         <v>2026</v>
       </c>
-      <c r="D496" s="2">
+      <c r="D496" s="1">
         <v>46230</v>
       </c>
       <c r="F496" t="s">
@@ -24744,7 +24718,7 @@
       <c r="C497">
         <v>2026</v>
       </c>
-      <c r="D497" s="2">
+      <c r="D497" s="1">
         <v>46230</v>
       </c>
       <c r="F497" t="s">
@@ -24785,7 +24759,7 @@
       <c r="C498">
         <v>2026</v>
       </c>
-      <c r="D498" s="2">
+      <c r="D498" s="1">
         <v>46157</v>
       </c>
       <c r="G498" t="s">
@@ -24823,7 +24797,7 @@
       <c r="C499">
         <v>2026</v>
       </c>
-      <c r="D499" s="2">
+      <c r="D499" s="1">
         <v>46213</v>
       </c>
       <c r="F499" t="s">
@@ -24899,7 +24873,7 @@
       <c r="C501">
         <v>2026</v>
       </c>
-      <c r="D501" s="2">
+      <c r="D501" s="1">
         <v>46205</v>
       </c>
       <c r="F501" t="s">
@@ -24943,7 +24917,7 @@
       <c r="C502">
         <v>2026</v>
       </c>
-      <c r="D502" s="2">
+      <c r="D502" s="1">
         <v>46176</v>
       </c>
       <c r="F502" t="s">
@@ -24984,7 +24958,7 @@
       <c r="C503">
         <v>2026</v>
       </c>
-      <c r="D503" s="2">
+      <c r="D503" s="1">
         <v>46150</v>
       </c>
       <c r="F503" t="s">
@@ -25089,7 +25063,7 @@
       <c r="C506">
         <v>2026</v>
       </c>
-      <c r="D506" s="2">
+      <c r="D506" s="1">
         <v>46220</v>
       </c>
       <c r="F506" t="s">
@@ -25133,7 +25107,7 @@
       <c r="C507">
         <v>2026</v>
       </c>
-      <c r="D507" s="2">
+      <c r="D507" s="1">
         <v>46224</v>
       </c>
       <c r="F507" t="s">
@@ -25209,7 +25183,7 @@
       <c r="C509">
         <v>2026</v>
       </c>
-      <c r="D509" s="2">
+      <c r="D509" s="1">
         <v>46155</v>
       </c>
       <c r="H509" t="s">
@@ -25244,7 +25218,7 @@
       <c r="C510">
         <v>2026</v>
       </c>
-      <c r="D510" s="2">
+      <c r="D510" s="1">
         <v>46156</v>
       </c>
       <c r="F510" t="s">
@@ -25285,7 +25259,7 @@
       <c r="C511">
         <v>2026</v>
       </c>
-      <c r="D511" s="2">
+      <c r="D511" s="1">
         <v>46185</v>
       </c>
       <c r="H511" t="s">
@@ -25320,7 +25294,7 @@
       <c r="C512">
         <v>2026</v>
       </c>
-      <c r="D512" s="2">
+      <c r="D512" s="1">
         <v>46230</v>
       </c>
       <c r="F512" t="s">
@@ -25361,7 +25335,7 @@
       <c r="C513">
         <v>2026</v>
       </c>
-      <c r="D513" s="2">
+      <c r="D513" s="1">
         <v>46230</v>
       </c>
       <c r="F513" t="s">
@@ -25402,7 +25376,7 @@
       <c r="C514">
         <v>2026</v>
       </c>
-      <c r="D514" s="2">
+      <c r="D514" s="1">
         <v>46230</v>
       </c>
       <c r="F514" t="s">
@@ -25443,7 +25417,7 @@
       <c r="C515">
         <v>2026</v>
       </c>
-      <c r="D515" s="2">
+      <c r="D515" s="1">
         <v>46230</v>
       </c>
       <c r="F515" t="s">
@@ -25484,7 +25458,7 @@
       <c r="C516">
         <v>2026</v>
       </c>
-      <c r="D516" s="2">
+      <c r="D516" s="1">
         <v>46230</v>
       </c>
       <c r="F516" t="s">
@@ -25589,7 +25563,7 @@
       <c r="C519">
         <v>2026</v>
       </c>
-      <c r="D519" s="2">
+      <c r="D519" s="1">
         <v>46147</v>
       </c>
       <c r="G519" t="s">
@@ -25723,7 +25697,7 @@
       <c r="C523">
         <v>2026</v>
       </c>
-      <c r="D523" s="2">
+      <c r="D523" s="1">
         <v>46164</v>
       </c>
       <c r="F523" t="s">
@@ -25860,7 +25834,7 @@
       <c r="C527">
         <v>2026</v>
       </c>
-      <c r="D527" s="2">
+      <c r="D527" s="1">
         <v>46230</v>
       </c>
       <c r="F527" t="s">
@@ -25997,7 +25971,7 @@
       <c r="C531">
         <v>2026</v>
       </c>
-      <c r="D531" s="2">
+      <c r="D531" s="1">
         <v>46171</v>
       </c>
       <c r="F531" t="s">
@@ -26102,7 +26076,7 @@
       <c r="C534">
         <v>2026</v>
       </c>
-      <c r="D534" s="2">
+      <c r="D534" s="1">
         <v>46176</v>
       </c>
       <c r="G534" t="s">
@@ -26140,7 +26114,7 @@
       <c r="C535">
         <v>2026</v>
       </c>
-      <c r="D535" s="2">
+      <c r="D535" s="1">
         <v>46230</v>
       </c>
       <c r="F535" t="s">
@@ -26341,7 +26315,7 @@
       <c r="C541">
         <v>2026</v>
       </c>
-      <c r="D541" s="2">
+      <c r="D541" s="1">
         <v>46211</v>
       </c>
       <c r="F541" t="s">
@@ -26385,7 +26359,7 @@
       <c r="C542">
         <v>2026</v>
       </c>
-      <c r="D542" s="2">
+      <c r="D542" s="1">
         <v>46183</v>
       </c>
       <c r="H542" t="s">
@@ -26420,7 +26394,7 @@
       <c r="C543">
         <v>2026</v>
       </c>
-      <c r="D543" s="2">
+      <c r="D543" s="1">
         <v>46191</v>
       </c>
       <c r="H543" t="s">
@@ -26455,7 +26429,7 @@
       <c r="C544">
         <v>2026</v>
       </c>
-      <c r="D544" s="2">
+      <c r="D544" s="1">
         <v>46191</v>
       </c>
       <c r="G544" t="s">
@@ -26653,7 +26627,7 @@
       <c r="C550">
         <v>2026</v>
       </c>
-      <c r="D550" s="2">
+      <c r="D550" s="1">
         <v>46230</v>
       </c>
       <c r="F550" t="s">
@@ -26758,7 +26732,7 @@
       <c r="C553">
         <v>2026</v>
       </c>
-      <c r="D553" s="2">
+      <c r="D553" s="1">
         <v>46230</v>
       </c>
       <c r="F553" t="s">
@@ -26799,7 +26773,7 @@
       <c r="C554">
         <v>2026</v>
       </c>
-      <c r="D554" s="2">
+      <c r="D554" s="1">
         <v>46191</v>
       </c>
       <c r="G554" t="s">
@@ -26965,7 +26939,7 @@
       <c r="C559">
         <v>2026</v>
       </c>
-      <c r="D559" s="2">
+      <c r="D559" s="1">
         <v>46191</v>
       </c>
       <c r="G559" t="s">
@@ -27163,7 +27137,7 @@
       <c r="C565">
         <v>2026</v>
       </c>
-      <c r="D565" s="2">
+      <c r="D565" s="1">
         <v>46230</v>
       </c>
       <c r="F565" t="s">
@@ -27783,7 +27757,7 @@
       <c r="C584">
         <v>2026</v>
       </c>
-      <c r="D584" s="2">
+      <c r="D584" s="1">
         <v>46226</v>
       </c>
       <c r="F584" t="s">
@@ -28307,7 +28281,7 @@
       <c r="C600">
         <v>2026</v>
       </c>
-      <c r="D600" s="2">
+      <c r="D600" s="1">
         <v>45802</v>
       </c>
       <c r="F600" t="s">
@@ -28351,7 +28325,7 @@
       <c r="C601">
         <v>2026</v>
       </c>
-      <c r="D601" s="2">
+      <c r="D601" s="1">
         <v>45860</v>
       </c>
       <c r="F601" t="s">
@@ -28392,7 +28366,7 @@
       <c r="C602">
         <v>2026</v>
       </c>
-      <c r="D602" s="2">
+      <c r="D602" s="1">
         <v>45860</v>
       </c>
       <c r="H602" t="s">
@@ -28427,7 +28401,7 @@
       <c r="C603">
         <v>2026</v>
       </c>
-      <c r="D603" s="2">
+      <c r="D603" s="1">
         <v>45856</v>
       </c>
       <c r="F603" t="s">
@@ -28468,7 +28442,7 @@
       <c r="C604">
         <v>2026</v>
       </c>
-      <c r="D604" s="2">
+      <c r="D604" s="1">
         <v>46101</v>
       </c>
       <c r="F604" t="s">
@@ -28509,7 +28483,7 @@
       <c r="C605">
         <v>2026</v>
       </c>
-      <c r="D605" s="2">
+      <c r="D605" s="1">
         <v>46101</v>
       </c>
       <c r="F605" t="s">
@@ -28550,7 +28524,7 @@
       <c r="C606">
         <v>2026</v>
       </c>
-      <c r="D606" s="2">
+      <c r="D606" s="1">
         <v>45863</v>
       </c>
       <c r="F606" t="s">
@@ -28591,7 +28565,7 @@
       <c r="C607">
         <v>2026</v>
       </c>
-      <c r="D607" s="2">
+      <c r="D607" s="1">
         <v>45863</v>
       </c>
       <c r="F607" t="s">
@@ -28632,7 +28606,7 @@
       <c r="C608">
         <v>2026</v>
       </c>
-      <c r="D608" s="2">
+      <c r="D608" s="1">
         <v>46086</v>
       </c>
       <c r="F608" t="s">
@@ -28673,7 +28647,7 @@
       <c r="C609">
         <v>2026</v>
       </c>
-      <c r="D609" s="2">
+      <c r="D609" s="1">
         <v>45874</v>
       </c>
       <c r="F609" t="s">
@@ -28714,7 +28688,7 @@
       <c r="C610">
         <v>2026</v>
       </c>
-      <c r="D610" s="2">
+      <c r="D610" s="1">
         <v>45894</v>
       </c>
       <c r="F610" t="s">
@@ -28755,7 +28729,7 @@
       <c r="C611">
         <v>2026</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="1">
         <v>45894</v>
       </c>
       <c r="F611" t="s">
@@ -28796,7 +28770,7 @@
       <c r="C612">
         <v>2026</v>
       </c>
-      <c r="D612" s="2">
+      <c r="D612" s="1">
         <v>46119</v>
       </c>
       <c r="F612" t="s">
@@ -28837,7 +28811,7 @@
       <c r="C613">
         <v>2026</v>
       </c>
-      <c r="D613" s="2">
+      <c r="D613" s="1">
         <v>45898</v>
       </c>
       <c r="F613" t="s">
@@ -28878,7 +28852,7 @@
       <c r="C614">
         <v>2026</v>
       </c>
-      <c r="D614" s="2">
+      <c r="D614" s="1">
         <v>45971</v>
       </c>
       <c r="F614" t="s">
@@ -28919,7 +28893,7 @@
       <c r="C615">
         <v>2026</v>
       </c>
-      <c r="D615" s="2">
+      <c r="D615" s="1">
         <v>46119</v>
       </c>
       <c r="F615" t="s">
@@ -28960,7 +28934,7 @@
       <c r="C616">
         <v>2026</v>
       </c>
-      <c r="D616" s="2">
+      <c r="D616" s="1">
         <v>46092</v>
       </c>
       <c r="F616" t="s">
@@ -29001,7 +28975,7 @@
       <c r="C617">
         <v>2026</v>
       </c>
-      <c r="D617" s="2">
+      <c r="D617" s="1">
         <v>46119</v>
       </c>
       <c r="F617" t="s">
@@ -29042,7 +29016,7 @@
       <c r="C618">
         <v>2026</v>
       </c>
-      <c r="D618" s="2">
+      <c r="D618" s="1">
         <v>46029</v>
       </c>
       <c r="F618" t="s">
@@ -29083,7 +29057,7 @@
       <c r="C619">
         <v>2026</v>
       </c>
-      <c r="D619" s="2">
+      <c r="D619" s="1">
         <v>46029</v>
       </c>
       <c r="F619" t="s">
@@ -29124,7 +29098,7 @@
       <c r="C620">
         <v>2026</v>
       </c>
-      <c r="D620" s="2">
+      <c r="D620" s="1">
         <v>46063</v>
       </c>
       <c r="H620" t="s">
@@ -29159,7 +29133,7 @@
       <c r="C621">
         <v>2026</v>
       </c>
-      <c r="D621" s="2">
+      <c r="D621" s="1">
         <v>46232</v>
       </c>
       <c r="G621" t="s">
@@ -29197,7 +29171,7 @@
       <c r="C622">
         <v>2026</v>
       </c>
-      <c r="D622" s="2">
+      <c r="D622" s="1">
         <v>46232</v>
       </c>
       <c r="G622" t="s">
@@ -29235,7 +29209,7 @@
       <c r="C623">
         <v>2026</v>
       </c>
-      <c r="D623" s="2">
+      <c r="D623" s="1">
         <v>46232</v>
       </c>
       <c r="G623" t="s">
@@ -29273,7 +29247,7 @@
       <c r="C624">
         <v>2026</v>
       </c>
-      <c r="D624" s="2">
+      <c r="D624" s="1">
         <v>46232</v>
       </c>
       <c r="G624" t="s">
@@ -29311,7 +29285,7 @@
       <c r="C625">
         <v>2026</v>
       </c>
-      <c r="D625" s="2">
+      <c r="D625" s="1">
         <v>46155</v>
       </c>
       <c r="H625" t="s">
@@ -29346,7 +29320,7 @@
       <c r="C626">
         <v>2026</v>
       </c>
-      <c r="D626" s="2">
+      <c r="D626" s="1">
         <v>46139</v>
       </c>
       <c r="F626" t="s">
@@ -29387,7 +29361,7 @@
       <c r="C627">
         <v>2026</v>
       </c>
-      <c r="D627" s="2">
+      <c r="D627" s="1">
         <v>46155</v>
       </c>
       <c r="F627" t="s">
@@ -29428,7 +29402,7 @@
       <c r="C628">
         <v>2026</v>
       </c>
-      <c r="D628" s="2">
+      <c r="D628" s="1">
         <v>46155</v>
       </c>
       <c r="H628" t="s">
@@ -29463,7 +29437,7 @@
       <c r="C629">
         <v>2026</v>
       </c>
-      <c r="D629" s="2">
+      <c r="D629" s="1">
         <v>46147</v>
       </c>
       <c r="H629" t="s">
@@ -29498,7 +29472,7 @@
       <c r="C630">
         <v>2026</v>
       </c>
-      <c r="D630" s="2">
+      <c r="D630" s="1">
         <v>46164</v>
       </c>
       <c r="F630" t="s">
@@ -29539,7 +29513,7 @@
       <c r="C631">
         <v>2026</v>
       </c>
-      <c r="D631" s="2">
+      <c r="D631" s="1">
         <v>46225</v>
       </c>
       <c r="F631" t="s">
@@ -29580,7 +29554,7 @@
       <c r="C632">
         <v>2026</v>
       </c>
-      <c r="D632" s="2">
+      <c r="D632" s="1">
         <v>46225</v>
       </c>
       <c r="F632" t="s">
@@ -29621,7 +29595,7 @@
       <c r="C633">
         <v>2026</v>
       </c>
-      <c r="D633" s="2">
+      <c r="D633" s="1">
         <v>46225</v>
       </c>
       <c r="F633" t="s">
@@ -29662,7 +29636,7 @@
       <c r="C634">
         <v>2026</v>
       </c>
-      <c r="D634" s="2">
+      <c r="D634" s="1">
         <v>46248</v>
       </c>
       <c r="H634" t="s">
@@ -29697,7 +29671,7 @@
       <c r="C635">
         <v>2026</v>
       </c>
-      <c r="D635" s="2">
+      <c r="D635" s="1">
         <v>46248</v>
       </c>
       <c r="F635" t="s">
@@ -29738,7 +29712,7 @@
       <c r="C636">
         <v>2026</v>
       </c>
-      <c r="D636" s="2">
+      <c r="D636" s="1">
         <v>46171</v>
       </c>
       <c r="H636" t="s">
@@ -29773,7 +29747,7 @@
       <c r="C637">
         <v>2026</v>
       </c>
-      <c r="D637" s="2">
+      <c r="D637" s="1">
         <v>46176</v>
       </c>
       <c r="H637" t="s">
@@ -29808,7 +29782,7 @@
       <c r="C638">
         <v>2026</v>
       </c>
-      <c r="D638" s="2">
+      <c r="D638" s="1">
         <v>46225</v>
       </c>
       <c r="F638" t="s">
@@ -29849,7 +29823,7 @@
       <c r="C639">
         <v>2026</v>
       </c>
-      <c r="D639" s="2">
+      <c r="D639" s="1">
         <v>46211</v>
       </c>
       <c r="H639" t="s">
@@ -29884,7 +29858,7 @@
       <c r="C640">
         <v>2026</v>
       </c>
-      <c r="D640" s="2">
+      <c r="D640" s="1">
         <v>46183</v>
       </c>
       <c r="H640" t="s">
@@ -29919,7 +29893,7 @@
       <c r="C641">
         <v>2026</v>
       </c>
-      <c r="D641" s="2">
+      <c r="D641" s="1">
         <v>46191</v>
       </c>
       <c r="F641" t="s">
@@ -29960,7 +29934,7 @@
       <c r="C642">
         <v>2026</v>
       </c>
-      <c r="D642" s="2">
+      <c r="D642" s="1">
         <v>46176</v>
       </c>
       <c r="H642" t="s">
@@ -29995,7 +29969,7 @@
       <c r="C643">
         <v>2026</v>
       </c>
-      <c r="D643" s="2">
+      <c r="D643" s="1">
         <v>46191</v>
       </c>
       <c r="H643" t="s">
@@ -30030,7 +30004,7 @@
       <c r="C644">
         <v>2026</v>
       </c>
-      <c r="D644" s="2">
+      <c r="D644" s="1">
         <v>46241</v>
       </c>
       <c r="F644" t="s">
@@ -30074,7 +30048,7 @@
       <c r="C645">
         <v>2026</v>
       </c>
-      <c r="D645" s="2">
+      <c r="D645" s="1">
         <v>46191</v>
       </c>
       <c r="F645" t="s">
@@ -30115,7 +30089,7 @@
       <c r="C646">
         <v>2026</v>
       </c>
-      <c r="D646" s="2">
+      <c r="D646" s="1">
         <v>46191</v>
       </c>
       <c r="F646" t="s">
@@ -30156,7 +30130,7 @@
       <c r="C647">
         <v>2026</v>
       </c>
-      <c r="D647" s="2">
+      <c r="D647" s="1">
         <v>46191</v>
       </c>
       <c r="H647" t="s">
@@ -30191,7 +30165,7 @@
       <c r="C648">
         <v>2026</v>
       </c>
-      <c r="D648" s="2">
+      <c r="D648" s="1">
         <v>46241</v>
       </c>
       <c r="F648" t="s">
@@ -30232,7 +30206,7 @@
       <c r="C649">
         <v>2026</v>
       </c>
-      <c r="D649" s="2">
+      <c r="D649" s="1">
         <v>46191</v>
       </c>
       <c r="H649" t="s">
@@ -30267,7 +30241,7 @@
       <c r="C650">
         <v>2026</v>
       </c>
-      <c r="D650" s="2">
+      <c r="D650" s="1">
         <v>46248</v>
       </c>
       <c r="H650" t="s">
@@ -30302,7 +30276,7 @@
       <c r="C651">
         <v>2026</v>
       </c>
-      <c r="D651" s="2">
+      <c r="D651" s="1">
         <v>46241</v>
       </c>
       <c r="F651" t="s">
@@ -30343,7 +30317,7 @@
       <c r="C652">
         <v>2026</v>
       </c>
-      <c r="D652" s="2">
+      <c r="D652" s="1">
         <v>46241</v>
       </c>
       <c r="F652" t="s">
@@ -30384,7 +30358,7 @@
       <c r="C653">
         <v>2026</v>
       </c>
-      <c r="D653" s="2">
+      <c r="D653" s="1">
         <v>46225</v>
       </c>
       <c r="F653" t="s">
@@ -30425,7 +30399,7 @@
       <c r="C654">
         <v>2026</v>
       </c>
-      <c r="D654" s="2">
+      <c r="D654" s="1">
         <v>46241</v>
       </c>
       <c r="F654" t="s">
@@ -30466,7 +30440,7 @@
       <c r="C655">
         <v>2026</v>
       </c>
-      <c r="D655" s="2">
+      <c r="D655" s="1">
         <v>46241</v>
       </c>
       <c r="F655" t="s">
@@ -30507,7 +30481,7 @@
       <c r="C656">
         <v>2026</v>
       </c>
-      <c r="D656" s="2">
+      <c r="D656" s="1">
         <v>46241</v>
       </c>
       <c r="F656" t="s">
@@ -30548,7 +30522,7 @@
       <c r="C657">
         <v>2026</v>
       </c>
-      <c r="D657" s="2">
+      <c r="D657" s="1">
         <v>46248</v>
       </c>
       <c r="H657" t="s">
@@ -30583,7 +30557,7 @@
       <c r="C658">
         <v>2026</v>
       </c>
-      <c r="D658" s="2">
+      <c r="D658" s="1">
         <v>46248</v>
       </c>
       <c r="H658" t="s">
@@ -30618,7 +30592,7 @@
       <c r="C659">
         <v>2026</v>
       </c>
-      <c r="D659" s="2">
+      <c r="D659" s="1">
         <v>46248</v>
       </c>
       <c r="F659" t="s">
@@ -30659,7 +30633,7 @@
       <c r="C660">
         <v>2026</v>
       </c>
-      <c r="D660" s="2">
+      <c r="D660" s="1">
         <v>46248</v>
       </c>
       <c r="F660" t="s">
@@ -30700,7 +30674,7 @@
       <c r="C661">
         <v>2026</v>
       </c>
-      <c r="D661" s="2">
+      <c r="D661" s="1">
         <v>46248</v>
       </c>
       <c r="F661" t="s">
@@ -30741,7 +30715,7 @@
       <c r="C662">
         <v>2026</v>
       </c>
-      <c r="D662" s="2">
+      <c r="D662" s="1">
         <v>45989</v>
       </c>
       <c r="G662" t="s">
@@ -30779,7 +30753,7 @@
       <c r="C663">
         <v>2026</v>
       </c>
-      <c r="D663" s="2">
+      <c r="D663" s="1">
         <v>46002</v>
       </c>
       <c r="G663" t="s">
@@ -30817,7 +30791,7 @@
       <c r="C664">
         <v>2026</v>
       </c>
-      <c r="D664" s="2">
+      <c r="D664" s="1">
         <v>46002</v>
       </c>
       <c r="G664" t="s">
@@ -30855,7 +30829,7 @@
       <c r="C665">
         <v>2026</v>
       </c>
-      <c r="D665" s="2">
+      <c r="D665" s="1">
         <v>46225</v>
       </c>
       <c r="F665" t="s">
@@ -30896,7 +30870,7 @@
       <c r="C666">
         <v>2026</v>
       </c>
-      <c r="D666" s="2">
+      <c r="D666" s="1">
         <v>46211</v>
       </c>
       <c r="F666" t="s">
@@ -30937,7 +30911,7 @@
       <c r="C667">
         <v>2026</v>
       </c>
-      <c r="D667" s="2">
+      <c r="D667" s="1">
         <v>46248</v>
       </c>
       <c r="F667" t="s">
@@ -30978,7 +30952,7 @@
       <c r="C668">
         <v>2026</v>
       </c>
-      <c r="D668" s="2">
+      <c r="D668" s="1">
         <v>46248</v>
       </c>
       <c r="F668" t="s">
@@ -31051,7 +31025,7 @@
       <c r="C670">
         <v>2026</v>
       </c>
-      <c r="D670" s="2">
+      <c r="D670" s="1">
         <v>46255</v>
       </c>
       <c r="F670" t="s">
@@ -31252,7 +31226,7 @@
       <c r="C676">
         <v>2026</v>
       </c>
-      <c r="D676" s="2">
+      <c r="D676" s="1">
         <v>46265</v>
       </c>
       <c r="H676" t="s">
@@ -31287,7 +31261,7 @@
       <c r="C677">
         <v>2026</v>
       </c>
-      <c r="D677" s="2">
+      <c r="D677" s="1">
         <v>46265</v>
       </c>
       <c r="H677" t="s">
@@ -31322,7 +31296,7 @@
       <c r="C678">
         <v>2026</v>
       </c>
-      <c r="D678" s="2">
+      <c r="D678" s="1">
         <v>46265</v>
       </c>
       <c r="H678" t="s">
@@ -31677,7 +31651,7 @@
       <c r="C689">
         <v>2026</v>
       </c>
-      <c r="D689" s="2">
+      <c r="D689" s="1">
         <v>46265</v>
       </c>
       <c r="H689" t="s">
@@ -31712,7 +31686,7 @@
       <c r="C690">
         <v>2026</v>
       </c>
-      <c r="D690" s="2">
+      <c r="D690" s="1">
         <v>46265</v>
       </c>
       <c r="H690" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
@@ -5765,8 +5765,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5782,7 +5790,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -5790,12 +5798,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6095,52 +6121,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6218,7 +6244,7 @@
       <c r="C4">
         <v>2026</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>45972</v>
       </c>
       <c r="F4" t="s">
@@ -6355,7 +6381,7 @@
       <c r="C8">
         <v>2026</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>46014</v>
       </c>
       <c r="F8" t="s">
@@ -6492,7 +6518,7 @@
       <c r="C12">
         <v>2026</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>45916</v>
       </c>
       <c r="F12" t="s">
@@ -6533,7 +6559,7 @@
       <c r="C13">
         <v>2026</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>45897</v>
       </c>
       <c r="H13" t="s">
@@ -6568,7 +6594,7 @@
       <c r="C14">
         <v>2026</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>45916</v>
       </c>
       <c r="F14" t="s">
@@ -6609,7 +6635,7 @@
       <c r="C15">
         <v>2026</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>46086</v>
       </c>
       <c r="G15" t="s">
@@ -6647,7 +6673,7 @@
       <c r="C16">
         <v>2026</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>45869</v>
       </c>
       <c r="F16" t="s">
@@ -6688,7 +6714,7 @@
       <c r="C17">
         <v>2026</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>45877</v>
       </c>
       <c r="F17" t="s">
@@ -6729,7 +6755,7 @@
       <c r="C18">
         <v>2026</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>46086</v>
       </c>
       <c r="G18" t="s">
@@ -6767,7 +6793,7 @@
       <c r="C19">
         <v>2026</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2">
         <v>45863</v>
       </c>
       <c r="F19" t="s">
@@ -6808,7 +6834,7 @@
       <c r="C20">
         <v>2026</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
         <v>45863</v>
       </c>
       <c r="F20" t="s">
@@ -6849,7 +6875,7 @@
       <c r="C21">
         <v>2026</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>45873</v>
       </c>
       <c r="F21" t="s">
@@ -6890,7 +6916,7 @@
       <c r="C22">
         <v>2026</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
@@ -6931,7 +6957,7 @@
       <c r="C23">
         <v>2026</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
         <v>46086</v>
       </c>
       <c r="G23" t="s">
@@ -7033,7 +7059,7 @@
       <c r="C26">
         <v>2026</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="2">
         <v>45838</v>
       </c>
       <c r="F26" t="s">
@@ -7074,7 +7100,7 @@
       <c r="C27">
         <v>2026</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="2">
         <v>45800</v>
       </c>
       <c r="F27" t="s">
@@ -7115,7 +7141,7 @@
       <c r="C28">
         <v>2026</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="2">
         <v>45849</v>
       </c>
       <c r="F28" t="s">
@@ -7156,7 +7182,7 @@
       <c r="C29">
         <v>2026</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="2">
         <v>45838</v>
       </c>
       <c r="F29" t="s">
@@ -7197,7 +7223,7 @@
       <c r="C30">
         <v>2026</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="2">
         <v>45915</v>
       </c>
       <c r="F30" t="s">
@@ -7238,7 +7264,7 @@
       <c r="C31">
         <v>2026</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="2">
         <v>45849</v>
       </c>
       <c r="F31" t="s">
@@ -7311,7 +7337,7 @@
       <c r="C33">
         <v>2026</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="2">
         <v>45800</v>
       </c>
       <c r="F33" t="s">
@@ -7384,7 +7410,7 @@
       <c r="C35">
         <v>2026</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="2">
         <v>46119</v>
       </c>
       <c r="F35" t="s">
@@ -7425,7 +7451,7 @@
       <c r="C36">
         <v>2026</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="2">
         <v>45854</v>
       </c>
       <c r="F36" t="s">
@@ -7466,7 +7492,7 @@
       <c r="C37">
         <v>2026</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="2">
         <v>45849</v>
       </c>
       <c r="F37" t="s">
@@ -7507,7 +7533,7 @@
       <c r="C38">
         <v>2026</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="2">
         <v>46119</v>
       </c>
       <c r="F38" t="s">
@@ -7580,7 +7606,7 @@
       <c r="C40">
         <v>2026</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="2">
         <v>46092</v>
       </c>
       <c r="F40" t="s">
@@ -7685,7 +7711,7 @@
       <c r="C43">
         <v>2026</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="2">
         <v>46122</v>
       </c>
       <c r="F43" t="s">
@@ -7726,7 +7752,7 @@
       <c r="C44">
         <v>2026</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="2">
         <v>46122</v>
       </c>
       <c r="F44" t="s">
@@ -7767,7 +7793,7 @@
       <c r="C45">
         <v>2026</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <v>46135</v>
       </c>
       <c r="F45" t="s">
@@ -7808,7 +7834,7 @@
       <c r="C46">
         <v>2026</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="2">
         <v>46086</v>
       </c>
       <c r="F46" t="s">
@@ -7849,7 +7875,7 @@
       <c r="C47">
         <v>2026</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="2">
         <v>46104</v>
       </c>
       <c r="F47" t="s">
@@ -7890,7 +7916,7 @@
       <c r="C48">
         <v>2026</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="2">
         <v>45972</v>
       </c>
       <c r="G48" t="s">
@@ -7928,7 +7954,7 @@
       <c r="C49">
         <v>2026</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>45810</v>
       </c>
       <c r="F49" t="s">
@@ -7969,7 +7995,7 @@
       <c r="C50">
         <v>2026</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="2">
         <v>45937</v>
       </c>
       <c r="F50" t="s">
@@ -8010,7 +8036,7 @@
       <c r="C51">
         <v>2026</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="2">
         <v>45937</v>
       </c>
       <c r="F51" t="s">
@@ -8083,7 +8109,7 @@
       <c r="C53">
         <v>2026</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="2">
         <v>45845</v>
       </c>
       <c r="F53" t="s">
@@ -8124,7 +8150,7 @@
       <c r="C54">
         <v>2026</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="2">
         <v>46077</v>
       </c>
       <c r="F54" t="s">
@@ -8197,7 +8223,7 @@
       <c r="C56">
         <v>2026</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>45971</v>
       </c>
       <c r="F56" t="s">
@@ -8270,7 +8296,7 @@
       <c r="C58">
         <v>2026</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <v>45817</v>
       </c>
       <c r="F58" t="s">
@@ -8343,7 +8369,7 @@
       <c r="C60">
         <v>2026</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <v>45965</v>
       </c>
       <c r="G60" t="s">
@@ -8413,7 +8439,7 @@
       <c r="C62">
         <v>2026</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="2">
         <v>46072</v>
       </c>
       <c r="F62" t="s">
@@ -8486,7 +8512,7 @@
       <c r="C64">
         <v>2026</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="2">
         <v>46072</v>
       </c>
       <c r="H64" t="s">
@@ -8521,7 +8547,7 @@
       <c r="C65">
         <v>2026</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="2">
         <v>45804</v>
       </c>
       <c r="F65" t="s">
@@ -8562,7 +8588,7 @@
       <c r="C66">
         <v>2026</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="2">
         <v>45804</v>
       </c>
       <c r="F66" t="s">
@@ -8603,7 +8629,7 @@
       <c r="C67">
         <v>2026</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="2">
         <v>45804</v>
       </c>
       <c r="F67" t="s">
@@ -8644,7 +8670,7 @@
       <c r="C68">
         <v>2026</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="2">
         <v>45804</v>
       </c>
       <c r="F68" t="s">
@@ -8685,7 +8711,7 @@
       <c r="C69">
         <v>2026</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="2">
         <v>45804</v>
       </c>
       <c r="F69" t="s">
@@ -8726,7 +8752,7 @@
       <c r="C70">
         <v>2026</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="2">
         <v>45804</v>
       </c>
       <c r="F70" t="s">
@@ -8767,7 +8793,7 @@
       <c r="C71">
         <v>2026</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="2">
         <v>45821</v>
       </c>
       <c r="F71" t="s">
@@ -8808,7 +8834,7 @@
       <c r="C72">
         <v>2026</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="2">
         <v>45821</v>
       </c>
       <c r="H72" t="s">
@@ -8843,7 +8869,7 @@
       <c r="C73">
         <v>2026</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="2">
         <v>45891</v>
       </c>
       <c r="F73" t="s">
@@ -8884,7 +8910,7 @@
       <c r="C74">
         <v>2026</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="2">
         <v>45817</v>
       </c>
       <c r="G74" t="s">
@@ -8922,7 +8948,7 @@
       <c r="C75">
         <v>2026</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="2">
         <v>45883</v>
       </c>
       <c r="G75" t="s">
@@ -8960,7 +8986,7 @@
       <c r="C76">
         <v>2026</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="2">
         <v>45817</v>
       </c>
       <c r="G76" t="s">
@@ -8998,7 +9024,7 @@
       <c r="C77">
         <v>2026</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="2">
         <v>45883</v>
       </c>
       <c r="G77" t="s">
@@ -9036,7 +9062,7 @@
       <c r="C78">
         <v>2026</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78" s="2">
         <v>45971</v>
       </c>
       <c r="F78" t="s">
@@ -9077,7 +9103,7 @@
       <c r="C79">
         <v>2026</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="2">
         <v>45849</v>
       </c>
       <c r="F79" t="s">
@@ -9118,7 +9144,7 @@
       <c r="C80">
         <v>2026</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80" s="2">
         <v>45849</v>
       </c>
       <c r="F80" t="s">
@@ -9159,7 +9185,7 @@
       <c r="C81">
         <v>2026</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81" s="2">
         <v>45863</v>
       </c>
       <c r="F81" t="s">
@@ -9200,7 +9226,7 @@
       <c r="C82">
         <v>2026</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82" s="2">
         <v>45810</v>
       </c>
       <c r="F82" t="s">
@@ -9241,7 +9267,7 @@
       <c r="C83">
         <v>2026</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="2">
         <v>45926</v>
       </c>
       <c r="F83" t="s">
@@ -9282,7 +9308,7 @@
       <c r="C84">
         <v>2026</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84" s="2">
         <v>45971</v>
       </c>
       <c r="F84" t="s">
@@ -9323,7 +9349,7 @@
       <c r="C85">
         <v>2026</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85" s="2">
         <v>46164</v>
       </c>
       <c r="F85" t="s">
@@ -9364,7 +9390,7 @@
       <c r="C86">
         <v>2026</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D86" s="2">
         <v>45986</v>
       </c>
       <c r="G86" t="s">
@@ -9443,7 +9469,7 @@
       <c r="C88">
         <v>2026</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88" s="2">
         <v>45786</v>
       </c>
       <c r="F88" t="s">
@@ -9484,7 +9510,7 @@
       <c r="C89">
         <v>2026</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89" s="2">
         <v>45777</v>
       </c>
       <c r="F89" t="s">
@@ -9525,7 +9551,7 @@
       <c r="C90">
         <v>2026</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90" s="2">
         <v>45869</v>
       </c>
       <c r="F90" t="s">
@@ -9566,7 +9592,7 @@
       <c r="C91">
         <v>2026</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91" s="2">
         <v>45891</v>
       </c>
       <c r="F91" t="s">
@@ -9607,7 +9633,7 @@
       <c r="C92">
         <v>2026</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92" s="2">
         <v>45863</v>
       </c>
       <c r="F92" t="s">
@@ -9648,7 +9674,7 @@
       <c r="C93">
         <v>2026</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D93" s="2">
         <v>45769</v>
       </c>
       <c r="F93" t="s">
@@ -9689,7 +9715,7 @@
       <c r="C94">
         <v>2026</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D94" s="2">
         <v>45769</v>
       </c>
       <c r="F94" t="s">
@@ -9730,7 +9756,7 @@
       <c r="C95">
         <v>2026</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D95" s="2">
         <v>45894</v>
       </c>
       <c r="F95" t="s">
@@ -9803,7 +9829,7 @@
       <c r="C97">
         <v>2026</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97" s="2">
         <v>45894</v>
       </c>
       <c r="F97" t="s">
@@ -9844,7 +9870,7 @@
       <c r="C98">
         <v>2026</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98" s="2">
         <v>45971</v>
       </c>
       <c r="F98" t="s">
@@ -9885,7 +9911,7 @@
       <c r="C99">
         <v>2026</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D99" s="2">
         <v>45971</v>
       </c>
       <c r="F99" t="s">
@@ -9926,7 +9952,7 @@
       <c r="C100">
         <v>2026</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100" s="2">
         <v>45971</v>
       </c>
       <c r="F100" t="s">
@@ -9967,7 +9993,7 @@
       <c r="C101">
         <v>2026</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D101" s="2">
         <v>45996</v>
       </c>
       <c r="G101" t="s">
@@ -10005,7 +10031,7 @@
       <c r="C102">
         <v>2026</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D102" s="2">
         <v>45986</v>
       </c>
       <c r="G102" t="s">
@@ -10075,7 +10101,7 @@
       <c r="C104">
         <v>2026</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104" s="2">
         <v>45769</v>
       </c>
       <c r="F104" t="s">
@@ -10116,7 +10142,7 @@
       <c r="C105">
         <v>2026</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105" s="2">
         <v>45769</v>
       </c>
       <c r="F105" t="s">
@@ -10157,7 +10183,7 @@
       <c r="C106">
         <v>2026</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D106" s="2">
         <v>45849</v>
       </c>
       <c r="F106" t="s">
@@ -10198,7 +10224,7 @@
       <c r="C107">
         <v>2026</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D107" s="2">
         <v>45849</v>
       </c>
       <c r="G107" t="s">
@@ -10300,7 +10326,7 @@
       <c r="C110">
         <v>2026</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D110" s="2">
         <v>45891</v>
       </c>
       <c r="F110" t="s">
@@ -10341,7 +10367,7 @@
       <c r="C111">
         <v>2026</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D111" s="2">
         <v>45769</v>
       </c>
       <c r="F111" t="s">
@@ -10382,7 +10408,7 @@
       <c r="C112">
         <v>2026</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D112" s="2">
         <v>45889</v>
       </c>
       <c r="F112" t="s">
@@ -10423,7 +10449,7 @@
       <c r="C113">
         <v>2026</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D113" s="2">
         <v>45945</v>
       </c>
       <c r="G113" t="s">
@@ -10461,7 +10487,7 @@
       <c r="C114">
         <v>2026</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="2">
         <v>45945</v>
       </c>
       <c r="G114" t="s">
@@ -10499,7 +10525,7 @@
       <c r="C115">
         <v>2026</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="2">
         <v>46119</v>
       </c>
       <c r="F115" t="s">
@@ -10540,7 +10566,7 @@
       <c r="C116">
         <v>2026</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="2">
         <v>46029</v>
       </c>
       <c r="F116" t="s">
@@ -10581,7 +10607,7 @@
       <c r="C117">
         <v>2026</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="2">
         <v>46029</v>
       </c>
       <c r="F117" t="s">
@@ -10622,7 +10648,7 @@
       <c r="C118">
         <v>2026</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D118" s="2">
         <v>46119</v>
       </c>
       <c r="F118" t="s">
@@ -10663,7 +10689,7 @@
       <c r="C119">
         <v>2026</v>
       </c>
-      <c r="D119" s="1">
+      <c r="D119" s="2">
         <v>46230</v>
       </c>
       <c r="F119" t="s">
@@ -10704,7 +10730,7 @@
       <c r="C120">
         <v>2026</v>
       </c>
-      <c r="D120" s="1">
+      <c r="D120" s="2">
         <v>46119</v>
       </c>
       <c r="F120" t="s">
@@ -10745,7 +10771,7 @@
       <c r="C121">
         <v>2026</v>
       </c>
-      <c r="D121" s="1">
+      <c r="D121" s="2">
         <v>46119</v>
       </c>
       <c r="F121" t="s">
@@ -10786,7 +10812,7 @@
       <c r="C122">
         <v>2026</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D122" s="2">
         <v>45931</v>
       </c>
       <c r="F122" t="s">
@@ -10827,7 +10853,7 @@
       <c r="C123">
         <v>2026</v>
       </c>
-      <c r="D123" s="1">
+      <c r="D123" s="2">
         <v>45894</v>
       </c>
       <c r="G123" t="s">
@@ -10865,7 +10891,7 @@
       <c r="C124">
         <v>2026</v>
       </c>
-      <c r="D124" s="1">
+      <c r="D124" s="2">
         <v>46119</v>
       </c>
       <c r="F124" t="s">
@@ -10906,7 +10932,7 @@
       <c r="C125">
         <v>2026</v>
       </c>
-      <c r="D125" s="1">
+      <c r="D125" s="2">
         <v>45889</v>
       </c>
       <c r="F125" t="s">
@@ -10947,7 +10973,7 @@
       <c r="C126">
         <v>2026</v>
       </c>
-      <c r="D126" s="1">
+      <c r="D126" s="2">
         <v>45876</v>
       </c>
       <c r="G126" t="s">
@@ -11017,7 +11043,7 @@
       <c r="C128">
         <v>2026</v>
       </c>
-      <c r="D128" s="1">
+      <c r="D128" s="2">
         <v>45876</v>
       </c>
       <c r="F128" t="s">
@@ -11090,7 +11116,7 @@
       <c r="C130">
         <v>2026</v>
       </c>
-      <c r="D130" s="1">
+      <c r="D130" s="2">
         <v>46230</v>
       </c>
       <c r="F130" t="s">
@@ -11131,7 +11157,7 @@
       <c r="C131">
         <v>2026</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D131" s="2">
         <v>45889</v>
       </c>
       <c r="F131" t="s">
@@ -11172,7 +11198,7 @@
       <c r="C132">
         <v>2026</v>
       </c>
-      <c r="D132" s="1">
+      <c r="D132" s="2">
         <v>46230</v>
       </c>
       <c r="F132" t="s">
@@ -11245,7 +11271,7 @@
       <c r="C134">
         <v>2026</v>
       </c>
-      <c r="D134" s="1">
+      <c r="D134" s="2">
         <v>46140</v>
       </c>
       <c r="F134" t="s">
@@ -11286,7 +11312,7 @@
       <c r="C135">
         <v>2026</v>
       </c>
-      <c r="D135" s="1">
+      <c r="D135" s="2">
         <v>45889</v>
       </c>
       <c r="F135" t="s">
@@ -11327,7 +11353,7 @@
       <c r="C136">
         <v>2026</v>
       </c>
-      <c r="D136" s="1">
+      <c r="D136" s="2">
         <v>45952</v>
       </c>
       <c r="F136" t="s">
@@ -11365,7 +11391,7 @@
       <c r="C137">
         <v>2026</v>
       </c>
-      <c r="D137" s="1">
+      <c r="D137" s="2">
         <v>46230</v>
       </c>
       <c r="F137" t="s">
@@ -11438,7 +11464,7 @@
       <c r="C139">
         <v>2026</v>
       </c>
-      <c r="D139" s="1">
+      <c r="D139" s="2">
         <v>46029</v>
       </c>
       <c r="G139" t="s">
@@ -11476,7 +11502,7 @@
       <c r="C140">
         <v>2026</v>
       </c>
-      <c r="D140" s="1">
+      <c r="D140" s="2">
         <v>46029</v>
       </c>
       <c r="G140" t="s">
@@ -11546,7 +11572,7 @@
       <c r="C142">
         <v>2026</v>
       </c>
-      <c r="D142" s="1">
+      <c r="D142" s="2">
         <v>46119</v>
       </c>
       <c r="F142" t="s">
@@ -11651,7 +11677,7 @@
       <c r="C145">
         <v>2026</v>
       </c>
-      <c r="D145" s="1">
+      <c r="D145" s="2">
         <v>46140</v>
       </c>
       <c r="F145" t="s">
@@ -11692,7 +11718,7 @@
       <c r="C146">
         <v>2026</v>
       </c>
-      <c r="D146" s="1">
+      <c r="D146" s="2">
         <v>46230</v>
       </c>
       <c r="F146" t="s">
@@ -11733,7 +11759,7 @@
       <c r="C147">
         <v>2026</v>
       </c>
-      <c r="D147" s="1">
+      <c r="D147" s="2">
         <v>46230</v>
       </c>
       <c r="F147" t="s">
@@ -11774,7 +11800,7 @@
       <c r="C148">
         <v>2026</v>
       </c>
-      <c r="D148" s="1">
+      <c r="D148" s="2">
         <v>46119</v>
       </c>
       <c r="F148" t="s">
@@ -11815,7 +11841,7 @@
       <c r="C149">
         <v>2026</v>
       </c>
-      <c r="D149" s="1">
+      <c r="D149" s="2">
         <v>46230</v>
       </c>
       <c r="F149" t="s">
@@ -11856,7 +11882,7 @@
       <c r="C150">
         <v>2026</v>
       </c>
-      <c r="D150" s="1">
+      <c r="D150" s="2">
         <v>46140</v>
       </c>
       <c r="F150" t="s">
@@ -11897,7 +11923,7 @@
       <c r="C151">
         <v>2026</v>
       </c>
-      <c r="D151" s="1">
+      <c r="D151" s="2">
         <v>45876</v>
       </c>
       <c r="F151" t="s">
@@ -11970,7 +11996,7 @@
       <c r="C153">
         <v>2026</v>
       </c>
-      <c r="D153" s="1">
+      <c r="D153" s="2">
         <v>45863</v>
       </c>
       <c r="F153" t="s">
@@ -12011,7 +12037,7 @@
       <c r="C154">
         <v>2026</v>
       </c>
-      <c r="D154" s="1">
+      <c r="D154" s="2">
         <v>45863</v>
       </c>
       <c r="F154" t="s">
@@ -12052,7 +12078,7 @@
       <c r="C155">
         <v>2026</v>
       </c>
-      <c r="D155" s="1">
+      <c r="D155" s="2">
         <v>45863</v>
       </c>
       <c r="F155" t="s">
@@ -12093,7 +12119,7 @@
       <c r="C156">
         <v>2026</v>
       </c>
-      <c r="D156" s="1">
+      <c r="D156" s="2">
         <v>45860</v>
       </c>
       <c r="F156" t="s">
@@ -12163,7 +12189,7 @@
       <c r="C158">
         <v>2026</v>
       </c>
-      <c r="D158" s="1">
+      <c r="D158" s="2">
         <v>46119</v>
       </c>
       <c r="F158" t="s">
@@ -12204,7 +12230,7 @@
       <c r="C159">
         <v>2026</v>
       </c>
-      <c r="D159" s="1">
+      <c r="D159" s="2">
         <v>45814</v>
       </c>
       <c r="F159" t="s">
@@ -12245,7 +12271,7 @@
       <c r="C160">
         <v>2026</v>
       </c>
-      <c r="D160" s="1">
+      <c r="D160" s="2">
         <v>45817</v>
       </c>
       <c r="F160" t="s">
@@ -12286,7 +12312,7 @@
       <c r="C161">
         <v>2026</v>
       </c>
-      <c r="D161" s="1">
+      <c r="D161" s="2">
         <v>45971</v>
       </c>
       <c r="F161" t="s">
@@ -12327,7 +12353,7 @@
       <c r="C162">
         <v>2026</v>
       </c>
-      <c r="D162" s="1">
+      <c r="D162" s="2">
         <v>45971</v>
       </c>
       <c r="F162" t="s">
@@ -12368,7 +12394,7 @@
       <c r="C163">
         <v>2026</v>
       </c>
-      <c r="D163" s="1">
+      <c r="D163" s="2">
         <v>45860</v>
       </c>
       <c r="G163" t="s">
@@ -12406,7 +12432,7 @@
       <c r="C164">
         <v>2026</v>
       </c>
-      <c r="D164" s="1">
+      <c r="D164" s="2">
         <v>45856</v>
       </c>
       <c r="F164" t="s">
@@ -12479,7 +12505,7 @@
       <c r="C166">
         <v>2026</v>
       </c>
-      <c r="D166" s="1">
+      <c r="D166" s="2">
         <v>46064</v>
       </c>
       <c r="F166" t="s">
@@ -12520,7 +12546,7 @@
       <c r="C167">
         <v>2026</v>
       </c>
-      <c r="D167" s="1">
+      <c r="D167" s="2">
         <v>45982</v>
       </c>
       <c r="G167" t="s">
@@ -12558,7 +12584,7 @@
       <c r="C168">
         <v>2026</v>
       </c>
-      <c r="D168" s="1">
+      <c r="D168" s="2">
         <v>46157</v>
       </c>
       <c r="H168" t="s">
@@ -12593,7 +12619,7 @@
       <c r="C169">
         <v>2026</v>
       </c>
-      <c r="D169" s="1">
+      <c r="D169" s="2">
         <v>45762</v>
       </c>
       <c r="F169" t="s">
@@ -12634,7 +12660,7 @@
       <c r="C170">
         <v>2026</v>
       </c>
-      <c r="D170" s="1">
+      <c r="D170" s="2">
         <v>45816</v>
       </c>
       <c r="F170" t="s">
@@ -12675,7 +12701,7 @@
       <c r="C171">
         <v>2026</v>
       </c>
-      <c r="D171" s="1">
+      <c r="D171" s="2">
         <v>45816</v>
       </c>
       <c r="F171" t="s">
@@ -12754,7 +12780,7 @@
       <c r="C173">
         <v>2026</v>
       </c>
-      <c r="D173" s="1">
+      <c r="D173" s="2">
         <v>46101</v>
       </c>
       <c r="F173" t="s">
@@ -12795,7 +12821,7 @@
       <c r="C174">
         <v>2026</v>
       </c>
-      <c r="D174" s="1">
+      <c r="D174" s="2">
         <v>46101</v>
       </c>
       <c r="F174" t="s">
@@ -12836,7 +12862,7 @@
       <c r="C175">
         <v>2026</v>
       </c>
-      <c r="D175" s="1">
+      <c r="D175" s="2">
         <v>46105</v>
       </c>
       <c r="F175" t="s">
@@ -12877,7 +12903,7 @@
       <c r="C176">
         <v>2026</v>
       </c>
-      <c r="D176" s="1">
+      <c r="D176" s="2">
         <v>45889</v>
       </c>
       <c r="F176" t="s">
@@ -12918,7 +12944,7 @@
       <c r="C177">
         <v>2026</v>
       </c>
-      <c r="D177" s="1">
+      <c r="D177" s="2">
         <v>45814</v>
       </c>
       <c r="F177" t="s">
@@ -12959,7 +12985,7 @@
       <c r="C178">
         <v>2026</v>
       </c>
-      <c r="D178" s="1">
+      <c r="D178" s="2">
         <v>45889</v>
       </c>
       <c r="F178" t="s">
@@ -13000,7 +13026,7 @@
       <c r="C179">
         <v>2026</v>
       </c>
-      <c r="D179" s="1">
+      <c r="D179" s="2">
         <v>45814</v>
       </c>
       <c r="F179" t="s">
@@ -13041,7 +13067,7 @@
       <c r="C180">
         <v>2026</v>
       </c>
-      <c r="D180" s="1">
+      <c r="D180" s="2">
         <v>45889</v>
       </c>
       <c r="F180" t="s">
@@ -13114,7 +13140,7 @@
       <c r="C182">
         <v>2026</v>
       </c>
-      <c r="D182" s="1">
+      <c r="D182" s="2">
         <v>46139</v>
       </c>
       <c r="H182" t="s">
@@ -13181,7 +13207,7 @@
       <c r="C184">
         <v>2026</v>
       </c>
-      <c r="D184" s="1">
+      <c r="D184" s="2">
         <v>45889</v>
       </c>
       <c r="F184" t="s">
@@ -13254,7 +13280,7 @@
       <c r="C186">
         <v>2026</v>
       </c>
-      <c r="D186" s="1">
+      <c r="D186" s="2">
         <v>45814</v>
       </c>
       <c r="F186" t="s">
@@ -13295,7 +13321,7 @@
       <c r="C187">
         <v>2026</v>
       </c>
-      <c r="D187" s="1">
+      <c r="D187" s="2">
         <v>45889</v>
       </c>
       <c r="F187" t="s">
@@ -13336,7 +13362,7 @@
       <c r="C188">
         <v>2026</v>
       </c>
-      <c r="D188" s="1">
+      <c r="D188" s="2">
         <v>45931</v>
       </c>
       <c r="F188" t="s">
@@ -13377,7 +13403,7 @@
       <c r="C189">
         <v>2026</v>
       </c>
-      <c r="D189" s="1">
+      <c r="D189" s="2">
         <v>45889</v>
       </c>
       <c r="F189" t="s">
@@ -13418,7 +13444,7 @@
       <c r="C190">
         <v>2026</v>
       </c>
-      <c r="D190" s="1">
+      <c r="D190" s="2">
         <v>45876</v>
       </c>
       <c r="F190" t="s">
@@ -13459,7 +13485,7 @@
       <c r="C191">
         <v>2026</v>
       </c>
-      <c r="D191" s="1">
+      <c r="D191" s="2">
         <v>45876</v>
       </c>
       <c r="F191" t="s">
@@ -13532,7 +13558,7 @@
       <c r="C193">
         <v>2026</v>
       </c>
-      <c r="D193" s="1">
+      <c r="D193" s="2">
         <v>45876</v>
       </c>
       <c r="F193" t="s">
@@ -13573,7 +13599,7 @@
       <c r="C194">
         <v>2026</v>
       </c>
-      <c r="D194" s="1">
+      <c r="D194" s="2">
         <v>46119</v>
       </c>
       <c r="F194" t="s">
@@ -13614,7 +13640,7 @@
       <c r="C195">
         <v>2026</v>
       </c>
-      <c r="D195" s="1">
+      <c r="D195" s="2">
         <v>46119</v>
       </c>
       <c r="F195" t="s">
@@ -13655,7 +13681,7 @@
       <c r="C196">
         <v>2026</v>
       </c>
-      <c r="D196" s="1">
+      <c r="D196" s="2">
         <v>45961</v>
       </c>
       <c r="F196" t="s">
@@ -13696,7 +13722,7 @@
       <c r="C197">
         <v>2026</v>
       </c>
-      <c r="D197" s="1">
+      <c r="D197" s="2">
         <v>45860</v>
       </c>
       <c r="F197" t="s">
@@ -13737,7 +13763,7 @@
       <c r="C198">
         <v>2026</v>
       </c>
-      <c r="D198" s="1">
+      <c r="D198" s="2">
         <v>45993</v>
       </c>
       <c r="G198" t="s">
@@ -13775,7 +13801,7 @@
       <c r="C199">
         <v>2026</v>
       </c>
-      <c r="D199" s="1">
+      <c r="D199" s="2">
         <v>45853</v>
       </c>
       <c r="F199" t="s">
@@ -13816,7 +13842,7 @@
       <c r="C200">
         <v>2026</v>
       </c>
-      <c r="D200" s="1">
+      <c r="D200" s="2">
         <v>46119</v>
       </c>
       <c r="F200" t="s">
@@ -13895,7 +13921,7 @@
       <c r="C202">
         <v>2026</v>
       </c>
-      <c r="D202" s="1">
+      <c r="D202" s="2">
         <v>46191</v>
       </c>
       <c r="F202" t="s">
@@ -13936,7 +13962,7 @@
       <c r="C203">
         <v>2026</v>
       </c>
-      <c r="D203" s="1">
+      <c r="D203" s="2">
         <v>46191</v>
       </c>
       <c r="F203" t="s">
@@ -13977,7 +14003,7 @@
       <c r="C204">
         <v>2026</v>
       </c>
-      <c r="D204" s="1">
+      <c r="D204" s="2">
         <v>46191</v>
       </c>
       <c r="F204" t="s">
@@ -14018,7 +14044,7 @@
       <c r="C205">
         <v>2026</v>
       </c>
-      <c r="D205" s="1">
+      <c r="D205" s="2">
         <v>45932</v>
       </c>
       <c r="G205" t="s">
@@ -14056,7 +14082,7 @@
       <c r="C206">
         <v>2026</v>
       </c>
-      <c r="D206" s="1">
+      <c r="D206" s="2">
         <v>46191</v>
       </c>
       <c r="F206" t="s">
@@ -14097,7 +14123,7 @@
       <c r="C207">
         <v>2026</v>
       </c>
-      <c r="D207" s="1">
+      <c r="D207" s="2">
         <v>46119</v>
       </c>
       <c r="F207" t="s">
@@ -14138,7 +14164,7 @@
       <c r="C208">
         <v>2026</v>
       </c>
-      <c r="D208" s="1">
+      <c r="D208" s="2">
         <v>45946</v>
       </c>
       <c r="G208" t="s">
@@ -14176,7 +14202,7 @@
       <c r="C209">
         <v>2026</v>
       </c>
-      <c r="D209" s="1">
+      <c r="D209" s="2">
         <v>45937</v>
       </c>
       <c r="F209" t="s">
@@ -14217,7 +14243,7 @@
       <c r="C210">
         <v>2026</v>
       </c>
-      <c r="D210" s="1">
+      <c r="D210" s="2">
         <v>45849</v>
       </c>
       <c r="F210" t="s">
@@ -14258,7 +14284,7 @@
       <c r="C211">
         <v>2026</v>
       </c>
-      <c r="D211" s="1">
+      <c r="D211" s="2">
         <v>45876</v>
       </c>
       <c r="F211" t="s">
@@ -14299,7 +14325,7 @@
       <c r="C212">
         <v>2026</v>
       </c>
-      <c r="D212" s="1">
+      <c r="D212" s="2">
         <v>46008</v>
       </c>
       <c r="F212" t="s">
@@ -14413,7 +14439,7 @@
       <c r="C215">
         <v>2026</v>
       </c>
-      <c r="D215" s="1">
+      <c r="D215" s="2">
         <v>45973</v>
       </c>
       <c r="F215" t="s">
@@ -14454,7 +14480,7 @@
       <c r="C216">
         <v>2026</v>
       </c>
-      <c r="D216" s="1">
+      <c r="D216" s="2">
         <v>46014</v>
       </c>
       <c r="F216" t="s">
@@ -14495,7 +14521,7 @@
       <c r="C217">
         <v>2026</v>
       </c>
-      <c r="D217" s="1">
+      <c r="D217" s="2">
         <v>45876</v>
       </c>
       <c r="F217" t="s">
@@ -14536,7 +14562,7 @@
       <c r="C218">
         <v>2026</v>
       </c>
-      <c r="D218" s="1">
+      <c r="D218" s="2">
         <v>45937</v>
       </c>
       <c r="F218" t="s">
@@ -14577,7 +14603,7 @@
       <c r="C219">
         <v>2026</v>
       </c>
-      <c r="D219" s="1">
+      <c r="D219" s="2">
         <v>45980</v>
       </c>
       <c r="F219" t="s">
@@ -14938,7 +14964,7 @@
       <c r="C230">
         <v>2026</v>
       </c>
-      <c r="D230" s="1">
+      <c r="D230" s="2">
         <v>45979</v>
       </c>
       <c r="F230" t="s">
@@ -14979,7 +15005,7 @@
       <c r="C231">
         <v>2026</v>
       </c>
-      <c r="D231" s="1">
+      <c r="D231" s="2">
         <v>45979</v>
       </c>
       <c r="F231" t="s">
@@ -15020,7 +15046,7 @@
       <c r="C232">
         <v>2026</v>
       </c>
-      <c r="D232" s="1">
+      <c r="D232" s="2">
         <v>45979</v>
       </c>
       <c r="F232" t="s">
@@ -15061,7 +15087,7 @@
       <c r="C233">
         <v>2026</v>
       </c>
-      <c r="D233" s="1">
+      <c r="D233" s="2">
         <v>45971</v>
       </c>
       <c r="F233" t="s">
@@ -15102,7 +15128,7 @@
       <c r="C234">
         <v>2026</v>
       </c>
-      <c r="D234" s="1">
+      <c r="D234" s="2">
         <v>45971</v>
       </c>
       <c r="F234" t="s">
@@ -15143,7 +15169,7 @@
       <c r="C235">
         <v>2026</v>
       </c>
-      <c r="D235" s="1">
+      <c r="D235" s="2">
         <v>45971</v>
       </c>
       <c r="F235" t="s">
@@ -15184,7 +15210,7 @@
       <c r="C236">
         <v>2026</v>
       </c>
-      <c r="D236" s="1">
+      <c r="D236" s="2">
         <v>45889</v>
       </c>
       <c r="F236" t="s">
@@ -15321,7 +15347,7 @@
       <c r="C240">
         <v>2026</v>
       </c>
-      <c r="D240" s="1">
+      <c r="D240" s="2">
         <v>45859</v>
       </c>
       <c r="F240" t="s">
@@ -15362,7 +15388,7 @@
       <c r="C241">
         <v>2026</v>
       </c>
-      <c r="D241" s="1">
+      <c r="D241" s="2">
         <v>45918</v>
       </c>
       <c r="F241" t="s">
@@ -15435,7 +15461,7 @@
       <c r="C243">
         <v>2026</v>
       </c>
-      <c r="D243" s="1">
+      <c r="D243" s="2">
         <v>45874</v>
       </c>
       <c r="F243" t="s">
@@ -15476,7 +15502,7 @@
       <c r="C244">
         <v>2026</v>
       </c>
-      <c r="D244" s="1">
+      <c r="D244" s="2">
         <v>45975</v>
       </c>
       <c r="F244" t="s">
@@ -15514,7 +15540,7 @@
       <c r="C245">
         <v>2026</v>
       </c>
-      <c r="D245" s="1">
+      <c r="D245" s="2">
         <v>45975</v>
       </c>
       <c r="F245" t="s">
@@ -15552,7 +15578,7 @@
       <c r="C246">
         <v>2026</v>
       </c>
-      <c r="D246" s="1">
+      <c r="D246" s="2">
         <v>45975</v>
       </c>
       <c r="F246" t="s">
@@ -15814,7 +15840,7 @@
       <c r="C254">
         <v>2026</v>
       </c>
-      <c r="D254" s="1">
+      <c r="D254" s="2">
         <v>46119</v>
       </c>
       <c r="F254" t="s">
@@ -15919,7 +15945,7 @@
       <c r="C257">
         <v>2026</v>
       </c>
-      <c r="D257" s="1">
+      <c r="D257" s="2">
         <v>45802</v>
       </c>
       <c r="F257" t="s">
@@ -15960,7 +15986,7 @@
       <c r="C258">
         <v>2026</v>
       </c>
-      <c r="D258" s="1">
+      <c r="D258" s="2">
         <v>45804</v>
       </c>
       <c r="F258" t="s">
@@ -16001,7 +16027,7 @@
       <c r="C259">
         <v>2026</v>
       </c>
-      <c r="D259" s="1">
+      <c r="D259" s="2">
         <v>46097</v>
       </c>
       <c r="F259" t="s">
@@ -16042,7 +16068,7 @@
       <c r="C260">
         <v>2026</v>
       </c>
-      <c r="D260" s="1">
+      <c r="D260" s="2">
         <v>45860</v>
       </c>
       <c r="G260" t="s">
@@ -16080,7 +16106,7 @@
       <c r="C261">
         <v>2026</v>
       </c>
-      <c r="D261" s="1">
+      <c r="D261" s="2">
         <v>45889</v>
       </c>
       <c r="F261" t="s">
@@ -16121,7 +16147,7 @@
       <c r="C262">
         <v>2026</v>
       </c>
-      <c r="D262" s="1">
+      <c r="D262" s="2">
         <v>45744</v>
       </c>
       <c r="F262" t="s">
@@ -16162,7 +16188,7 @@
       <c r="C263">
         <v>2026</v>
       </c>
-      <c r="D263" s="1">
+      <c r="D263" s="2">
         <v>45744</v>
       </c>
       <c r="F263" t="s">
@@ -16203,7 +16229,7 @@
       <c r="C264">
         <v>2026</v>
       </c>
-      <c r="D264" s="1">
+      <c r="D264" s="2">
         <v>46408</v>
       </c>
       <c r="F264" t="s">
@@ -16247,7 +16273,7 @@
       <c r="C265">
         <v>2026</v>
       </c>
-      <c r="D265" s="1">
+      <c r="D265" s="2">
         <v>45898</v>
       </c>
       <c r="F265" t="s">
@@ -16288,7 +16314,7 @@
       <c r="C266">
         <v>2026</v>
       </c>
-      <c r="D266" s="1">
+      <c r="D266" s="2">
         <v>45971</v>
       </c>
       <c r="F266" t="s">
@@ -16329,7 +16355,7 @@
       <c r="C267">
         <v>2026</v>
       </c>
-      <c r="D267" s="1">
+      <c r="D267" s="2">
         <v>45744</v>
       </c>
       <c r="F267" t="s">
@@ -16370,7 +16396,7 @@
       <c r="C268">
         <v>2026</v>
       </c>
-      <c r="D268" s="1">
+      <c r="D268" s="2">
         <v>46092</v>
       </c>
       <c r="F268" t="s">
@@ -16411,7 +16437,7 @@
       <c r="C269">
         <v>2026</v>
       </c>
-      <c r="D269" s="1">
+      <c r="D269" s="2">
         <v>46204</v>
       </c>
       <c r="F269" t="s">
@@ -16455,7 +16481,7 @@
       <c r="C270">
         <v>2026</v>
       </c>
-      <c r="D270" s="1">
+      <c r="D270" s="2">
         <v>46185</v>
       </c>
       <c r="H270" t="s">
@@ -16490,7 +16516,7 @@
       <c r="C271">
         <v>2026</v>
       </c>
-      <c r="D271" s="1">
+      <c r="D271" s="2">
         <v>45890</v>
       </c>
       <c r="G271" t="s">
@@ -16528,7 +16554,7 @@
       <c r="C272">
         <v>2026</v>
       </c>
-      <c r="D272" s="1">
+      <c r="D272" s="2">
         <v>46185</v>
       </c>
       <c r="H272" t="s">
@@ -16563,7 +16589,7 @@
       <c r="C273">
         <v>2026</v>
       </c>
-      <c r="D273" s="1">
+      <c r="D273" s="2">
         <v>46175</v>
       </c>
       <c r="F273" t="s">
@@ -16604,7 +16630,7 @@
       <c r="C274">
         <v>2026</v>
       </c>
-      <c r="D274" s="1">
+      <c r="D274" s="2">
         <v>45890</v>
       </c>
       <c r="G274" t="s">
@@ -16642,7 +16668,7 @@
       <c r="C275">
         <v>2026</v>
       </c>
-      <c r="D275" s="1">
+      <c r="D275" s="2">
         <v>46175</v>
       </c>
       <c r="F275" t="s">
@@ -16683,7 +16709,7 @@
       <c r="C276">
         <v>2026</v>
       </c>
-      <c r="D276" s="1">
+      <c r="D276" s="2">
         <v>46185</v>
       </c>
       <c r="G276" t="s">
@@ -16721,7 +16747,7 @@
       <c r="C277">
         <v>2026</v>
       </c>
-      <c r="D277" s="1">
+      <c r="D277" s="2">
         <v>45890</v>
       </c>
       <c r="G277" t="s">
@@ -16759,7 +16785,7 @@
       <c r="C278">
         <v>2026</v>
       </c>
-      <c r="D278" s="1">
+      <c r="D278" s="2">
         <v>45890</v>
       </c>
       <c r="G278" t="s">
@@ -16797,7 +16823,7 @@
       <c r="C279">
         <v>2026</v>
       </c>
-      <c r="D279" s="1">
+      <c r="D279" s="2">
         <v>45890</v>
       </c>
       <c r="G279" t="s">
@@ -16835,7 +16861,7 @@
       <c r="C280">
         <v>2026</v>
       </c>
-      <c r="D280" s="1">
+      <c r="D280" s="2">
         <v>46175</v>
       </c>
       <c r="F280" t="s">
@@ -16876,7 +16902,7 @@
       <c r="C281">
         <v>2026</v>
       </c>
-      <c r="D281" s="1">
+      <c r="D281" s="2">
         <v>45890</v>
       </c>
       <c r="G281" t="s">
@@ -16914,7 +16940,7 @@
       <c r="C282">
         <v>2026</v>
       </c>
-      <c r="D282" s="1">
+      <c r="D282" s="2">
         <v>46119</v>
       </c>
       <c r="F282" t="s">
@@ -16955,7 +16981,7 @@
       <c r="C283">
         <v>2026</v>
       </c>
-      <c r="D283" s="1">
+      <c r="D283" s="2">
         <v>46119</v>
       </c>
       <c r="F283" t="s">
@@ -16996,7 +17022,7 @@
       <c r="C284">
         <v>2026</v>
       </c>
-      <c r="D284" s="1">
+      <c r="D284" s="2">
         <v>46119</v>
       </c>
       <c r="F284" t="s">
@@ -17101,7 +17127,7 @@
       <c r="C287">
         <v>2026</v>
       </c>
-      <c r="D287" s="1">
+      <c r="D287" s="2">
         <v>45856</v>
       </c>
       <c r="F287" t="s">
@@ -17142,7 +17168,7 @@
       <c r="C288">
         <v>2026</v>
       </c>
-      <c r="D288" s="1">
+      <c r="D288" s="2">
         <v>45769</v>
       </c>
       <c r="F288" t="s">
@@ -17183,7 +17209,7 @@
       <c r="C289">
         <v>2026</v>
       </c>
-      <c r="D289" s="1">
+      <c r="D289" s="2">
         <v>45769</v>
       </c>
       <c r="F289" t="s">
@@ -17224,7 +17250,7 @@
       <c r="C290">
         <v>2026</v>
       </c>
-      <c r="D290" s="1">
+      <c r="D290" s="2">
         <v>45769</v>
       </c>
       <c r="F290" t="s">
@@ -17265,7 +17291,7 @@
       <c r="C291">
         <v>2026</v>
       </c>
-      <c r="D291" s="1">
+      <c r="D291" s="2">
         <v>45769</v>
       </c>
       <c r="F291" t="s">
@@ -17306,7 +17332,7 @@
       <c r="C292">
         <v>2026</v>
       </c>
-      <c r="D292" s="1">
+      <c r="D292" s="2">
         <v>45769</v>
       </c>
       <c r="F292" t="s">
@@ -17347,7 +17373,7 @@
       <c r="C293">
         <v>2026</v>
       </c>
-      <c r="D293" s="1">
+      <c r="D293" s="2">
         <v>45769</v>
       </c>
       <c r="F293" t="s">
@@ -17388,7 +17414,7 @@
       <c r="C294">
         <v>2026</v>
       </c>
-      <c r="D294" s="1">
+      <c r="D294" s="2">
         <v>45769</v>
       </c>
       <c r="F294" t="s">
@@ -17429,7 +17455,7 @@
       <c r="C295">
         <v>2026</v>
       </c>
-      <c r="D295" s="1">
+      <c r="D295" s="2">
         <v>46147</v>
       </c>
       <c r="H295" t="s">
@@ -17464,7 +17490,7 @@
       <c r="C296">
         <v>2026</v>
       </c>
-      <c r="D296" s="1">
+      <c r="D296" s="2">
         <v>46147</v>
       </c>
       <c r="H296" t="s">
@@ -17499,7 +17525,7 @@
       <c r="C297">
         <v>2026</v>
       </c>
-      <c r="D297" s="1">
+      <c r="D297" s="2">
         <v>46147</v>
       </c>
       <c r="H297" t="s">
@@ -17534,7 +17560,7 @@
       <c r="C298">
         <v>2026</v>
       </c>
-      <c r="D298" s="1">
+      <c r="D298" s="2">
         <v>45814</v>
       </c>
       <c r="F298" t="s">
@@ -17607,7 +17633,7 @@
       <c r="C300">
         <v>2026</v>
       </c>
-      <c r="D300" s="1">
+      <c r="D300" s="2">
         <v>45860</v>
       </c>
       <c r="F300" t="s">
@@ -17648,7 +17674,7 @@
       <c r="C301">
         <v>2026</v>
       </c>
-      <c r="D301" s="1">
+      <c r="D301" s="2">
         <v>45971</v>
       </c>
       <c r="F301" t="s">
@@ -17689,7 +17715,7 @@
       <c r="C302">
         <v>2026</v>
       </c>
-      <c r="D302" s="1">
+      <c r="D302" s="2">
         <v>45863</v>
       </c>
       <c r="F302" t="s">
@@ -17730,7 +17756,7 @@
       <c r="C303">
         <v>2026</v>
       </c>
-      <c r="D303" s="1">
+      <c r="D303" s="2">
         <v>45905</v>
       </c>
       <c r="G303" t="s">
@@ -17768,7 +17794,7 @@
       <c r="C304">
         <v>2026</v>
       </c>
-      <c r="D304" s="1">
+      <c r="D304" s="2">
         <v>45971</v>
       </c>
       <c r="F304" t="s">
@@ -17809,7 +17835,7 @@
       <c r="C305">
         <v>2026</v>
       </c>
-      <c r="D305" s="1">
+      <c r="D305" s="2">
         <v>45971</v>
       </c>
       <c r="F305" t="s">
@@ -17850,7 +17876,7 @@
       <c r="C306">
         <v>2026</v>
       </c>
-      <c r="D306" s="1">
+      <c r="D306" s="2">
         <v>45744</v>
       </c>
       <c r="F306" t="s">
@@ -17891,7 +17917,7 @@
       <c r="C307">
         <v>2026</v>
       </c>
-      <c r="D307" s="1">
+      <c r="D307" s="2">
         <v>45814</v>
       </c>
       <c r="F307" t="s">
@@ -17932,7 +17958,7 @@
       <c r="C308">
         <v>2026</v>
       </c>
-      <c r="D308" s="1">
+      <c r="D308" s="2">
         <v>45807</v>
       </c>
       <c r="F308" t="s">
@@ -17973,7 +17999,7 @@
       <c r="C309">
         <v>2026</v>
       </c>
-      <c r="D309" s="1">
+      <c r="D309" s="2">
         <v>45802</v>
       </c>
       <c r="F309" t="s">
@@ -18014,7 +18040,7 @@
       <c r="C310">
         <v>2026</v>
       </c>
-      <c r="D310" s="1">
+      <c r="D310" s="2">
         <v>45802</v>
       </c>
       <c r="F310" t="s">
@@ -18055,7 +18081,7 @@
       <c r="C311">
         <v>2026</v>
       </c>
-      <c r="D311" s="1">
+      <c r="D311" s="2">
         <v>45802</v>
       </c>
       <c r="F311" t="s">
@@ -18096,7 +18122,7 @@
       <c r="C312">
         <v>2026</v>
       </c>
-      <c r="D312" s="1">
+      <c r="D312" s="2">
         <v>45897</v>
       </c>
       <c r="H312" t="s">
@@ -18131,7 +18157,7 @@
       <c r="C313">
         <v>2026</v>
       </c>
-      <c r="D313" s="1">
+      <c r="D313" s="2">
         <v>45802</v>
       </c>
       <c r="F313" t="s">
@@ -18172,7 +18198,7 @@
       <c r="C314">
         <v>2026</v>
       </c>
-      <c r="D314" s="1">
+      <c r="D314" s="2">
         <v>45802</v>
       </c>
       <c r="F314" t="s">
@@ -18213,7 +18239,7 @@
       <c r="C315">
         <v>2026</v>
       </c>
-      <c r="D315" s="1">
+      <c r="D315" s="2">
         <v>45876</v>
       </c>
       <c r="F315" t="s">
@@ -18254,7 +18280,7 @@
       <c r="C316">
         <v>2026</v>
       </c>
-      <c r="D316" s="1">
+      <c r="D316" s="2">
         <v>45889</v>
       </c>
       <c r="F316" t="s">
@@ -18295,7 +18321,7 @@
       <c r="C317">
         <v>2026</v>
       </c>
-      <c r="D317" s="1">
+      <c r="D317" s="2">
         <v>45876</v>
       </c>
       <c r="F317" t="s">
@@ -18336,7 +18362,7 @@
       <c r="C318">
         <v>2026</v>
       </c>
-      <c r="D318" s="1">
+      <c r="D318" s="2">
         <v>45926</v>
       </c>
       <c r="F318" t="s">
@@ -18377,7 +18403,7 @@
       <c r="C319">
         <v>2026</v>
       </c>
-      <c r="D319" s="1">
+      <c r="D319" s="2">
         <v>45909</v>
       </c>
       <c r="F319" t="s">
@@ -18418,7 +18444,7 @@
       <c r="C320">
         <v>2026</v>
       </c>
-      <c r="D320" s="1">
+      <c r="D320" s="2">
         <v>46119</v>
       </c>
       <c r="F320" t="s">
@@ -18523,7 +18549,7 @@
       <c r="C323">
         <v>2026</v>
       </c>
-      <c r="D323" s="1">
+      <c r="D323" s="2">
         <v>46119</v>
       </c>
       <c r="F323" t="s">
@@ -18564,7 +18590,7 @@
       <c r="C324">
         <v>2026</v>
       </c>
-      <c r="D324" s="1">
+      <c r="D324" s="2">
         <v>46119</v>
       </c>
       <c r="F324" t="s">
@@ -18701,7 +18727,7 @@
       <c r="C328">
         <v>2026</v>
       </c>
-      <c r="D328" s="1">
+      <c r="D328" s="2">
         <v>46086</v>
       </c>
       <c r="G328" t="s">
@@ -18771,7 +18797,7 @@
       <c r="C330">
         <v>2026</v>
       </c>
-      <c r="D330" s="1">
+      <c r="D330" s="2">
         <v>45965</v>
       </c>
       <c r="F330" t="s">
@@ -18812,7 +18838,7 @@
       <c r="C331">
         <v>2026</v>
       </c>
-      <c r="D331" s="1">
+      <c r="D331" s="2">
         <v>46064</v>
       </c>
       <c r="H331" t="s">
@@ -18844,7 +18870,7 @@
       <c r="C332">
         <v>2026</v>
       </c>
-      <c r="D332" s="1">
+      <c r="D332" s="2">
         <v>46049</v>
       </c>
       <c r="F332" t="s">
@@ -18885,7 +18911,7 @@
       <c r="C333">
         <v>2026</v>
       </c>
-      <c r="D333" s="1">
+      <c r="D333" s="2">
         <v>45996</v>
       </c>
       <c r="G333" t="s">
@@ -18923,7 +18949,7 @@
       <c r="C334">
         <v>2026</v>
       </c>
-      <c r="D334" s="1">
+      <c r="D334" s="2">
         <v>45996</v>
       </c>
       <c r="G334" t="s">
@@ -18961,7 +18987,7 @@
       <c r="C335">
         <v>2026</v>
       </c>
-      <c r="D335" s="1">
+      <c r="D335" s="2">
         <v>45989</v>
       </c>
       <c r="G335" t="s">
@@ -18999,7 +19025,7 @@
       <c r="C336">
         <v>2026</v>
       </c>
-      <c r="D336" s="1">
+      <c r="D336" s="2">
         <v>46156</v>
       </c>
       <c r="H336" t="s">
@@ -19034,7 +19060,7 @@
       <c r="C337">
         <v>2026</v>
       </c>
-      <c r="D337" s="1">
+      <c r="D337" s="2">
         <v>45996</v>
       </c>
       <c r="G337" t="s">
@@ -19072,7 +19098,7 @@
       <c r="C338">
         <v>2026</v>
       </c>
-      <c r="D338" s="1">
+      <c r="D338" s="2">
         <v>45989</v>
       </c>
       <c r="G338" t="s">
@@ -19110,7 +19136,7 @@
       <c r="C339">
         <v>2026</v>
       </c>
-      <c r="D339" s="1">
+      <c r="D339" s="2">
         <v>46002</v>
       </c>
       <c r="G339" t="s">
@@ -19148,7 +19174,7 @@
       <c r="C340">
         <v>2026</v>
       </c>
-      <c r="D340" s="1">
+      <c r="D340" s="2">
         <v>46002</v>
       </c>
       <c r="G340" t="s">
@@ -19186,7 +19212,7 @@
       <c r="C341">
         <v>2026</v>
       </c>
-      <c r="D341" s="1">
+      <c r="D341" s="2">
         <v>45996</v>
       </c>
       <c r="G341" t="s">
@@ -19224,7 +19250,7 @@
       <c r="C342">
         <v>2026</v>
       </c>
-      <c r="D342" s="1">
+      <c r="D342" s="2">
         <v>46002</v>
       </c>
       <c r="G342" t="s">
@@ -19262,7 +19288,7 @@
       <c r="C343">
         <v>2026</v>
       </c>
-      <c r="D343" s="1">
+      <c r="D343" s="2">
         <v>46031</v>
       </c>
       <c r="G343" t="s">
@@ -19300,7 +19326,7 @@
       <c r="C344">
         <v>2026</v>
       </c>
-      <c r="D344" s="1">
+      <c r="D344" s="2">
         <v>46153</v>
       </c>
       <c r="F344" t="s">
@@ -19341,7 +19367,7 @@
       <c r="C345">
         <v>2026</v>
       </c>
-      <c r="D345" s="1">
+      <c r="D345" s="2">
         <v>46135</v>
       </c>
       <c r="F345" t="s">
@@ -19446,7 +19472,7 @@
       <c r="C348">
         <v>2026</v>
       </c>
-      <c r="D348" s="1">
+      <c r="D348" s="2">
         <v>46230</v>
       </c>
       <c r="F348" t="s">
@@ -19551,7 +19577,7 @@
       <c r="C351">
         <v>2026</v>
       </c>
-      <c r="D351" s="1">
+      <c r="D351" s="2">
         <v>45996</v>
       </c>
       <c r="G351" t="s">
@@ -19589,7 +19615,7 @@
       <c r="C352">
         <v>2026</v>
       </c>
-      <c r="D352" s="1">
+      <c r="D352" s="2">
         <v>45996</v>
       </c>
       <c r="G352" t="s">
@@ -19659,7 +19685,7 @@
       <c r="C354">
         <v>2026</v>
       </c>
-      <c r="D354" s="1">
+      <c r="D354" s="2">
         <v>46164</v>
       </c>
       <c r="H354" t="s">
@@ -19694,7 +19720,7 @@
       <c r="C355">
         <v>2026</v>
       </c>
-      <c r="D355" s="1">
+      <c r="D355" s="2">
         <v>46020</v>
       </c>
       <c r="G355" t="s">
@@ -19732,7 +19758,7 @@
       <c r="C356">
         <v>2026</v>
       </c>
-      <c r="D356" s="1">
+      <c r="D356" s="2">
         <v>46225</v>
       </c>
       <c r="F356" t="s">
@@ -19776,7 +19802,7 @@
       <c r="C357">
         <v>2026</v>
       </c>
-      <c r="D357" s="1">
+      <c r="D357" s="2">
         <v>46176</v>
       </c>
       <c r="H357" t="s">
@@ -19811,7 +19837,7 @@
       <c r="C358">
         <v>2026</v>
       </c>
-      <c r="D358" s="1">
+      <c r="D358" s="2">
         <v>46086</v>
       </c>
       <c r="G358" t="s">
@@ -19849,7 +19875,7 @@
       <c r="C359">
         <v>2026</v>
       </c>
-      <c r="D359" s="1">
+      <c r="D359" s="2">
         <v>46052</v>
       </c>
       <c r="G359" t="s">
@@ -19925,7 +19951,7 @@
       <c r="C361">
         <v>2026</v>
       </c>
-      <c r="D361" s="1">
+      <c r="D361" s="2">
         <v>46010</v>
       </c>
       <c r="G361" t="s">
@@ -19963,7 +19989,7 @@
       <c r="C362">
         <v>2026</v>
       </c>
-      <c r="D362" s="1">
+      <c r="D362" s="2">
         <v>46010</v>
       </c>
       <c r="G362" t="s">
@@ -20033,7 +20059,7 @@
       <c r="C364">
         <v>2026</v>
       </c>
-      <c r="D364" s="1">
+      <c r="D364" s="2">
         <v>46079</v>
       </c>
       <c r="F364" t="s">
@@ -20074,7 +20100,7 @@
       <c r="C365">
         <v>2026</v>
       </c>
-      <c r="D365" s="1">
+      <c r="D365" s="2">
         <v>46010</v>
       </c>
       <c r="G365" t="s">
@@ -20112,7 +20138,7 @@
       <c r="C366">
         <v>2026</v>
       </c>
-      <c r="D366" s="1">
+      <c r="D366" s="2">
         <v>46010</v>
       </c>
       <c r="G366" t="s">
@@ -20150,7 +20176,7 @@
       <c r="C367">
         <v>2026</v>
       </c>
-      <c r="D367" s="1">
+      <c r="D367" s="2">
         <v>46230</v>
       </c>
       <c r="F367" t="s">
@@ -20194,7 +20220,7 @@
       <c r="C368">
         <v>2026</v>
       </c>
-      <c r="D368" s="1">
+      <c r="D368" s="2">
         <v>46063</v>
       </c>
       <c r="G368" t="s">
@@ -20232,7 +20258,7 @@
       <c r="C369">
         <v>2026</v>
       </c>
-      <c r="D369" s="1">
+      <c r="D369" s="2">
         <v>46063</v>
       </c>
       <c r="F369" t="s">
@@ -20273,7 +20299,7 @@
       <c r="C370">
         <v>2026</v>
       </c>
-      <c r="D370" s="1">
+      <c r="D370" s="2">
         <v>46063</v>
       </c>
       <c r="F370" t="s">
@@ -20314,7 +20340,7 @@
       <c r="C371">
         <v>2026</v>
       </c>
-      <c r="D371" s="1">
+      <c r="D371" s="2">
         <v>46063</v>
       </c>
       <c r="F371" t="s">
@@ -20355,7 +20381,7 @@
       <c r="C372">
         <v>2026</v>
       </c>
-      <c r="D372" s="1">
+      <c r="D372" s="2">
         <v>46063</v>
       </c>
       <c r="G372" t="s">
@@ -20521,7 +20547,7 @@
       <c r="C377">
         <v>2026</v>
       </c>
-      <c r="D377" s="1">
+      <c r="D377" s="2">
         <v>46114</v>
       </c>
       <c r="F377" t="s">
@@ -20562,7 +20588,7 @@
       <c r="C378">
         <v>2026</v>
       </c>
-      <c r="D378" s="1">
+      <c r="D378" s="2">
         <v>46191</v>
       </c>
       <c r="F378" t="s">
@@ -20603,7 +20629,7 @@
       <c r="C379">
         <v>2026</v>
       </c>
-      <c r="D379" s="1">
+      <c r="D379" s="2">
         <v>46230</v>
       </c>
       <c r="F379" t="s">
@@ -20644,7 +20670,7 @@
       <c r="C380">
         <v>2026</v>
       </c>
-      <c r="D380" s="1">
+      <c r="D380" s="2">
         <v>46230</v>
       </c>
       <c r="F380" t="s">
@@ -20685,7 +20711,7 @@
       <c r="C381">
         <v>2026</v>
       </c>
-      <c r="D381" s="1">
+      <c r="D381" s="2">
         <v>46230</v>
       </c>
       <c r="F381" t="s">
@@ -20726,7 +20752,7 @@
       <c r="C382">
         <v>2026</v>
       </c>
-      <c r="D382" s="1">
+      <c r="D382" s="2">
         <v>46230</v>
       </c>
       <c r="F382" t="s">
@@ -20767,7 +20793,7 @@
       <c r="C383">
         <v>2026</v>
       </c>
-      <c r="D383" s="1">
+      <c r="D383" s="2">
         <v>46230</v>
       </c>
       <c r="F383" t="s">
@@ -20808,7 +20834,7 @@
       <c r="C384">
         <v>2026</v>
       </c>
-      <c r="D384" s="1">
+      <c r="D384" s="2">
         <v>46230</v>
       </c>
       <c r="F384" t="s">
@@ -20849,7 +20875,7 @@
       <c r="C385">
         <v>2026</v>
       </c>
-      <c r="D385" s="1">
+      <c r="D385" s="2">
         <v>46230</v>
       </c>
       <c r="F385" t="s">
@@ -20922,7 +20948,7 @@
       <c r="C387">
         <v>2026</v>
       </c>
-      <c r="D387" s="1">
+      <c r="D387" s="2">
         <v>45996</v>
       </c>
       <c r="G387" t="s">
@@ -21152,7 +21178,7 @@
       <c r="C394">
         <v>2026</v>
       </c>
-      <c r="D394" s="1">
+      <c r="D394" s="2">
         <v>46052</v>
       </c>
       <c r="F394" t="s">
@@ -21193,7 +21219,7 @@
       <c r="C395">
         <v>2026</v>
       </c>
-      <c r="D395" s="1">
+      <c r="D395" s="2">
         <v>46057</v>
       </c>
       <c r="F395" t="s">
@@ -21234,7 +21260,7 @@
       <c r="C396">
         <v>2026</v>
       </c>
-      <c r="D396" s="1">
+      <c r="D396" s="2">
         <v>46112</v>
       </c>
       <c r="F396" t="s">
@@ -21307,7 +21333,7 @@
       <c r="C398">
         <v>2026</v>
       </c>
-      <c r="D398" s="1">
+      <c r="D398" s="2">
         <v>46063</v>
       </c>
       <c r="G398" t="s">
@@ -21345,7 +21371,7 @@
       <c r="C399">
         <v>2026</v>
       </c>
-      <c r="D399" s="1">
+      <c r="D399" s="2">
         <v>46048</v>
       </c>
       <c r="G399" t="s">
@@ -21383,7 +21409,7 @@
       <c r="C400">
         <v>2026</v>
       </c>
-      <c r="D400" s="1">
+      <c r="D400" s="2">
         <v>46063</v>
       </c>
       <c r="H400" t="s">
@@ -21450,7 +21476,7 @@
       <c r="C402">
         <v>2026</v>
       </c>
-      <c r="D402" s="1">
+      <c r="D402" s="2">
         <v>46119</v>
       </c>
       <c r="F402" t="s">
@@ -21523,7 +21549,7 @@
       <c r="C404">
         <v>2026</v>
       </c>
-      <c r="D404" s="1">
+      <c r="D404" s="2">
         <v>46119</v>
       </c>
       <c r="F404" t="s">
@@ -21564,7 +21590,7 @@
       <c r="C405">
         <v>2026</v>
       </c>
-      <c r="D405" s="1">
+      <c r="D405" s="2">
         <v>46113</v>
       </c>
       <c r="F405" t="s">
@@ -21605,7 +21631,7 @@
       <c r="C406">
         <v>2026</v>
       </c>
-      <c r="D406" s="1">
+      <c r="D406" s="2">
         <v>46104</v>
       </c>
       <c r="F406" t="s">
@@ -21646,7 +21672,7 @@
       <c r="C407">
         <v>2026</v>
       </c>
-      <c r="D407" s="1">
+      <c r="D407" s="2">
         <v>46135</v>
       </c>
       <c r="H407" t="s">
@@ -21713,7 +21739,7 @@
       <c r="C409">
         <v>2026</v>
       </c>
-      <c r="D409" s="1">
+      <c r="D409" s="2">
         <v>46230</v>
       </c>
       <c r="F409" t="s">
@@ -21754,7 +21780,7 @@
       <c r="C410">
         <v>2026</v>
       </c>
-      <c r="D410" s="1">
+      <c r="D410" s="2">
         <v>46086</v>
       </c>
       <c r="G410" t="s">
@@ -21792,7 +21818,7 @@
       <c r="C411">
         <v>2026</v>
       </c>
-      <c r="D411" s="1">
+      <c r="D411" s="2">
         <v>46086</v>
       </c>
       <c r="G411" t="s">
@@ -21830,7 +21856,7 @@
       <c r="C412">
         <v>2026</v>
       </c>
-      <c r="D412" s="1">
+      <c r="D412" s="2">
         <v>46086</v>
       </c>
       <c r="H412" t="s">
@@ -21865,7 +21891,7 @@
       <c r="C413">
         <v>2026</v>
       </c>
-      <c r="D413" s="1">
+      <c r="D413" s="2">
         <v>46230</v>
       </c>
       <c r="F413" t="s">
@@ -22002,7 +22028,7 @@
       <c r="C417">
         <v>2026</v>
       </c>
-      <c r="D417" s="1">
+      <c r="D417" s="2">
         <v>46176</v>
       </c>
       <c r="H417" t="s">
@@ -22037,7 +22063,7 @@
       <c r="C418">
         <v>2026</v>
       </c>
-      <c r="D418" s="1">
+      <c r="D418" s="2">
         <v>46147</v>
       </c>
       <c r="H418" t="s">
@@ -22072,7 +22098,7 @@
       <c r="C419">
         <v>2026</v>
       </c>
-      <c r="D419" s="1">
+      <c r="D419" s="2">
         <v>46135</v>
       </c>
       <c r="H419" t="s">
@@ -22139,7 +22165,7 @@
       <c r="C421">
         <v>2026</v>
       </c>
-      <c r="D421" s="1">
+      <c r="D421" s="2">
         <v>46227</v>
       </c>
       <c r="G421" t="s">
@@ -22180,7 +22206,7 @@
       <c r="C422">
         <v>2026</v>
       </c>
-      <c r="D422" s="1">
+      <c r="D422" s="2">
         <v>46230</v>
       </c>
       <c r="F422" t="s">
@@ -22221,7 +22247,7 @@
       <c r="C423">
         <v>2026</v>
       </c>
-      <c r="D423" s="1">
+      <c r="D423" s="2">
         <v>46083</v>
       </c>
       <c r="F423" t="s">
@@ -22262,7 +22288,7 @@
       <c r="C424">
         <v>2026</v>
       </c>
-      <c r="D424" s="1">
+      <c r="D424" s="2">
         <v>46083</v>
       </c>
       <c r="G424" t="s">
@@ -22300,7 +22326,7 @@
       <c r="C425">
         <v>2026</v>
       </c>
-      <c r="D425" s="1">
+      <c r="D425" s="2">
         <v>46083</v>
       </c>
       <c r="F425" t="s">
@@ -22341,7 +22367,7 @@
       <c r="C426">
         <v>2026</v>
       </c>
-      <c r="D426" s="1">
+      <c r="D426" s="2">
         <v>46127</v>
       </c>
       <c r="F426" t="s">
@@ -22382,7 +22408,7 @@
       <c r="C427">
         <v>2026</v>
       </c>
-      <c r="D427" s="1">
+      <c r="D427" s="2">
         <v>46100</v>
       </c>
       <c r="F427" t="s">
@@ -22580,7 +22606,7 @@
       <c r="C433">
         <v>2026</v>
       </c>
-      <c r="D433" s="1">
+      <c r="D433" s="2">
         <v>46230</v>
       </c>
       <c r="F433" t="s">
@@ -22621,7 +22647,7 @@
       <c r="C434">
         <v>2026</v>
       </c>
-      <c r="D434" s="1">
+      <c r="D434" s="2">
         <v>46079</v>
       </c>
       <c r="H434" t="s">
@@ -22752,7 +22778,7 @@
       <c r="C438">
         <v>2026</v>
       </c>
-      <c r="D438" s="1">
+      <c r="D438" s="2">
         <v>46176</v>
       </c>
       <c r="F438" t="s">
@@ -22793,7 +22819,7 @@
       <c r="C439">
         <v>2026</v>
       </c>
-      <c r="D439" s="1">
+      <c r="D439" s="2">
         <v>46176</v>
       </c>
       <c r="F439" t="s">
@@ -22834,7 +22860,7 @@
       <c r="C440">
         <v>2026</v>
       </c>
-      <c r="D440" s="1">
+      <c r="D440" s="2">
         <v>46155</v>
       </c>
       <c r="F440" t="s">
@@ -22875,7 +22901,7 @@
       <c r="C441">
         <v>2026</v>
       </c>
-      <c r="D441" s="1">
+      <c r="D441" s="2">
         <v>46155</v>
       </c>
       <c r="G441" t="s">
@@ -22913,7 +22939,7 @@
       <c r="C442">
         <v>2026</v>
       </c>
-      <c r="D442" s="1">
+      <c r="D442" s="2">
         <v>46129</v>
       </c>
       <c r="F442" t="s">
@@ -22954,7 +22980,7 @@
       <c r="C443">
         <v>2026</v>
       </c>
-      <c r="D443" s="1">
+      <c r="D443" s="2">
         <v>46119</v>
       </c>
       <c r="F443" t="s">
@@ -22995,7 +23021,7 @@
       <c r="C444">
         <v>2026</v>
       </c>
-      <c r="D444" s="1">
+      <c r="D444" s="2">
         <v>46135</v>
       </c>
       <c r="H444" t="s">
@@ -23030,7 +23056,7 @@
       <c r="C445">
         <v>2026</v>
       </c>
-      <c r="D445" s="1">
+      <c r="D445" s="2">
         <v>46127</v>
       </c>
       <c r="H445" t="s">
@@ -23065,7 +23091,7 @@
       <c r="C446">
         <v>2026</v>
       </c>
-      <c r="D446" s="1">
+      <c r="D446" s="2">
         <v>46127</v>
       </c>
       <c r="H446" t="s">
@@ -23132,7 +23158,7 @@
       <c r="C448">
         <v>2026</v>
       </c>
-      <c r="D448" s="1">
+      <c r="D448" s="2">
         <v>46175</v>
       </c>
       <c r="F448" t="s">
@@ -23173,7 +23199,7 @@
       <c r="C449">
         <v>2026</v>
       </c>
-      <c r="D449" s="1">
+      <c r="D449" s="2">
         <v>46139</v>
       </c>
       <c r="H449" t="s">
@@ -23208,7 +23234,7 @@
       <c r="C450">
         <v>2026</v>
       </c>
-      <c r="D450" s="1">
+      <c r="D450" s="2">
         <v>46155</v>
       </c>
       <c r="H450" t="s">
@@ -23243,7 +23269,7 @@
       <c r="C451">
         <v>2026</v>
       </c>
-      <c r="D451" s="1">
+      <c r="D451" s="2">
         <v>46175</v>
       </c>
       <c r="F451" t="s">
@@ -23316,7 +23342,7 @@
       <c r="C453">
         <v>2026</v>
       </c>
-      <c r="D453" s="1">
+      <c r="D453" s="2">
         <v>46156</v>
       </c>
       <c r="F453" t="s">
@@ -23357,7 +23383,7 @@
       <c r="C454">
         <v>2026</v>
       </c>
-      <c r="D454" s="1">
+      <c r="D454" s="2">
         <v>46157</v>
       </c>
       <c r="G454" t="s">
@@ -23395,7 +23421,7 @@
       <c r="C455">
         <v>2026</v>
       </c>
-      <c r="D455" s="1">
+      <c r="D455" s="2">
         <v>46183</v>
       </c>
       <c r="H455" t="s">
@@ -23430,7 +23456,7 @@
       <c r="C456">
         <v>2026</v>
       </c>
-      <c r="D456" s="1">
+      <c r="D456" s="2">
         <v>46183</v>
       </c>
       <c r="H456" t="s">
@@ -23529,7 +23555,7 @@
       <c r="C459">
         <v>2026</v>
       </c>
-      <c r="D459" s="1">
+      <c r="D459" s="2">
         <v>46230</v>
       </c>
       <c r="F459" t="s">
@@ -23573,7 +23599,7 @@
       <c r="C460">
         <v>2026</v>
       </c>
-      <c r="D460" s="1">
+      <c r="D460" s="2">
         <v>46185</v>
       </c>
       <c r="H460" t="s">
@@ -23640,7 +23666,7 @@
       <c r="C462">
         <v>2026</v>
       </c>
-      <c r="D462" s="1">
+      <c r="D462" s="2">
         <v>46185</v>
       </c>
       <c r="H462" t="s">
@@ -23739,7 +23765,7 @@
       <c r="C465">
         <v>2026</v>
       </c>
-      <c r="D465" s="1">
+      <c r="D465" s="2">
         <v>46175</v>
       </c>
       <c r="F465" t="s">
@@ -23780,7 +23806,7 @@
       <c r="C466">
         <v>2026</v>
       </c>
-      <c r="D466" s="1">
+      <c r="D466" s="2">
         <v>46175</v>
       </c>
       <c r="F466" t="s">
@@ -23821,7 +23847,7 @@
       <c r="C467">
         <v>2026</v>
       </c>
-      <c r="D467" s="1">
+      <c r="D467" s="2">
         <v>46230</v>
       </c>
       <c r="F467" t="s">
@@ -23862,7 +23888,7 @@
       <c r="C468">
         <v>2026</v>
       </c>
-      <c r="D468" s="1">
+      <c r="D468" s="2">
         <v>46175</v>
       </c>
       <c r="G468" t="s">
@@ -23900,7 +23926,7 @@
       <c r="C469">
         <v>2026</v>
       </c>
-      <c r="D469" s="1">
+      <c r="D469" s="2">
         <v>46175</v>
       </c>
       <c r="G469" t="s">
@@ -23938,7 +23964,7 @@
       <c r="C470">
         <v>2026</v>
       </c>
-      <c r="D470" s="1">
+      <c r="D470" s="2">
         <v>46175</v>
       </c>
       <c r="G470" t="s">
@@ -23976,7 +24002,7 @@
       <c r="C471">
         <v>2026</v>
       </c>
-      <c r="D471" s="1">
+      <c r="D471" s="2">
         <v>46230</v>
       </c>
       <c r="F471" t="s">
@@ -24017,7 +24043,7 @@
       <c r="C472">
         <v>2026</v>
       </c>
-      <c r="D472" s="1">
+      <c r="D472" s="2">
         <v>46175</v>
       </c>
       <c r="G472" t="s">
@@ -24055,7 +24081,7 @@
       <c r="C473">
         <v>2026</v>
       </c>
-      <c r="D473" s="1">
+      <c r="D473" s="2">
         <v>46175</v>
       </c>
       <c r="G473" t="s">
@@ -24093,7 +24119,7 @@
       <c r="C474">
         <v>2026</v>
       </c>
-      <c r="D474" s="1">
+      <c r="D474" s="2">
         <v>46175</v>
       </c>
       <c r="G474" t="s">
@@ -24131,7 +24157,7 @@
       <c r="C475">
         <v>2026</v>
       </c>
-      <c r="D475" s="1">
+      <c r="D475" s="2">
         <v>46230</v>
       </c>
       <c r="F475" t="s">
@@ -24204,7 +24230,7 @@
       <c r="C477">
         <v>2026</v>
       </c>
-      <c r="D477" s="1">
+      <c r="D477" s="2">
         <v>46209</v>
       </c>
       <c r="F477" t="s">
@@ -24376,7 +24402,7 @@
       <c r="C482">
         <v>2026</v>
       </c>
-      <c r="D482" s="1">
+      <c r="D482" s="2">
         <v>46230</v>
       </c>
       <c r="F482" t="s">
@@ -24417,7 +24443,7 @@
       <c r="C483">
         <v>2026</v>
       </c>
-      <c r="D483" s="1">
+      <c r="D483" s="2">
         <v>46230</v>
       </c>
       <c r="F483" t="s">
@@ -24458,7 +24484,7 @@
       <c r="C484">
         <v>2026</v>
       </c>
-      <c r="D484" s="1">
+      <c r="D484" s="2">
         <v>46230</v>
       </c>
       <c r="F484" t="s">
@@ -24723,7 +24749,7 @@
       <c r="C492">
         <v>2026</v>
       </c>
-      <c r="D492" s="1">
+      <c r="D492" s="2">
         <v>46230</v>
       </c>
       <c r="F492" t="s">
@@ -24764,7 +24790,7 @@
       <c r="C493">
         <v>2026</v>
       </c>
-      <c r="D493" s="1">
+      <c r="D493" s="2">
         <v>46230</v>
       </c>
       <c r="F493" t="s">
@@ -24869,7 +24895,7 @@
       <c r="C496">
         <v>2026</v>
       </c>
-      <c r="D496" s="1">
+      <c r="D496" s="2">
         <v>46230</v>
       </c>
       <c r="F496" t="s">
@@ -24913,7 +24939,7 @@
       <c r="C497">
         <v>2026</v>
       </c>
-      <c r="D497" s="1">
+      <c r="D497" s="2">
         <v>46230</v>
       </c>
       <c r="F497" t="s">
@@ -24954,7 +24980,7 @@
       <c r="C498">
         <v>2026</v>
       </c>
-      <c r="D498" s="1">
+      <c r="D498" s="2">
         <v>46157</v>
       </c>
       <c r="G498" t="s">
@@ -24992,7 +25018,7 @@
       <c r="C499">
         <v>2026</v>
       </c>
-      <c r="D499" s="1">
+      <c r="D499" s="2">
         <v>46213</v>
       </c>
       <c r="F499" t="s">
@@ -25068,7 +25094,7 @@
       <c r="C501">
         <v>2026</v>
       </c>
-      <c r="D501" s="1">
+      <c r="D501" s="2">
         <v>46205</v>
       </c>
       <c r="F501" t="s">
@@ -25112,7 +25138,7 @@
       <c r="C502">
         <v>2026</v>
       </c>
-      <c r="D502" s="1">
+      <c r="D502" s="2">
         <v>46176</v>
       </c>
       <c r="F502" t="s">
@@ -25153,7 +25179,7 @@
       <c r="C503">
         <v>2026</v>
       </c>
-      <c r="D503" s="1">
+      <c r="D503" s="2">
         <v>46150</v>
       </c>
       <c r="F503" t="s">
@@ -25258,7 +25284,7 @@
       <c r="C506">
         <v>2026</v>
       </c>
-      <c r="D506" s="1">
+      <c r="D506" s="2">
         <v>46220</v>
       </c>
       <c r="F506" t="s">
@@ -25302,7 +25328,7 @@
       <c r="C507">
         <v>2026</v>
       </c>
-      <c r="D507" s="1">
+      <c r="D507" s="2">
         <v>46224</v>
       </c>
       <c r="F507" t="s">
@@ -25378,7 +25404,7 @@
       <c r="C509">
         <v>2026</v>
       </c>
-      <c r="D509" s="1">
+      <c r="D509" s="2">
         <v>46155</v>
       </c>
       <c r="H509" t="s">
@@ -25413,7 +25439,7 @@
       <c r="C510">
         <v>2026</v>
       </c>
-      <c r="D510" s="1">
+      <c r="D510" s="2">
         <v>46156</v>
       </c>
       <c r="F510" t="s">
@@ -25454,7 +25480,7 @@
       <c r="C511">
         <v>2026</v>
       </c>
-      <c r="D511" s="1">
+      <c r="D511" s="2">
         <v>46185</v>
       </c>
       <c r="H511" t="s">
@@ -25489,7 +25515,7 @@
       <c r="C512">
         <v>2026</v>
       </c>
-      <c r="D512" s="1">
+      <c r="D512" s="2">
         <v>46230</v>
       </c>
       <c r="F512" t="s">
@@ -25530,7 +25556,7 @@
       <c r="C513">
         <v>2026</v>
       </c>
-      <c r="D513" s="1">
+      <c r="D513" s="2">
         <v>46230</v>
       </c>
       <c r="F513" t="s">
@@ -25571,7 +25597,7 @@
       <c r="C514">
         <v>2026</v>
       </c>
-      <c r="D514" s="1">
+      <c r="D514" s="2">
         <v>46230</v>
       </c>
       <c r="F514" t="s">
@@ -25612,7 +25638,7 @@
       <c r="C515">
         <v>2026</v>
       </c>
-      <c r="D515" s="1">
+      <c r="D515" s="2">
         <v>46230</v>
       </c>
       <c r="F515" t="s">
@@ -25653,7 +25679,7 @@
       <c r="C516">
         <v>2026</v>
       </c>
-      <c r="D516" s="1">
+      <c r="D516" s="2">
         <v>46230</v>
       </c>
       <c r="F516" t="s">
@@ -25758,7 +25784,7 @@
       <c r="C519">
         <v>2026</v>
       </c>
-      <c r="D519" s="1">
+      <c r="D519" s="2">
         <v>46147</v>
       </c>
       <c r="G519" t="s">
@@ -25892,7 +25918,7 @@
       <c r="C523">
         <v>2026</v>
       </c>
-      <c r="D523" s="1">
+      <c r="D523" s="2">
         <v>46164</v>
       </c>
       <c r="F523" t="s">
@@ -26029,7 +26055,7 @@
       <c r="C527">
         <v>2026</v>
       </c>
-      <c r="D527" s="1">
+      <c r="D527" s="2">
         <v>46230</v>
       </c>
       <c r="F527" t="s">
@@ -26166,7 +26192,7 @@
       <c r="C531">
         <v>2026</v>
       </c>
-      <c r="D531" s="1">
+      <c r="D531" s="2">
         <v>46171</v>
       </c>
       <c r="F531" t="s">
@@ -26271,7 +26297,7 @@
       <c r="C534">
         <v>2026</v>
       </c>
-      <c r="D534" s="1">
+      <c r="D534" s="2">
         <v>46176</v>
       </c>
       <c r="G534" t="s">
@@ -26309,7 +26335,7 @@
       <c r="C535">
         <v>2026</v>
       </c>
-      <c r="D535" s="1">
+      <c r="D535" s="2">
         <v>46230</v>
       </c>
       <c r="F535" t="s">
@@ -26510,7 +26536,7 @@
       <c r="C541">
         <v>2026</v>
       </c>
-      <c r="D541" s="1">
+      <c r="D541" s="2">
         <v>46211</v>
       </c>
       <c r="F541" t="s">
@@ -26554,7 +26580,7 @@
       <c r="C542">
         <v>2026</v>
       </c>
-      <c r="D542" s="1">
+      <c r="D542" s="2">
         <v>46183</v>
       </c>
       <c r="H542" t="s">
@@ -26589,7 +26615,7 @@
       <c r="C543">
         <v>2026</v>
       </c>
-      <c r="D543" s="1">
+      <c r="D543" s="2">
         <v>46191</v>
       </c>
       <c r="H543" t="s">
@@ -26624,7 +26650,7 @@
       <c r="C544">
         <v>2026</v>
       </c>
-      <c r="D544" s="1">
+      <c r="D544" s="2">
         <v>46191</v>
       </c>
       <c r="G544" t="s">
@@ -26822,7 +26848,7 @@
       <c r="C550">
         <v>2026</v>
       </c>
-      <c r="D550" s="1">
+      <c r="D550" s="2">
         <v>46230</v>
       </c>
       <c r="F550" t="s">
@@ -26927,7 +26953,7 @@
       <c r="C553">
         <v>2026</v>
       </c>
-      <c r="D553" s="1">
+      <c r="D553" s="2">
         <v>46230</v>
       </c>
       <c r="F553" t="s">
@@ -26968,7 +26994,7 @@
       <c r="C554">
         <v>2026</v>
       </c>
-      <c r="D554" s="1">
+      <c r="D554" s="2">
         <v>46191</v>
       </c>
       <c r="G554" t="s">
@@ -27134,7 +27160,7 @@
       <c r="C559">
         <v>2026</v>
       </c>
-      <c r="D559" s="1">
+      <c r="D559" s="2">
         <v>46191</v>
       </c>
       <c r="G559" t="s">
@@ -27332,7 +27358,7 @@
       <c r="C565">
         <v>2026</v>
       </c>
-      <c r="D565" s="1">
+      <c r="D565" s="2">
         <v>46230</v>
       </c>
       <c r="F565" t="s">
@@ -27952,7 +27978,7 @@
       <c r="C584">
         <v>2026</v>
       </c>
-      <c r="D584" s="1">
+      <c r="D584" s="2">
         <v>46226</v>
       </c>
       <c r="F584" t="s">
@@ -28476,7 +28502,7 @@
       <c r="C600">
         <v>2026</v>
       </c>
-      <c r="D600" s="1">
+      <c r="D600" s="2">
         <v>45802</v>
       </c>
       <c r="F600" t="s">
@@ -28520,7 +28546,7 @@
       <c r="C601">
         <v>2026</v>
       </c>
-      <c r="D601" s="1">
+      <c r="D601" s="2">
         <v>45860</v>
       </c>
       <c r="F601" t="s">
@@ -28561,7 +28587,7 @@
       <c r="C602">
         <v>2026</v>
       </c>
-      <c r="D602" s="1">
+      <c r="D602" s="2">
         <v>45860</v>
       </c>
       <c r="H602" t="s">
@@ -28596,7 +28622,7 @@
       <c r="C603">
         <v>2026</v>
       </c>
-      <c r="D603" s="1">
+      <c r="D603" s="2">
         <v>45856</v>
       </c>
       <c r="F603" t="s">
@@ -28637,7 +28663,7 @@
       <c r="C604">
         <v>2026</v>
       </c>
-      <c r="D604" s="1">
+      <c r="D604" s="2">
         <v>46101</v>
       </c>
       <c r="F604" t="s">
@@ -28678,7 +28704,7 @@
       <c r="C605">
         <v>2026</v>
       </c>
-      <c r="D605" s="1">
+      <c r="D605" s="2">
         <v>46101</v>
       </c>
       <c r="F605" t="s">
@@ -28719,7 +28745,7 @@
       <c r="C606">
         <v>2026</v>
       </c>
-      <c r="D606" s="1">
+      <c r="D606" s="2">
         <v>45863</v>
       </c>
       <c r="F606" t="s">
@@ -28760,7 +28786,7 @@
       <c r="C607">
         <v>2026</v>
       </c>
-      <c r="D607" s="1">
+      <c r="D607" s="2">
         <v>45863</v>
       </c>
       <c r="F607" t="s">
@@ -28801,7 +28827,7 @@
       <c r="C608">
         <v>2026</v>
       </c>
-      <c r="D608" s="1">
+      <c r="D608" s="2">
         <v>46086</v>
       </c>
       <c r="F608" t="s">
@@ -28842,7 +28868,7 @@
       <c r="C609">
         <v>2026</v>
       </c>
-      <c r="D609" s="1">
+      <c r="D609" s="2">
         <v>45874</v>
       </c>
       <c r="F609" t="s">
@@ -28883,7 +28909,7 @@
       <c r="C610">
         <v>2026</v>
       </c>
-      <c r="D610" s="1">
+      <c r="D610" s="2">
         <v>45894</v>
       </c>
       <c r="F610" t="s">
@@ -28924,7 +28950,7 @@
       <c r="C611">
         <v>2026</v>
       </c>
-      <c r="D611" s="1">
+      <c r="D611" s="2">
         <v>45894</v>
       </c>
       <c r="F611" t="s">
@@ -28965,7 +28991,7 @@
       <c r="C612">
         <v>2026</v>
       </c>
-      <c r="D612" s="1">
+      <c r="D612" s="2">
         <v>46119</v>
       </c>
       <c r="F612" t="s">
@@ -29006,7 +29032,7 @@
       <c r="C613">
         <v>2026</v>
       </c>
-      <c r="D613" s="1">
+      <c r="D613" s="2">
         <v>45898</v>
       </c>
       <c r="F613" t="s">
@@ -29047,7 +29073,7 @@
       <c r="C614">
         <v>2026</v>
       </c>
-      <c r="D614" s="1">
+      <c r="D614" s="2">
         <v>45971</v>
       </c>
       <c r="F614" t="s">
@@ -29088,7 +29114,7 @@
       <c r="C615">
         <v>2026</v>
       </c>
-      <c r="D615" s="1">
+      <c r="D615" s="2">
         <v>46119</v>
       </c>
       <c r="F615" t="s">
@@ -29129,7 +29155,7 @@
       <c r="C616">
         <v>2026</v>
       </c>
-      <c r="D616" s="1">
+      <c r="D616" s="2">
         <v>46092</v>
       </c>
       <c r="F616" t="s">
@@ -29170,7 +29196,7 @@
       <c r="C617">
         <v>2026</v>
       </c>
-      <c r="D617" s="1">
+      <c r="D617" s="2">
         <v>46119</v>
       </c>
       <c r="F617" t="s">
@@ -29211,7 +29237,7 @@
       <c r="C618">
         <v>2026</v>
       </c>
-      <c r="D618" s="1">
+      <c r="D618" s="2">
         <v>46029</v>
       </c>
       <c r="F618" t="s">
@@ -29252,7 +29278,7 @@
       <c r="C619">
         <v>2026</v>
       </c>
-      <c r="D619" s="1">
+      <c r="D619" s="2">
         <v>46029</v>
       </c>
       <c r="F619" t="s">
@@ -29293,7 +29319,7 @@
       <c r="C620">
         <v>2026</v>
       </c>
-      <c r="D620" s="1">
+      <c r="D620" s="2">
         <v>46063</v>
       </c>
       <c r="H620" t="s">
@@ -29328,7 +29354,7 @@
       <c r="C621">
         <v>2026</v>
       </c>
-      <c r="D621" s="1">
+      <c r="D621" s="2">
         <v>46232</v>
       </c>
       <c r="G621" t="s">
@@ -29366,7 +29392,7 @@
       <c r="C622">
         <v>2026</v>
       </c>
-      <c r="D622" s="1">
+      <c r="D622" s="2">
         <v>46232</v>
       </c>
       <c r="G622" t="s">
@@ -29404,7 +29430,7 @@
       <c r="C623">
         <v>2026</v>
       </c>
-      <c r="D623" s="1">
+      <c r="D623" s="2">
         <v>46232</v>
       </c>
       <c r="G623" t="s">
@@ -29442,7 +29468,7 @@
       <c r="C624">
         <v>2026</v>
       </c>
-      <c r="D624" s="1">
+      <c r="D624" s="2">
         <v>46232</v>
       </c>
       <c r="G624" t="s">
@@ -29480,7 +29506,7 @@
       <c r="C625">
         <v>2026</v>
       </c>
-      <c r="D625" s="1">
+      <c r="D625" s="2">
         <v>46155</v>
       </c>
       <c r="H625" t="s">
@@ -29515,7 +29541,7 @@
       <c r="C626">
         <v>2026</v>
       </c>
-      <c r="D626" s="1">
+      <c r="D626" s="2">
         <v>46139</v>
       </c>
       <c r="F626" t="s">
@@ -29556,7 +29582,7 @@
       <c r="C627">
         <v>2026</v>
       </c>
-      <c r="D627" s="1">
+      <c r="D627" s="2">
         <v>46155</v>
       </c>
       <c r="F627" t="s">
@@ -29597,7 +29623,7 @@
       <c r="C628">
         <v>2026</v>
       </c>
-      <c r="D628" s="1">
+      <c r="D628" s="2">
         <v>46155</v>
       </c>
       <c r="H628" t="s">
@@ -29632,7 +29658,7 @@
       <c r="C629">
         <v>2026</v>
       </c>
-      <c r="D629" s="1">
+      <c r="D629" s="2">
         <v>46147</v>
       </c>
       <c r="H629" t="s">
@@ -29667,7 +29693,7 @@
       <c r="C630">
         <v>2026</v>
       </c>
-      <c r="D630" s="1">
+      <c r="D630" s="2">
         <v>46164</v>
       </c>
       <c r="F630" t="s">
@@ -29708,7 +29734,7 @@
       <c r="C631">
         <v>2026</v>
       </c>
-      <c r="D631" s="1">
+      <c r="D631" s="2">
         <v>46225</v>
       </c>
       <c r="F631" t="s">
@@ -29749,7 +29775,7 @@
       <c r="C632">
         <v>2026</v>
       </c>
-      <c r="D632" s="1">
+      <c r="D632" s="2">
         <v>46225</v>
       </c>
       <c r="F632" t="s">
@@ -29790,7 +29816,7 @@
       <c r="C633">
         <v>2026</v>
       </c>
-      <c r="D633" s="1">
+      <c r="D633" s="2">
         <v>46225</v>
       </c>
       <c r="F633" t="s">
@@ -29831,7 +29857,7 @@
       <c r="C634">
         <v>2026</v>
       </c>
-      <c r="D634" s="1">
+      <c r="D634" s="2">
         <v>46248</v>
       </c>
       <c r="H634" t="s">
@@ -29866,7 +29892,7 @@
       <c r="C635">
         <v>2026</v>
       </c>
-      <c r="D635" s="1">
+      <c r="D635" s="2">
         <v>46248</v>
       </c>
       <c r="F635" t="s">
@@ -29907,7 +29933,7 @@
       <c r="C636">
         <v>2026</v>
       </c>
-      <c r="D636" s="1">
+      <c r="D636" s="2">
         <v>46171</v>
       </c>
       <c r="H636" t="s">
@@ -29942,7 +29968,7 @@
       <c r="C637">
         <v>2026</v>
       </c>
-      <c r="D637" s="1">
+      <c r="D637" s="2">
         <v>46176</v>
       </c>
       <c r="H637" t="s">
@@ -29977,7 +30003,7 @@
       <c r="C638">
         <v>2026</v>
       </c>
-      <c r="D638" s="1">
+      <c r="D638" s="2">
         <v>46225</v>
       </c>
       <c r="F638" t="s">
@@ -30018,7 +30044,7 @@
       <c r="C639">
         <v>2026</v>
       </c>
-      <c r="D639" s="1">
+      <c r="D639" s="2">
         <v>46211</v>
       </c>
       <c r="H639" t="s">
@@ -30053,7 +30079,7 @@
       <c r="C640">
         <v>2026</v>
       </c>
-      <c r="D640" s="1">
+      <c r="D640" s="2">
         <v>46183</v>
       </c>
       <c r="H640" t="s">
@@ -30088,7 +30114,7 @@
       <c r="C641">
         <v>2026</v>
       </c>
-      <c r="D641" s="1">
+      <c r="D641" s="2">
         <v>46191</v>
       </c>
       <c r="F641" t="s">
@@ -30129,7 +30155,7 @@
       <c r="C642">
         <v>2026</v>
       </c>
-      <c r="D642" s="1">
+      <c r="D642" s="2">
         <v>46176</v>
       </c>
       <c r="H642" t="s">
@@ -30164,7 +30190,7 @@
       <c r="C643">
         <v>2026</v>
       </c>
-      <c r="D643" s="1">
+      <c r="D643" s="2">
         <v>46191</v>
       </c>
       <c r="H643" t="s">
@@ -30199,7 +30225,7 @@
       <c r="C644">
         <v>2026</v>
       </c>
-      <c r="D644" s="1">
+      <c r="D644" s="2">
         <v>46241</v>
       </c>
       <c r="F644" t="s">
@@ -30243,7 +30269,7 @@
       <c r="C645">
         <v>2026</v>
       </c>
-      <c r="D645" s="1">
+      <c r="D645" s="2">
         <v>46191</v>
       </c>
       <c r="F645" t="s">
@@ -30284,7 +30310,7 @@
       <c r="C646">
         <v>2026</v>
       </c>
-      <c r="D646" s="1">
+      <c r="D646" s="2">
         <v>46191</v>
       </c>
       <c r="F646" t="s">
@@ -30325,7 +30351,7 @@
       <c r="C647">
         <v>2026</v>
       </c>
-      <c r="D647" s="1">
+      <c r="D647" s="2">
         <v>46191</v>
       </c>
       <c r="H647" t="s">
@@ -30360,7 +30386,7 @@
       <c r="C648">
         <v>2026</v>
       </c>
-      <c r="D648" s="1">
+      <c r="D648" s="2">
         <v>46241</v>
       </c>
       <c r="F648" t="s">
@@ -30401,7 +30427,7 @@
       <c r="C649">
         <v>2026</v>
       </c>
-      <c r="D649" s="1">
+      <c r="D649" s="2">
         <v>46191</v>
       </c>
       <c r="H649" t="s">
@@ -30436,7 +30462,7 @@
       <c r="C650">
         <v>2026</v>
       </c>
-      <c r="D650" s="1">
+      <c r="D650" s="2">
         <v>46248</v>
       </c>
       <c r="H650" t="s">
@@ -30471,7 +30497,7 @@
       <c r="C651">
         <v>2026</v>
       </c>
-      <c r="D651" s="1">
+      <c r="D651" s="2">
         <v>46241</v>
       </c>
       <c r="F651" t="s">
@@ -30512,7 +30538,7 @@
       <c r="C652">
         <v>2026</v>
       </c>
-      <c r="D652" s="1">
+      <c r="D652" s="2">
         <v>46241</v>
       </c>
       <c r="F652" t="s">
@@ -30553,7 +30579,7 @@
       <c r="C653">
         <v>2026</v>
       </c>
-      <c r="D653" s="1">
+      <c r="D653" s="2">
         <v>46225</v>
       </c>
       <c r="F653" t="s">
@@ -30594,7 +30620,7 @@
       <c r="C654">
         <v>2026</v>
       </c>
-      <c r="D654" s="1">
+      <c r="D654" s="2">
         <v>46241</v>
       </c>
       <c r="F654" t="s">
@@ -30635,7 +30661,7 @@
       <c r="C655">
         <v>2026</v>
       </c>
-      <c r="D655" s="1">
+      <c r="D655" s="2">
         <v>46241</v>
       </c>
       <c r="F655" t="s">
@@ -30676,7 +30702,7 @@
       <c r="C656">
         <v>2026</v>
       </c>
-      <c r="D656" s="1">
+      <c r="D656" s="2">
         <v>46241</v>
       </c>
       <c r="F656" t="s">
@@ -30717,7 +30743,7 @@
       <c r="C657">
         <v>2026</v>
       </c>
-      <c r="D657" s="1">
+      <c r="D657" s="2">
         <v>46248</v>
       </c>
       <c r="H657" t="s">
@@ -30752,7 +30778,7 @@
       <c r="C658">
         <v>2026</v>
       </c>
-      <c r="D658" s="1">
+      <c r="D658" s="2">
         <v>46248</v>
       </c>
       <c r="H658" t="s">
@@ -30787,7 +30813,7 @@
       <c r="C659">
         <v>2026</v>
       </c>
-      <c r="D659" s="1">
+      <c r="D659" s="2">
         <v>46248</v>
       </c>
       <c r="F659" t="s">
@@ -30828,7 +30854,7 @@
       <c r="C660">
         <v>2026</v>
       </c>
-      <c r="D660" s="1">
+      <c r="D660" s="2">
         <v>46248</v>
       </c>
       <c r="F660" t="s">
@@ -30869,7 +30895,7 @@
       <c r="C661">
         <v>2026</v>
       </c>
-      <c r="D661" s="1">
+      <c r="D661" s="2">
         <v>46248</v>
       </c>
       <c r="F661" t="s">
@@ -30910,7 +30936,7 @@
       <c r="C662">
         <v>2026</v>
       </c>
-      <c r="D662" s="1">
+      <c r="D662" s="2">
         <v>45989</v>
       </c>
       <c r="G662" t="s">
@@ -30948,7 +30974,7 @@
       <c r="C663">
         <v>2026</v>
       </c>
-      <c r="D663" s="1">
+      <c r="D663" s="2">
         <v>46002</v>
       </c>
       <c r="G663" t="s">
@@ -30986,7 +31012,7 @@
       <c r="C664">
         <v>2026</v>
       </c>
-      <c r="D664" s="1">
+      <c r="D664" s="2">
         <v>46002</v>
       </c>
       <c r="G664" t="s">
@@ -31024,7 +31050,7 @@
       <c r="C665">
         <v>2026</v>
       </c>
-      <c r="D665" s="1">
+      <c r="D665" s="2">
         <v>46225</v>
       </c>
       <c r="F665" t="s">
@@ -31065,7 +31091,7 @@
       <c r="C666">
         <v>2026</v>
       </c>
-      <c r="D666" s="1">
+      <c r="D666" s="2">
         <v>46211</v>
       </c>
       <c r="F666" t="s">
@@ -31106,7 +31132,7 @@
       <c r="C667">
         <v>2026</v>
       </c>
-      <c r="D667" s="1">
+      <c r="D667" s="2">
         <v>46248</v>
       </c>
       <c r="F667" t="s">
@@ -31147,7 +31173,7 @@
       <c r="C668">
         <v>2026</v>
       </c>
-      <c r="D668" s="1">
+      <c r="D668" s="2">
         <v>46248</v>
       </c>
       <c r="F668" t="s">
@@ -31220,7 +31246,7 @@
       <c r="C670">
         <v>2026</v>
       </c>
-      <c r="D670" s="1">
+      <c r="D670" s="2">
         <v>46255</v>
       </c>
       <c r="F670" t="s">
@@ -31421,7 +31447,7 @@
       <c r="C676">
         <v>2026</v>
       </c>
-      <c r="D676" s="1">
+      <c r="D676" s="2">
         <v>46265</v>
       </c>
       <c r="H676" t="s">
@@ -31456,7 +31482,7 @@
       <c r="C677">
         <v>2026</v>
       </c>
-      <c r="D677" s="1">
+      <c r="D677" s="2">
         <v>46265</v>
       </c>
       <c r="H677" t="s">
@@ -31491,7 +31517,7 @@
       <c r="C678">
         <v>2026</v>
       </c>
-      <c r="D678" s="1">
+      <c r="D678" s="2">
         <v>46265</v>
       </c>
       <c r="H678" t="s">
@@ -31846,7 +31872,7 @@
       <c r="C689">
         <v>2026</v>
       </c>
-      <c r="D689" s="1">
+      <c r="D689" s="2">
         <v>46265</v>
       </c>
       <c r="H689" t="s">
@@ -31881,7 +31907,7 @@
       <c r="C690">
         <v>2026</v>
       </c>
-      <c r="D690" s="1">
+      <c r="D690" s="2">
         <v>46265</v>
       </c>
       <c r="H690" t="s">
@@ -32972,7 +32998,7 @@
       <c r="C724">
         <v>2026</v>
       </c>
-      <c r="D724" s="1">
+      <c r="D724" s="2">
         <v>45802</v>
       </c>
       <c r="F724" t="s">
@@ -33016,7 +33042,7 @@
       <c r="C725">
         <v>2026</v>
       </c>
-      <c r="D725" s="1">
+      <c r="D725" s="2">
         <v>45860</v>
       </c>
       <c r="F725" t="s">
@@ -33057,7 +33083,7 @@
       <c r="C726">
         <v>2026</v>
       </c>
-      <c r="D726" s="1">
+      <c r="D726" s="2">
         <v>45860</v>
       </c>
       <c r="H726" t="s">
@@ -33092,7 +33118,7 @@
       <c r="C727">
         <v>2026</v>
       </c>
-      <c r="D727" s="1">
+      <c r="D727" s="2">
         <v>45856</v>
       </c>
       <c r="F727" t="s">
@@ -33133,7 +33159,7 @@
       <c r="C728">
         <v>2026</v>
       </c>
-      <c r="D728" s="1">
+      <c r="D728" s="2">
         <v>46101</v>
       </c>
       <c r="F728" t="s">
@@ -33174,7 +33200,7 @@
       <c r="C729">
         <v>2026</v>
       </c>
-      <c r="D729" s="1">
+      <c r="D729" s="2">
         <v>46101</v>
       </c>
       <c r="F729" t="s">
@@ -33215,7 +33241,7 @@
       <c r="C730">
         <v>2026</v>
       </c>
-      <c r="D730" s="1">
+      <c r="D730" s="2">
         <v>45863</v>
       </c>
       <c r="F730" t="s">
@@ -33256,7 +33282,7 @@
       <c r="C731">
         <v>2026</v>
       </c>
-      <c r="D731" s="1">
+      <c r="D731" s="2">
         <v>45863</v>
       </c>
       <c r="F731" t="s">
@@ -33297,7 +33323,7 @@
       <c r="C732">
         <v>2026</v>
       </c>
-      <c r="D732" s="1">
+      <c r="D732" s="2">
         <v>46086</v>
       </c>
       <c r="F732" t="s">
@@ -33338,7 +33364,7 @@
       <c r="C733">
         <v>2026</v>
       </c>
-      <c r="D733" s="1">
+      <c r="D733" s="2">
         <v>45874</v>
       </c>
       <c r="F733" t="s">
@@ -33379,7 +33405,7 @@
       <c r="C734">
         <v>2026</v>
       </c>
-      <c r="D734" s="1">
+      <c r="D734" s="2">
         <v>45894</v>
       </c>
       <c r="F734" t="s">
@@ -33420,7 +33446,7 @@
       <c r="C735">
         <v>2026</v>
       </c>
-      <c r="D735" s="1">
+      <c r="D735" s="2">
         <v>45894</v>
       </c>
       <c r="F735" t="s">
@@ -33461,7 +33487,7 @@
       <c r="C736">
         <v>2026</v>
       </c>
-      <c r="D736" s="1">
+      <c r="D736" s="2">
         <v>46119</v>
       </c>
       <c r="F736" t="s">
@@ -33502,7 +33528,7 @@
       <c r="C737">
         <v>2026</v>
       </c>
-      <c r="D737" s="1">
+      <c r="D737" s="2">
         <v>45898</v>
       </c>
       <c r="F737" t="s">
@@ -33543,7 +33569,7 @@
       <c r="C738">
         <v>2026</v>
       </c>
-      <c r="D738" s="1">
+      <c r="D738" s="2">
         <v>45971</v>
       </c>
       <c r="F738" t="s">
@@ -33584,7 +33610,7 @@
       <c r="C739">
         <v>2026</v>
       </c>
-      <c r="D739" s="1">
+      <c r="D739" s="2">
         <v>46119</v>
       </c>
       <c r="F739" t="s">
@@ -33625,7 +33651,7 @@
       <c r="C740">
         <v>2026</v>
       </c>
-      <c r="D740" s="1">
+      <c r="D740" s="2">
         <v>46092</v>
       </c>
       <c r="F740" t="s">
@@ -33666,7 +33692,7 @@
       <c r="C741">
         <v>2026</v>
       </c>
-      <c r="D741" s="1">
+      <c r="D741" s="2">
         <v>46119</v>
       </c>
       <c r="F741" t="s">
@@ -33707,7 +33733,7 @@
       <c r="C742">
         <v>2026</v>
       </c>
-      <c r="D742" s="1">
+      <c r="D742" s="2">
         <v>46029</v>
       </c>
       <c r="F742" t="s">
@@ -33748,7 +33774,7 @@
       <c r="C743">
         <v>2026</v>
       </c>
-      <c r="D743" s="1">
+      <c r="D743" s="2">
         <v>46029</v>
       </c>
       <c r="F743" t="s">
@@ -33789,7 +33815,7 @@
       <c r="C744">
         <v>2026</v>
       </c>
-      <c r="D744" s="1">
+      <c r="D744" s="2">
         <v>46063</v>
       </c>
       <c r="H744" t="s">
@@ -33824,7 +33850,7 @@
       <c r="C745">
         <v>2026</v>
       </c>
-      <c r="D745" s="1">
+      <c r="D745" s="2">
         <v>46232</v>
       </c>
       <c r="G745" t="s">
@@ -33862,7 +33888,7 @@
       <c r="C746">
         <v>2026</v>
       </c>
-      <c r="D746" s="1">
+      <c r="D746" s="2">
         <v>46232</v>
       </c>
       <c r="G746" t="s">
@@ -33900,7 +33926,7 @@
       <c r="C747">
         <v>2026</v>
       </c>
-      <c r="D747" s="1">
+      <c r="D747" s="2">
         <v>46232</v>
       </c>
       <c r="G747" t="s">
@@ -33938,7 +33964,7 @@
       <c r="C748">
         <v>2026</v>
       </c>
-      <c r="D748" s="1">
+      <c r="D748" s="2">
         <v>46232</v>
       </c>
       <c r="G748" t="s">
@@ -33976,7 +34002,7 @@
       <c r="C749">
         <v>2026</v>
       </c>
-      <c r="D749" s="1">
+      <c r="D749" s="2">
         <v>46155</v>
       </c>
       <c r="H749" t="s">
@@ -34011,7 +34037,7 @@
       <c r="C750">
         <v>2026</v>
       </c>
-      <c r="D750" s="1">
+      <c r="D750" s="2">
         <v>46139</v>
       </c>
       <c r="F750" t="s">
@@ -34052,7 +34078,7 @@
       <c r="C751">
         <v>2026</v>
       </c>
-      <c r="D751" s="1">
+      <c r="D751" s="2">
         <v>46155</v>
       </c>
       <c r="F751" t="s">
@@ -34093,7 +34119,7 @@
       <c r="C752">
         <v>2026</v>
       </c>
-      <c r="D752" s="1">
+      <c r="D752" s="2">
         <v>46155</v>
       </c>
       <c r="H752" t="s">
@@ -34128,7 +34154,7 @@
       <c r="C753">
         <v>2026</v>
       </c>
-      <c r="D753" s="1">
+      <c r="D753" s="2">
         <v>46147</v>
       </c>
       <c r="H753" t="s">
@@ -34163,7 +34189,7 @@
       <c r="C754">
         <v>2026</v>
       </c>
-      <c r="D754" s="1">
+      <c r="D754" s="2">
         <v>46164</v>
       </c>
       <c r="F754" t="s">
@@ -34204,7 +34230,7 @@
       <c r="C755">
         <v>2026</v>
       </c>
-      <c r="D755" s="1">
+      <c r="D755" s="2">
         <v>46225</v>
       </c>
       <c r="F755" t="s">
@@ -34245,7 +34271,7 @@
       <c r="C756">
         <v>2026</v>
       </c>
-      <c r="D756" s="1">
+      <c r="D756" s="2">
         <v>46225</v>
       </c>
       <c r="F756" t="s">
@@ -34286,7 +34312,7 @@
       <c r="C757">
         <v>2026</v>
       </c>
-      <c r="D757" s="1">
+      <c r="D757" s="2">
         <v>46225</v>
       </c>
       <c r="F757" t="s">
@@ -34327,7 +34353,7 @@
       <c r="C758">
         <v>2026</v>
       </c>
-      <c r="D758" s="1">
+      <c r="D758" s="2">
         <v>46248</v>
       </c>
       <c r="H758" t="s">
@@ -34362,7 +34388,7 @@
       <c r="C759">
         <v>2026</v>
       </c>
-      <c r="D759" s="1">
+      <c r="D759" s="2">
         <v>46248</v>
       </c>
       <c r="F759" t="s">
@@ -34403,7 +34429,7 @@
       <c r="C760">
         <v>2026</v>
       </c>
-      <c r="D760" s="1">
+      <c r="D760" s="2">
         <v>46171</v>
       </c>
       <c r="H760" t="s">
@@ -34438,7 +34464,7 @@
       <c r="C761">
         <v>2026</v>
       </c>
-      <c r="D761" s="1">
+      <c r="D761" s="2">
         <v>46176</v>
       </c>
       <c r="H761" t="s">
@@ -34473,7 +34499,7 @@
       <c r="C762">
         <v>2026</v>
       </c>
-      <c r="D762" s="1">
+      <c r="D762" s="2">
         <v>46225</v>
       </c>
       <c r="F762" t="s">
@@ -34514,7 +34540,7 @@
       <c r="C763">
         <v>2026</v>
       </c>
-      <c r="D763" s="1">
+      <c r="D763" s="2">
         <v>46211</v>
       </c>
       <c r="H763" t="s">
@@ -34549,7 +34575,7 @@
       <c r="C764">
         <v>2026</v>
       </c>
-      <c r="D764" s="1">
+      <c r="D764" s="2">
         <v>46183</v>
       </c>
       <c r="H764" t="s">
@@ -34584,7 +34610,7 @@
       <c r="C765">
         <v>2026</v>
       </c>
-      <c r="D765" s="1">
+      <c r="D765" s="2">
         <v>46191</v>
       </c>
       <c r="F765" t="s">
@@ -34625,7 +34651,7 @@
       <c r="C766">
         <v>2026</v>
       </c>
-      <c r="D766" s="1">
+      <c r="D766" s="2">
         <v>46176</v>
       </c>
       <c r="H766" t="s">
@@ -34660,7 +34686,7 @@
       <c r="C767">
         <v>2026</v>
       </c>
-      <c r="D767" s="1">
+      <c r="D767" s="2">
         <v>46191</v>
       </c>
       <c r="H767" t="s">
@@ -34695,7 +34721,7 @@
       <c r="C768">
         <v>2026</v>
       </c>
-      <c r="D768" s="1">
+      <c r="D768" s="2">
         <v>46241</v>
       </c>
       <c r="F768" t="s">
@@ -34739,7 +34765,7 @@
       <c r="C769">
         <v>2026</v>
       </c>
-      <c r="D769" s="1">
+      <c r="D769" s="2">
         <v>46191</v>
       </c>
       <c r="F769" t="s">
@@ -34780,7 +34806,7 @@
       <c r="C770">
         <v>2026</v>
       </c>
-      <c r="D770" s="1">
+      <c r="D770" s="2">
         <v>46191</v>
       </c>
       <c r="F770" t="s">
@@ -34821,7 +34847,7 @@
       <c r="C771">
         <v>2026</v>
       </c>
-      <c r="D771" s="1">
+      <c r="D771" s="2">
         <v>46191</v>
       </c>
       <c r="H771" t="s">
@@ -34856,7 +34882,7 @@
       <c r="C772">
         <v>2026</v>
       </c>
-      <c r="D772" s="1">
+      <c r="D772" s="2">
         <v>46241</v>
       </c>
       <c r="F772" t="s">
@@ -34897,7 +34923,7 @@
       <c r="C773">
         <v>2026</v>
       </c>
-      <c r="D773" s="1">
+      <c r="D773" s="2">
         <v>46191</v>
       </c>
       <c r="H773" t="s">
@@ -34932,7 +34958,7 @@
       <c r="C774">
         <v>2026</v>
       </c>
-      <c r="D774" s="1">
+      <c r="D774" s="2">
         <v>46248</v>
       </c>
       <c r="H774" t="s">
@@ -34967,7 +34993,7 @@
       <c r="C775">
         <v>2026</v>
       </c>
-      <c r="D775" s="1">
+      <c r="D775" s="2">
         <v>46241</v>
       </c>
       <c r="F775" t="s">
@@ -35008,7 +35034,7 @@
       <c r="C776">
         <v>2026</v>
       </c>
-      <c r="D776" s="1">
+      <c r="D776" s="2">
         <v>46241</v>
       </c>
       <c r="F776" t="s">
@@ -35049,7 +35075,7 @@
       <c r="C777">
         <v>2026</v>
       </c>
-      <c r="D777" s="1">
+      <c r="D777" s="2">
         <v>46225</v>
       </c>
       <c r="F777" t="s">
@@ -35090,7 +35116,7 @@
       <c r="C778">
         <v>2026</v>
       </c>
-      <c r="D778" s="1">
+      <c r="D778" s="2">
         <v>46241</v>
       </c>
       <c r="F778" t="s">
@@ -35131,7 +35157,7 @@
       <c r="C779">
         <v>2026</v>
       </c>
-      <c r="D779" s="1">
+      <c r="D779" s="2">
         <v>46241</v>
       </c>
       <c r="F779" t="s">
@@ -35172,7 +35198,7 @@
       <c r="C780">
         <v>2026</v>
       </c>
-      <c r="D780" s="1">
+      <c r="D780" s="2">
         <v>46241</v>
       </c>
       <c r="F780" t="s">
@@ -35213,7 +35239,7 @@
       <c r="C781">
         <v>2026</v>
       </c>
-      <c r="D781" s="1">
+      <c r="D781" s="2">
         <v>46248</v>
       </c>
       <c r="H781" t="s">
@@ -35248,7 +35274,7 @@
       <c r="C782">
         <v>2026</v>
       </c>
-      <c r="D782" s="1">
+      <c r="D782" s="2">
         <v>46248</v>
       </c>
       <c r="H782" t="s">
@@ -35283,7 +35309,7 @@
       <c r="C783">
         <v>2026</v>
       </c>
-      <c r="D783" s="1">
+      <c r="D783" s="2">
         <v>46248</v>
       </c>
       <c r="F783" t="s">
@@ -35324,7 +35350,7 @@
       <c r="C784">
         <v>2026</v>
       </c>
-      <c r="D784" s="1">
+      <c r="D784" s="2">
         <v>46248</v>
       </c>
       <c r="F784" t="s">
@@ -35365,7 +35391,7 @@
       <c r="C785">
         <v>2026</v>
       </c>
-      <c r="D785" s="1">
+      <c r="D785" s="2">
         <v>46248</v>
       </c>
       <c r="F785" t="s">
@@ -35406,7 +35432,7 @@
       <c r="C786">
         <v>2026</v>
       </c>
-      <c r="D786" s="1">
+      <c r="D786" s="2">
         <v>45989</v>
       </c>
       <c r="G786" t="s">
@@ -35444,7 +35470,7 @@
       <c r="C787">
         <v>2026</v>
       </c>
-      <c r="D787" s="1">
+      <c r="D787" s="2">
         <v>46002</v>
       </c>
       <c r="G787" t="s">
@@ -35482,7 +35508,7 @@
       <c r="C788">
         <v>2026</v>
       </c>
-      <c r="D788" s="1">
+      <c r="D788" s="2">
         <v>46002</v>
       </c>
       <c r="G788" t="s">
@@ -35520,7 +35546,7 @@
       <c r="C789">
         <v>2026</v>
       </c>
-      <c r="D789" s="1">
+      <c r="D789" s="2">
         <v>46225</v>
       </c>
       <c r="F789" t="s">
@@ -35561,7 +35587,7 @@
       <c r="C790">
         <v>2026</v>
       </c>
-      <c r="D790" s="1">
+      <c r="D790" s="2">
         <v>46211</v>
       </c>
       <c r="F790" t="s">
@@ -35602,7 +35628,7 @@
       <c r="C791">
         <v>2026</v>
       </c>
-      <c r="D791" s="1">
+      <c r="D791" s="2">
         <v>46248</v>
       </c>
       <c r="F791" t="s">
@@ -35643,7 +35669,7 @@
       <c r="C792">
         <v>2026</v>
       </c>
-      <c r="D792" s="1">
+      <c r="D792" s="2">
         <v>46248</v>
       </c>
       <c r="F792" t="s">
@@ -35716,7 +35742,7 @@
       <c r="C794">
         <v>2026</v>
       </c>
-      <c r="D794" s="1">
+      <c r="D794" s="2">
         <v>46255</v>
       </c>
       <c r="F794" t="s">
@@ -35917,7 +35943,7 @@
       <c r="C800">
         <v>2026</v>
       </c>
-      <c r="D800" s="1">
+      <c r="D800" s="2">
         <v>46265</v>
       </c>
       <c r="H800" t="s">
@@ -35952,7 +35978,7 @@
       <c r="C801">
         <v>2026</v>
       </c>
-      <c r="D801" s="1">
+      <c r="D801" s="2">
         <v>46265</v>
       </c>
       <c r="H801" t="s">
@@ -35987,7 +36013,7 @@
       <c r="C802">
         <v>2026</v>
       </c>
-      <c r="D802" s="1">
+      <c r="D802" s="2">
         <v>46265</v>
       </c>
       <c r="H802" t="s">
@@ -36342,7 +36368,7 @@
       <c r="C813">
         <v>2026</v>
       </c>
-      <c r="D813" s="1">
+      <c r="D813" s="2">
         <v>46265</v>
       </c>
       <c r="H813" t="s">
@@ -36377,7 +36403,7 @@
       <c r="C814">
         <v>2026</v>
       </c>
-      <c r="D814" s="1">
+      <c r="D814" s="2">
         <v>46265</v>
       </c>
       <c r="H814" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/reparaveis_complemento_rma.xlsx
@@ -5765,16 +5765,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5790,7 +5782,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -5798,30 +5790,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6121,52 +6095,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6244,7 +6218,7 @@
       <c r="C4">
         <v>2026</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>45972</v>
       </c>
       <c r="F4" t="s">
@@ -6381,7 +6355,7 @@
       <c r="C8">
         <v>2026</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>46014</v>
       </c>
       <c r="F8" t="s">
@@ -6518,7 +6492,7 @@
       <c r="C12">
         <v>2026</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>45916</v>
       </c>
       <c r="F12" t="s">
@@ -6559,7 +6533,7 @@
       <c r="C13">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>45897</v>
       </c>
       <c r="H13" t="s">
@@ -6594,7 +6568,7 @@
       <c r="C14">
         <v>2026</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>45916</v>
       </c>
       <c r="F14" t="s">
@@ -6635,7 +6609,7 @@
       <c r="C15">
         <v>2026</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>46086</v>
       </c>
       <c r="G15" t="s">
@@ -6673,7 +6647,7 @@
       <c r="C16">
         <v>2026</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>45869</v>
       </c>
       <c r="F16" t="s">
@@ -6714,7 +6688,7 @@
       <c r="C17">
         <v>2026</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>45877</v>
       </c>
       <c r="F17" t="s">
@@ -6755,7 +6729,7 @@
       <c r="C18">
         <v>2026</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>46086</v>
       </c>
       <c r="G18" t="s">
@@ -6793,7 +6767,7 @@
       <c r="C19">
         <v>2026</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>45863</v>
       </c>
       <c r="F19" t="s">
@@ -6834,7 +6808,7 @@
       <c r="C20">
         <v>2026</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>45863</v>
       </c>
       <c r="F20" t="s">
@@ -6875,7 +6849,7 @@
       <c r="C21">
         <v>2026</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>45873</v>
       </c>
       <c r="F21" t="s">
@@ -6916,7 +6890,7 @@
       <c r="C22">
         <v>2026</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
@@ -6957,7 +6931,7 @@
       <c r="C23">
         <v>2026</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>46086</v>
       </c>
       <c r="G23" t="s">
@@ -7059,7 +7033,7 @@
       <c r="C26">
         <v>2026</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>45838</v>
       </c>
       <c r="F26" t="s">
@@ -7100,7 +7074,7 @@
       <c r="C27">
         <v>2026</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>45800</v>
       </c>
       <c r="F27" t="s">
@@ -7141,7 +7115,7 @@
       <c r="C28">
         <v>2026</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>45849</v>
       </c>
       <c r="F28" t="s">
@@ -7182,7 +7156,7 @@
       <c r="C29">
         <v>2026</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>45838</v>
       </c>
       <c r="F29" t="s">
@@ -7223,7 +7197,7 @@
       <c r="C30">
         <v>2026</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>45915</v>
       </c>
       <c r="F30" t="s">
@@ -7264,7 +7238,7 @@
       <c r="C31">
         <v>2026</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>45849</v>
       </c>
       <c r="F31" t="s">
@@ -7337,7 +7311,7 @@
       <c r="C33">
         <v>2026</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>45800</v>
       </c>
       <c r="F33" t="s">
@@ -7410,7 +7384,7 @@
       <c r="C35">
         <v>2026</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>46119</v>
       </c>
       <c r="F35" t="s">
@@ -7451,7 +7425,7 @@
       <c r="C36">
         <v>2026</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>45854</v>
       </c>
       <c r="F36" t="s">
@@ -7492,7 +7466,7 @@
       <c r="C37">
         <v>2026</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>45849</v>
       </c>
       <c r="F37" t="s">
@@ -7533,7 +7507,7 @@
       <c r="C38">
         <v>2026</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>46119</v>
       </c>
       <c r="F38" t="s">
@@ -7606,7 +7580,7 @@
       <c r="C40">
         <v>2026</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>46092</v>
       </c>
       <c r="F40" t="s">
@@ -7711,7 +7685,7 @@
       <c r="C43">
         <v>2026</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>46122</v>
       </c>
       <c r="F43" t="s">
@@ -7752,7 +7726,7 @@
       <c r="C44">
         <v>2026</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>46122</v>
       </c>
       <c r="F44" t="s">
@@ -7793,7 +7767,7 @@
       <c r="C45">
         <v>2026</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>46135</v>
       </c>
       <c r="F45" t="s">
@@ -7834,7 +7808,7 @@
       <c r="C46">
         <v>2026</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>46086</v>
       </c>
       <c r="F46" t="s">
@@ -7875,7 +7849,7 @@
       <c r="C47">
         <v>2026</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>46104</v>
       </c>
       <c r="F47" t="s">
@@ -7916,7 +7890,7 @@
       <c r="C48">
         <v>2026</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>45972</v>
       </c>
       <c r="G48" t="s">
@@ -7954,7 +7928,7 @@
       <c r="C49">
         <v>2026</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>45810</v>
       </c>
       <c r="F49" t="s">
@@ -7995,7 +7969,7 @@
       <c r="C50">
         <v>2026</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>45937</v>
       </c>
       <c r="F50" t="s">
@@ -8036,7 +8010,7 @@
       <c r="C51">
         <v>2026</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>45937</v>
       </c>
       <c r="F51" t="s">
@@ -8109,7 +8083,7 @@
       <c r="C53">
         <v>2026</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="1">
         <v>45845</v>
       </c>
       <c r="F53" t="s">
@@ -8150,7 +8124,7 @@
       <c r="C54">
         <v>2026</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="1">
         <v>46077</v>
       </c>
       <c r="F54" t="s">
@@ -8223,7 +8197,7 @@
       <c r="C56">
         <v>2026</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>45971</v>
       </c>
       <c r="F56" t="s">
@@ -8296,7 +8270,7 @@
       <c r="C58">
         <v>2026</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>45817</v>
       </c>
       <c r="F58" t="s">
@@ -8369,7 +8343,7 @@
       <c r="C60">
         <v>2026</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>45965</v>
       </c>
       <c r="G60" t="s">
@@ -8439,7 +8413,7 @@
       <c r="C62">
         <v>2026</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>46072</v>
       </c>
       <c r="F62" t="s">
@@ -8512,7 +8486,7 @@
       <c r="C64">
         <v>2026</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>46072</v>
       </c>
       <c r="H64" t="s">
@@ -8547,7 +8521,7 @@
       <c r="C65">
         <v>2026</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>45804</v>
       </c>
       <c r="F65" t="s">
@@ -8588,7 +8562,7 @@
       <c r="C66">
         <v>2026</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>45804</v>
       </c>
       <c r="F66" t="s">
@@ -8629,7 +8603,7 @@
       <c r="C67">
         <v>2026</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>45804</v>
       </c>
       <c r="F67" t="s">
@@ -8670,7 +8644,7 @@
       <c r="C68">
         <v>2026</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="1">
         <v>45804</v>
       </c>
       <c r="F68" t="s">
@@ -8711,7 +8685,7 @@
       <c r="C69">
         <v>2026</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="1">
         <v>45804</v>
       </c>
       <c r="F69" t="s">
@@ -8752,7 +8726,7 @@
       <c r="C70">
         <v>2026</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>45804</v>
       </c>
       <c r="F70" t="s">
@@ -8793,7 +8767,7 @@
       <c r="C71">
         <v>2026</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="1">
         <v>45821</v>
       </c>
       <c r="F71" t="s">
@@ -8834,7 +8808,7 @@
       <c r="C72">
         <v>2026</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="1">
         <v>45821</v>
       </c>
       <c r="H72" t="s">
@@ -8869,7 +8843,7 @@
       <c r="C73">
         <v>2026</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="1">
         <v>45891</v>
       </c>
       <c r="F73" t="s">
@@ -8910,7 +8884,7 @@
       <c r="C74">
         <v>2026</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="1">
         <v>45817</v>
       </c>
       <c r="G74" t="s">
@@ -8948,7 +8922,7 @@
       <c r="C75">
         <v>2026</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="1">
         <v>45883</v>
       </c>
       <c r="G75" t="s">
@@ -8986,7 +8960,7 @@
       <c r="C76">
         <v>2026</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="1">
         <v>45817</v>
       </c>
       <c r="G76" t="s">
@@ -9024,7 +8998,7 @@
       <c r="C77">
         <v>2026</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="1">
         <v>45883</v>
       </c>
       <c r="G77" t="s">
@@ -9062,7 +9036,7 @@
       <c r="C78">
         <v>2026</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>45971</v>
       </c>
       <c r="F78" t="s">
@@ -9103,7 +9077,7 @@
       <c r="C79">
         <v>2026</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>45849</v>
       </c>
       <c r="F79" t="s">
@@ -9144,7 +9118,7 @@
       <c r="C80">
         <v>2026</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="1">
         <v>45849</v>
       </c>
       <c r="F80" t="s">
@@ -9185,7 +9159,7 @@
       <c r="C81">
         <v>2026</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="1">
         <v>45863</v>
       </c>
       <c r="F81" t="s">
@@ -9226,7 +9200,7 @@
       <c r="C82">
         <v>2026</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>45810</v>
       </c>
       <c r="F82" t="s">
@@ -9267,7 +9241,7 @@
       <c r="C83">
         <v>2026</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="1">
         <v>45926</v>
       </c>
       <c r="F83" t="s">
@@ -9308,7 +9282,7 @@
       <c r="C84">
         <v>2026</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="1">
         <v>45971</v>
       </c>
       <c r="F84" t="s">
@@ -9349,7 +9323,7 @@
       <c r="C85">
         <v>2026</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="1">
         <v>46164</v>
       </c>
       <c r="F85" t="s">
@@ -9390,7 +9364,7 @@
       <c r="C86">
         <v>2026</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>45986</v>
       </c>
       <c r="G86" t="s">
@@ -9469,7 +9443,7 @@
       <c r="C88">
         <v>2026</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="1">
         <v>45786</v>
       </c>
       <c r="F88" t="s">
@@ -9510,7 +9484,7 @@
       <c r="C89">
         <v>2026</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="1">
         <v>45777</v>
       </c>
       <c r="F89" t="s">
@@ -9551,7 +9525,7 @@
       <c r="C90">
         <v>2026</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="1">
         <v>45869</v>
       </c>
       <c r="F90" t="s">
@@ -9592,7 +9566,7 @@
       <c r="C91">
         <v>2026</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="1">
         <v>45891</v>
       </c>
       <c r="F91" t="s">
@@ -9633,7 +9607,7 @@
       <c r="C92">
         <v>2026</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="1">
         <v>45863</v>
       </c>
       <c r="F92" t="s">
@@ -9674,7 +9648,7 @@
       <c r="C93">
         <v>2026</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="1">
         <v>45769</v>
       </c>
       <c r="F93" t="s">
@@ -9715,7 +9689,7 @@
       <c r="C94">
         <v>2026</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="1">
         <v>45769</v>
       </c>
       <c r="F94" t="s">
@@ -9756,7 +9730,7 @@
       <c r="C95">
         <v>2026</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="1">
         <v>45894</v>
       </c>
       <c r="F95" t="s">
@@ -9829,7 +9803,7 @@
       <c r="C97">
         <v>2026</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="1">
         <v>45894</v>
       </c>
       <c r="F97" t="s">
@@ -9870,7 +9844,7 @@
       <c r="C98">
         <v>2026</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="1">
         <v>45971</v>
       </c>
       <c r="F98" t="s">
@@ -9911,7 +9885,7 @@
       <c r="C99">
         <v>2026</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>45971</v>
       </c>
       <c r="F99" t="s">
@@ -9952,7 +9926,7 @@
       <c r="C100">
         <v>2026</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="1">
         <v>45971</v>
       </c>
       <c r="F100" t="s">
@@ -9993,7 +9967,7 @@
       <c r="C101">
         <v>2026</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="1">
         <v>45996</v>
       </c>
       <c r="G101" t="s">
@@ -10031,7 +10005,7 @@
       <c r="C102">
         <v>2026</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="1">
         <v>45986</v>
       </c>
       <c r="G102" t="s">
@@ -10101,7 +10075,7 @@
       <c r="C104">
         <v>2026</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="1">
         <v>45769</v>
       </c>
       <c r="F104" t="s">
@@ -10142,7 +10116,7 @@
       <c r="C105">
         <v>2026</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="1">
         <v>45769</v>
       </c>
       <c r="F105" t="s">
@@ -10183,7 +10157,7 @@
       <c r="C106">
         <v>2026</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="1">
         <v>45849</v>
       </c>
       <c r="F106" t="s">
@@ -10224,7 +10198,7 @@
       <c r="C107">
         <v>2026</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="1">
         <v>45849</v>
       </c>
       <c r="G107" t="s">
@@ -10326,7 +10300,7 @@
       <c r="C110">
         <v>2026</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="1">
         <v>45891</v>
       </c>
       <c r="F110" t="s">
@@ -10367,7 +10341,7 @@
       <c r="C111">
         <v>2026</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="1">
         <v>45769</v>
       </c>
       <c r="F111" t="s">
@@ -10408,7 +10382,7 @@
       <c r="C112">
         <v>2026</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="1">
         <v>45889</v>
       </c>
       <c r="F112" t="s">
@@ -10449,7 +10423,7 @@
       <c r="C113">
         <v>2026</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="1">
         <v>45945</v>
       </c>
       <c r="G113" t="s">
@@ -10487,7 +10461,7 @@
       <c r="C114">
         <v>2026</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="1">
         <v>45945</v>
       </c>
       <c r="G114" t="s">
@@ -10525,7 +10499,7 @@
       <c r="C115">
         <v>2026</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="1">
         <v>46119</v>
       </c>
       <c r="F115" t="s">
@@ -10566,7 +10540,7 @@
       <c r="C116">
         <v>2026</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="1">
         <v>46029</v>
       </c>
       <c r="F116" t="s">
@@ -10607,7 +10581,7 @@
       <c r="C117">
         <v>2026</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="1">
         <v>46029</v>
       </c>
       <c r="F117" t="s">
@@ -10648,7 +10622,7 @@
       <c r="C118">
         <v>2026</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="1">
         <v>46119</v>
       </c>
       <c r="F118" t="s">
@@ -10689,7 +10663,7 @@
       <c r="C119">
         <v>2026</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="1">
         <v>46230</v>
       </c>
       <c r="F119" t="s">
@@ -10730,7 +10704,7 @@
       <c r="C120">
         <v>2026</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="1">
         <v>46119</v>
       </c>
       <c r="F120" t="s">
@@ -10771,7 +10745,7 @@
       <c r="C121">
         <v>2026</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="1">
         <v>46119</v>
       </c>
       <c r="F121" t="s">
@@ -10812,7 +10786,7 @@
       <c r="C122">
         <v>2026</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="1">
         <v>45931</v>
       </c>
       <c r="F122" t="s">
@@ -10853,7 +10827,7 @@
       <c r="C123">
         <v>2026</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="1">
         <v>45894</v>
       </c>
       <c r="G123" t="s">
@@ -10891,7 +10865,7 @@
       <c r="C124">
         <v>2026</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="1">
         <v>46119</v>
       </c>
       <c r="F124" t="s">
@@ -10932,7 +10906,7 @@
       <c r="C125">
         <v>2026</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="1">
         <v>45889</v>
       </c>
       <c r="F125" t="s">
@@ -10973,7 +10947,7 @@
       <c r="C126">
         <v>2026</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="1">
         <v>45876</v>
       </c>
       <c r="G126" t="s">
@@ -11043,7 +11017,7 @@
       <c r="C128">
         <v>2026</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="1">
         <v>45876</v>
       </c>
       <c r="F128" t="s">
@@ -11116,7 +11090,7 @@
       <c r="C130">
         <v>2026</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="1">
         <v>46230</v>
       </c>
       <c r="F130" t="s">
@@ -11157,7 +11131,7 @@
       <c r="C131">
         <v>2026</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="1">
         <v>45889</v>
       </c>
       <c r="F131" t="s">
@@ -11198,7 +11172,7 @@
       <c r="C132">
         <v>2026</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="1">
         <v>46230</v>
       </c>
       <c r="F132" t="s">
@@ -11271,7 +11245,7 @@
       <c r="C134">
         <v>2026</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="1">
         <v>46140</v>
       </c>
       <c r="F134" t="s">
@@ -11312,7 +11286,7 @@
       <c r="C135">
         <v>2026</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="1">
         <v>45889</v>
       </c>
       <c r="F135" t="s">
@@ -11353,7 +11327,7 @@
       <c r="C136">
         <v>2026</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="1">
         <v>45952</v>
       </c>
       <c r="F136" t="s">
@@ -11391,7 +11365,7 @@
       <c r="C137">
         <v>2026</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="1">
         <v>46230</v>
       </c>
       <c r="F137" t="s">
@@ -11464,7 +11438,7 @@
       <c r="C139">
         <v>2026</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="1">
         <v>46029</v>
       </c>
       <c r="G139" t="s">
@@ -11502,7 +11476,7 @@
       <c r="C140">
         <v>2026</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="1">
         <v>46029</v>
       </c>
       <c r="G140" t="s">
@@ -11572,7 +11546,7 @@
       <c r="C142">
         <v>2026</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="1">
         <v>46119</v>
       </c>
       <c r="F142" t="s">
@@ -11677,7 +11651,7 @@
       <c r="C145">
         <v>2026</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="1">
         <v>46140</v>
       </c>
       <c r="F145" t="s">
@@ -11718,7 +11692,7 @@
       <c r="C146">
         <v>2026</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="1">
         <v>46230</v>
       </c>
       <c r="F146" t="s">
@@ -11759,7 +11733,7 @@
       <c r="C147">
         <v>2026</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="1">
         <v>46230</v>
       </c>
       <c r="F147" t="s">
@@ -11800,7 +11774,7 @@
       <c r="C148">
         <v>2026</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="1">
         <v>46119</v>
       </c>
       <c r="F148" t="s">
@@ -11841,7 +11815,7 @@
       <c r="C149">
         <v>2026</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="1">
         <v>46230</v>
       </c>
       <c r="F149" t="s">
@@ -11882,7 +11856,7 @@
       <c r="C150">
         <v>2026</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="1">
         <v>46140</v>
       </c>
       <c r="F150" t="s">
@@ -11923,7 +11897,7 @@
       <c r="C151">
         <v>2026</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="1">
         <v>45876</v>
       </c>
       <c r="F151" t="s">
@@ -11996,7 +11970,7 @@
       <c r="C153">
         <v>2026</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="1">
         <v>45863</v>
       </c>
       <c r="F153" t="s">
@@ -12037,7 +12011,7 @@
       <c r="C154">
         <v>2026</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="1">
         <v>45863</v>
       </c>
       <c r="F154" t="s">
@@ -12078,7 +12052,7 @@
       <c r="C155">
         <v>2026</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="1">
         <v>45863</v>
       </c>
       <c r="F155" t="s">
@@ -12119,7 +12093,7 @@
       <c r="C156">
         <v>2026</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="1">
         <v>45860</v>
       </c>
       <c r="F156" t="s">
@@ -12189,7 +12163,7 @@
       <c r="C158">
         <v>2026</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="1">
         <v>46119</v>
       </c>
       <c r="F158" t="s">
@@ -12230,7 +12204,7 @@
       <c r="C159">
         <v>2026</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="1">
         <v>45814</v>
       </c>
       <c r="F159" t="s">
@@ -12271,7 +12245,7 @@
       <c r="C160">
         <v>2026</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="1">
         <v>45817</v>
       </c>
       <c r="F160" t="s">
@@ -12312,7 +12286,7 @@
       <c r="C161">
         <v>2026</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="1">
         <v>45971</v>
       </c>
       <c r="F161" t="s">
@@ -12353,7 +12327,7 @@
       <c r="C162">
         <v>2026</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="1">
         <v>45971</v>
       </c>
       <c r="F162" t="s">
@@ -12394,7 +12368,7 @@
       <c r="C163">
         <v>2026</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="1">
         <v>45860</v>
       </c>
       <c r="G163" t="s">
@@ -12432,7 +12406,7 @@
       <c r="C164">
         <v>2026</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="1">
         <v>45856</v>
       </c>
       <c r="F164" t="s">
@@ -12505,7 +12479,7 @@
       <c r="C166">
         <v>2026</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="1">
         <v>46064</v>
       </c>
       <c r="F166" t="s">
@@ -12546,7 +12520,7 @@
       <c r="C167">
         <v>2026</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="1">
         <v>45982</v>
       </c>
       <c r="G167" t="s">
@@ -12584,7 +12558,7 @@
       <c r="C168">
         <v>2026</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="1">
         <v>46157</v>
       </c>
       <c r="H168" t="s">
@@ -12619,7 +12593,7 @@
       <c r="C169">
         <v>2026</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="1">
         <v>45762</v>
       </c>
       <c r="F169" t="s">
@@ -12660,7 +12634,7 @@
       <c r="C170">
         <v>2026</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="1">
         <v>45816</v>
       </c>
       <c r="F170" t="s">
@@ -12701,7 +12675,7 @@
       <c r="C171">
         <v>2026</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="1">
         <v>45816</v>
       </c>
       <c r="F171" t="s">
@@ -12780,7 +12754,7 @@
       <c r="C173">
         <v>2026</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="1">
         <v>46101</v>
       </c>
       <c r="F173" t="s">
@@ -12821,7 +12795,7 @@
       <c r="C174">
         <v>2026</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="1">
         <v>46101</v>
       </c>
       <c r="F174" t="s">
@@ -12862,7 +12836,7 @@
       <c r="C175">
         <v>2026</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="1">
         <v>46105</v>
       </c>
       <c r="F175" t="s">
@@ -12903,7 +12877,7 @@
       <c r="C176">
         <v>2026</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="1">
         <v>45889</v>
       </c>
       <c r="F176" t="s">
@@ -12944,7 +12918,7 @@
       <c r="C177">
         <v>2026</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="1">
         <v>45814</v>
       </c>
       <c r="F177" t="s">
@@ -12985,7 +12959,7 @@
       <c r="C178">
         <v>2026</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="1">
         <v>45889</v>
       </c>
       <c r="F178" t="s">
@@ -13026,7 +13000,7 @@
       <c r="C179">
         <v>2026</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="1">
         <v>45814</v>
       </c>
       <c r="F179" t="s">
@@ -13067,7 +13041,7 @@
       <c r="C180">
         <v>2026</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="1">
         <v>45889</v>
       </c>
       <c r="F180" t="s">
@@ -13140,7 +13114,7 @@
       <c r="C182">
         <v>2026</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="1">
         <v>46139</v>
       </c>
       <c r="H182" t="s">
@@ -13207,7 +13181,7 @@
       <c r="C184">
         <v>2026</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="1">
         <v>45889</v>
       </c>
       <c r="F184" t="s">
@@ -13280,7 +13254,7 @@
       <c r="C186">
         <v>2026</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="1">
         <v>45814</v>
       </c>
       <c r="F186" t="s">
@@ -13321,7 +13295,7 @@
       <c r="C187">
         <v>2026</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="1">
         <v>45889</v>
       </c>
       <c r="F187" t="s">
@@ -13362,7 +13336,7 @@
       <c r="C188">
         <v>2026</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="1">
         <v>45931</v>
       </c>
       <c r="F188" t="s">
@@ -13403,7 +13377,7 @@
       <c r="C189">
         <v>2026</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="1">
         <v>45889</v>
       </c>
       <c r="F189" t="s">
@@ -13444,7 +13418,7 @@
       <c r="C190">
         <v>2026</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="1">
         <v>45876</v>
       </c>
       <c r="F190" t="s">
@@ -13485,7 +13459,7 @@
       <c r="C191">
         <v>2026</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="1">
         <v>45876</v>
       </c>
       <c r="F191" t="s">
@@ -13558,7 +13532,7 @@
       <c r="C193">
         <v>2026</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="1">
         <v>45876</v>
       </c>
       <c r="F193" t="s">
@@ -13599,7 +13573,7 @@
       <c r="C194">
         <v>2026</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194" s="1">
         <v>46119</v>
       </c>
       <c r="F194" t="s">
@@ -13640,7 +13614,7 @@
       <c r="C195">
         <v>2026</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="1">
         <v>46119</v>
       </c>
       <c r="F195" t="s">
@@ -13681,7 +13655,7 @@
       <c r="C196">
         <v>2026</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196" s="1">
         <v>45961</v>
       </c>
       <c r="F196" t="s">
@@ -13722,7 +13696,7 @@
       <c r="C197">
         <v>2026</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="1">
         <v>45860</v>
       </c>
       <c r="F197" t="s">
@@ -13763,7 +13737,7 @@
       <c r="C198">
         <v>2026</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="1">
         <v>45993</v>
       </c>
       <c r="G198" t="s">
@@ -13801,7 +13775,7 @@
       <c r="C199">
         <v>2026</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="1">
         <v>45853</v>
       </c>
       <c r="F199" t="s">
@@ -13842,7 +13816,7 @@
       <c r="C200">
         <v>2026</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200" s="1">
         <v>46119</v>
       </c>
       <c r="F200" t="s">
@@ -13921,7 +13895,7 @@
       <c r="C202">
         <v>2026</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202" s="1">
         <v>46191</v>
       </c>
       <c r="F202" t="s">
@@ -13962,7 +13936,7 @@
       <c r="C203">
         <v>2026</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203" s="1">
         <v>46191</v>
       </c>
       <c r="F203" t="s">
@@ -14003,7 +13977,7 @@
       <c r="C204">
         <v>2026</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="1">
         <v>46191</v>
       </c>
       <c r="F204" t="s">
@@ -14044,7 +14018,7 @@
       <c r="C205">
         <v>2026</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="1">
         <v>45932</v>
       </c>
       <c r="G205" t="s">
@@ -14082,7 +14056,7 @@
       <c r="C206">
         <v>2026</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206" s="1">
         <v>46191</v>
       </c>
       <c r="F206" t="s">
@@ -14123,7 +14097,7 @@
       <c r="C207">
         <v>2026</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207" s="1">
         <v>46119</v>
       </c>
       <c r="F207" t="s">
@@ -14164,7 +14138,7 @@
       <c r="C208">
         <v>2026</v>
       </c>
-      <c r="D208" s="2">
+      <c r="D208" s="1">
         <v>45946</v>
       </c>
       <c r="G208" t="s">
@@ -14202,7 +14176,7 @@
       <c r="C209">
         <v>2026</v>
       </c>
-      <c r="D209" s="2">
+      <c r="D209" s="1">
         <v>45937</v>
       </c>
       <c r="F209" t="s">
@@ -14243,7 +14217,7 @@
       <c r="C210">
         <v>2026</v>
       </c>
-      <c r="D210" s="2">
+      <c r="D210" s="1">
         <v>45849</v>
       </c>
       <c r="F210" t="s">
@@ -14284,7 +14258,7 @@
       <c r="C211">
         <v>2026</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211" s="1">
         <v>45876</v>
       </c>
       <c r="F211" t="s">
@@ -14325,7 +14299,7 @@
       <c r="C212">
         <v>2026</v>
       </c>
-      <c r="D212" s="2">
+      <c r="D212" s="1">
         <v>46008</v>
       </c>
       <c r="F212" t="s">
@@ -14439,7 +14413,7 @@
       <c r="C215">
         <v>2026</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215" s="1">
         <v>45973</v>
       </c>
       <c r="F215" t="s">
@@ -14480,7 +14454,7 @@
       <c r="C216">
         <v>2026</v>
       </c>
-      <c r="D216" s="2">
+      <c r="D216" s="1">
         <v>46014</v>
       </c>
       <c r="F216" t="s">
@@ -14521,7 +14495,7 @@
       <c r="C217">
         <v>2026</v>
       </c>
-      <c r="D217" s="2">
+      <c r="D217" s="1">
         <v>45876</v>
       </c>
       <c r="F217" t="s">
@@ -14562,7 +14536,7 @@
       <c r="C218">
         <v>2026</v>
       </c>
-      <c r="D218" s="2">
+      <c r="D218" s="1">
         <v>45937</v>
       </c>
       <c r="F218" t="s">
@@ -14603,7 +14577,7 @@
       <c r="C219">
         <v>2026</v>
       </c>
-      <c r="D219" s="2">
+      <c r="D219" s="1">
         <v>45980</v>
       </c>
       <c r="F219" t="s">
@@ -14964,7 +14938,7 @@
       <c r="C230">
         <v>2026</v>
       </c>
-      <c r="D230" s="2">
+      <c r="D230" s="1">
         <v>45979</v>
       </c>
       <c r="F230" t="s">
@@ -15005,7 +14979,7 @@
       <c r="C231">
         <v>2026</v>
       </c>
-      <c r="D231" s="2">
+      <c r="D231" s="1">
         <v>45979</v>
       </c>
       <c r="F231" t="s">
@@ -15046,7 +15020,7 @@
       <c r="C232">
         <v>2026</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232" s="1">
         <v>45979</v>
       </c>
       <c r="F232" t="s">
@@ -15087,7 +15061,7 @@
       <c r="C233">
         <v>2026</v>
       </c>
-      <c r="D233" s="2">
+      <c r="D233" s="1">
         <v>45971</v>
       </c>
       <c r="F233" t="s">
@@ -15128,7 +15102,7 @@
       <c r="C234">
         <v>2026</v>
       </c>
-      <c r="D234" s="2">
+      <c r="D234" s="1">
         <v>45971</v>
       </c>
       <c r="F234" t="s">
@@ -15169,7 +15143,7 @@
       <c r="C235">
         <v>2026</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235" s="1">
         <v>45971</v>
       </c>
       <c r="F235" t="s">
@@ -15210,7 +15184,7 @@
       <c r="C236">
         <v>2026</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236" s="1">
         <v>45889</v>
       </c>
       <c r="F236" t="s">
@@ -15347,7 +15321,7 @@
       <c r="C240">
         <v>2026</v>
       </c>
-      <c r="D240" s="2">
+      <c r="D240" s="1">
         <v>45859</v>
       </c>
       <c r="F240" t="s">
@@ -15388,7 +15362,7 @@
       <c r="C241">
         <v>2026</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241" s="1">
         <v>45918</v>
       </c>
       <c r="F241" t="s">
@@ -15461,7 +15435,7 @@
       <c r="C243">
         <v>2026</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="1">
         <v>45874</v>
       </c>
       <c r="F243" t="s">
@@ -15502,7 +15476,7 @@
       <c r="C244">
         <v>2026</v>
       </c>
-      <c r="D244" s="2">
+      <c r="D244" s="1">
         <v>45975</v>
       </c>
       <c r="F244" t="s">
@@ -15540,7 +15514,7 @@
       <c r="C245">
         <v>2026</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245" s="1">
         <v>45975</v>
       </c>
       <c r="F245" t="s">
@@ -15578,7 +15552,7 @@
       <c r="C246">
         <v>2026</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="1">
         <v>45975</v>
       </c>
       <c r="F246" t="s">
@@ -15840,7 +15814,7 @@
       <c r="C254">
         <v>2026</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254" s="1">
         <v>46119</v>
       </c>
       <c r="F254" t="s">
@@ -15945,7 +15919,7 @@
       <c r="C257">
         <v>2026</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257" s="1">
         <v>45802</v>
       </c>
       <c r="F257" t="s">
@@ -15986,7 +15960,7 @@
       <c r="C258">
         <v>2026</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="1">
         <v>45804</v>
       </c>
       <c r="F258" t="s">
@@ -16027,7 +16001,7 @@
       <c r="C259">
         <v>2026</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="1">
         <v>46097</v>
       </c>
       <c r="F259" t="s">
@@ -16068,7 +16042,7 @@
       <c r="C260">
         <v>2026</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="1">
         <v>45860</v>
       </c>
       <c r="G260" t="s">
@@ -16106,7 +16080,7 @@
       <c r="C261">
         <v>2026</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="1">
         <v>45889</v>
       </c>
       <c r="F261" t="s">
@@ -16147,7 +16121,7 @@
       <c r="C262">
         <v>2026</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="1">
         <v>45744</v>
       </c>
       <c r="F262" t="s">
@@ -16188,7 +16162,7 @@
       <c r="C263">
         <v>2026</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="1">
         <v>45744</v>
       </c>
       <c r="F263" t="s">
@@ -16229,7 +16203,7 @@
       <c r="C264">
         <v>2026</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="1">
         <v>46408</v>
       </c>
       <c r="F264" t="s">
@@ -16273,7 +16247,7 @@
       <c r="C265">
         <v>2026</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="1">
         <v>45898</v>
       </c>
       <c r="F265" t="s">
@@ -16314,7 +16288,7 @@
       <c r="C266">
         <v>2026</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="1">
         <v>45971</v>
       </c>
       <c r="F266" t="s">
@@ -16355,7 +16329,7 @@
       <c r="C267">
         <v>2026</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="1">
         <v>45744</v>
       </c>
       <c r="F267" t="s">
@@ -16396,7 +16370,7 @@
       <c r="C268">
         <v>2026</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="1">
         <v>46092</v>
       </c>
       <c r="F268" t="s">
@@ -16437,7 +16411,7 @@
       <c r="C269">
         <v>2026</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="1">
         <v>46204</v>
       </c>
       <c r="F269" t="s">
@@ -16481,7 +16455,7 @@
       <c r="C270">
         <v>2026</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="1">
         <v>46185</v>
       </c>
       <c r="H270" t="s">
@@ -16516,7 +16490,7 @@
       <c r="C271">
         <v>2026</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="1">
         <v>45890</v>
       </c>
       <c r="G271" t="s">
@@ -16554,7 +16528,7 @@
       <c r="C272">
         <v>2026</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="1">
         <v>46185</v>
       </c>
       <c r="H272" t="s">
@@ -16589,7 +16563,7 @@
       <c r="C273">
         <v>2026</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="1">
         <v>46175</v>
       </c>
       <c r="F273" t="s">
@@ -16630,7 +16604,7 @@
       <c r="C274">
         <v>2026</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="1">
         <v>45890</v>
       </c>
       <c r="G274" t="s">
@@ -16668,7 +16642,7 @@
       <c r="C275">
         <v>2026</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="1">
         <v>46175</v>
       </c>
       <c r="F275" t="s">
@@ -16709,7 +16683,7 @@
       <c r="C276">
         <v>2026</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="1">
         <v>46185</v>
       </c>
       <c r="G276" t="s">
@@ -16747,7 +16721,7 @@
       <c r="C277">
         <v>2026</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="1">
         <v>45890</v>
       </c>
       <c r="G277" t="s">
@@ -16785,7 +16759,7 @@
       <c r="C278">
         <v>2026</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="1">
         <v>45890</v>
       </c>
       <c r="G278" t="s">
@@ -16823,7 +16797,7 @@
       <c r="C279">
         <v>2026</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="1">
         <v>45890</v>
       </c>
       <c r="G279" t="s">
@@ -16861,7 +16835,7 @@
       <c r="C280">
         <v>2026</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="1">
         <v>46175</v>
       </c>
       <c r="F280" t="s">
@@ -16902,7 +16876,7 @@
       <c r="C281">
         <v>2026</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="1">
         <v>45890</v>
       </c>
       <c r="G281" t="s">
@@ -16940,7 +16914,7 @@
       <c r="C282">
         <v>2026</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="1">
         <v>46119</v>
       </c>
       <c r="F282" t="s">
@@ -16981,7 +16955,7 @@
       <c r="C283">
         <v>2026</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="1">
         <v>46119</v>
       </c>
       <c r="F283" t="s">
@@ -17022,7 +16996,7 @@
       <c r="C284">
         <v>2026</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="1">
         <v>46119</v>
       </c>
       <c r="F284" t="s">
@@ -17127,7 +17101,7 @@
       <c r="C287">
         <v>2026</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="1">
         <v>45856</v>
       </c>
       <c r="F287" t="s">
@@ -17168,7 +17142,7 @@
       <c r="C288">
         <v>2026</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="1">
         <v>45769</v>
       </c>
       <c r="F288" t="s">
@@ -17209,7 +17183,7 @@
       <c r="C289">
         <v>2026</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="1">
         <v>45769</v>
       </c>
       <c r="F289" t="s">
@@ -17250,7 +17224,7 @@
       <c r="C290">
         <v>2026</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="1">
         <v>45769</v>
       </c>
       <c r="F290" t="s">
@@ -17291,7 +17265,7 @@
       <c r="C291">
         <v>2026</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="1">
         <v>45769</v>
       </c>
       <c r="F291" t="s">
@@ -17332,7 +17306,7 @@
       <c r="C292">
         <v>2026</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292" s="1">
         <v>45769</v>
       </c>
       <c r="F292" t="s">
@@ -17373,7 +17347,7 @@
       <c r="C293">
         <v>2026</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293" s="1">
         <v>45769</v>
       </c>
       <c r="F293" t="s">
@@ -17414,7 +17388,7 @@
       <c r="C294">
         <v>2026</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294" s="1">
         <v>45769</v>
       </c>
       <c r="F294" t="s">
@@ -17455,7 +17429,7 @@
       <c r="C295">
         <v>2026</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295" s="1">
         <v>46147</v>
       </c>
       <c r="H295" t="s">
@@ -17490,7 +17464,7 @@
       <c r="C296">
         <v>2026</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296" s="1">
         <v>46147</v>
       </c>
       <c r="H296" t="s">
@@ -17525,7 +17499,7 @@
       <c r="C297">
         <v>2026</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="1">
         <v>46147</v>
       </c>
       <c r="H297" t="s">
@@ -17560,7 +17534,7 @@
       <c r="C298">
         <v>2026</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298" s="1">
         <v>45814</v>
       </c>
       <c r="F298" t="s">
@@ -17633,7 +17607,7 @@
       <c r="C300">
         <v>2026</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="1">
         <v>45860</v>
       </c>
       <c r="F300" t="s">
@@ -17674,7 +17648,7 @@
       <c r="C301">
         <v>2026</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="1">
         <v>45971</v>
       </c>
       <c r="F301" t="s">
@@ -17715,7 +17689,7 @@
       <c r="C302">
         <v>2026</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302" s="1">
         <v>45863</v>
       </c>
       <c r="F302" t="s">
@@ -17756,7 +17730,7 @@
       <c r="C303">
         <v>2026</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303" s="1">
         <v>45905</v>
       </c>
       <c r="G303" t="s">
@@ -17794,7 +17768,7 @@
       <c r="C304">
         <v>2026</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304" s="1">
         <v>45971</v>
       </c>
       <c r="F304" t="s">
@@ -17835,7 +17809,7 @@
       <c r="C305">
         <v>2026</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305" s="1">
         <v>45971</v>
       </c>
       <c r="F305" t="s">
@@ -17876,7 +17850,7 @@
       <c r="C306">
         <v>2026</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306" s="1">
         <v>45744</v>
       </c>
       <c r="F306" t="s">
@@ -17917,7 +17891,7 @@
       <c r="C307">
         <v>2026</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="1">
         <v>45814</v>
       </c>
       <c r="F307" t="s">
@@ -17958,7 +17932,7 @@
       <c r="C308">
         <v>2026</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="1">
         <v>45807</v>
       </c>
       <c r="F308" t="s">
@@ -17999,7 +17973,7 @@
       <c r="C309">
         <v>2026</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309" s="1">
         <v>45802</v>
       </c>
       <c r="F309" t="s">
@@ -18040,7 +18014,7 @@
       <c r="C310">
         <v>2026</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310" s="1">
         <v>45802</v>
       </c>
       <c r="F310" t="s">
@@ -18081,7 +18055,7 @@
       <c r="C311">
         <v>2026</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311" s="1">
         <v>45802</v>
       </c>
       <c r="F311" t="s">
@@ -18122,7 +18096,7 @@
       <c r="C312">
         <v>2026</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312" s="1">
         <v>45897</v>
       </c>
       <c r="H312" t="s">
@@ -18157,7 +18131,7 @@
       <c r="C313">
         <v>2026</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313" s="1">
         <v>45802</v>
       </c>
       <c r="F313" t="s">
@@ -18198,7 +18172,7 @@
       <c r="C314">
         <v>2026</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314" s="1">
         <v>45802</v>
       </c>
       <c r="F314" t="s">
@@ -18239,7 +18213,7 @@
       <c r="C315">
         <v>2026</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="1">
         <v>45876</v>
       </c>
       <c r="F315" t="s">
@@ -18280,7 +18254,7 @@
       <c r="C316">
         <v>2026</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316" s="1">
         <v>45889</v>
       </c>
       <c r="F316" t="s">
@@ -18321,7 +18295,7 @@
       <c r="C317">
         <v>2026</v>
       </c>
-      <c r="D317" s="2">
+      <c r="D317" s="1">
         <v>45876</v>
       </c>
       <c r="F317" t="s">
@@ -18362,7 +18336,7 @@
       <c r="C318">
         <v>2026</v>
       </c>
-      <c r="D318" s="2">
+      <c r="D318" s="1">
         <v>45926</v>
       </c>
       <c r="F318" t="s">
@@ -18403,7 +18377,7 @@
       <c r="C319">
         <v>2026</v>
       </c>
-      <c r="D319" s="2">
+      <c r="D319" s="1">
         <v>45909</v>
       </c>
       <c r="F319" t="s">
@@ -18444,7 +18418,7 @@
       <c r="C320">
         <v>2026</v>
       </c>
-      <c r="D320" s="2">
+      <c r="D320" s="1">
         <v>46119</v>
       </c>
       <c r="F320" t="s">
@@ -18549,7 +18523,7 @@
       <c r="C323">
         <v>2026</v>
       </c>
-      <c r="D323" s="2">
+      <c r="D323" s="1">
         <v>46119</v>
       </c>
       <c r="F323" t="s">
@@ -18590,7 +18564,7 @@
       <c r="C324">
         <v>2026</v>
       </c>
-      <c r="D324" s="2">
+      <c r="D324" s="1">
         <v>46119</v>
       </c>
       <c r="F324" t="s">
@@ -18727,7 +18701,7 @@
       <c r="C328">
         <v>2026</v>
       </c>
-      <c r="D328" s="2">
+      <c r="D328" s="1">
         <v>46086</v>
       </c>
       <c r="G328" t="s">
@@ -18797,7 +18771,7 @@
       <c r="C330">
         <v>2026</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330" s="1">
         <v>45965</v>
       </c>
       <c r="F330" t="s">
@@ -18838,7 +18812,7 @@
       <c r="C331">
         <v>2026</v>
       </c>
-      <c r="D331" s="2">
+      <c r="D331" s="1">
         <v>46064</v>
       </c>
       <c r="H331" t="s">
@@ -18870,7 +18844,7 @@
       <c r="C332">
         <v>2026</v>
       </c>
-      <c r="D332" s="2">
+      <c r="D332" s="1">
         <v>46049</v>
       </c>
       <c r="F332" t="s">
@@ -18911,7 +18885,7 @@
       <c r="C333">
         <v>2026</v>
       </c>
-      <c r="D333" s="2">
+      <c r="D333" s="1">
         <v>45996</v>
       </c>
       <c r="G333" t="s">
@@ -18949,7 +18923,7 @@
       <c r="C334">
         <v>2026</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334" s="1">
         <v>45996</v>
       </c>
       <c r="G334" t="s">
@@ -18987,7 +18961,7 @@
       <c r="C335">
         <v>2026</v>
       </c>
-      <c r="D335" s="2">
+      <c r="D335" s="1">
         <v>45989</v>
       </c>
       <c r="G335" t="s">
@@ -19025,7 +18999,7 @@
       <c r="C336">
         <v>2026</v>
       </c>
-      <c r="D336" s="2">
+      <c r="D336" s="1">
         <v>46156</v>
       </c>
       <c r="H336" t="s">
@@ -19060,7 +19034,7 @@
       <c r="C337">
         <v>2026</v>
       </c>
-      <c r="D337" s="2">
+      <c r="D337" s="1">
         <v>45996</v>
       </c>
       <c r="G337" t="s">
@@ -19098,7 +19072,7 @@
       <c r="C338">
         <v>2026</v>
       </c>
-      <c r="D338" s="2">
+      <c r="D338" s="1">
         <v>45989</v>
       </c>
       <c r="G338" t="s">
@@ -19136,7 +19110,7 @@
       <c r="C339">
         <v>2026</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339" s="1">
         <v>46002</v>
       </c>
       <c r="G339" t="s">
@@ -19174,7 +19148,7 @@
       <c r="C340">
         <v>2026</v>
       </c>
-      <c r="D340" s="2">
+      <c r="D340" s="1">
         <v>46002</v>
       </c>
       <c r="G340" t="s">
@@ -19212,7 +19186,7 @@
       <c r="C341">
         <v>2026</v>
       </c>
-      <c r="D341" s="2">
+      <c r="D341" s="1">
         <v>45996</v>
       </c>
       <c r="G341" t="s">
@@ -19250,7 +19224,7 @@
       <c r="C342">
         <v>2026</v>
       </c>
-      <c r="D342" s="2">
+      <c r="D342" s="1">
         <v>46002</v>
       </c>
       <c r="G342" t="s">
@@ -19288,7 +19262,7 @@
       <c r="C343">
         <v>2026</v>
       </c>
-      <c r="D343" s="2">
+      <c r="D343" s="1">
         <v>46031</v>
       </c>
       <c r="G343" t="s">
@@ -19326,7 +19300,7 @@
       <c r="C344">
         <v>2026</v>
       </c>
-      <c r="D344" s="2">
+      <c r="D344" s="1">
         <v>46153</v>
       </c>
       <c r="F344" t="s">
@@ -19367,7 +19341,7 @@
       <c r="C345">
         <v>2026</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345" s="1">
         <v>46135</v>
       </c>
       <c r="F345" t="s">
@@ -19472,7 +19446,7 @@
       <c r="C348">
         <v>2026</v>
       </c>
-      <c r="D348" s="2">
+      <c r="D348" s="1">
         <v>46230</v>
       </c>
       <c r="F348" t="s">
@@ -19577,7 +19551,7 @@
       <c r="C351">
         <v>2026</v>
       </c>
-      <c r="D351" s="2">
+      <c r="D351" s="1">
         <v>45996</v>
       </c>
       <c r="G351" t="s">
@@ -19615,7 +19589,7 @@
       <c r="C352">
         <v>2026</v>
       </c>
-      <c r="D352" s="2">
+      <c r="D352" s="1">
         <v>45996</v>
       </c>
       <c r="G352" t="s">
@@ -19685,7 +19659,7 @@
       <c r="C354">
         <v>2026</v>
       </c>
-      <c r="D354" s="2">
+      <c r="D354" s="1">
         <v>46164</v>
       </c>
       <c r="H354" t="s">
@@ -19720,7 +19694,7 @@
       <c r="C355">
         <v>2026</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355" s="1">
         <v>46020</v>
       </c>
       <c r="G355" t="s">
@@ -19758,7 +19732,7 @@
       <c r="C356">
         <v>2026</v>
       </c>
-      <c r="D356" s="2">
+      <c r="D356" s="1">
         <v>46225</v>
       </c>
       <c r="F356" t="s">
@@ -19802,7 +19776,7 @@
       <c r="C357">
         <v>2026</v>
       </c>
-      <c r="D357" s="2">
+      <c r="D357" s="1">
         <v>46176</v>
       </c>
       <c r="H357" t="s">
@@ -19837,7 +19811,7 @@
       <c r="C358">
         <v>2026</v>
       </c>
-      <c r="D358" s="2">
+      <c r="D358" s="1">
         <v>46086</v>
       </c>
       <c r="G358" t="s">
@@ -19875,7 +19849,7 @@
       <c r="C359">
         <v>2026</v>
       </c>
-      <c r="D359" s="2">
+      <c r="D359" s="1">
         <v>46052</v>
       </c>
       <c r="G359" t="s">
@@ -19951,7 +19925,7 @@
       <c r="C361">
         <v>2026</v>
       </c>
-      <c r="D361" s="2">
+      <c r="D361" s="1">
         <v>46010</v>
       </c>
       <c r="G361" t="s">
@@ -19989,7 +19963,7 @@
       <c r="C362">
         <v>2026</v>
       </c>
-      <c r="D362" s="2">
+      <c r="D362" s="1">
         <v>46010</v>
       </c>
       <c r="G362" t="s">
@@ -20059,7 +20033,7 @@
       <c r="C364">
         <v>2026</v>
       </c>
-      <c r="D364" s="2">
+      <c r="D364" s="1">
         <v>46079</v>
       </c>
       <c r="F364" t="s">
@@ -20100,7 +20074,7 @@
       <c r="C365">
         <v>2026</v>
       </c>
-      <c r="D365" s="2">
+      <c r="D365" s="1">
         <v>46010</v>
       </c>
       <c r="G365" t="s">
@@ -20138,7 +20112,7 @@
       <c r="C366">
         <v>2026</v>
       </c>
-      <c r="D366" s="2">
+      <c r="D366" s="1">
         <v>46010</v>
       </c>
       <c r="G366" t="s">
@@ -20176,7 +20150,7 @@
       <c r="C367">
         <v>2026</v>
       </c>
-      <c r="D367" s="2">
+      <c r="D367" s="1">
         <v>46230</v>
       </c>
       <c r="F367" t="s">
@@ -20220,7 +20194,7 @@
       <c r="C368">
         <v>2026</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368" s="1">
         <v>46063</v>
       </c>
       <c r="G368" t="s">
@@ -20258,7 +20232,7 @@
       <c r="C369">
         <v>2026</v>
       </c>
-      <c r="D369" s="2">
+      <c r="D369" s="1">
         <v>46063</v>
       </c>
       <c r="F369" t="s">
@@ -20299,7 +20273,7 @@
       <c r="C370">
         <v>2026</v>
       </c>
-      <c r="D370" s="2">
+      <c r="D370" s="1">
         <v>46063</v>
       </c>
       <c r="F370" t="s">
@@ -20340,7 +20314,7 @@
       <c r="C371">
         <v>2026</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371" s="1">
         <v>46063</v>
       </c>
       <c r="F371" t="s">
@@ -20381,7 +20355,7 @@
       <c r="C372">
         <v>2026</v>
       </c>
-      <c r="D372" s="2">
+      <c r="D372" s="1">
         <v>46063</v>
       </c>
       <c r="G372" t="s">
@@ -20547,7 +20521,7 @@
       <c r="C377">
         <v>2026</v>
       </c>
-      <c r="D377" s="2">
+      <c r="D377" s="1">
         <v>46114</v>
       </c>
       <c r="F377" t="s">
@@ -20588,7 +20562,7 @@
       <c r="C378">
         <v>2026</v>
       </c>
-      <c r="D378" s="2">
+      <c r="D378" s="1">
         <v>46191</v>
       </c>
       <c r="F378" t="s">
@@ -20629,7 +20603,7 @@
       <c r="C379">
         <v>2026</v>
       </c>
-      <c r="D379" s="2">
+      <c r="D379" s="1">
         <v>46230</v>
       </c>
       <c r="F379" t="s">
@@ -20670,7 +20644,7 @@
       <c r="C380">
         <v>2026</v>
       </c>
-      <c r="D380" s="2">
+      <c r="D380" s="1">
         <v>46230</v>
       </c>
       <c r="F380" t="s">
@@ -20711,7 +20685,7 @@
       <c r="C381">
         <v>2026</v>
       </c>
-      <c r="D381" s="2">
+      <c r="D381" s="1">
         <v>46230</v>
       </c>
       <c r="F381" t="s">
@@ -20752,7 +20726,7 @@
       <c r="C382">
         <v>2026</v>
       </c>
-      <c r="D382" s="2">
+      <c r="D382" s="1">
         <v>46230</v>
       </c>
       <c r="F382" t="s">
@@ -20793,7 +20767,7 @@
       <c r="C383">
         <v>2026</v>
       </c>
-      <c r="D383" s="2">
+      <c r="D383" s="1">
         <v>46230</v>
       </c>
       <c r="F383" t="s">
@@ -20834,7 +20808,7 @@
       <c r="C384">
         <v>2026</v>
       </c>
-      <c r="D384" s="2">
+      <c r="D384" s="1">
         <v>46230</v>
       </c>
       <c r="F384" t="s">
@@ -20875,7 +20849,7 @@
       <c r="C385">
         <v>2026</v>
       </c>
-      <c r="D385" s="2">
+      <c r="D385" s="1">
         <v>46230</v>
       </c>
       <c r="F385" t="s">
@@ -20948,7 +20922,7 @@
       <c r="C387">
         <v>2026</v>
       </c>
-      <c r="D387" s="2">
+      <c r="D387" s="1">
         <v>45996</v>
       </c>
       <c r="G387" t="s">
@@ -21178,7 +21152,7 @@
       <c r="C394">
         <v>2026</v>
       </c>
-      <c r="D394" s="2">
+      <c r="D394" s="1">
         <v>46052</v>
       </c>
       <c r="F394" t="s">
@@ -21219,7 +21193,7 @@
       <c r="C395">
         <v>2026</v>
       </c>
-      <c r="D395" s="2">
+      <c r="D395" s="1">
         <v>46057</v>
       </c>
       <c r="F395" t="s">
@@ -21260,7 +21234,7 @@
       <c r="C396">
         <v>2026</v>
       </c>
-      <c r="D396" s="2">
+      <c r="D396" s="1">
         <v>46112</v>
       </c>
       <c r="F396" t="s">
@@ -21333,7 +21307,7 @@
       <c r="C398">
         <v>2026</v>
       </c>
-      <c r="D398" s="2">
+      <c r="D398" s="1">
         <v>46063</v>
       </c>
       <c r="G398" t="s">
@@ -21371,7 +21345,7 @@
       <c r="C399">
         <v>2026</v>
       </c>
-      <c r="D399" s="2">
+      <c r="D399" s="1">
         <v>46048</v>
       </c>
       <c r="G399" t="s">
@@ -21409,7 +21383,7 @@
       <c r="C400">
         <v>2026</v>
       </c>
-      <c r="D400" s="2">
+      <c r="D400" s="1">
         <v>46063</v>
       </c>
       <c r="H400" t="s">
@@ -21476,7 +21450,7 @@
       <c r="C402">
         <v>2026</v>
       </c>
-      <c r="D402" s="2">
+      <c r="D402" s="1">
         <v>46119</v>
       </c>
       <c r="F402" t="s">
@@ -21549,7 +21523,7 @@
       <c r="C404">
         <v>2026</v>
       </c>
-      <c r="D404" s="2">
+      <c r="D404" s="1">
         <v>46119</v>
       </c>
       <c r="F404" t="s">
@@ -21590,7 +21564,7 @@
       <c r="C405">
         <v>2026</v>
       </c>
-      <c r="D405" s="2">
+      <c r="D405" s="1">
         <v>46113</v>
       </c>
       <c r="F405" t="s">
@@ -21631,7 +21605,7 @@
       <c r="C406">
         <v>2026</v>
       </c>
-      <c r="D406" s="2">
+      <c r="D406" s="1">
         <v>46104</v>
       </c>
       <c r="F406" t="s">
@@ -21672,7 +21646,7 @@
       <c r="C407">
         <v>2026</v>
       </c>
-      <c r="D407" s="2">
+      <c r="D407" s="1">
         <v>46135</v>
       </c>
       <c r="H407" t="s">
@@ -21739,7 +21713,7 @@
       <c r="C409">
         <v>2026</v>
       </c>
-      <c r="D409" s="2">
+      <c r="D409" s="1">
         <v>46230</v>
       </c>
       <c r="F409" t="s">
@@ -21780,7 +21754,7 @@
       <c r="C410">
         <v>2026</v>
       </c>
-      <c r="D410" s="2">
+      <c r="D410" s="1">
         <v>46086</v>
       </c>
       <c r="G410" t="s">
@@ -21818,7 +21792,7 @@
       <c r="C411">
         <v>2026</v>
       </c>
-      <c r="D411" s="2">
+      <c r="D411" s="1">
         <v>46086</v>
       </c>
       <c r="G411" t="s">
@@ -21856,7 +21830,7 @@
       <c r="C412">
         <v>2026</v>
       </c>
-      <c r="D412" s="2">
+      <c r="D412" s="1">
         <v>46086</v>
       </c>
       <c r="H412" t="s">
@@ -21891,7 +21865,7 @@
       <c r="C413">
         <v>2026</v>
       </c>
-      <c r="D413" s="2">
+      <c r="D413" s="1">
         <v>46230</v>
       </c>
       <c r="F413" t="s">
@@ -22028,7 +22002,7 @@
       <c r="C417">
         <v>2026</v>
       </c>
-      <c r="D417" s="2">
+      <c r="D417" s="1">
         <v>46176</v>
       </c>
       <c r="H417" t="s">
@@ -22063,7 +22037,7 @@
       <c r="C418">
         <v>2026</v>
       </c>
-      <c r="D418" s="2">
+      <c r="D418" s="1">
         <v>46147</v>
       </c>
       <c r="H418" t="s">
@@ -22098,7 +22072,7 @@
       <c r="C419">
         <v>2026</v>
       </c>
-      <c r="D419" s="2">
+      <c r="D419" s="1">
         <v>46135</v>
       </c>
       <c r="H419" t="s">
@@ -22165,7 +22139,7 @@
       <c r="C421">
         <v>2026</v>
       </c>
-      <c r="D421" s="2">
+      <c r="D421" s="1">
         <v>46227</v>
       </c>
       <c r="G421" t="s">
@@ -22206,7 +22180,7 @@
       <c r="C422">
         <v>2026</v>
       </c>
-      <c r="D422" s="2">
+      <c r="D422" s="1">
         <v>46230</v>
       </c>
       <c r="F422" t="s">
@@ -22247,7 +22221,7 @@
       <c r="C423">
         <v>2026</v>
       </c>
-      <c r="D423" s="2">
+      <c r="D423" s="1">
         <v>46083</v>
       </c>
       <c r="F423" t="s">
@@ -22288,7 +22262,7 @@
       <c r="C424">
         <v>2026</v>
       </c>
-      <c r="D424" s="2">
+      <c r="D424" s="1">
         <v>46083</v>
       </c>
       <c r="G424" t="s">
@@ -22326,7 +22300,7 @@
       <c r="C425">
         <v>2026</v>
       </c>
-      <c r="D425" s="2">
+      <c r="D425" s="1">
         <v>46083</v>
       </c>
       <c r="F425" t="s">
@@ -22367,7 +22341,7 @@
       <c r="C426">
         <v>2026</v>
       </c>
-      <c r="D426" s="2">
+      <c r="D426" s="1">
         <v>46127</v>
       </c>
       <c r="F426" t="s">
@@ -22408,7 +22382,7 @@
       <c r="C427">
         <v>2026</v>
       </c>
-      <c r="D427" s="2">
+      <c r="D427" s="1">
         <v>46100</v>
       </c>
       <c r="F427" t="s">
@@ -22606,7 +22580,7 @@
       <c r="C433">
         <v>2026</v>
       </c>
-      <c r="D433" s="2">
+      <c r="D433" s="1">
         <v>46230</v>
       </c>
       <c r="F433" t="s">
@@ -22647,7 +22621,7 @@
       <c r="C434">
         <v>2026</v>
       </c>
-      <c r="D434" s="2">
+      <c r="D434" s="1">
         <v>46079</v>
       </c>
       <c r="H434" t="s">
@@ -22778,7 +22752,7 @@
       <c r="C438">
         <v>2026</v>
       </c>
-      <c r="D438" s="2">
+      <c r="D438" s="1">
         <v>46176</v>
       </c>
       <c r="F438" t="s">
@@ -22819,7 +22793,7 @@
       <c r="C439">
         <v>2026</v>
       </c>
-      <c r="D439" s="2">
+      <c r="D439" s="1">
         <v>46176</v>
       </c>
       <c r="F439" t="s">
@@ -22860,7 +22834,7 @@
       <c r="C440">
         <v>2026</v>
       </c>
-      <c r="D440" s="2">
+      <c r="D440" s="1">
         <v>46155</v>
       </c>
       <c r="F440" t="s">
@@ -22901,7 +22875,7 @@
       <c r="C441">
         <v>2026</v>
       </c>
-      <c r="D441" s="2">
+      <c r="D441" s="1">
         <v>46155</v>
       </c>
       <c r="G441" t="s">
@@ -22939,7 +22913,7 @@
       <c r="C442">
         <v>2026</v>
       </c>
-      <c r="D442" s="2">
+      <c r="D442" s="1">
         <v>46129</v>
       </c>
       <c r="F442" t="s">
@@ -22980,7 +22954,7 @@
       <c r="C443">
         <v>2026</v>
       </c>
-      <c r="D443" s="2">
+      <c r="D443" s="1">
         <v>46119</v>
       </c>
       <c r="F443" t="s">
@@ -23021,7 +22995,7 @@
       <c r="C444">
         <v>2026</v>
       </c>
-      <c r="D444" s="2">
+      <c r="D444" s="1">
         <v>46135</v>
       </c>
       <c r="H444" t="s">
@@ -23056,7 +23030,7 @@
       <c r="C445">
         <v>2026</v>
       </c>
-      <c r="D445" s="2">
+      <c r="D445" s="1">
         <v>46127</v>
       </c>
       <c r="H445" t="s">
@@ -23091,7 +23065,7 @@
       <c r="C446">
         <v>2026</v>
       </c>
-      <c r="D446" s="2">
+      <c r="D446" s="1">
         <v>46127</v>
       </c>
       <c r="H446" t="s">
@@ -23158,7 +23132,7 @@
       <c r="C448">
         <v>2026</v>
       </c>
-      <c r="D448" s="2">
+      <c r="D448" s="1">
         <v>46175</v>
       </c>
       <c r="F448" t="s">
@@ -23199,7 +23173,7 @@
       <c r="C449">
         <v>2026</v>
       </c>
-      <c r="D449" s="2">
+      <c r="D449" s="1">
         <v>46139</v>
       </c>
       <c r="H449" t="s">
@@ -23234,7 +23208,7 @@
       <c r="C450">
         <v>2026</v>
       </c>
-      <c r="D450" s="2">
+      <c r="D450" s="1">
         <v>46155</v>
       </c>
       <c r="H450" t="s">
@@ -23269,7 +23243,7 @@
       <c r="C451">
         <v>2026</v>
       </c>
-      <c r="D451" s="2">
+      <c r="D451" s="1">
         <v>46175</v>
       </c>
       <c r="F451" t="s">
@@ -23342,7 +23316,7 @@
       <c r="C453">
         <v>2026</v>
       </c>
-      <c r="D453" s="2">
+      <c r="D453" s="1">
         <v>46156</v>
       </c>
       <c r="F453" t="s">
@@ -23383,7 +23357,7 @@
       <c r="C454">
         <v>2026</v>
       </c>
-      <c r="D454" s="2">
+      <c r="D454" s="1">
         <v>46157</v>
       </c>
       <c r="G454" t="s">
@@ -23421,7 +23395,7 @@
       <c r="C455">
         <v>2026</v>
       </c>
-      <c r="D455" s="2">
+      <c r="D455" s="1">
         <v>46183</v>
       </c>
       <c r="H455" t="s">
@@ -23456,7 +23430,7 @@
       <c r="C456">
         <v>2026</v>
       </c>
-      <c r="D456" s="2">
+      <c r="D456" s="1">
         <v>46183</v>
       </c>
       <c r="H456" t="s">
@@ -23555,7 +23529,7 @@
       <c r="C459">
         <v>2026</v>
       </c>
-      <c r="D459" s="2">
+      <c r="D459" s="1">
         <v>46230</v>
       </c>
       <c r="F459" t="s">
@@ -23599,7 +23573,7 @@
       <c r="C460">
         <v>2026</v>
       </c>
-      <c r="D460" s="2">
+      <c r="D460" s="1">
         <v>46185</v>
       </c>
       <c r="H460" t="s">
@@ -23666,7 +23640,7 @@
       <c r="C462">
         <v>2026</v>
       </c>
-      <c r="D462" s="2">
+      <c r="D462" s="1">
         <v>46185</v>
       </c>
       <c r="H462" t="s">
@@ -23765,7 +23739,7 @@
       <c r="C465">
         <v>2026</v>
       </c>
-      <c r="D465" s="2">
+      <c r="D465" s="1">
         <v>46175</v>
       </c>
       <c r="F465" t="s">
@@ -23806,7 +23780,7 @@
       <c r="C466">
         <v>2026</v>
       </c>
-      <c r="D466" s="2">
+      <c r="D466" s="1">
         <v>46175</v>
       </c>
       <c r="F466" t="s">
@@ -23847,7 +23821,7 @@
       <c r="C467">
         <v>2026</v>
       </c>
-      <c r="D467" s="2">
+      <c r="D467" s="1">
         <v>46230</v>
       </c>
       <c r="F467" t="s">
@@ -23888,7 +23862,7 @@
       <c r="C468">
         <v>2026</v>
       </c>
-      <c r="D468" s="2">
+      <c r="D468" s="1">
         <v>46175</v>
       </c>
       <c r="G468" t="s">
@@ -23926,7 +23900,7 @@
       <c r="C469">
         <v>2026</v>
       </c>
-      <c r="D469" s="2">
+      <c r="D469" s="1">
         <v>46175</v>
       </c>
       <c r="G469" t="s">
@@ -23964,7 +23938,7 @@
       <c r="C470">
         <v>2026</v>
       </c>
-      <c r="D470" s="2">
+      <c r="D470" s="1">
         <v>46175</v>
       </c>
       <c r="G470" t="s">
@@ -24002,7 +23976,7 @@
       <c r="C471">
         <v>2026</v>
       </c>
-      <c r="D471" s="2">
+      <c r="D471" s="1">
         <v>46230</v>
       </c>
       <c r="F471" t="s">
@@ -24043,7 +24017,7 @@
       <c r="C472">
         <v>2026</v>
       </c>
-      <c r="D472" s="2">
+      <c r="D472" s="1">
         <v>46175</v>
       </c>
       <c r="G472" t="s">
@@ -24081,7 +24055,7 @@
       <c r="C473">
         <v>2026</v>
       </c>
-      <c r="D473" s="2">
+      <c r="D473" s="1">
         <v>46175</v>
       </c>
       <c r="G473" t="s">
@@ -24119,7 +24093,7 @@
       <c r="C474">
         <v>2026</v>
       </c>
-      <c r="D474" s="2">
+      <c r="D474" s="1">
         <v>46175</v>
       </c>
       <c r="G474" t="s">
@@ -24157,7 +24131,7 @@
       <c r="C475">
         <v>2026</v>
       </c>
-      <c r="D475" s="2">
+      <c r="D475" s="1">
         <v>46230</v>
       </c>
       <c r="F475" t="s">
@@ -24230,7 +24204,7 @@
       <c r="C477">
         <v>2026</v>
       </c>
-      <c r="D477" s="2">
+      <c r="D477" s="1">
         <v>46209</v>
       </c>
       <c r="F477" t="s">
@@ -24402,7 +24376,7 @@
       <c r="C482">
         <v>2026</v>
       </c>
-      <c r="D482" s="2">
+      <c r="D482" s="1">
         <v>46230</v>
       </c>
       <c r="F482" t="s">
@@ -24443,7 +24417,7 @@
       <c r="C483">
         <v>2026</v>
       </c>
-      <c r="D483" s="2">
+      <c r="D483" s="1">
         <v>46230</v>
       </c>
       <c r="F483" t="s">
@@ -24484,7 +24458,7 @@
       <c r="C484">
         <v>2026</v>
       </c>
-      <c r="D484" s="2">
+      <c r="D484" s="1">
         <v>46230</v>
       </c>
       <c r="F484" t="s">
@@ -24749,7 +24723,7 @@
       <c r="C492">
         <v>2026</v>
       </c>
-      <c r="D492" s="2">
+      <c r="D492" s="1">
         <v>46230</v>
       </c>
       <c r="F492" t="s">
@@ -24790,7 +24764,7 @@
       <c r="C493">
         <v>2026</v>
       </c>
-      <c r="D493" s="2">
+      <c r="D493" s="1">
         <v>46230</v>
       </c>
       <c r="F493" t="s">
@@ -24895,7 +24869,7 @@
       <c r="C496">
         <v>2026</v>
       </c>
-      <c r="D496" s="2">
+      <c r="D496" s="1">
         <v>46230</v>
       </c>
       <c r="F496" t="s">
@@ -24939,7 +24913,7 @@
       <c r="C497">
         <v>2026</v>
       </c>
-      <c r="D497" s="2">
+      <c r="D497" s="1">
         <v>46230</v>
       </c>
       <c r="F497" t="s">
@@ -24980,7 +24954,7 @@
       <c r="C498">
         <v>2026</v>
       </c>
-      <c r="D498" s="2">
+      <c r="D498" s="1">
         <v>46157</v>
       </c>
       <c r="G498" t="s">
@@ -25018,7 +24992,7 @@
       <c r="C499">
         <v>2026</v>
       </c>
-      <c r="D499" s="2">
+      <c r="D499" s="1">
         <v>46213</v>
       </c>
       <c r="F499" t="s">
@@ -25094,7 +25068,7 @@
       <c r="C501">
         <v>2026</v>
       </c>
-      <c r="D501" s="2">
+      <c r="D501" s="1">
         <v>46205</v>
       </c>
       <c r="F501" t="s">
@@ -25138,7 +25112,7 @@
       <c r="C502">
         <v>2026</v>
       </c>
-      <c r="D502" s="2">
+      <c r="D502" s="1">
         <v>46176</v>
       </c>
       <c r="F502" t="s">
@@ -25179,7 +25153,7 @@
       <c r="C503">
         <v>2026</v>
       </c>
-      <c r="D503" s="2">
+      <c r="D503" s="1">
         <v>46150</v>
       </c>
       <c r="F503" t="s">
@@ -25284,7 +25258,7 @@
       <c r="C506">
         <v>2026</v>
       </c>
-      <c r="D506" s="2">
+      <c r="D506" s="1">
         <v>46220</v>
       </c>
       <c r="F506" t="s">
@@ -25328,7 +25302,7 @@
       <c r="C507">
         <v>2026</v>
       </c>
-      <c r="D507" s="2">
+      <c r="D507" s="1">
         <v>46224</v>
       </c>
       <c r="F507" t="s">
@@ -25404,7 +25378,7 @@
       <c r="C509">
         <v>2026</v>
       </c>
-      <c r="D509" s="2">
+      <c r="D509" s="1">
         <v>46155</v>
       </c>
       <c r="H509" t="s">
@@ -25439,7 +25413,7 @@
       <c r="C510">
         <v>2026</v>
       </c>
-      <c r="D510" s="2">
+      <c r="D510" s="1">
         <v>46156</v>
       </c>
       <c r="F510" t="s">
@@ -25480,7 +25454,7 @@
       <c r="C511">
         <v>2026</v>
       </c>
-      <c r="D511" s="2">
+      <c r="D511" s="1">
         <v>46185</v>
       </c>
       <c r="H511" t="s">
@@ -25515,7 +25489,7 @@
       <c r="C512">
         <v>2026</v>
       </c>
-      <c r="D512" s="2">
+      <c r="D512" s="1">
         <v>46230</v>
       </c>
       <c r="F512" t="s">
@@ -25556,7 +25530,7 @@
       <c r="C513">
         <v>2026</v>
       </c>
-      <c r="D513" s="2">
+      <c r="D513" s="1">
         <v>46230</v>
       </c>
       <c r="F513" t="s">
@@ -25597,7 +25571,7 @@
       <c r="C514">
         <v>2026</v>
       </c>
-      <c r="D514" s="2">
+      <c r="D514" s="1">
         <v>46230</v>
       </c>
       <c r="F514" t="s">
@@ -25638,7 +25612,7 @@
       <c r="C515">
         <v>2026</v>
       </c>
-      <c r="D515" s="2">
+      <c r="D515" s="1">
         <v>46230</v>
       </c>
       <c r="F515" t="s">
@@ -25679,7 +25653,7 @@
       <c r="C516">
         <v>2026</v>
       </c>
-      <c r="D516" s="2">
+      <c r="D516" s="1">
         <v>46230</v>
       </c>
       <c r="F516" t="s">
@@ -25784,7 +25758,7 @@
       <c r="C519">
         <v>2026</v>
       </c>
-      <c r="D519" s="2">
+      <c r="D519" s="1">
         <v>46147</v>
       </c>
       <c r="G519" t="s">
@@ -25918,7 +25892,7 @@
       <c r="C523">
         <v>2026</v>
       </c>
-      <c r="D523" s="2">
+      <c r="D523" s="1">
         <v>46164</v>
       </c>
       <c r="F523" t="s">
@@ -26055,7 +26029,7 @@
       <c r="C527">
         <v>2026</v>
       </c>
-      <c r="D527" s="2">
+      <c r="D527" s="1">
         <v>46230</v>
       </c>
       <c r="F527" t="s">
@@ -26192,7 +26166,7 @@
       <c r="C531">
         <v>2026</v>
       </c>
-      <c r="D531" s="2">
+      <c r="D531" s="1">
         <v>46171</v>
       </c>
       <c r="F531" t="s">
@@ -26297,7 +26271,7 @@
       <c r="C534">
         <v>2026</v>
       </c>
-      <c r="D534" s="2">
+      <c r="D534" s="1">
         <v>46176</v>
       </c>
       <c r="G534" t="s">
@@ -26335,7 +26309,7 @@
       <c r="C535">
         <v>2026</v>
       </c>
-      <c r="D535" s="2">
+      <c r="D535" s="1">
         <v>46230</v>
       </c>
       <c r="F535" t="s">
@@ -26536,7 +26510,7 @@
       <c r="C541">
         <v>2026</v>
       </c>
-      <c r="D541" s="2">
+      <c r="D541" s="1">
         <v>46211</v>
       </c>
       <c r="F541" t="s">
@@ -26580,7 +26554,7 @@
       <c r="C542">
         <v>2026</v>
       </c>
-      <c r="D542" s="2">
+      <c r="D542" s="1">
         <v>46183</v>
       </c>
       <c r="H542" t="s">
@@ -26615,7 +26589,7 @@
       <c r="C543">
         <v>2026</v>
       </c>
-      <c r="D543" s="2">
+      <c r="D543" s="1">
         <v>46191</v>
       </c>
       <c r="H543" t="s">
@@ -26650,7 +26624,7 @@
       <c r="C544">
         <v>2026</v>
       </c>
-      <c r="D544" s="2">
+      <c r="D544" s="1">
         <v>46191</v>
       </c>
       <c r="G544" t="s">
@@ -26848,7 +26822,7 @@
       <c r="C550">
         <v>2026</v>
       </c>
-      <c r="D550" s="2">
+      <c r="D550" s="1">
         <v>46230</v>
       </c>
       <c r="F550" t="s">
@@ -26953,7 +26927,7 @@
       <c r="C553">
         <v>2026</v>
       </c>
-      <c r="D553" s="2">
+      <c r="D553" s="1">
         <v>46230</v>
       </c>
       <c r="F553" t="s">
@@ -26994,7 +26968,7 @@
       <c r="C554">
         <v>2026</v>
       </c>
-      <c r="D554" s="2">
+      <c r="D554" s="1">
         <v>46191</v>
       </c>
       <c r="G554" t="s">
@@ -27160,7 +27134,7 @@
       <c r="C559">
         <v>2026</v>
       </c>
-      <c r="D559" s="2">
+      <c r="D559" s="1">
         <v>46191</v>
       </c>
       <c r="G559" t="s">
@@ -27358,7 +27332,7 @@
       <c r="C565">
         <v>2026</v>
       </c>
-      <c r="D565" s="2">
+      <c r="D565" s="1">
         <v>46230</v>
       </c>
       <c r="F565" t="s">
@@ -27978,7 +27952,7 @@
       <c r="C584">
         <v>2026</v>
       </c>
-      <c r="D584" s="2">
+      <c r="D584" s="1">
         <v>46226</v>
       </c>
       <c r="F584" t="s">
@@ -28502,7 +28476,7 @@
       <c r="C600">
         <v>2026</v>
       </c>
-      <c r="D600" s="2">
+      <c r="D600" s="1">
         <v>45802</v>
       </c>
       <c r="F600" t="s">
@@ -28546,7 +28520,7 @@
       <c r="C601">
         <v>2026</v>
       </c>
-      <c r="D601" s="2">
+      <c r="D601" s="1">
         <v>45860</v>
       </c>
       <c r="F601" t="s">
@@ -28587,7 +28561,7 @@
       <c r="C602">
         <v>2026</v>
       </c>
-      <c r="D602" s="2">
+      <c r="D602" s="1">
         <v>45860</v>
       </c>
       <c r="H602" t="s">
@@ -28622,7 +28596,7 @@
       <c r="C603">
         <v>2026</v>
       </c>
-      <c r="D603" s="2">
+      <c r="D603" s="1">
         <v>45856</v>
       </c>
       <c r="F603" t="s">
@@ -28663,7 +28637,7 @@
       <c r="C604">
         <v>2026</v>
       </c>
-      <c r="D604" s="2">
+      <c r="D604" s="1">
         <v>46101</v>
       </c>
       <c r="F604" t="s">
@@ -28704,7 +28678,7 @@
       <c r="C605">
         <v>2026</v>
       </c>
-      <c r="D605" s="2">
+      <c r="D605" s="1">
         <v>46101</v>
       </c>
       <c r="F605" t="s">
@@ -28745,7 +28719,7 @@
       <c r="C606">
         <v>2026</v>
       </c>
-      <c r="D606" s="2">
+      <c r="D606" s="1">
         <v>45863</v>
       </c>
       <c r="F606" t="s">
@@ -28786,7 +28760,7 @@
       <c r="C607">
         <v>2026</v>
       </c>
-      <c r="D607" s="2">
+      <c r="D607" s="1">
         <v>45863</v>
       </c>
       <c r="F607" t="s">
@@ -28827,7 +28801,7 @@
       <c r="C608">
         <v>2026</v>
       </c>
-      <c r="D608" s="2">
+      <c r="D608" s="1">
         <v>46086</v>
       </c>
       <c r="F608" t="s">
@@ -28868,7 +28842,7 @@
       <c r="C609">
         <v>2026</v>
       </c>
-      <c r="D609" s="2">
+      <c r="D609" s="1">
         <v>45874</v>
       </c>
       <c r="F609" t="s">
@@ -28909,7 +28883,7 @@
       <c r="C610">
         <v>2026</v>
       </c>
-      <c r="D610" s="2">
+      <c r="D610" s="1">
         <v>45894</v>
       </c>
       <c r="F610" t="s">
@@ -28950,7 +28924,7 @@
       <c r="C611">
         <v>2026</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="1">
         <v>45894</v>
       </c>
       <c r="F611" t="s">
@@ -28991,7 +28965,7 @@
       <c r="C612">
         <v>2026</v>
       </c>
-      <c r="D612" s="2">
+      <c r="D612" s="1">
         <v>46119</v>
       </c>
       <c r="F612" t="s">
@@ -29032,7 +29006,7 @@
       <c r="C613">
         <v>2026</v>
       </c>
-      <c r="D613" s="2">
+      <c r="D613" s="1">
         <v>45898</v>
       </c>
       <c r="F613" t="s">
@@ -29073,7 +29047,7 @@
       <c r="C614">
         <v>2026</v>
       </c>
-      <c r="D614" s="2">
+      <c r="D614" s="1">
         <v>45971</v>
       </c>
       <c r="F614" t="s">
@@ -29114,7 +29088,7 @@
       <c r="C615">
         <v>2026</v>
       </c>
-      <c r="D615" s="2">
+      <c r="D615" s="1">
         <v>46119</v>
       </c>
       <c r="F615" t="s">
@@ -29155,7 +29129,7 @@
       <c r="C616">
         <v>2026</v>
       </c>
-      <c r="D616" s="2">
+      <c r="D616" s="1">
         <v>46092</v>
       </c>
       <c r="F616" t="s">
@@ -29196,7 +29170,7 @@
       <c r="C617">
         <v>2026</v>
       </c>
-      <c r="D617" s="2">
+      <c r="D617" s="1">
         <v>46119</v>
       </c>
       <c r="F617" t="s">
@@ -29237,7 +29211,7 @@
       <c r="C618">
         <v>2026</v>
       </c>
-      <c r="D618" s="2">
+      <c r="D618" s="1">
         <v>46029</v>
       </c>
       <c r="F618" t="s">
@@ -29278,7 +29252,7 @@
       <c r="C619">
         <v>2026</v>
       </c>
-      <c r="D619" s="2">
+      <c r="D619" s="1">
         <v>46029</v>
       </c>
       <c r="F619" t="s">
@@ -29319,7 +29293,7 @@
       <c r="C620">
         <v>2026</v>
       </c>
-      <c r="D620" s="2">
+      <c r="D620" s="1">
         <v>46063</v>
       </c>
       <c r="H620" t="s">
@@ -29354,7 +29328,7 @@
       <c r="C621">
         <v>2026</v>
       </c>
-      <c r="D621" s="2">
+      <c r="D621" s="1">
         <v>46232</v>
       </c>
       <c r="G621" t="s">
@@ -29392,7 +29366,7 @@
       <c r="C622">
         <v>2026</v>
       </c>
-      <c r="D622" s="2">
+      <c r="D622" s="1">
         <v>46232</v>
       </c>
       <c r="G622" t="s">
@@ -29430,7 +29404,7 @@
       <c r="C623">
         <v>2026</v>
       </c>
-      <c r="D623" s="2">
+      <c r="D623" s="1">
         <v>46232</v>
       </c>
       <c r="G623" t="s">
@@ -29468,7 +29442,7 @@
       <c r="C624">
         <v>2026</v>
       </c>
-      <c r="D624" s="2">
+      <c r="D624" s="1">
         <v>46232</v>
       </c>
       <c r="G624" t="s">
@@ -29506,7 +29480,7 @@
       <c r="C625">
         <v>2026</v>
       </c>
-      <c r="D625" s="2">
+      <c r="D625" s="1">
         <v>46155</v>
       </c>
       <c r="H625" t="s">
@@ -29541,7 +29515,7 @@
       <c r="C626">
         <v>2026</v>
       </c>
-      <c r="D626" s="2">
+      <c r="D626" s="1">
         <v>46139</v>
       </c>
       <c r="F626" t="s">
@@ -29582,7 +29556,7 @@
       <c r="C627">
         <v>2026</v>
       </c>
-      <c r="D627" s="2">
+      <c r="D627" s="1">
         <v>46155</v>
       </c>
       <c r="F627" t="s">
@@ -29623,7 +29597,7 @@
       <c r="C628">
         <v>2026</v>
       </c>
-      <c r="D628" s="2">
+      <c r="D628" s="1">
         <v>46155</v>
       </c>
       <c r="H628" t="s">
@@ -29658,7 +29632,7 @@
       <c r="C629">
         <v>2026</v>
       </c>
-      <c r="D629" s="2">
+      <c r="D629" s="1">
         <v>46147</v>
       </c>
       <c r="H629" t="s">
@@ -29693,7 +29667,7 @@
       <c r="C630">
         <v>2026</v>
       </c>
-      <c r="D630" s="2">
+      <c r="D630" s="1">
         <v>46164</v>
       </c>
       <c r="F630" t="s">
@@ -29734,7 +29708,7 @@
       <c r="C631">
         <v>2026</v>
       </c>
-      <c r="D631" s="2">
+      <c r="D631" s="1">
         <v>46225</v>
       </c>
       <c r="F631" t="s">
@@ -29775,7 +29749,7 @@
       <c r="C632">
         <v>2026</v>
       </c>
-      <c r="D632" s="2">
+      <c r="D632" s="1">
         <v>46225</v>
       </c>
       <c r="F632" t="s">
@@ -29816,7 +29790,7 @@
       <c r="C633">
         <v>2026</v>
       </c>
-      <c r="D633" s="2">
+      <c r="D633" s="1">
         <v>46225</v>
       </c>
       <c r="F633" t="s">
@@ -29857,7 +29831,7 @@
       <c r="C634">
         <v>2026</v>
       </c>
-      <c r="D634" s="2">
+      <c r="D634" s="1">
         <v>46248</v>
       </c>
       <c r="H634" t="s">
@@ -29892,7 +29866,7 @@
       <c r="C635">
         <v>2026</v>
       </c>
-      <c r="D635" s="2">
+      <c r="D635" s="1">
         <v>46248</v>
       </c>
       <c r="F635" t="s">
@@ -29933,7 +29907,7 @@
       <c r="C636">
         <v>2026</v>
       </c>
-      <c r="D636" s="2">
+      <c r="D636" s="1">
         <v>46171</v>
       </c>
       <c r="H636" t="s">
@@ -29968,7 +29942,7 @@
       <c r="C637">
         <v>2026</v>
       </c>
-      <c r="D637" s="2">
+      <c r="D637" s="1">
         <v>46176</v>
       </c>
       <c r="H637" t="s">
@@ -30003,7 +29977,7 @@
       <c r="C638">
         <v>2026</v>
       </c>
-      <c r="D638" s="2">
+      <c r="D638" s="1">
         <v>46225</v>
       </c>
       <c r="F638" t="s">
@@ -30044,7 +30018,7 @@
       <c r="C639">
         <v>2026</v>
       </c>
-      <c r="D639" s="2">
+      <c r="D639" s="1">
         <v>46211</v>
       </c>
       <c r="H639" t="s">
@@ -30079,7 +30053,7 @@
       <c r="C640">
         <v>2026</v>
       </c>
-      <c r="D640" s="2">
+      <c r="D640" s="1">
         <v>46183</v>
       </c>
       <c r="H640" t="s">
@@ -30114,7 +30088,7 @@
       <c r="C641">
         <v>2026</v>
       </c>
-      <c r="D641" s="2">
+      <c r="D641" s="1">
         <v>46191</v>
       </c>
       <c r="F641" t="s">
@@ -30155,7 +30129,7 @@
       <c r="C642">
         <v>2026</v>
       </c>
-      <c r="D642" s="2">
+      <c r="D642" s="1">
         <v>46176</v>
       </c>
       <c r="H642" t="s">
@@ -30190,7 +30164,7 @@
       <c r="C643">
         <v>2026</v>
       </c>
-      <c r="D643" s="2">
+      <c r="D643" s="1">
         <v>46191</v>
       </c>
       <c r="H643" t="s">
@@ -30225,7 +30199,7 @@
       <c r="C644">
         <v>2026</v>
       </c>
-      <c r="D644" s="2">
+      <c r="D644" s="1">
         <v>46241</v>
       </c>
       <c r="F644" t="s">
@@ -30269,7 +30243,7 @@
       <c r="C645">
         <v>2026</v>
       </c>
-      <c r="D645" s="2">
+      <c r="D645" s="1">
         <v>46191</v>
       </c>
       <c r="F645" t="s">
@@ -30310,7 +30284,7 @@
       <c r="C646">
         <v>2026</v>
       </c>
-      <c r="D646" s="2">
+      <c r="D646" s="1">
         <v>46191</v>
       </c>
       <c r="F646" t="s">
@@ -30351,7 +30325,7 @@
       <c r="C647">
         <v>2026</v>
       </c>
-      <c r="D647" s="2">
+      <c r="D647" s="1">
         <v>46191</v>
       </c>
       <c r="H647" t="s">
@@ -30386,7 +30360,7 @@
       <c r="C648">
         <v>2026</v>
       </c>
-      <c r="D648" s="2">
+      <c r="D648" s="1">
         <v>46241</v>
       </c>
       <c r="F648" t="s">
@@ -30427,7 +30401,7 @@
       <c r="C649">
         <v>2026</v>
       </c>
-      <c r="D649" s="2">
+      <c r="D649" s="1">
         <v>46191</v>
       </c>
       <c r="H649" t="s">
@@ -30462,7 +30436,7 @@
       <c r="C650">
         <v>2026</v>
       </c>
-      <c r="D650" s="2">
+      <c r="D650" s="1">
         <v>46248</v>
       </c>
       <c r="H650" t="s">
@@ -30497,7 +30471,7 @@
       <c r="C651">
         <v>2026</v>
       </c>
-      <c r="D651" s="2">
+      <c r="D651" s="1">
         <v>46241</v>
       </c>
       <c r="F651" t="s">
@@ -30538,7 +30512,7 @@
       <c r="C652">
         <v>2026</v>
       </c>
-      <c r="D652" s="2">
+      <c r="D652" s="1">
         <v>46241</v>
       </c>
       <c r="F652" t="s">
@@ -30579,7 +30553,7 @@
       <c r="C653">
         <v>2026</v>
       </c>
-      <c r="D653" s="2">
+      <c r="D653" s="1">
         <v>46225</v>
       </c>
       <c r="F653" t="s">
@@ -30620,7 +30594,7 @@
       <c r="C654">
         <v>2026</v>
       </c>
-      <c r="D654" s="2">
+      <c r="D654" s="1">
         <v>46241</v>
       </c>
       <c r="F654" t="s">
@@ -30661,7 +30635,7 @@
       <c r="C655">
         <v>2026</v>
       </c>
-      <c r="D655" s="2">
+      <c r="D655" s="1">
         <v>46241</v>
       </c>
       <c r="F655" t="s">
@@ -30702,7 +30676,7 @@
       <c r="C656">
         <v>2026</v>
       </c>
-      <c r="D656" s="2">
+      <c r="D656" s="1">
         <v>46241</v>
       </c>
       <c r="F656" t="s">
@@ -30743,7 +30717,7 @@
       <c r="C657">
         <v>2026</v>
       </c>
-      <c r="D657" s="2">
+      <c r="D657" s="1">
         <v>46248</v>
       </c>
       <c r="H657" t="s">
@@ -30778,7 +30752,7 @@
       <c r="C658">
         <v>2026</v>
       </c>
-      <c r="D658" s="2">
+      <c r="D658" s="1">
         <v>46248</v>
       </c>
       <c r="H658" t="s">
@@ -30813,7 +30787,7 @@
       <c r="C659">
         <v>2026</v>
       </c>
-      <c r="D659" s="2">
+      <c r="D659" s="1">
         <v>46248</v>
       </c>
       <c r="F659" t="s">
@@ -30854,7 +30828,7 @@
       <c r="C660">
         <v>2026</v>
       </c>
-      <c r="D660" s="2">
+      <c r="D660" s="1">
         <v>46248</v>
       </c>
       <c r="F660" t="s">
@@ -30895,7 +30869,7 @@
       <c r="C661">
         <v>2026</v>
       </c>
-      <c r="D661" s="2">
+      <c r="D661" s="1">
         <v>46248</v>
       </c>
       <c r="F661" t="s">
@@ -30936,7 +30910,7 @@
       <c r="C662">
         <v>2026</v>
       </c>
-      <c r="D662" s="2">
+      <c r="D662" s="1">
         <v>45989</v>
       </c>
       <c r="G662" t="s">
@@ -30974,7 +30948,7 @@
       <c r="C663">
         <v>2026</v>
       </c>
-      <c r="D663" s="2">
+      <c r="D663" s="1">
         <v>46002</v>
       </c>
       <c r="G663" t="s">
@@ -31012,7 +30986,7 @@
       <c r="C664">
         <v>2026</v>
       </c>
-      <c r="D664" s="2">
+      <c r="D664" s="1">
         <v>46002</v>
       </c>
       <c r="G664" t="s">
@@ -31050,7 +31024,7 @@
       <c r="C665">
         <v>2026</v>
       </c>
-      <c r="D665" s="2">
+      <c r="D665" s="1">
         <v>46225</v>
       </c>
       <c r="F665" t="s">
@@ -31091,7 +31065,7 @@
       <c r="C666">
         <v>2026</v>
       </c>
-      <c r="D666" s="2">
+      <c r="D666" s="1">
         <v>46211</v>
       </c>
       <c r="F666" t="s">
@@ -31132,7 +31106,7 @@
       <c r="C667">
         <v>2026</v>
       </c>
-      <c r="D667" s="2">
+      <c r="D667" s="1">
         <v>46248</v>
       </c>
       <c r="F667" t="s">
@@ -31173,7 +31147,7 @@
       <c r="C668">
         <v>2026</v>
       </c>
-      <c r="D668" s="2">
+      <c r="D668" s="1">
         <v>46248</v>
       </c>
       <c r="F668" t="s">
@@ -31246,7 +31220,7 @@
       <c r="C670">
         <v>2026</v>
       </c>
-      <c r="D670" s="2">
+      <c r="D670" s="1">
         <v>46255</v>
       </c>
       <c r="F670" t="s">
@@ -31447,7 +31421,7 @@
       <c r="C676">
         <v>2026</v>
       </c>
-      <c r="D676" s="2">
+      <c r="D676" s="1">
         <v>46265</v>
       </c>
       <c r="H676" t="s">
@@ -31482,7 +31456,7 @@
       <c r="C677">
         <v>2026</v>
       </c>
-      <c r="D677" s="2">
+      <c r="D677" s="1">
         <v>46265</v>
       </c>
       <c r="H677" t="s">
@@ -31517,7 +31491,7 @@
       <c r="C678">
         <v>2026</v>
       </c>
-      <c r="D678" s="2">
+      <c r="D678" s="1">
         <v>46265</v>
       </c>
       <c r="H678" t="s">
@@ -31872,7 +31846,7 @@
       <c r="C689">
         <v>2026</v>
       </c>
-      <c r="D689" s="2">
+      <c r="D689" s="1">
         <v>46265</v>
       </c>
       <c r="H689" t="s">
@@ -31907,7 +31881,7 @@
       <c r="C690">
         <v>2026</v>
       </c>
-      <c r="D690" s="2">
+      <c r="D690" s="1">
         <v>46265</v>
       </c>
       <c r="H690" t="s">
@@ -32998,7 +32972,7 @@
       <c r="C724">
         <v>2026</v>
       </c>
-      <c r="D724" s="2">
+      <c r="D724" s="1">
         <v>45802</v>
       </c>
       <c r="F724" t="s">
@@ -33042,7 +33016,7 @@
       <c r="C725">
         <v>2026</v>
       </c>
-      <c r="D725" s="2">
+      <c r="D725" s="1">
         <v>45860</v>
       </c>
       <c r="F725" t="s">
@@ -33083,7 +33057,7 @@
       <c r="C726">
         <v>2026</v>
       </c>
-      <c r="D726" s="2">
+      <c r="D726" s="1">
         <v>45860</v>
       </c>
       <c r="H726" t="s">
@@ -33118,7 +33092,7 @@
       <c r="C727">
         <v>2026</v>
       </c>
-      <c r="D727" s="2">
+      <c r="D727" s="1">
         <v>45856</v>
       </c>
       <c r="F727" t="s">
@@ -33159,7 +33133,7 @@
       <c r="C728">
         <v>2026</v>
       </c>
-      <c r="D728" s="2">
+      <c r="D728" s="1">
         <v>46101</v>
       </c>
       <c r="F728" t="s">
@@ -33200,7 +33174,7 @@
       <c r="C729">
         <v>2026</v>
       </c>
-      <c r="D729" s="2">
+      <c r="D729" s="1">
         <v>46101</v>
       </c>
       <c r="F729" t="s">
@@ -33241,7 +33215,7 @@
       <c r="C730">
         <v>2026</v>
       </c>
-      <c r="D730" s="2">
+      <c r="D730" s="1">
         <v>45863</v>
       </c>
       <c r="F730" t="s">
@@ -33282,7 +33256,7 @@
       <c r="C731">
         <v>2026</v>
       </c>
-      <c r="D731" s="2">
+      <c r="D731" s="1">
         <v>45863</v>
       </c>
       <c r="F731" t="s">
@@ -33323,7 +33297,7 @@
       <c r="C732">
         <v>2026</v>
       </c>
-      <c r="D732" s="2">
+      <c r="D732" s="1">
         <v>46086</v>
       </c>
       <c r="F732" t="s">
@@ -33364,7 +33338,7 @@
       <c r="C733">
         <v>2026</v>
       </c>
-      <c r="D733" s="2">
+      <c r="D733" s="1">
         <v>45874</v>
       </c>
       <c r="F733" t="s">
@@ -33405,7 +33379,7 @@
       <c r="C734">
         <v>2026</v>
       </c>
-      <c r="D734" s="2">
+      <c r="D734" s="1">
         <v>45894</v>
       </c>
       <c r="F734" t="s">
@@ -33446,7 +33420,7 @@
       <c r="C735">
         <v>2026</v>
       </c>
-      <c r="D735" s="2">
+      <c r="D735" s="1">
         <v>45894</v>
       </c>
       <c r="F735" t="s">
@@ -33487,7 +33461,7 @@
       <c r="C736">
         <v>2026</v>
       </c>
-      <c r="D736" s="2">
+      <c r="D736" s="1">
         <v>46119</v>
       </c>
       <c r="F736" t="s">
@@ -33528,7 +33502,7 @@
       <c r="C737">
         <v>2026</v>
       </c>
-      <c r="D737" s="2">
+      <c r="D737" s="1">
         <v>45898</v>
       </c>
       <c r="F737" t="s">
@@ -33569,7 +33543,7 @@
       <c r="C738">
         <v>2026</v>
       </c>
-      <c r="D738" s="2">
+      <c r="D738" s="1">
         <v>45971</v>
       </c>
       <c r="F738" t="s">
@@ -33610,7 +33584,7 @@
       <c r="C739">
         <v>2026</v>
       </c>
-      <c r="D739" s="2">
+      <c r="D739" s="1">
         <v>46119</v>
       </c>
       <c r="F739" t="s">
@@ -33651,7 +33625,7 @@
       <c r="C740">
         <v>2026</v>
       </c>
-      <c r="D740" s="2">
+      <c r="D740" s="1">
         <v>46092</v>
       </c>
       <c r="F740" t="s">
@@ -33692,7 +33666,7 @@
       <c r="C741">
         <v>2026</v>
       </c>
-      <c r="D741" s="2">
+      <c r="D741" s="1">
         <v>46119</v>
       </c>
       <c r="F741" t="s">
@@ -33733,7 +33707,7 @@
       <c r="C742">
         <v>2026</v>
       </c>
-      <c r="D742" s="2">
+      <c r="D742" s="1">
         <v>46029</v>
       </c>
       <c r="F742" t="s">
@@ -33774,7 +33748,7 @@
       <c r="C743">
         <v>2026</v>
       </c>
-      <c r="D743" s="2">
+      <c r="D743" s="1">
         <v>46029</v>
       </c>
       <c r="F743" t="s">
@@ -33815,7 +33789,7 @@
       <c r="C744">
         <v>2026</v>
       </c>
-      <c r="D744" s="2">
+      <c r="D744" s="1">
         <v>46063</v>
       </c>
       <c r="H744" t="s">
@@ -33850,7 +33824,7 @@
       <c r="C745">
         <v>2026</v>
       </c>
-      <c r="D745" s="2">
+      <c r="D745" s="1">
         <v>46232</v>
       </c>
       <c r="G745" t="s">
@@ -33888,7 +33862,7 @@
       <c r="C746">
         <v>2026</v>
       </c>
-      <c r="D746" s="2">
+      <c r="D746" s="1">
         <v>46232</v>
       </c>
       <c r="G746" t="s">
@@ -33926,7 +33900,7 @@
       <c r="C747">
         <v>2026</v>
       </c>
-      <c r="D747" s="2">
+      <c r="D747" s="1">
         <v>46232</v>
       </c>
       <c r="G747" t="s">
@@ -33964,7 +33938,7 @@
       <c r="C748">
         <v>2026</v>
       </c>
-      <c r="D748" s="2">
+      <c r="D748" s="1">
         <v>46232</v>
       </c>
       <c r="G748" t="s">
@@ -34002,7 +33976,7 @@
       <c r="C749">
         <v>2026</v>
       </c>
-      <c r="D749" s="2">
+      <c r="D749" s="1">
         <v>46155</v>
       </c>
       <c r="H749" t="s">
@@ -34037,7 +34011,7 @@
       <c r="C750">
         <v>2026</v>
       </c>
-      <c r="D750" s="2">
+      <c r="D750" s="1">
         <v>46139</v>
       </c>
       <c r="F750" t="s">
@@ -34078,7 +34052,7 @@
       <c r="C751">
         <v>2026</v>
       </c>
-      <c r="D751" s="2">
+      <c r="D751" s="1">
         <v>46155</v>
       </c>
       <c r="F751" t="s">
@@ -34119,7 +34093,7 @@
       <c r="C752">
         <v>2026</v>
       </c>
-      <c r="D752" s="2">
+      <c r="D752" s="1">
         <v>46155</v>
       </c>
       <c r="H752" t="s">
@@ -34154,7 +34128,7 @@
       <c r="C753">
         <v>2026</v>
       </c>
-      <c r="D753" s="2">
+      <c r="D753" s="1">
         <v>46147</v>
       </c>
       <c r="H753" t="s">
@@ -34189,7 +34163,7 @@
       <c r="C754">
         <v>2026</v>
       </c>
-      <c r="D754" s="2">
+      <c r="D754" s="1">
         <v>46164</v>
       </c>
       <c r="F754" t="s">
@@ -34230,7 +34204,7 @@
       <c r="C755">
         <v>2026</v>
       </c>
-      <c r="D755" s="2">
+      <c r="D755" s="1">
         <v>46225</v>
       </c>
       <c r="F755" t="s">
@@ -34271,7 +34245,7 @@
       <c r="C756">
         <v>2026</v>
       </c>
-      <c r="D756" s="2">
+      <c r="D756" s="1">
         <v>46225</v>
       </c>
       <c r="F756" t="s">
@@ -34312,7 +34286,7 @@
       <c r="C757">
         <v>2026</v>
       </c>
-      <c r="D757" s="2">
+      <c r="D757" s="1">
         <v>46225</v>
       </c>
       <c r="F757" t="s">
@@ -34353,7 +34327,7 @@
       <c r="C758">
         <v>2026</v>
       </c>
-      <c r="D758" s="2">
+      <c r="D758" s="1">
         <v>46248</v>
       </c>
       <c r="H758" t="s">
@@ -34388,7 +34362,7 @@
       <c r="C759">
         <v>2026</v>
       </c>
-      <c r="D759" s="2">
+      <c r="D759" s="1">
         <v>46248</v>
       </c>
       <c r="F759" t="s">
@@ -34429,7 +34403,7 @@
       <c r="C760">
         <v>2026</v>
       </c>
-      <c r="D760" s="2">
+      <c r="D760" s="1">
         <v>46171</v>
       </c>
       <c r="H760" t="s">
@@ -34464,7 +34438,7 @@
       <c r="C761">
         <v>2026</v>
       </c>
-      <c r="D761" s="2">
+      <c r="D761" s="1">
         <v>46176</v>
       </c>
       <c r="H761" t="s">
@@ -34499,7 +34473,7 @@
       <c r="C762">
         <v>2026</v>
       </c>
-      <c r="D762" s="2">
+      <c r="D762" s="1">
         <v>46225</v>
       </c>
       <c r="F762" t="s">
@@ -34540,7 +34514,7 @@
       <c r="C763">
         <v>2026</v>
       </c>
-      <c r="D763" s="2">
+      <c r="D763" s="1">
         <v>46211</v>
       </c>
       <c r="H763" t="s">
@@ -34575,7 +34549,7 @@
       <c r="C764">
         <v>2026</v>
       </c>
-      <c r="D764" s="2">
+      <c r="D764" s="1">
         <v>46183</v>
       </c>
       <c r="H764" t="s">
@@ -34610,7 +34584,7 @@
       <c r="C765">
         <v>2026</v>
       </c>
-      <c r="D765" s="2">
+      <c r="D765" s="1">
         <v>46191</v>
       </c>
       <c r="F765" t="s">
@@ -34651,7 +34625,7 @@
       <c r="C766">
         <v>2026</v>
       </c>
-      <c r="D766" s="2">
+      <c r="D766" s="1">
         <v>46176</v>
       </c>
       <c r="H766" t="s">
@@ -34686,7 +34660,7 @@
       <c r="C767">
         <v>2026</v>
       </c>
-      <c r="D767" s="2">
+      <c r="D767" s="1">
         <v>46191</v>
       </c>
       <c r="H767" t="s">
@@ -34721,7 +34695,7 @@
       <c r="C768">
         <v>2026</v>
       </c>
-      <c r="D768" s="2">
+      <c r="D768" s="1">
         <v>46241</v>
       </c>
       <c r="F768" t="s">
@@ -34765,7 +34739,7 @@
       <c r="C769">
         <v>2026</v>
       </c>
-      <c r="D769" s="2">
+      <c r="D769" s="1">
         <v>46191</v>
       </c>
       <c r="F769" t="s">
@@ -34806,7 +34780,7 @@
       <c r="C770">
         <v>2026</v>
       </c>
-      <c r="D770" s="2">
+      <c r="D770" s="1">
         <v>46191</v>
       </c>
       <c r="F770" t="s">
@@ -34847,7 +34821,7 @@
       <c r="C771">
         <v>2026</v>
       </c>
-      <c r="D771" s="2">
+      <c r="D771" s="1">
         <v>46191</v>
       </c>
       <c r="H771" t="s">
@@ -34882,7 +34856,7 @@
       <c r="C772">
         <v>2026</v>
       </c>
-      <c r="D772" s="2">
+      <c r="D772" s="1">
         <v>46241</v>
       </c>
       <c r="F772" t="s">
@@ -34923,7 +34897,7 @@
       <c r="C773">
         <v>2026</v>
       </c>
-      <c r="D773" s="2">
+      <c r="D773" s="1">
         <v>46191</v>
       </c>
       <c r="H773" t="s">
@@ -34958,7 +34932,7 @@
       <c r="C774">
         <v>2026</v>
       </c>
-      <c r="D774" s="2">
+      <c r="D774" s="1">
         <v>46248</v>
       </c>
       <c r="H774" t="s">
@@ -34993,7 +34967,7 @@
       <c r="C775">
         <v>2026</v>
       </c>
-      <c r="D775" s="2">
+      <c r="D775" s="1">
         <v>46241</v>
       </c>
       <c r="F775" t="s">
@@ -35034,7 +35008,7 @@
       <c r="C776">
         <v>2026</v>
       </c>
-      <c r="D776" s="2">
+      <c r="D776" s="1">
         <v>46241</v>
       </c>
       <c r="F776" t="s">
@@ -35075,7 +35049,7 @@
       <c r="C777">
         <v>2026</v>
       </c>
-      <c r="D777" s="2">
+      <c r="D777" s="1">
         <v>46225</v>
       </c>
       <c r="F777" t="s">
@@ -35116,7 +35090,7 @@
       <c r="C778">
         <v>2026</v>
       </c>
-      <c r="D778" s="2">
+      <c r="D778" s="1">
         <v>46241</v>
       </c>
       <c r="F778" t="s">
@@ -35157,7 +35131,7 @@
       <c r="C779">
         <v>2026</v>
       </c>
-      <c r="D779" s="2">
+      <c r="D779" s="1">
         <v>46241</v>
       </c>
       <c r="F779" t="s">
@@ -35198,7 +35172,7 @@
       <c r="C780">
         <v>2026</v>
       </c>
-      <c r="D780" s="2">
+      <c r="D780" s="1">
         <v>46241</v>
       </c>
       <c r="F780" t="s">
@@ -35239,7 +35213,7 @@
       <c r="C781">
         <v>2026</v>
       </c>
-      <c r="D781" s="2">
+      <c r="D781" s="1">
         <v>46248</v>
       </c>
       <c r="H781" t="s">
@@ -35274,7 +35248,7 @@
       <c r="C782">
         <v>2026</v>
       </c>
-      <c r="D782" s="2">
+      <c r="D782" s="1">
         <v>46248</v>
       </c>
       <c r="H782" t="s">
@@ -35309,7 +35283,7 @@
       <c r="C783">
         <v>2026</v>
       </c>
-      <c r="D783" s="2">
+      <c r="D783" s="1">
         <v>46248</v>
       </c>
       <c r="F783" t="s">
@@ -35350,7 +35324,7 @@
       <c r="C784">
         <v>2026</v>
       </c>
-      <c r="D784" s="2">
+      <c r="D784" s="1">
         <v>46248</v>
       </c>
       <c r="F784" t="s">
@@ -35391,7 +35365,7 @@
       <c r="C785">
         <v>2026</v>
       </c>
-      <c r="D785" s="2">
+      <c r="D785" s="1">
         <v>46248</v>
       </c>
       <c r="F785" t="s">
@@ -35432,7 +35406,7 @@
       <c r="C786">
         <v>2026</v>
       </c>
-      <c r="D786" s="2">
+      <c r="D786" s="1">
         <v>45989</v>
       </c>
       <c r="G786" t="s">
@@ -35470,7 +35444,7 @@
       <c r="C787">
         <v>2026</v>
       </c>
-      <c r="D787" s="2">
+      <c r="D787" s="1">
         <v>46002</v>
       </c>
       <c r="G787" t="s">
@@ -35508,7 +35482,7 @@
       <c r="C788">
         <v>2026</v>
       </c>
-      <c r="D788" s="2">
+      <c r="D788" s="1">
         <v>46002</v>
       </c>
       <c r="G788" t="s">
@@ -35546,7 +35520,7 @@
       <c r="C789">
         <v>2026</v>
       </c>
-      <c r="D789" s="2">
+      <c r="D789" s="1">
         <v>46225</v>
       </c>
       <c r="F789" t="s">
@@ -35587,7 +35561,7 @@
       <c r="C790">
         <v>2026</v>
       </c>
-      <c r="D790" s="2">
+      <c r="D790" s="1">
         <v>46211</v>
       </c>
       <c r="F790" t="s">
@@ -35628,7 +35602,7 @@
       <c r="C791">
         <v>2026</v>
       </c>
-      <c r="D791" s="2">
+      <c r="D791" s="1">
         <v>46248</v>
       </c>
       <c r="F791" t="s">
@@ -35669,7 +35643,7 @@
       <c r="C792">
         <v>2026</v>
       </c>
-      <c r="D792" s="2">
+      <c r="D792" s="1">
         <v>46248</v>
       </c>
       <c r="F792" t="s">
@@ -35742,7 +35716,7 @@
       <c r="C794">
         <v>2026</v>
       </c>
-      <c r="D794" s="2">
+      <c r="D794" s="1">
         <v>46255</v>
       </c>
       <c r="F794" t="s">
@@ -35943,7 +35917,7 @@
       <c r="C800">
         <v>2026</v>
       </c>
-      <c r="D800" s="2">
+      <c r="D800" s="1">
         <v>46265</v>
       </c>
       <c r="H800" t="s">
@@ -35978,7 +35952,7 @@
       <c r="C801">
         <v>2026</v>
       </c>
-      <c r="D801" s="2">
+      <c r="D801" s="1">
         <v>46265</v>
       </c>
       <c r="H801" t="s">
@@ -36013,7 +35987,7 @@
       <c r="C802">
         <v>2026</v>
       </c>
-      <c r="D802" s="2">
+      <c r="D802" s="1">
         <v>46265</v>
       </c>
       <c r="H802" t="s">
@@ -36368,7 +36342,7 @@
       <c r="C813">
         <v>2026</v>
       </c>
-      <c r="D813" s="2">
+      <c r="D813" s="1">
         <v>46265</v>
       </c>
       <c r="H813" t="s">
@@ -36403,7 +36377,7 @@
       <c r="C814">
         <v>2026</v>
       </c>
-      <c r="D814" s="2">
+      <c r="D814" s="1">
         <v>46265</v>
       </c>
       <c r="H814" t="s">
